--- a/research/traditional_assets/database/data/australia/australia_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/australia/australia_financial_svcs_non_bank_insurance.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ42"/>
+  <dimension ref="A1:AQ43"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>41</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0539</v>
+        <v>0.07200000000000001</v>
       </c>
       <c r="E2">
-        <v>0.1325</v>
+        <v>0.1185</v>
       </c>
       <c r="F2">
-        <v>0.1145</v>
+        <v>0.04005</v>
       </c>
       <c r="G2">
-        <v>0.0881272295272069</v>
+        <v>0.03736148910246911</v>
       </c>
       <c r="H2">
-        <v>0.08645913174724837</v>
+        <v>0.03510384176339058</v>
       </c>
       <c r="I2">
-        <v>0.08461146160197125</v>
+        <v>0.02195059470511513</v>
       </c>
       <c r="J2">
-        <v>0.07395448306201623</v>
+        <v>0.01899729054214386</v>
       </c>
       <c r="K2">
-        <v>3985.705</v>
+        <v>3482.649</v>
       </c>
       <c r="L2">
-        <v>0.1897957654030711</v>
+        <v>0.1761412529189137</v>
       </c>
       <c r="M2">
-        <v>1679.7876</v>
+        <v>2752.8431</v>
       </c>
       <c r="N2">
-        <v>0.01969234325843513</v>
+        <v>0.04222760796801993</v>
       </c>
       <c r="O2">
-        <v>0.4214530679014126</v>
+        <v>0.7904451754971575</v>
       </c>
       <c r="P2">
-        <v>1530.7706</v>
+        <v>2022.4281</v>
       </c>
       <c r="Q2">
-        <v>0.01794539982621654</v>
+        <v>0.03102330857516267</v>
       </c>
       <c r="R2">
-        <v>0.3840652030192901</v>
+        <v>0.5807154553904226</v>
       </c>
       <c r="S2">
-        <v>149.017</v>
+        <v>730.415</v>
       </c>
       <c r="T2">
-        <v>0.08871181094562194</v>
+        <v>0.2653311407395503</v>
       </c>
       <c r="U2">
-        <v>30669.304</v>
+        <v>43775.685</v>
       </c>
       <c r="V2">
-        <v>0.3595397786394528</v>
+        <v>0.6715030234420301</v>
       </c>
       <c r="W2">
-        <v>0.1106330153172001</v>
+        <v>0.06876876876876878</v>
       </c>
       <c r="X2">
-        <v>0.02879826397509223</v>
+        <v>0.06704965351188377</v>
       </c>
       <c r="Y2">
-        <v>0.08183475134210784</v>
+        <v>0.001719115256885007</v>
       </c>
       <c r="Z2">
-        <v>0.1493961426426159</v>
+        <v>0.09343381337955699</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.02384747346420635</v>
+        <v>0.04626069781341397</v>
       </c>
       <c r="AC2">
-        <v>-0.02398207936561486</v>
+        <v>-0.04518298311975139</v>
       </c>
       <c r="AD2">
-        <v>205430.226</v>
+        <v>252711.26</v>
       </c>
       <c r="AE2">
-        <v>0.6800696268751022</v>
+        <v>377.8790852199358</v>
       </c>
       <c r="AF2">
-        <v>205430.9060696269</v>
+        <v>253089.1390852199</v>
       </c>
       <c r="AG2">
-        <v>174761.6020696269</v>
+        <v>209313.4540852199</v>
       </c>
       <c r="AH2">
-        <v>0.706597748943624</v>
+        <v>0.7951782913126459</v>
       </c>
       <c r="AI2">
-        <v>0.8567318248040285</v>
+        <v>0.8719241912061345</v>
       </c>
       <c r="AJ2">
-        <v>0.6719967590905391</v>
+        <v>0.7625149828214868</v>
       </c>
       <c r="AK2">
-        <v>0.835719780214782</v>
+        <v>0.8491783590004005</v>
       </c>
       <c r="AL2">
-        <v>629.871</v>
+        <v>451.901</v>
       </c>
       <c r="AM2">
-        <v>629.067</v>
+        <v>451.696</v>
       </c>
       <c r="AN2">
-        <v>104.6367672301823</v>
+        <v>376.4443901559785</v>
       </c>
       <c r="AO2">
-        <v>2.820328289443394</v>
+        <v>1.067711733322122</v>
       </c>
       <c r="AP2">
-        <v>89.01557201486646</v>
+        <v>311.7980400816015</v>
       </c>
       <c r="AQ2">
-        <v>2.823932903808339</v>
+        <v>1.068196309021997</v>
       </c>
     </row>
     <row r="3">
@@ -725,49 +725,49 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0229</v>
+        <v>0.0304</v>
       </c>
       <c r="E3">
-        <v>0.0244</v>
+        <v>0.0321</v>
       </c>
       <c r="F3">
-        <v>0.0371</v>
+        <v>0.0429</v>
       </c>
       <c r="G3">
-        <v>0.7069236821400472</v>
+        <v>0.7009383378016085</v>
       </c>
       <c r="H3">
-        <v>0.7069236821400472</v>
+        <v>0.7009383378016085</v>
       </c>
       <c r="I3">
-        <v>0.6900078678206137</v>
+        <v>0.687265415549598</v>
       </c>
       <c r="J3">
-        <v>0.4823498862697911</v>
+        <v>0.4785727376959044</v>
       </c>
       <c r="K3">
-        <v>360.5</v>
+        <v>350.4</v>
       </c>
       <c r="L3">
-        <v>0.472724888539208</v>
+        <v>0.4697050938337801</v>
       </c>
       <c r="M3">
-        <v>341</v>
+        <v>303.6</v>
       </c>
       <c r="N3">
-        <v>0.02607631719813413</v>
+        <v>0.03392444101773324</v>
       </c>
       <c r="O3">
-        <v>0.9459084604715673</v>
+        <v>0.8664383561643837</v>
       </c>
       <c r="P3">
-        <v>341</v>
+        <v>303.6</v>
       </c>
       <c r="Q3">
-        <v>0.02607631719813413</v>
+        <v>0.03392444101773324</v>
       </c>
       <c r="R3">
-        <v>0.9459084604715673</v>
+        <v>0.8664383561643837</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -776,73 +776,64 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>4016.9</v>
+        <v>3425.8</v>
       </c>
       <c r="V3">
-        <v>0.3071728989829471</v>
+        <v>0.3828008894550412</v>
       </c>
       <c r="W3">
-        <v>0.1403488281554154</v>
+        <v>0.125089247465372</v>
       </c>
       <c r="X3">
-        <v>0.02296170377869717</v>
+        <v>0.04816887954801183</v>
       </c>
       <c r="Y3">
-        <v>0.1173871243767182</v>
-      </c>
-      <c r="Z3">
-        <v>3.633158646974748</v>
-      </c>
-      <c r="AA3">
-        <v>1.752453660168378</v>
+        <v>0.07692036791736015</v>
       </c>
       <c r="AB3">
-        <v>0.0229365136211969</v>
-      </c>
-      <c r="AC3">
-        <v>1.729517146547181</v>
+        <v>0.04809776206260877</v>
       </c>
       <c r="AD3">
-        <v>54.3</v>
+        <v>46.6</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>54.3</v>
+        <v>46.6</v>
       </c>
       <c r="AG3">
-        <v>-3962.6</v>
+        <v>-3379.2</v>
       </c>
       <c r="AH3">
-        <v>0.004135157981311827</v>
+        <v>0.005180137618248313</v>
       </c>
       <c r="AI3">
-        <v>0.01901593416214323</v>
+        <v>0.01746299419149335</v>
       </c>
       <c r="AJ3">
-        <v>-0.43476257351005</v>
+        <v>-0.6066677438466098</v>
       </c>
       <c r="AK3">
-        <v>3.41191665231617</v>
+        <v>4.462168229235441</v>
       </c>
       <c r="AL3">
-        <v>10.5</v>
+        <v>9.51</v>
       </c>
       <c r="AM3">
-        <v>10.5</v>
+        <v>9.51</v>
       </c>
       <c r="AN3">
-        <v>0.100723427935448</v>
+        <v>0.08911837827500478</v>
       </c>
       <c r="AO3">
-        <v>50.11428571428572</v>
+        <v>53.91167192429022</v>
       </c>
       <c r="AP3">
-        <v>-7.350398812836208</v>
+        <v>-6.462421113023524</v>
       </c>
       <c r="AQ3">
-        <v>50.11428571428572</v>
+        <v>53.91167192429022</v>
       </c>
     </row>
     <row r="4">
@@ -853,7 +844,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Yellow Brick Road Holdings Limited (ASX:YBR)</t>
+          <t>WT Financial Group Limited (ASX:WTL)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -862,34 +853,37 @@
         </is>
       </c>
       <c r="D4">
-        <v>-0.0498</v>
+        <v>0.556</v>
+      </c>
+      <c r="E4">
+        <v>0.141</v>
       </c>
       <c r="G4">
-        <v>0.09808612440191387</v>
+        <v>0.03851640513552069</v>
       </c>
       <c r="H4">
-        <v>0.09808612440191387</v>
+        <v>0.03851640513552069</v>
       </c>
       <c r="I4">
-        <v>0.09728867623604465</v>
+        <v>0.03366619115549215</v>
       </c>
       <c r="J4">
-        <v>0.09728867623604465</v>
+        <v>0.02682904492700023</v>
       </c>
       <c r="K4">
-        <v>-0.345</v>
+        <v>1.29</v>
       </c>
       <c r="L4">
-        <v>-0.002751196172248803</v>
+        <v>0.01840228245363766</v>
       </c>
       <c r="M4">
-        <v>0.005</v>
+        <v>-0</v>
       </c>
       <c r="N4">
-        <v>0.0001694915254237288</v>
+        <v>-0</v>
       </c>
       <c r="O4">
-        <v>-0.01449275362318841</v>
+        <v>-0</v>
       </c>
       <c r="P4">
         <v>-0</v>
@@ -898,82 +892,79 @@
         <v>-0</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S4">
-        <v>0.005</v>
-      </c>
-      <c r="T4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U4">
-        <v>9.380000000000001</v>
+        <v>2.33</v>
       </c>
       <c r="V4">
-        <v>0.3179661016949153</v>
+        <v>0.1153465346534654</v>
       </c>
       <c r="W4">
-        <v>-0.01134868421052631</v>
+        <v>0.2885906040268457</v>
       </c>
       <c r="X4">
-        <v>0.0234318407941564</v>
+        <v>0.04964552938063471</v>
       </c>
       <c r="Y4">
-        <v>-0.03478052500468271</v>
+        <v>0.238945074646211</v>
       </c>
       <c r="Z4">
-        <v>4.632434429257481</v>
+        <v>76.52838427947594</v>
       </c>
       <c r="AA4">
-        <v>0.4506834133727373</v>
+        <v>2.053183460024798</v>
       </c>
       <c r="AB4">
-        <v>0.02284747566029521</v>
+        <v>0.04805214690345079</v>
       </c>
       <c r="AC4">
-        <v>0.4278359377124421</v>
+        <v>2.005131313121348</v>
       </c>
       <c r="AD4">
-        <v>2.65</v>
+        <v>4.67</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>2.65</v>
+        <v>4.67</v>
       </c>
       <c r="AG4">
-        <v>-6.73</v>
+        <v>2.34</v>
       </c>
       <c r="AH4">
-        <v>0.08242612752721618</v>
+        <v>0.1877764374748693</v>
       </c>
       <c r="AI4">
-        <v>0.075177304964539</v>
+        <v>0.2528424472116946</v>
       </c>
       <c r="AJ4">
-        <v>-0.2955643390425999</v>
+        <v>0.1038154392191659</v>
       </c>
       <c r="AK4">
-        <v>-0.2601468882875918</v>
+        <v>0.1449814126394052</v>
       </c>
       <c r="AL4">
-        <v>0.146</v>
+        <v>0.412</v>
       </c>
       <c r="AM4">
-        <v>0.146</v>
+        <v>0.412</v>
       </c>
       <c r="AN4">
-        <v>0.2154471544715447</v>
+        <v>1.729629629629629</v>
       </c>
       <c r="AO4">
-        <v>83.56164383561644</v>
+        <v>5.728155339805825</v>
       </c>
       <c r="AP4">
-        <v>-0.5471544715447154</v>
+        <v>0.8666666666666666</v>
       </c>
       <c r="AQ4">
-        <v>83.56164383561644</v>
+        <v>5.728155339805825</v>
       </c>
     </row>
     <row r="5">
@@ -984,7 +975,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ClearView Wealth Limited (ASX:CVW)</t>
+          <t>N1 Holdings Limited (ASX:N1H)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -993,46 +984,43 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.148</v>
-      </c>
-      <c r="E5">
-        <v>-0.223</v>
+        <v>0.207</v>
       </c>
       <c r="G5">
-        <v>0.2183987153016747</v>
+        <v>0.557312252964427</v>
       </c>
       <c r="H5">
-        <v>0.2183987153016747</v>
+        <v>0.557312252964427</v>
       </c>
       <c r="I5">
-        <v>0.2177104840559762</v>
+        <v>0.546772068511199</v>
       </c>
       <c r="J5">
-        <v>0.2177104840559762</v>
+        <v>0.546772068511199</v>
       </c>
       <c r="K5">
-        <v>5.01</v>
+        <v>0.759</v>
       </c>
       <c r="L5">
-        <v>0.01149346180316586</v>
+        <v>0.1</v>
       </c>
       <c r="M5">
-        <v>4.685099999999999</v>
+        <v>0.0881</v>
       </c>
       <c r="N5">
-        <v>0.01218808532778356</v>
+        <v>0.009332627118644068</v>
       </c>
       <c r="O5">
-        <v>0.9351497005988023</v>
+        <v>0.1160737812911726</v>
       </c>
       <c r="P5">
-        <v>4.685099999999999</v>
+        <v>0.0881</v>
       </c>
       <c r="Q5">
-        <v>0.01218808532778356</v>
+        <v>0.009332627118644068</v>
       </c>
       <c r="R5">
-        <v>0.9351497005988023</v>
+        <v>0.1160737812911726</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1041,73 +1029,73 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>90.3</v>
+        <v>9.74</v>
       </c>
       <c r="V5">
-        <v>0.2349115504682622</v>
+        <v>1.031779661016949</v>
       </c>
       <c r="W5">
-        <v>0.01602687140115163</v>
+        <v>-0.6837837837837837</v>
       </c>
       <c r="X5">
-        <v>0.0240466454689154</v>
+        <v>0.08406019886214552</v>
       </c>
       <c r="Y5">
-        <v>-0.008019774067763771</v>
+        <v>-0.7678439826459292</v>
       </c>
       <c r="Z5">
-        <v>1.999908240044044</v>
+        <v>0.9885386819484241</v>
       </c>
       <c r="AA5">
-        <v>0.4354009910075243</v>
+        <v>0.5405053399322741</v>
       </c>
       <c r="AB5">
-        <v>0.02275257870106464</v>
+        <v>0.04776218254415802</v>
       </c>
       <c r="AC5">
-        <v>0.4126484123064597</v>
+        <v>0.4927431573881161</v>
       </c>
       <c r="AD5">
-        <v>77.59999999999999</v>
+        <v>51.9</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>77.59999999999999</v>
+        <v>51.9</v>
       </c>
       <c r="AG5">
-        <v>-12.7</v>
+        <v>42.16</v>
       </c>
       <c r="AH5">
-        <v>0.167965367965368</v>
+        <v>0.8461036843821325</v>
       </c>
       <c r="AI5">
-        <v>0.07643061164187924</v>
+        <v>0.9917639639983948</v>
       </c>
       <c r="AJ5">
-        <v>-0.03416733925208502</v>
+        <v>0.8170542635658915</v>
       </c>
       <c r="AK5">
-        <v>-0.01372972972972973</v>
+        <v>0.9898804911835835</v>
       </c>
       <c r="AL5">
-        <v>4.32</v>
+        <v>3.37</v>
       </c>
       <c r="AM5">
-        <v>4.32</v>
+        <v>3.37</v>
       </c>
       <c r="AN5">
-        <v>0.8151260504201679</v>
+        <v>12.26950354609929</v>
       </c>
       <c r="AO5">
-        <v>21.96759259259259</v>
+        <v>1.231454005934718</v>
       </c>
       <c r="AP5">
-        <v>-0.1334033613445378</v>
+        <v>9.96690307328605</v>
       </c>
       <c r="AQ5">
-        <v>21.96759259259259</v>
+        <v>1.231454005934718</v>
       </c>
     </row>
     <row r="6">
@@ -1127,121 +1115,121 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.0535</v>
+        <v>0.113</v>
       </c>
       <c r="E6">
-        <v>0.005390000000000001</v>
+        <v>0.09179999999999999</v>
       </c>
       <c r="G6">
-        <v>0.1781425891181989</v>
+        <v>0.2344637223974763</v>
       </c>
       <c r="H6">
-        <v>0.1369606003752345</v>
+        <v>0.2018927444794953</v>
       </c>
       <c r="I6">
-        <v>0.1913696060037523</v>
+        <v>0.2034700315457413</v>
       </c>
       <c r="J6">
-        <v>0.148262122589505</v>
+        <v>0.1556802216154601</v>
       </c>
       <c r="K6">
-        <v>15.1</v>
+        <v>18.2</v>
       </c>
       <c r="L6">
-        <v>0.1416510318949343</v>
+        <v>0.1435331230283912</v>
       </c>
       <c r="M6">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="N6">
-        <v>0.003533742331288343</v>
+        <v>0.003266018449264523</v>
       </c>
       <c r="O6">
-        <v>0.09536423841059602</v>
+        <v>0.07197802197802199</v>
       </c>
       <c r="P6">
-        <v>1.44</v>
+        <v>-0</v>
       </c>
       <c r="Q6">
-        <v>0.003533742331288343</v>
+        <v>-0</v>
       </c>
       <c r="R6">
-        <v>0.09536423841059602</v>
+        <v>-0</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U6">
-        <v>29.6</v>
+        <v>43.3</v>
       </c>
       <c r="V6">
-        <v>0.07263803680981595</v>
+        <v>0.1079531288955373</v>
       </c>
       <c r="W6">
-        <v>0.2843691148775894</v>
+        <v>0.2749244712990936</v>
       </c>
       <c r="X6">
-        <v>0.02302886933461009</v>
+        <v>0.04904553196088826</v>
       </c>
       <c r="Y6">
-        <v>0.2613402455429794</v>
+        <v>0.2258789393382054</v>
       </c>
       <c r="Z6">
-        <v>2.220833333333333</v>
+        <v>2.929759704251387</v>
       </c>
       <c r="AA6">
-        <v>0.3292654639175256</v>
+        <v>0.4561056400379007</v>
       </c>
       <c r="AB6">
-        <v>0.02292102630938142</v>
+        <v>0.04775560802956735</v>
       </c>
       <c r="AC6">
-        <v>0.3063444376081442</v>
+        <v>0.4083500320083333</v>
       </c>
       <c r="AD6">
-        <v>6.68</v>
+        <v>55.9</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>6.68</v>
+        <v>55.9</v>
       </c>
       <c r="AG6">
-        <v>-22.92</v>
+        <v>12.6</v>
       </c>
       <c r="AH6">
-        <v>0.01612825341638901</v>
+        <v>0.1223194748358862</v>
       </c>
       <c r="AI6">
-        <v>0.09165751920965971</v>
+        <v>0.4056603773584905</v>
       </c>
       <c r="AJ6">
-        <v>-0.0595974829684331</v>
+        <v>0.03045685279187817</v>
       </c>
       <c r="AK6">
-        <v>-0.5295748613678374</v>
+        <v>0.1333333333333334</v>
       </c>
       <c r="AL6">
-        <v>0.737</v>
+        <v>1.82</v>
       </c>
       <c r="AM6">
-        <v>0.737</v>
+        <v>1.82</v>
       </c>
       <c r="AN6">
-        <v>0.3180952380952381</v>
+        <v>2.109433962264151</v>
       </c>
       <c r="AO6">
-        <v>27.6797829036635</v>
+        <v>14.17582417582418</v>
       </c>
       <c r="AP6">
-        <v>-1.091428571428571</v>
+        <v>0.4754716981132076</v>
       </c>
       <c r="AQ6">
-        <v>27.6797829036635</v>
+        <v>14.17582417582418</v>
       </c>
     </row>
     <row r="7">
@@ -1252,7 +1240,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Litigation Capital Management Limited (AIM:LIT)</t>
+          <t>Yellow Brick Road Holdings Limited (ASX:YBR)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1261,25 +1249,25 @@
         </is>
       </c>
       <c r="D7">
-        <v>1.229</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="G7">
-        <v>0.4280575539568345</v>
+        <v>0.04692816635160681</v>
       </c>
       <c r="H7">
-        <v>0.4280575539568345</v>
+        <v>0.04692816635160681</v>
       </c>
       <c r="I7">
-        <v>0.427145872663634</v>
+        <v>0.04673913043478261</v>
       </c>
       <c r="J7">
-        <v>0.2928371188879553</v>
+        <v>0.04673913043478261</v>
       </c>
       <c r="K7">
-        <v>6.64</v>
+        <v>-1.69</v>
       </c>
       <c r="L7">
-        <v>0.2388489208633093</v>
+        <v>-0.007986767485822307</v>
       </c>
       <c r="M7">
         <v>-0</v>
@@ -1288,7 +1276,7 @@
         <v>-0</v>
       </c>
       <c r="O7">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P7">
         <v>-0</v>
@@ -1297,79 +1285,79 @@
         <v>-0</v>
       </c>
       <c r="R7">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S7">
         <v>0</v>
       </c>
       <c r="U7">
-        <v>37.3</v>
+        <v>6.95</v>
       </c>
       <c r="V7">
-        <v>0.227023737066342</v>
+        <v>0.337378640776699</v>
       </c>
       <c r="W7">
-        <v>0.118783542039356</v>
+        <v>-0.05184049079754601</v>
       </c>
       <c r="X7">
-        <v>0.02421243107741153</v>
+        <v>0.04927678783344761</v>
       </c>
       <c r="Y7">
-        <v>0.09457111096194447</v>
+        <v>-0.1011172786309936</v>
       </c>
       <c r="Z7">
-        <v>0.8097467008392154</v>
+        <v>8.1793583301121</v>
       </c>
       <c r="AA7">
-        <v>0.2371238909027829</v>
+        <v>0.3822960958639351</v>
       </c>
       <c r="AB7">
-        <v>0.02333883983823396</v>
+        <v>0.04767362931276945</v>
       </c>
       <c r="AC7">
-        <v>0.213785051064549</v>
+        <v>0.3346224665511656</v>
       </c>
       <c r="AD7">
-        <v>37.8</v>
+        <v>3.6</v>
       </c>
       <c r="AE7">
-        <v>0.3317236997548624</v>
+        <v>0</v>
       </c>
       <c r="AF7">
-        <v>38.13172369975486</v>
+        <v>3.6</v>
       </c>
       <c r="AG7">
-        <v>0.8317236997548605</v>
+        <v>-3.35</v>
       </c>
       <c r="AH7">
-        <v>0.1883683199591361</v>
+        <v>0.1487603305785124</v>
       </c>
       <c r="AI7">
-        <v>0.3640895265800358</v>
+        <v>0.1128526645768025</v>
       </c>
       <c r="AJ7">
-        <v>0.005036728746725334</v>
+        <v>-0.1942028985507246</v>
       </c>
       <c r="AK7">
-        <v>0.0123343087514443</v>
+        <v>-0.1342685370741483</v>
       </c>
       <c r="AL7">
-        <v>0.926</v>
+        <v>0.256</v>
       </c>
       <c r="AM7">
-        <v>0.923</v>
+        <v>0.256</v>
       </c>
       <c r="AN7">
-        <v>3.087983007924189</v>
+        <v>0.3625377643504532</v>
       </c>
       <c r="AO7">
-        <v>12.52699784017278</v>
+        <v>38.6328125</v>
       </c>
       <c r="AP7">
-        <v>0.06794573153785316</v>
+        <v>-0.3373615307150051</v>
       </c>
       <c r="AQ7">
-        <v>12.56771397616468</v>
+        <v>38.6328125</v>
       </c>
     </row>
     <row r="8">
@@ -1380,7 +1368,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Money3 Corporation Limited (ASX:MNY)</t>
+          <t>Solvar Limited (ASX:SVR)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1389,46 +1377,46 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.08460000000000001</v>
+        <v>0.114</v>
       </c>
       <c r="E8">
-        <v>0.142</v>
+        <v>0.122</v>
       </c>
       <c r="G8">
-        <v>0.6555147058823529</v>
+        <v>0.6488408037094281</v>
       </c>
       <c r="H8">
-        <v>0.6185661764705882</v>
+        <v>0.6143740340030912</v>
       </c>
       <c r="I8">
-        <v>0.6084558823529412</v>
+        <v>0.6081916537867079</v>
       </c>
       <c r="J8">
-        <v>0.4228984146850229</v>
+        <v>0.4258541165567679</v>
       </c>
       <c r="K8">
-        <v>29.4</v>
+        <v>35.6</v>
       </c>
       <c r="L8">
-        <v>0.2702205882352941</v>
+        <v>0.2751159196290572</v>
       </c>
       <c r="M8">
-        <v>8.85</v>
+        <v>17.7</v>
       </c>
       <c r="N8">
-        <v>0.01617029051708387</v>
+        <v>0.0671217292377702</v>
       </c>
       <c r="O8">
-        <v>0.3010204081632653</v>
+        <v>0.497191011235955</v>
       </c>
       <c r="P8">
-        <v>8.85</v>
+        <v>17.7</v>
       </c>
       <c r="Q8">
-        <v>0.01617029051708387</v>
+        <v>0.0671217292377702</v>
       </c>
       <c r="R8">
-        <v>0.3010204081632653</v>
+        <v>0.497191011235955</v>
       </c>
       <c r="S8">
         <v>0</v>
@@ -1437,73 +1425,73 @@
         <v>0</v>
       </c>
       <c r="U8">
-        <v>41.7</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="V8">
-        <v>0.07619221633473416</v>
+        <v>0.3200606750094805</v>
       </c>
       <c r="W8">
-        <v>0.1704347826086957</v>
+        <v>0.1411018628616726</v>
       </c>
       <c r="X8">
-        <v>0.02491605099166195</v>
+        <v>0.05540520824237007</v>
       </c>
       <c r="Y8">
-        <v>0.1455187316170337</v>
+        <v>0.08569665461930255</v>
       </c>
       <c r="Z8">
-        <v>0.4385328496573961</v>
+        <v>0.3340216830149716</v>
       </c>
       <c r="AA8">
-        <v>0.1854548469074183</v>
+        <v>0.1422445087311455</v>
       </c>
       <c r="AB8">
-        <v>0.02350127119723325</v>
+        <v>0.04366330535543526</v>
       </c>
       <c r="AC8">
-        <v>0.1619535757101851</v>
+        <v>0.09858120337571023</v>
       </c>
       <c r="AD8">
-        <v>197.2</v>
+        <v>293.4</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>197.2</v>
+        <v>293.4</v>
       </c>
       <c r="AG8">
-        <v>155.5</v>
+        <v>209</v>
       </c>
       <c r="AH8">
-        <v>0.2648757555406313</v>
+        <v>0.5266558966074314</v>
       </c>
       <c r="AI8">
-        <v>0.4387096774193548</v>
+        <v>0.5357925493060629</v>
       </c>
       <c r="AJ8">
-        <v>0.2212578258394992</v>
+        <v>0.4421408927438121</v>
       </c>
       <c r="AK8">
-        <v>0.3813143697891123</v>
+        <v>0.4512089810017271</v>
       </c>
       <c r="AL8">
-        <v>23.3</v>
+        <v>24.2</v>
       </c>
       <c r="AM8">
-        <v>23.3</v>
+        <v>24.2</v>
       </c>
       <c r="AN8">
-        <v>2.930163447251114</v>
+        <v>3.690566037735849</v>
       </c>
       <c r="AO8">
-        <v>2.841201716738198</v>
+        <v>3.25206611570248</v>
       </c>
       <c r="AP8">
-        <v>2.310549777117385</v>
+        <v>2.628930817610063</v>
       </c>
       <c r="AQ8">
-        <v>2.841201716738198</v>
+        <v>3.25206611570248</v>
       </c>
     </row>
     <row r="9">
@@ -1514,7 +1502,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Earlypay Ltd (ASX:EPY)</t>
+          <t>Litigation Capital Management Limited (AIM:LIT)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1523,124 +1511,115 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.101</v>
-      </c>
-      <c r="E9">
-        <v>1.857</v>
-      </c>
-      <c r="F9">
-        <v>0.15</v>
+        <v>0.8490000000000001</v>
       </c>
       <c r="G9">
-        <v>0.4693617021276596</v>
+        <v>0.3975535168195719</v>
       </c>
       <c r="H9">
-        <v>0.4680851063829787</v>
+        <v>0.3975535168195719</v>
       </c>
       <c r="I9">
-        <v>0.4285714285714286</v>
+        <v>0.3914373088685015</v>
       </c>
       <c r="J9">
-        <v>0.3006644518272426</v>
+        <v>0.2435846297034969</v>
       </c>
       <c r="K9">
-        <v>5.43</v>
+        <v>4.58</v>
       </c>
       <c r="L9">
-        <v>0.1650455927051672</v>
+        <v>0.1400611620795107</v>
       </c>
       <c r="M9">
-        <v>4.62</v>
+        <v>-0</v>
       </c>
       <c r="N9">
-        <v>0.05191011235955056</v>
+        <v>-0</v>
       </c>
       <c r="O9">
-        <v>0.850828729281768</v>
+        <v>-0</v>
       </c>
       <c r="P9">
-        <v>4.62</v>
+        <v>-0</v>
       </c>
       <c r="Q9">
-        <v>0.05191011235955056</v>
+        <v>-0</v>
       </c>
       <c r="R9">
-        <v>0.850828729281768</v>
+        <v>-0</v>
       </c>
       <c r="S9">
         <v>0</v>
       </c>
-      <c r="T9">
-        <v>0</v>
-      </c>
       <c r="U9">
-        <v>33.6</v>
+        <v>34.4</v>
       </c>
       <c r="V9">
-        <v>0.3775280898876405</v>
+        <v>0.3429710867397807</v>
       </c>
       <c r="W9">
-        <v>0.15</v>
+        <v>0.06876876876876878</v>
       </c>
       <c r="X9">
-        <v>0.03252618104137409</v>
+        <v>0.0512489541308601</v>
       </c>
       <c r="Y9">
-        <v>0.1174738189586259</v>
+        <v>0.01751981463790868</v>
       </c>
       <c r="Z9">
-        <v>0.2653225806451612</v>
+        <v>0.4873323397913563</v>
       </c>
       <c r="AA9">
-        <v>0.07977306826706676</v>
+        <v>0.1187066675306162</v>
       </c>
       <c r="AB9">
-        <v>0.02223335165492841</v>
+        <v>0.04713416677464732</v>
       </c>
       <c r="AC9">
-        <v>0.05753971661213836</v>
+        <v>0.07157250075596891</v>
       </c>
       <c r="AD9">
-        <v>155.5</v>
+        <v>47.8</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>155.5</v>
+        <v>47.8</v>
       </c>
       <c r="AG9">
-        <v>121.9</v>
+        <v>13.4</v>
       </c>
       <c r="AH9">
-        <v>0.6359918200408998</v>
+        <v>0.3227548953409858</v>
       </c>
       <c r="AI9">
-        <v>0.779839518555667</v>
+        <v>0.4245115452930728</v>
       </c>
       <c r="AJ9">
-        <v>0.5779990516832623</v>
+        <v>0.1178540017590149</v>
       </c>
       <c r="AK9">
-        <v>0.7352231604342582</v>
+        <v>0.1713554987212276</v>
       </c>
       <c r="AL9">
-        <v>6.36</v>
+        <v>3.02</v>
       </c>
       <c r="AM9">
-        <v>6.36</v>
+        <v>3.019</v>
       </c>
       <c r="AN9">
-        <v>10.0974025974026</v>
+        <v>3.676923076923077</v>
       </c>
       <c r="AO9">
-        <v>2.216981132075472</v>
+        <v>4.23841059602649</v>
       </c>
       <c r="AP9">
-        <v>7.915584415584416</v>
+        <v>1.030769230769231</v>
       </c>
       <c r="AQ9">
-        <v>2.216981132075472</v>
+        <v>4.23981450811527</v>
       </c>
     </row>
     <row r="10">
@@ -1651,7 +1630,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Challenger Limited (ASX:CGF)</t>
+          <t>Earlypay Limited (ASX:EPY)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1660,49 +1639,49 @@
         </is>
       </c>
       <c r="D10">
-        <v>0.104</v>
+        <v>0.061</v>
       </c>
       <c r="E10">
-        <v>0.126</v>
+        <v>0.392</v>
       </c>
       <c r="F10">
-        <v>0.112</v>
+        <v>0.0394</v>
       </c>
       <c r="G10">
-        <v>0.3268010377170225</v>
+        <v>0.4974393530997305</v>
       </c>
       <c r="H10">
-        <v>0.3268010377170225</v>
+        <v>0.4932614555256065</v>
       </c>
       <c r="I10">
-        <v>0.325364198762722</v>
+        <v>0.4636118598382749</v>
       </c>
       <c r="J10">
-        <v>0.231992459050343</v>
+        <v>0.4009138749839558</v>
       </c>
       <c r="K10">
-        <v>444.1</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="L10">
-        <v>0.1772500498902415</v>
+        <v>0.2455525606469003</v>
       </c>
       <c r="M10">
-        <v>48</v>
+        <v>4.52</v>
       </c>
       <c r="N10">
-        <v>0.01498220862725513</v>
+        <v>0.1147208121827411</v>
       </c>
       <c r="O10">
-        <v>0.1080837649178113</v>
+        <v>0.4961580680570801</v>
       </c>
       <c r="P10">
-        <v>48</v>
+        <v>4.52</v>
       </c>
       <c r="Q10">
-        <v>0.01498220862725513</v>
+        <v>0.1147208121827411</v>
       </c>
       <c r="R10">
-        <v>0.1080837649178113</v>
+        <v>0.4961580680570801</v>
       </c>
       <c r="S10">
         <v>0</v>
@@ -1711,73 +1690,73 @@
         <v>0</v>
       </c>
       <c r="U10">
-        <v>741.8</v>
+        <v>36.3</v>
       </c>
       <c r="V10">
-        <v>0.231537549160372</v>
+        <v>0.9213197969543147</v>
       </c>
       <c r="W10">
-        <v>0.1979408094134427</v>
+        <v>0.2075170842824601</v>
       </c>
       <c r="X10">
-        <v>0.03159985024682326</v>
+        <v>0.08168583656895653</v>
       </c>
       <c r="Y10">
-        <v>0.1663409591666194</v>
+        <v>0.1258312477135036</v>
       </c>
       <c r="Z10">
-        <v>0.3501502340856684</v>
+        <v>0.2542837559972584</v>
       </c>
       <c r="AA10">
-        <v>0.08123221384258744</v>
+        <v>0.1019458859623356</v>
       </c>
       <c r="AB10">
-        <v>0.02472539721337098</v>
+        <v>0.0455398095193086</v>
       </c>
       <c r="AC10">
-        <v>0.05650681662921646</v>
+        <v>0.05640607644302698</v>
       </c>
       <c r="AD10">
-        <v>5056.8</v>
+        <v>202.3</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>5056.8</v>
+        <v>202.3</v>
       </c>
       <c r="AG10">
-        <v>4315</v>
+        <v>166</v>
       </c>
       <c r="AH10">
-        <v>0.6121589230806479</v>
+        <v>0.8369880016549441</v>
       </c>
       <c r="AI10">
-        <v>0.6380739675209146</v>
+        <v>0.7753928708317362</v>
       </c>
       <c r="AJ10">
-        <v>0.5738947704420918</v>
+        <v>0.8081791626095424</v>
       </c>
       <c r="AK10">
-        <v>0.6006988431500843</v>
+        <v>0.7390917186108638</v>
       </c>
       <c r="AL10">
-        <v>242.7</v>
+        <v>6.71</v>
       </c>
       <c r="AM10">
-        <v>242.7</v>
+        <v>6.71</v>
       </c>
       <c r="AN10">
-        <v>6.175867122618467</v>
+        <v>11.05464480874317</v>
       </c>
       <c r="AO10">
-        <v>3.358879274824887</v>
+        <v>2.563338301043219</v>
       </c>
       <c r="AP10">
-        <v>5.269907181240841</v>
+        <v>9.071038251366121</v>
       </c>
       <c r="AQ10">
-        <v>3.358879274824887</v>
+        <v>2.563338301043219</v>
       </c>
     </row>
     <row r="11">
@@ -1788,7 +1767,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Eclipx Group Limited (ASX:ECX)</t>
+          <t>Helia Group Limited (ASX:HLI)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1797,118 +1776,121 @@
         </is>
       </c>
       <c r="D11">
-        <v>-0.153</v>
+        <v>-0.123</v>
       </c>
       <c r="E11">
-        <v>0.106</v>
+        <v>-0.00461</v>
       </c>
       <c r="G11">
-        <v>1.399624765478424</v>
+        <v>1.151079136690648</v>
       </c>
       <c r="H11">
-        <v>1.399624765478424</v>
+        <v>1.151079136690648</v>
       </c>
       <c r="I11">
-        <v>0.5647279549718573</v>
+        <v>0.8644161593801881</v>
       </c>
       <c r="J11">
-        <v>0.3987167846399506</v>
+        <v>0.6087437742114</v>
       </c>
       <c r="K11">
-        <v>55</v>
+        <v>105</v>
       </c>
       <c r="L11">
-        <v>0.3439649781113195</v>
+        <v>0.5810736026563365</v>
       </c>
       <c r="M11">
-        <v>-0</v>
+        <v>150.5</v>
       </c>
       <c r="N11">
-        <v>-0</v>
+        <v>0.2317523868186018</v>
       </c>
       <c r="O11">
-        <v>-0</v>
+        <v>1.433333333333333</v>
       </c>
       <c r="P11">
-        <v>-0</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="Q11">
-        <v>-0</v>
+        <v>0.1256544502617801</v>
       </c>
       <c r="R11">
-        <v>-0</v>
+        <v>0.7771428571428571</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>68.90000000000001</v>
+      </c>
+      <c r="T11">
+        <v>0.4578073089700997</v>
       </c>
       <c r="U11">
-        <v>55.3</v>
+        <v>13.1</v>
       </c>
       <c r="V11">
-        <v>0.1087512291052114</v>
+        <v>0.02017246689251617</v>
       </c>
       <c r="W11">
-        <v>0.1508916323731138</v>
+        <v>0.09680095879044896</v>
       </c>
       <c r="X11">
-        <v>0.03263682556395958</v>
+        <v>0.04947815899443358</v>
       </c>
       <c r="Y11">
-        <v>0.1182548068091543</v>
+        <v>0.04732279979601538</v>
       </c>
       <c r="Z11">
-        <v>0.1582854880221738</v>
+        <v>0.1558887470237068</v>
       </c>
       <c r="AA11">
-        <v>0.06311108083936658</v>
+        <v>0.09489630422029743</v>
       </c>
       <c r="AB11">
-        <v>0.02429481109665415</v>
+        <v>0.04760616483712501</v>
       </c>
       <c r="AC11">
-        <v>0.03881626974271243</v>
+        <v>0.04729013938317243</v>
       </c>
       <c r="AD11">
-        <v>898.7</v>
+        <v>133.5</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>898.7</v>
+        <v>133.5</v>
       </c>
       <c r="AG11">
-        <v>843.4000000000001</v>
+        <v>120.4</v>
       </c>
       <c r="AH11">
-        <v>0.6386441159749858</v>
+        <v>0.1705198620513476</v>
       </c>
       <c r="AI11">
-        <v>0.6830584479744622</v>
+        <v>0.122996130458817</v>
       </c>
       <c r="AJ11">
-        <v>0.623862711739034</v>
+        <v>0.1564042608469733</v>
       </c>
       <c r="AK11">
-        <v>0.6691526499523961</v>
+        <v>0.1122820106313532</v>
       </c>
       <c r="AL11">
-        <v>6.95</v>
+        <v>7.08</v>
       </c>
       <c r="AM11">
-        <v>6.95</v>
+        <v>7.08</v>
       </c>
       <c r="AN11">
-        <v>4.015638963360143</v>
+        <v>0.8514030612244897</v>
       </c>
       <c r="AO11">
-        <v>12.99280575539568</v>
+        <v>22.06214689265537</v>
       </c>
       <c r="AP11">
-        <v>3.768543342269884</v>
+        <v>0.7678571428571428</v>
       </c>
       <c r="AQ11">
-        <v>12.99280575539568</v>
+        <v>22.06214689265537</v>
       </c>
     </row>
     <row r="12">
@@ -1919,7 +1901,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Genworth Mortgage Insurance Australia Limited (ASX:GMA)</t>
+          <t>Eclipx Group Limited (ASX:ECX)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1928,121 +1910,121 @@
         </is>
       </c>
       <c r="D12">
-        <v>-0.1</v>
+        <v>0.0228</v>
       </c>
       <c r="E12">
-        <v>-0.301</v>
+        <v>0.138</v>
       </c>
       <c r="G12">
-        <v>-0.3944265809217578</v>
+        <v>0.4840559761413168</v>
       </c>
       <c r="H12">
-        <v>-0.3944265809217578</v>
+        <v>0.4712089928882772</v>
       </c>
       <c r="I12">
-        <v>0.1832797427652733</v>
+        <v>0.2284927735719202</v>
       </c>
       <c r="J12">
-        <v>0.1331010660917182</v>
+        <v>0.1596089227156795</v>
       </c>
       <c r="K12">
-        <v>31.3</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="L12">
-        <v>0.1118256520185781</v>
+        <v>0.1527873365450791</v>
       </c>
       <c r="M12">
-        <v>15.2255</v>
+        <v>51.7</v>
       </c>
       <c r="N12">
-        <v>0.02193560005762858</v>
+        <v>0.1457569777276572</v>
       </c>
       <c r="O12">
-        <v>0.4864376996805111</v>
+        <v>0.7762762762762764</v>
       </c>
       <c r="P12">
-        <v>15.2255</v>
+        <v>-0</v>
       </c>
       <c r="Q12">
-        <v>0.02193560005762858</v>
+        <v>-0</v>
       </c>
       <c r="R12">
-        <v>0.4864376996805111</v>
+        <v>-0</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>51.7</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U12">
-        <v>67.2</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="V12">
-        <v>0.09681602074629016</v>
+        <v>0.1843811671835354</v>
       </c>
       <c r="W12">
-        <v>0.03225474031327288</v>
+        <v>0.1597122302158273</v>
       </c>
       <c r="X12">
-        <v>0.02411289333193161</v>
+        <v>0.06234951859459027</v>
       </c>
       <c r="Y12">
-        <v>0.008141846981341263</v>
+        <v>0.09736271162123704</v>
       </c>
       <c r="Z12">
-        <v>0.2650066275326642</v>
+        <v>0.4623462028001697</v>
       </c>
       <c r="AA12">
-        <v>0.0352726646459685</v>
+        <v>0.07379457935062017</v>
       </c>
       <c r="AB12">
-        <v>0.02331309089566195</v>
+        <v>0.04601080906108601</v>
       </c>
       <c r="AC12">
-        <v>0.01195957375030655</v>
+        <v>0.02778377028953416</v>
       </c>
       <c r="AD12">
-        <v>148.5</v>
+        <v>771.6</v>
       </c>
       <c r="AE12">
         <v>0</v>
       </c>
       <c r="AF12">
-        <v>148.5</v>
+        <v>771.6</v>
       </c>
       <c r="AG12">
-        <v>81.3</v>
+        <v>706.2</v>
       </c>
       <c r="AH12">
-        <v>0.1762402088772846</v>
+        <v>0.6850750244162301</v>
       </c>
       <c r="AI12">
-        <v>0.1204184236133636</v>
+        <v>0.6586989926583575</v>
       </c>
       <c r="AJ12">
-        <v>0.1048491101367036</v>
+        <v>0.6656612310302573</v>
       </c>
       <c r="AK12">
-        <v>0.06972555746140652</v>
+        <v>0.6385171790235081</v>
       </c>
       <c r="AL12">
-        <v>8.15</v>
+        <v>3.92</v>
       </c>
       <c r="AM12">
-        <v>8.15</v>
+        <v>3.92</v>
       </c>
       <c r="AN12">
-        <v>2.855769230769231</v>
+        <v>3.756572541382668</v>
       </c>
       <c r="AO12">
-        <v>6.294478527607361</v>
+        <v>25.40816326530612</v>
       </c>
       <c r="AP12">
-        <v>1.563461538461538</v>
+        <v>3.438169425511198</v>
       </c>
       <c r="AQ12">
-        <v>6.294478527607361</v>
+        <v>25.40816326530612</v>
       </c>
     </row>
     <row r="13">
@@ -2053,7 +2035,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>AMP Limited (ASX:AMP)</t>
+          <t>Australian Finance Group Limited (ASX:AFG)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2062,124 +2044,112 @@
         </is>
       </c>
       <c r="D13">
-        <v>-0.216</v>
+        <v>0.09619999999999999</v>
       </c>
       <c r="E13">
-        <v>-0.344</v>
-      </c>
-      <c r="F13">
-        <v>0.08400000000000001</v>
+        <v>-0.00142</v>
       </c>
       <c r="G13">
-        <v>0.159500313283208</v>
+        <v>0.0001564210855623338</v>
       </c>
       <c r="H13">
-        <v>0.159500313283208</v>
+        <v>0</v>
       </c>
       <c r="I13">
-        <v>0.1444627192982456</v>
+        <v>0</v>
       </c>
       <c r="J13">
-        <v>0.1444627192982456</v>
+        <v>0</v>
       </c>
       <c r="K13">
-        <v>90</v>
+        <v>26.7</v>
       </c>
       <c r="L13">
-        <v>0.03524436090225564</v>
+        <v>0.04176442984514313</v>
       </c>
       <c r="M13">
-        <v>146.9</v>
+        <v>26.7</v>
       </c>
       <c r="N13">
-        <v>0.06128493950771798</v>
+        <v>0.09988776655443321</v>
       </c>
       <c r="O13">
-        <v>1.632222222222222</v>
+        <v>1</v>
       </c>
       <c r="P13">
-        <v>-0</v>
+        <v>26.7</v>
       </c>
       <c r="Q13">
-        <v>-0</v>
+        <v>0.09988776655443321</v>
       </c>
       <c r="R13">
-        <v>-0</v>
+        <v>1</v>
       </c>
       <c r="S13">
-        <v>146.9</v>
+        <v>0</v>
       </c>
       <c r="T13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U13">
-        <v>1690.7</v>
+        <v>58.3</v>
       </c>
       <c r="V13">
-        <v>0.7053400083437631</v>
+        <v>0.2181069958847736</v>
       </c>
       <c r="W13">
-        <v>0.02613392183053603</v>
+        <v>0.1754270696452037</v>
       </c>
       <c r="X13">
-        <v>0.06552560388311887</v>
+        <v>0.131930624081409</v>
       </c>
       <c r="Y13">
-        <v>-0.03939168205258284</v>
+        <v>0.0434964455637947</v>
       </c>
       <c r="Z13">
-        <v>0.1359491042670429</v>
+        <v>0.2395817718482986</v>
       </c>
       <c r="AA13">
-        <v>0.01963957728857774</v>
+        <v>0</v>
       </c>
       <c r="AB13">
-        <v>0.02769449321948534</v>
+        <v>0.04025858943383417</v>
       </c>
       <c r="AC13">
-        <v>-0.008054915930907597</v>
+        <v>-0.04025858943383417</v>
       </c>
       <c r="AD13">
-        <v>18603.2</v>
+        <v>3427.8</v>
       </c>
       <c r="AE13">
         <v>0</v>
       </c>
       <c r="AF13">
-        <v>18603.2</v>
+        <v>3427.8</v>
       </c>
       <c r="AG13">
-        <v>16912.5</v>
+        <v>3369.5</v>
       </c>
       <c r="AH13">
-        <v>0.8858582299216198</v>
+        <v>0.9276609564017212</v>
       </c>
       <c r="AI13">
-        <v>0.8520055325034578</v>
+        <v>0.9603563723979491</v>
       </c>
       <c r="AJ13">
-        <v>0.8758642119164142</v>
+        <v>0.926501319841619</v>
       </c>
       <c r="AK13">
-        <v>0.8395841917404275</v>
+        <v>0.959698091711763</v>
       </c>
       <c r="AL13">
-        <v>286.4</v>
+        <v>0</v>
       </c>
       <c r="AM13">
-        <v>286.4</v>
-      </c>
-      <c r="AN13">
-        <v>48.75052410901468</v>
-      </c>
-      <c r="AO13">
-        <v>1.288058659217877</v>
-      </c>
-      <c r="AP13">
-        <v>44.31996855345912</v>
+        <v>-0.178</v>
       </c>
       <c r="AQ13">
-        <v>1.288058659217877</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="14">
@@ -2190,7 +2160,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>FSA Group Limited (ASX:FSA)</t>
+          <t>Liberty Financial Group Limited (ASX:LFG)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2199,13 +2169,16 @@
         </is>
       </c>
       <c r="D14">
-        <v>0.00688</v>
+        <v>0.234</v>
       </c>
       <c r="E14">
-        <v>0.0833</v>
+        <v>0.6679999999999999</v>
+      </c>
+      <c r="F14">
+        <v>0.0998</v>
       </c>
       <c r="G14">
-        <v>0</v>
+        <v>-0.001057916861279776</v>
       </c>
       <c r="H14">
         <v>0</v>
@@ -2217,28 +2190,28 @@
         <v>0</v>
       </c>
       <c r="K14">
-        <v>15.1</v>
+        <v>151.3</v>
       </c>
       <c r="L14">
-        <v>0.3261339092872571</v>
+        <v>0.3533395609528258</v>
       </c>
       <c r="M14">
-        <v>5.61</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="N14">
-        <v>0.05742067553735927</v>
+        <v>0.1152678246082837</v>
       </c>
       <c r="O14">
-        <v>0.3715231788079471</v>
+        <v>0.627230667547918</v>
       </c>
       <c r="P14">
-        <v>5.61</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="Q14">
-        <v>0.05742067553735927</v>
+        <v>0.1152678246082837</v>
       </c>
       <c r="R14">
-        <v>0.3715231788079471</v>
+        <v>0.627230667547918</v>
       </c>
       <c r="S14">
         <v>0</v>
@@ -2247,55 +2220,55 @@
         <v>0</v>
       </c>
       <c r="U14">
-        <v>26.3</v>
+        <v>376.8</v>
       </c>
       <c r="V14">
-        <v>0.2691914022517912</v>
+        <v>0.4576703510263574</v>
       </c>
       <c r="W14">
-        <v>0.3682926829268293</v>
+        <v>0.1945480262311945</v>
       </c>
       <c r="X14">
-        <v>0.04109680784452259</v>
+        <v>0.1187607987523245</v>
       </c>
       <c r="Y14">
-        <v>0.3271958750823067</v>
+        <v>0.07578722747887007</v>
       </c>
       <c r="Z14">
-        <v>0.1386800534352517</v>
+        <v>0.04451883889212342</v>
       </c>
       <c r="AA14">
         <v>0</v>
       </c>
       <c r="AB14">
-        <v>0.02208697598721349</v>
+        <v>0.04036342041728781</v>
       </c>
       <c r="AC14">
-        <v>-0.02208697598721349</v>
+        <v>-0.04036342041728781</v>
       </c>
       <c r="AD14">
-        <v>323.3</v>
+        <v>8898.5</v>
       </c>
       <c r="AE14">
         <v>0</v>
       </c>
       <c r="AF14">
-        <v>323.3</v>
+        <v>8898.5</v>
       </c>
       <c r="AG14">
-        <v>297</v>
+        <v>8521.700000000001</v>
       </c>
       <c r="AH14">
-        <v>0.7679334916864609</v>
+        <v>0.9153140364952993</v>
       </c>
       <c r="AI14">
-        <v>0.8507894736842105</v>
+        <v>0.9204551331781743</v>
       </c>
       <c r="AJ14">
-        <v>0.7524702305548518</v>
+        <v>0.9118994114499733</v>
       </c>
       <c r="AK14">
-        <v>0.8396946564885497</v>
+        <v>0.9172290570140033</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2312,7 +2285,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Auswide Bank Ltd (ASX:ABA)</t>
+          <t>Latitude Group Holdings Limited (ASX:LFS)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2320,11 +2293,8 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D15">
-        <v>0.06709999999999999</v>
-      </c>
-      <c r="E15">
-        <v>0.156</v>
+      <c r="F15">
+        <v>0.0161</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -2339,85 +2309,85 @@
         <v>0</v>
       </c>
       <c r="K15">
-        <v>18.1</v>
+        <v>70.3</v>
       </c>
       <c r="L15">
-        <v>0.2746585735963581</v>
+        <v>0.1467028380634391</v>
       </c>
       <c r="M15">
-        <v>8.529</v>
+        <v>110.2</v>
       </c>
       <c r="N15">
-        <v>0.04047935453251068</v>
+        <v>0.1195487090475157</v>
       </c>
       <c r="O15">
-        <v>0.4712154696132596</v>
+        <v>1.567567567567568</v>
       </c>
       <c r="P15">
-        <v>7.98</v>
+        <v>110.2</v>
       </c>
       <c r="Q15">
-        <v>0.03787375415282392</v>
+        <v>0.1195487090475157</v>
       </c>
       <c r="R15">
-        <v>0.4408839779005524</v>
+        <v>1.567567567567568</v>
       </c>
       <c r="S15">
-        <v>0.5489999999999995</v>
+        <v>0</v>
       </c>
       <c r="T15">
-        <v>0.06436862469222646</v>
+        <v>0</v>
       </c>
       <c r="U15">
-        <v>69.40000000000001</v>
+        <v>262</v>
       </c>
       <c r="V15">
-        <v>0.3293782629330803</v>
+        <v>0.2842265133434584</v>
       </c>
       <c r="W15">
-        <v>0.1083183722321963</v>
+        <v>0.07104598281960586</v>
       </c>
       <c r="X15">
-        <v>0.0365958262284335</v>
+        <v>0.07684211323740416</v>
       </c>
       <c r="Y15">
-        <v>0.07172254600376279</v>
+        <v>-0.005796130417798293</v>
       </c>
       <c r="Z15">
-        <v>0.1269749518304432</v>
+        <v>0.1012102139523095</v>
       </c>
       <c r="AA15">
         <v>0</v>
       </c>
       <c r="AB15">
-        <v>0.02214750596481906</v>
+        <v>0.0412186718258552</v>
       </c>
       <c r="AC15">
-        <v>-0.02214750596481906</v>
+        <v>-0.0412186718258552</v>
       </c>
       <c r="AD15">
-        <v>524.4</v>
+        <v>4049.7</v>
       </c>
       <c r="AE15">
         <v>0</v>
       </c>
       <c r="AF15">
-        <v>524.4</v>
+        <v>4049.7</v>
       </c>
       <c r="AG15">
-        <v>455</v>
+        <v>3787.7</v>
       </c>
       <c r="AH15">
-        <v>0.713372330295198</v>
+        <v>0.8145831238056924</v>
       </c>
       <c r="AI15">
-        <v>0.7316868982838006</v>
+        <v>0.7924118498806402</v>
       </c>
       <c r="AJ15">
-        <v>0.6834910620399579</v>
+        <v>0.8042679689988321</v>
       </c>
       <c r="AK15">
-        <v>0.7029198207940677</v>
+        <v>0.7811945716289237</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2434,7 +2404,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>MyState Limited (ASX:MYS)</t>
+          <t>FSA Group Limited (ASX:FSA)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2443,10 +2413,10 @@
         </is>
       </c>
       <c r="D16">
-        <v>0.0269</v>
+        <v>-0.0416</v>
       </c>
       <c r="E16">
-        <v>0.051</v>
+        <v>0.0264</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -2461,85 +2431,85 @@
         <v>0</v>
       </c>
       <c r="K16">
-        <v>27.2</v>
+        <v>11.9</v>
       </c>
       <c r="L16">
-        <v>0.260038240917782</v>
+        <v>0.2967581047381546</v>
       </c>
       <c r="M16">
-        <v>8.74</v>
+        <v>9</v>
       </c>
       <c r="N16">
-        <v>0.02247364361018257</v>
+        <v>0.1012373453318335</v>
       </c>
       <c r="O16">
-        <v>0.3213235294117647</v>
+        <v>0.7563025210084033</v>
       </c>
       <c r="P16">
-        <v>8.74</v>
+        <v>5.63</v>
       </c>
       <c r="Q16">
-        <v>0.02247364361018257</v>
+        <v>0.06332958380202475</v>
       </c>
       <c r="R16">
-        <v>0.3213235294117647</v>
+        <v>0.473109243697479</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>0.3744444444444445</v>
       </c>
       <c r="U16">
-        <v>60.2</v>
+        <v>24.8</v>
       </c>
       <c r="V16">
-        <v>0.1547955772692209</v>
+        <v>0.2789651293588301</v>
       </c>
       <c r="W16">
-        <v>0.1178509532062392</v>
+        <v>0.2203703703703704</v>
       </c>
       <c r="X16">
-        <v>0.03544006969506541</v>
+        <v>0.07404458735745217</v>
       </c>
       <c r="Y16">
-        <v>0.08241088351117376</v>
+        <v>0.1463257830129182</v>
       </c>
       <c r="Z16">
-        <v>0.08927199795169413</v>
+        <v>0.1143293769476623</v>
       </c>
       <c r="AA16">
         <v>0</v>
       </c>
       <c r="AB16">
-        <v>0.02216793646435198</v>
+        <v>0.04135441507946873</v>
       </c>
       <c r="AC16">
-        <v>-0.02216793646435198</v>
+        <v>-0.04135441507946873</v>
       </c>
       <c r="AD16">
-        <v>886</v>
+        <v>352.5</v>
       </c>
       <c r="AE16">
         <v>0</v>
       </c>
       <c r="AF16">
-        <v>886</v>
+        <v>352.5</v>
       </c>
       <c r="AG16">
-        <v>825.8</v>
+        <v>327.7</v>
       </c>
       <c r="AH16">
-        <v>0.6949564671738959</v>
+        <v>0.7985953783416403</v>
       </c>
       <c r="AI16">
-        <v>0.7399983295748769</v>
+        <v>0.8418915691425842</v>
       </c>
       <c r="AJ16">
-        <v>0.6798386432864082</v>
+        <v>0.7866058569371098</v>
       </c>
       <c r="AK16">
-        <v>0.7262334007563099</v>
+        <v>0.831937039857832</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -2556,7 +2526,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Cash Converters International Limited (ASX:CCV)</t>
+          <t>MyState Limited (ASX:MYS)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2565,7 +2535,10 @@
         </is>
       </c>
       <c r="D17">
-        <v>-0.08789999999999999</v>
+        <v>0.0257</v>
+      </c>
+      <c r="E17">
+        <v>0.0126</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -2580,28 +2553,28 @@
         <v>0</v>
       </c>
       <c r="K17">
-        <v>12.1</v>
+        <v>22.1</v>
       </c>
       <c r="L17">
-        <v>0.08509142053445852</v>
+        <v>0.2271325796505653</v>
       </c>
       <c r="M17">
-        <v>4.62</v>
+        <v>16.9</v>
       </c>
       <c r="N17">
-        <v>0.0375</v>
+        <v>0.05817555938037865</v>
       </c>
       <c r="O17">
-        <v>0.3818181818181818</v>
+        <v>0.764705882352941</v>
       </c>
       <c r="P17">
-        <v>4.62</v>
+        <v>16.9</v>
       </c>
       <c r="Q17">
-        <v>0.0375</v>
+        <v>0.05817555938037865</v>
       </c>
       <c r="R17">
-        <v>0.3818181818181818</v>
+        <v>0.764705882352941</v>
       </c>
       <c r="S17">
         <v>0</v>
@@ -2610,55 +2583,55 @@
         <v>0</v>
       </c>
       <c r="U17">
-        <v>54.1</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="V17">
-        <v>0.4391233766233766</v>
+        <v>0.2826161790017211</v>
       </c>
       <c r="W17">
-        <v>0.05721040189125295</v>
+        <v>0.07099261162865403</v>
       </c>
       <c r="X17">
-        <v>0.02740621195275685</v>
+        <v>0.06863554367731156</v>
       </c>
       <c r="Y17">
-        <v>0.0298041899384961</v>
+        <v>0.002357067951342467</v>
       </c>
       <c r="Z17">
-        <v>0.8821339950372208</v>
+        <v>0.08940549480841679</v>
       </c>
       <c r="AA17">
         <v>0</v>
       </c>
       <c r="AB17">
-        <v>0.0224410554136829</v>
+        <v>0.04169654666632749</v>
       </c>
       <c r="AC17">
-        <v>-0.0224410554136829</v>
+        <v>-0.04169654666632749</v>
       </c>
       <c r="AD17">
-        <v>100.3</v>
+        <v>911.4</v>
       </c>
       <c r="AE17">
         <v>0</v>
       </c>
       <c r="AF17">
-        <v>100.3</v>
+        <v>911.4</v>
       </c>
       <c r="AG17">
-        <v>46.2</v>
+        <v>829.3</v>
       </c>
       <c r="AH17">
-        <v>0.4487695749440716</v>
+        <v>0.7582993593476994</v>
       </c>
       <c r="AI17">
-        <v>0.295</v>
+        <v>0.7547201059953628</v>
       </c>
       <c r="AJ17">
-        <v>0.2727272727272727</v>
+        <v>0.7405786747633506</v>
       </c>
       <c r="AK17">
-        <v>0.161594963273872</v>
+        <v>0.7368280764104842</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -2675,7 +2648,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Asset Resolution Limited (NSX:ASS)</t>
+          <t>Auswide Bank Ltd (ASX:ABA)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2683,6 +2656,12 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D18">
+        <v>0.075</v>
+      </c>
+      <c r="E18">
+        <v>0.115</v>
+      </c>
       <c r="G18">
         <v>0</v>
       </c>
@@ -2696,82 +2675,85 @@
         <v>0</v>
       </c>
       <c r="K18">
-        <v>6.09</v>
+        <v>18</v>
       </c>
       <c r="L18">
-        <v>3.80625</v>
+        <v>0.274390243902439</v>
       </c>
       <c r="M18">
-        <v>-0</v>
+        <v>9.92</v>
       </c>
       <c r="N18">
-        <v>-0</v>
+        <v>0.05414847161572053</v>
       </c>
       <c r="O18">
-        <v>-0</v>
+        <v>0.5511111111111111</v>
       </c>
       <c r="P18">
-        <v>-0</v>
+        <v>9.92</v>
       </c>
       <c r="Q18">
-        <v>-0</v>
+        <v>0.05414847161572053</v>
       </c>
       <c r="R18">
-        <v>-0</v>
+        <v>0.5511111111111111</v>
       </c>
       <c r="S18">
         <v>0</v>
       </c>
+      <c r="T18">
+        <v>0</v>
+      </c>
       <c r="U18">
-        <v>3.6</v>
+        <v>123</v>
       </c>
       <c r="V18">
-        <v>0.3157894736842105</v>
+        <v>0.6713973799126638</v>
       </c>
       <c r="W18">
-        <v>0.9590551181102362</v>
+        <v>0.09360374414976598</v>
       </c>
       <c r="X18">
-        <v>0.02293891894203839</v>
+        <v>0.06704965351188377</v>
       </c>
       <c r="Y18">
-        <v>0.9361161991681979</v>
+        <v>0.02655409063788221</v>
       </c>
       <c r="Z18">
-        <v>0.453257790368272</v>
+        <v>0.1097907949790795</v>
       </c>
       <c r="AA18">
         <v>0</v>
       </c>
       <c r="AB18">
-        <v>0.02293891894203839</v>
+        <v>0.04182442820375208</v>
       </c>
       <c r="AC18">
-        <v>-0.02293891894203839</v>
+        <v>-0.04182442820375208</v>
       </c>
       <c r="AD18">
-        <v>0</v>
+        <v>530.3</v>
       </c>
       <c r="AE18">
         <v>0</v>
       </c>
       <c r="AF18">
-        <v>0</v>
+        <v>530.3</v>
       </c>
       <c r="AG18">
-        <v>-3.6</v>
+        <v>407.3</v>
       </c>
       <c r="AH18">
-        <v>0</v>
+        <v>0.7432375613174491</v>
       </c>
       <c r="AI18">
-        <v>0</v>
+        <v>0.731852056306928</v>
       </c>
       <c r="AJ18">
-        <v>-0.4615384615384615</v>
+        <v>0.6897544453852666</v>
       </c>
       <c r="AK18">
-        <v>-0.3789473684210526</v>
+        <v>0.6770279255319149</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -2788,7 +2770,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Credit Corp Group Limited (ASX:CCP)</t>
+          <t>Cash Converters International Limited (ASX:CCV)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2797,13 +2779,10 @@
         </is>
       </c>
       <c r="D19">
-        <v>0.11</v>
+        <v>-0.0227</v>
       </c>
       <c r="E19">
-        <v>0.139</v>
-      </c>
-      <c r="F19">
-        <v>0.117</v>
+        <v>-0.115</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -2818,85 +2797,85 @@
         <v>0</v>
       </c>
       <c r="K19">
-        <v>66.09999999999999</v>
+        <v>7.7</v>
       </c>
       <c r="L19">
-        <v>0.2624057165541882</v>
+        <v>0.04785581106277191</v>
       </c>
       <c r="M19">
-        <v>18.2</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="N19">
-        <v>0.01102161933022467</v>
+        <v>0.09681274900398407</v>
       </c>
       <c r="O19">
-        <v>0.2753403933434191</v>
+        <v>1.262337662337662</v>
       </c>
       <c r="P19">
-        <v>18.2</v>
+        <v>8.65</v>
       </c>
       <c r="Q19">
-        <v>0.01102161933022467</v>
+        <v>0.08615537848605577</v>
       </c>
       <c r="R19">
-        <v>0.2753403933434191</v>
+        <v>1.123376623376623</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>0.110082304526749</v>
       </c>
       <c r="U19">
-        <v>46.2</v>
+        <v>40</v>
       </c>
       <c r="V19">
-        <v>0.02797795676133955</v>
+        <v>0.398406374501992</v>
       </c>
       <c r="W19">
-        <v>0.1611016329514989</v>
+        <v>0.03231221149811162</v>
       </c>
       <c r="X19">
-        <v>0.02300936620001686</v>
+        <v>0.05410953281334133</v>
       </c>
       <c r="Y19">
-        <v>0.138092266751482</v>
+        <v>-0.02179732131522971</v>
       </c>
       <c r="Z19">
-        <v>0.611336543315342</v>
+        <v>0.7945679012345679</v>
       </c>
       <c r="AA19">
         <v>0</v>
       </c>
       <c r="AB19">
-        <v>0.02296583032193888</v>
+        <v>0.04407957905546031</v>
       </c>
       <c r="AC19">
-        <v>-0.02296583032193888</v>
+        <v>-0.04407957905546031</v>
       </c>
       <c r="AD19">
-        <v>21.2</v>
+        <v>91.8</v>
       </c>
       <c r="AE19">
         <v>0</v>
       </c>
       <c r="AF19">
-        <v>21.2</v>
+        <v>91.8</v>
       </c>
       <c r="AG19">
-        <v>-25</v>
+        <v>51.8</v>
       </c>
       <c r="AH19">
-        <v>0.01267563527653214</v>
+        <v>0.477627471383975</v>
       </c>
       <c r="AI19">
-        <v>0.04066756186456934</v>
+        <v>0.2969912649627952</v>
       </c>
       <c r="AJ19">
-        <v>-0.01537231753059091</v>
+        <v>0.3403416557161629</v>
       </c>
       <c r="AK19">
-        <v>-0.05262050094716902</v>
+        <v>0.1924934968413229</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -2913,7 +2892,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Propell Holdings Limited (ASX:PHL)</t>
+          <t>Prospa Group Limited (ASX:PGL)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2921,32 +2900,38 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D20">
+        <v>0.221</v>
+      </c>
+      <c r="E20">
+        <v>0.412</v>
+      </c>
       <c r="G20">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H20">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I20">
-        <v>-0</v>
+        <v>0.001807010331917303</v>
       </c>
       <c r="J20">
-        <v>-0</v>
+        <v>0.001807010331917303</v>
       </c>
       <c r="K20">
-        <v>-3.25</v>
+        <v>4.63</v>
       </c>
       <c r="L20">
-        <v>14.77272727272727</v>
+        <v>0.07004538577912255</v>
       </c>
       <c r="M20">
-        <v>-0</v>
+        <v>0.298</v>
       </c>
       <c r="N20">
-        <v>-0</v>
+        <v>0.00438880706921944</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>0.06436285097192225</v>
       </c>
       <c r="P20">
         <v>-0</v>
@@ -2955,67 +2940,76 @@
         <v>-0</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>0.298</v>
+      </c>
+      <c r="T20">
+        <v>1</v>
       </c>
       <c r="U20">
-        <v>2.83</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="V20">
-        <v>0.452076677316294</v>
+        <v>1.073637702503682</v>
       </c>
       <c r="W20">
-        <v>2.241379310344828</v>
+        <v>0.04957173447537472</v>
       </c>
       <c r="X20">
-        <v>0.02432387810336338</v>
+        <v>0.09128765093709723</v>
       </c>
       <c r="Y20">
-        <v>2.217055432241465</v>
+        <v>-0.04171591646172251</v>
       </c>
       <c r="Z20">
-        <v>-0.7829181494661924</v>
+        <v>0.2143961444583828</v>
       </c>
       <c r="AA20">
-        <v>0</v>
+        <v>0.0003874160481595324</v>
       </c>
       <c r="AB20">
-        <v>0.02379658988808117</v>
+        <v>0.04544214113374451</v>
       </c>
       <c r="AC20">
-        <v>-0.02379658988808117</v>
+        <v>-0.04505472508558497</v>
       </c>
       <c r="AD20">
-        <v>1.58</v>
+        <v>448.1</v>
       </c>
       <c r="AE20">
-        <v>0</v>
+        <v>0.3077830853013312</v>
       </c>
       <c r="AF20">
-        <v>1.58</v>
+        <v>448.4077830853013</v>
       </c>
       <c r="AG20">
-        <v>-1.25</v>
+        <v>375.5077830853013</v>
       </c>
       <c r="AH20">
-        <v>0.201530612244898</v>
+        <v>0.8684892960662923</v>
       </c>
       <c r="AI20">
-        <v>0.4831804281345566</v>
+        <v>0.8235103280701037</v>
       </c>
       <c r="AJ20">
-        <v>-0.249500998003992</v>
+        <v>0.8468678210212255</v>
       </c>
       <c r="AK20">
-        <v>-2.840909090909091</v>
+        <v>0.7962289778779624</v>
       </c>
       <c r="AL20">
         <v>0</v>
       </c>
       <c r="AM20">
         <v>0</v>
+      </c>
+      <c r="AN20">
+        <v>2475.690607734807</v>
+      </c>
+      <c r="AP20">
+        <v>2074.628635830394</v>
       </c>
     </row>
     <row r="21">
@@ -3026,7 +3020,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>QuickFee Limited (ASX:QFE)</t>
+          <t>Resimac Group Limited (ASX:RMC)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3034,8 +3028,17 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D21">
+        <v>0.175</v>
+      </c>
+      <c r="E21">
+        <v>0.453</v>
+      </c>
+      <c r="F21">
+        <v>0.03700000000000001</v>
+      </c>
       <c r="G21">
-        <v>0.4802744425385935</v>
+        <v>0</v>
       </c>
       <c r="H21">
         <v>0</v>
@@ -3047,82 +3050,85 @@
         <v>0</v>
       </c>
       <c r="K21">
-        <v>-6.41</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="L21">
-        <v>-1.099485420240137</v>
+        <v>0.3878787878787879</v>
       </c>
       <c r="M21">
-        <v>-0</v>
+        <v>26.76</v>
       </c>
       <c r="N21">
-        <v>-0</v>
+        <v>0.09502840909090909</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>0.3801136363636364</v>
       </c>
       <c r="P21">
-        <v>-0</v>
+        <v>21.3</v>
       </c>
       <c r="Q21">
-        <v>-0</v>
+        <v>0.07563920454545454</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>0.3025568181818182</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>5.460000000000001</v>
+      </c>
+      <c r="T21">
+        <v>0.2040358744394619</v>
       </c>
       <c r="U21">
-        <v>16</v>
+        <v>642.7</v>
       </c>
       <c r="V21">
-        <v>0.599250936329588</v>
+        <v>2.282315340909091</v>
       </c>
       <c r="W21">
-        <v>-0.5723214285714286</v>
+        <v>0.292358803986711</v>
       </c>
       <c r="X21">
-        <v>0.02667928700651663</v>
+        <v>0.3087310996499874</v>
       </c>
       <c r="Y21">
-        <v>-0.5990007155779453</v>
+        <v>-0.01637229566327636</v>
       </c>
       <c r="Z21">
-        <v>0.2259689922480621</v>
+        <v>0.01739372101046499</v>
       </c>
       <c r="AA21">
         <v>0</v>
       </c>
       <c r="AB21">
-        <v>0.02379949900305577</v>
+        <v>0.04511023954668489</v>
       </c>
       <c r="AC21">
-        <v>-0.02379949900305577</v>
+        <v>-0.04511023954668489</v>
       </c>
       <c r="AD21">
-        <v>18.2</v>
+        <v>11230.4</v>
       </c>
       <c r="AE21">
         <v>0</v>
       </c>
       <c r="AF21">
-        <v>18.2</v>
+        <v>11230.4</v>
       </c>
       <c r="AG21">
-        <v>2.199999999999999</v>
+        <v>10587.7</v>
       </c>
       <c r="AH21">
-        <v>0.4053452115812918</v>
+        <v>0.9755385684503127</v>
       </c>
       <c r="AI21">
-        <v>0.4986301369863014</v>
+        <v>0.9773298871280752</v>
       </c>
       <c r="AJ21">
-        <v>0.07612456747404842</v>
+        <v>0.9740921678488955</v>
       </c>
       <c r="AK21">
-        <v>0.1073170731707317</v>
+        <v>0.9759867996533987</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3139,7 +3145,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>MoneyMe Limited (ASX:MME)</t>
+          <t>Pepper Money Limited (ASX:PPM)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3147,8 +3153,17 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D22">
+        <v>0.0291</v>
+      </c>
+      <c r="E22">
+        <v>0.176</v>
+      </c>
+      <c r="F22">
+        <v>-0.018</v>
+      </c>
       <c r="G22">
-        <v>0.2256198347107438</v>
+        <v>0.04937458854509546</v>
       </c>
       <c r="H22">
         <v>0</v>
@@ -3160,82 +3175,85 @@
         <v>0</v>
       </c>
       <c r="K22">
-        <v>-5.94</v>
+        <v>101.2</v>
       </c>
       <c r="L22">
-        <v>-0.490909090909091</v>
+        <v>0.3331138907175774</v>
       </c>
       <c r="M22">
-        <v>-0</v>
+        <v>27.3</v>
       </c>
       <c r="N22">
-        <v>-0</v>
+        <v>0.0643412679707754</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>0.2697628458498024</v>
       </c>
       <c r="P22">
-        <v>-0</v>
+        <v>27.3</v>
       </c>
       <c r="Q22">
-        <v>-0</v>
+        <v>0.0643412679707754</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>0.2697628458498024</v>
       </c>
       <c r="S22">
         <v>0</v>
       </c>
+      <c r="T22">
+        <v>0</v>
+      </c>
       <c r="U22">
-        <v>19.6</v>
+        <v>872.2</v>
       </c>
       <c r="V22">
-        <v>0.07114337568058077</v>
+        <v>2.055621022861183</v>
       </c>
       <c r="W22">
-        <v>-0.1839009287925697</v>
+        <v>0.2531265632816408</v>
       </c>
       <c r="X22">
-        <v>0.02743825924078441</v>
+        <v>0.2501683360892432</v>
       </c>
       <c r="Y22">
-        <v>-0.2113391880333541</v>
+        <v>0.002958227192397633</v>
       </c>
       <c r="Z22">
-        <v>0.1382857142857143</v>
+        <v>0.02814813442170316</v>
       </c>
       <c r="AA22">
         <v>0</v>
       </c>
       <c r="AB22">
-        <v>0.02389544792535694</v>
+        <v>0.04513153474139155</v>
       </c>
       <c r="AC22">
-        <v>-0.02389544792535694</v>
+        <v>-0.04513153474139155</v>
       </c>
       <c r="AD22">
-        <v>225.9</v>
+        <v>13118.7</v>
       </c>
       <c r="AE22">
         <v>0</v>
       </c>
       <c r="AF22">
-        <v>225.9</v>
+        <v>13118.7</v>
       </c>
       <c r="AG22">
-        <v>206.3</v>
+        <v>12246.5</v>
       </c>
       <c r="AH22">
-        <v>0.4505384922217791</v>
+        <v>0.968670161707155</v>
       </c>
       <c r="AI22">
-        <v>0.8820773135493947</v>
+        <v>0.9618238338929864</v>
       </c>
       <c r="AJ22">
-        <v>0.4281859692818597</v>
+        <v>0.966513558733466</v>
       </c>
       <c r="AK22">
-        <v>0.8723044397463002</v>
+        <v>0.9592158029951751</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -3252,7 +3270,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Prospa Group Limited (ASX:PGL)</t>
+          <t>MoneyMe Limited (ASX:MME)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3261,34 +3279,34 @@
         </is>
       </c>
       <c r="D23">
-        <v>0.358</v>
+        <v>-0.00642</v>
       </c>
       <c r="G23">
-        <v>0</v>
+        <v>0.8539325842696629</v>
       </c>
       <c r="H23">
         <v>0</v>
       </c>
       <c r="I23">
-        <v>0.00243092554698893</v>
+        <v>0</v>
       </c>
       <c r="J23">
-        <v>0.00243092554698893</v>
+        <v>0</v>
       </c>
       <c r="K23">
-        <v>-7.12</v>
+        <v>-34.7</v>
       </c>
       <c r="L23">
-        <v>-0.1438383838383838</v>
+        <v>-6.498127340823971</v>
       </c>
       <c r="M23">
-        <v>0.004</v>
+        <v>-0</v>
       </c>
       <c r="N23">
-        <v>4.694835680751174e-05</v>
+        <v>-0</v>
       </c>
       <c r="O23">
-        <v>-0.0005617977528089888</v>
+        <v>0</v>
       </c>
       <c r="P23">
         <v>-0</v>
@@ -3300,73 +3318,64 @@
         <v>0</v>
       </c>
       <c r="S23">
-        <v>0.004</v>
-      </c>
-      <c r="T23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U23">
-        <v>60.3</v>
+        <v>55.6</v>
       </c>
       <c r="V23">
-        <v>0.7077464788732394</v>
+        <v>1.177966101694915</v>
       </c>
       <c r="W23">
-        <v>-0.07991021324354658</v>
+        <v>-1.149006622516556</v>
       </c>
       <c r="X23">
-        <v>0.04066608597087625</v>
+        <v>0.1779506371746427</v>
       </c>
       <c r="Y23">
-        <v>-0.1205762992144228</v>
+        <v>-1.326957259691199</v>
       </c>
       <c r="Z23">
-        <v>0.202165956288444</v>
+        <v>0.02257928118393234</v>
       </c>
       <c r="AA23">
-        <v>0.0004914503878730258</v>
+        <v>0</v>
       </c>
       <c r="AB23">
-        <v>0.02456016119374582</v>
+        <v>0.04518298311975139</v>
       </c>
       <c r="AC23">
-        <v>-0.02406871080587279</v>
+        <v>-0.04518298311975139</v>
       </c>
       <c r="AD23">
-        <v>274.9</v>
+        <v>937.7</v>
       </c>
       <c r="AE23">
-        <v>0.3483459271202398</v>
+        <v>0</v>
       </c>
       <c r="AF23">
-        <v>275.2483459271202</v>
+        <v>937.7</v>
       </c>
       <c r="AG23">
-        <v>214.9483459271202</v>
+        <v>882.1</v>
       </c>
       <c r="AH23">
-        <v>0.7636277126453321</v>
+        <v>0.9520763529292313</v>
       </c>
       <c r="AI23">
-        <v>0.7466420206901874</v>
+        <v>0.9371377173695783</v>
       </c>
       <c r="AJ23">
-        <v>0.7161403647358843</v>
+        <v>0.94920908210481</v>
       </c>
       <c r="AK23">
-        <v>0.6970958293316883</v>
+        <v>0.9334391534391535</v>
       </c>
       <c r="AL23">
         <v>0</v>
       </c>
       <c r="AM23">
         <v>0</v>
-      </c>
-      <c r="AN23">
-        <v>1446.842105263158</v>
-      </c>
-      <c r="AP23">
-        <v>1131.307083826948</v>
       </c>
     </row>
     <row r="24">
@@ -3377,7 +3386,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Wisr Limited (ASX:WZR)</t>
+          <t>Plenti Group Limited (ASX:PLT)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3385,11 +3394,8 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D24">
-        <v>0.5870000000000001</v>
-      </c>
       <c r="G24">
-        <v>0</v>
+        <v>0.1270833333333333</v>
       </c>
       <c r="H24">
         <v>0</v>
@@ -3401,10 +3407,10 @@
         <v>0</v>
       </c>
       <c r="K24">
-        <v>-13.2</v>
+        <v>2.41</v>
       </c>
       <c r="L24">
-        <v>-1.505131128848347</v>
+        <v>0.05020833333333333</v>
       </c>
       <c r="M24">
         <v>-0</v>
@@ -3413,7 +3419,7 @@
         <v>-0</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P24">
         <v>-0</v>
@@ -3422,61 +3428,61 @@
         <v>-0</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S24">
         <v>0</v>
       </c>
       <c r="U24">
-        <v>69.3</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="V24">
-        <v>0.2927756653992395</v>
+        <v>1.35</v>
       </c>
       <c r="W24">
-        <v>-0.532258064516129</v>
+        <v>0.08397212543554007</v>
       </c>
       <c r="X24">
-        <v>0.02979391611910862</v>
+        <v>0.1722642137500369</v>
       </c>
       <c r="Y24">
-        <v>-0.5620519806352376</v>
+        <v>-0.08829208831449682</v>
       </c>
       <c r="Z24">
-        <v>0.1496587030716724</v>
+        <v>0.07433792783026173</v>
       </c>
       <c r="AA24">
         <v>0</v>
       </c>
       <c r="AB24">
-        <v>0.02411809732868515</v>
+        <v>0.04518944947444156</v>
       </c>
       <c r="AC24">
-        <v>-0.02411809732868515</v>
+        <v>-0.04518944947444156</v>
       </c>
       <c r="AD24">
-        <v>295.7</v>
+        <v>1025.8</v>
       </c>
       <c r="AE24">
         <v>0</v>
       </c>
       <c r="AF24">
-        <v>295.7</v>
+        <v>1025.8</v>
       </c>
       <c r="AG24">
-        <v>226.4</v>
+        <v>952.9</v>
       </c>
       <c r="AH24">
-        <v>0.5554094665664914</v>
+        <v>0.9499907390257455</v>
       </c>
       <c r="AI24">
-        <v>0.8450985995998858</v>
+        <v>0.9552989383497859</v>
       </c>
       <c r="AJ24">
-        <v>0.488879291729648</v>
+        <v>0.9463700466779223</v>
       </c>
       <c r="AK24">
-        <v>0.8068424803991447</v>
+        <v>0.9520431611549606</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -3493,7 +3499,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Plenti Group Limited (ASX:PLT)</t>
+          <t>Humm Group Limited (ASX:HUM)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3501,8 +3507,11 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D25">
+        <v>-0.00345</v>
+      </c>
       <c r="G25">
-        <v>0.1299435028248588</v>
+        <v>0</v>
       </c>
       <c r="H25">
         <v>0</v>
@@ -3514,82 +3523,85 @@
         <v>0</v>
       </c>
       <c r="K25">
-        <v>-11.6</v>
+        <v>-117.3</v>
       </c>
       <c r="L25">
-        <v>-0.327683615819209</v>
+        <v>-0.5812685827552031</v>
       </c>
       <c r="M25">
-        <v>-0</v>
+        <v>9.917000000000002</v>
       </c>
       <c r="N25">
-        <v>-0</v>
+        <v>0.05165104166666667</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>-0.08454390451832909</v>
       </c>
       <c r="P25">
-        <v>-0</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="Q25">
-        <v>-0</v>
+        <v>0.05057291666666667</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>-0.08277919863597615</v>
       </c>
       <c r="S25">
-        <v>0</v>
+        <v>0.2070000000000007</v>
+      </c>
+      <c r="T25">
+        <v>0.0208732479580519</v>
       </c>
       <c r="U25">
-        <v>71.2</v>
+        <v>193.6</v>
       </c>
       <c r="V25">
-        <v>0.4447220487195503</v>
+        <v>1.008333333333333</v>
       </c>
       <c r="W25">
-        <v>-0.3036649214659686</v>
+        <v>-0.20611491829204</v>
       </c>
       <c r="X25">
-        <v>0.04652618197225433</v>
+        <v>0.1194550851483329</v>
       </c>
       <c r="Y25">
-        <v>-0.3501911034382229</v>
+        <v>-0.325570003440373</v>
       </c>
       <c r="Z25">
-        <v>0.1204901293396868</v>
+        <v>0.09017382367398007</v>
       </c>
       <c r="AA25">
         <v>0</v>
       </c>
       <c r="AB25">
-        <v>0.02466130869827017</v>
+        <v>0.0452946215896485</v>
       </c>
       <c r="AC25">
-        <v>-0.02466130869827017</v>
+        <v>-0.0452946215896485</v>
       </c>
       <c r="AD25">
-        <v>688.2</v>
+        <v>2095.6</v>
       </c>
       <c r="AE25">
         <v>0</v>
       </c>
       <c r="AF25">
-        <v>688.2</v>
+        <v>2095.6</v>
       </c>
       <c r="AG25">
-        <v>617</v>
+        <v>1902</v>
       </c>
       <c r="AH25">
-        <v>0.8112695980195685</v>
+        <v>0.9160692428746284</v>
       </c>
       <c r="AI25">
-        <v>0.9599665225275491</v>
+        <v>0.8289229065305961</v>
       </c>
       <c r="AJ25">
-        <v>0.7939776090593231</v>
+        <v>0.9083094555873925</v>
       </c>
       <c r="AK25">
-        <v>0.9555521139848226</v>
+        <v>0.8147354893981581</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -3606,7 +3618,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Australian Finance Group Limited (ASX:AFG)</t>
+          <t>Wisr Limited (ASX:WZR)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3615,16 +3627,10 @@
         </is>
       </c>
       <c r="D26">
-        <v>0.07150000000000001</v>
-      </c>
-      <c r="E26">
-        <v>0.177</v>
-      </c>
-      <c r="F26">
-        <v>0.177</v>
+        <v>0.861</v>
       </c>
       <c r="G26">
-        <v>0.0004732988033577425</v>
+        <v>0</v>
       </c>
       <c r="H26">
         <v>0</v>
@@ -3636,94 +3642,88 @@
         <v>0</v>
       </c>
       <c r="K26">
-        <v>38.5</v>
+        <v>-13.7</v>
       </c>
       <c r="L26">
-        <v>0.068762278978389</v>
+        <v>-0.8203592814371258</v>
       </c>
       <c r="M26">
-        <v>21.3</v>
+        <v>-0</v>
       </c>
       <c r="N26">
-        <v>0.0403103709311128</v>
+        <v>-0</v>
       </c>
       <c r="O26">
-        <v>0.5532467532467533</v>
+        <v>0</v>
       </c>
       <c r="P26">
-        <v>21.3</v>
+        <v>-0</v>
       </c>
       <c r="Q26">
-        <v>0.0403103709311128</v>
+        <v>-0</v>
       </c>
       <c r="R26">
-        <v>0.5532467532467533</v>
+        <v>0</v>
       </c>
       <c r="S26">
         <v>0</v>
       </c>
-      <c r="T26">
-        <v>0</v>
-      </c>
       <c r="U26">
-        <v>80.2</v>
+        <v>49.3</v>
       </c>
       <c r="V26">
-        <v>0.151778955336866</v>
+        <v>0.8772241992882561</v>
       </c>
       <c r="W26">
-        <v>0.3130081300813008</v>
+        <v>-0.2527675276752767</v>
       </c>
       <c r="X26">
-        <v>0.0499015956997521</v>
+        <v>0.110897630231807</v>
       </c>
       <c r="Y26">
-        <v>0.2631065343815487</v>
+        <v>-0.3636651579070838</v>
       </c>
       <c r="Z26">
-        <v>0.2711248849934627</v>
+        <v>0.05951532430506059</v>
       </c>
       <c r="AA26">
         <v>0</v>
       </c>
       <c r="AB26">
-        <v>0.02470298810025978</v>
+        <v>0.04532675640776436</v>
       </c>
       <c r="AC26">
-        <v>-0.02470298810025978</v>
+        <v>-0.04532675640776436</v>
       </c>
       <c r="AD26">
-        <v>2596.4</v>
+        <v>539.8</v>
       </c>
       <c r="AE26">
         <v>0</v>
       </c>
       <c r="AF26">
-        <v>2596.4</v>
+        <v>539.8</v>
       </c>
       <c r="AG26">
-        <v>2516.2</v>
+        <v>490.4999999999999</v>
       </c>
       <c r="AH26">
-        <v>0.8309011776753712</v>
+        <v>0.9057046979865772</v>
       </c>
       <c r="AI26">
-        <v>0.9446263552353926</v>
+        <v>0.9096730704415233</v>
       </c>
       <c r="AJ26">
-        <v>0.826446823884911</v>
+        <v>0.8972013901591367</v>
       </c>
       <c r="AK26">
-        <v>0.9429620746514766</v>
+        <v>0.9014886969307113</v>
       </c>
       <c r="AL26">
         <v>0</v>
       </c>
       <c r="AM26">
-        <v>-0.5649999999999999</v>
-      </c>
-      <c r="AQ26">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -3734,7 +3734,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Humm Group Limited (ASX:HUM)</t>
+          <t>Pioneer Credit Limited (ASX:PNC)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3743,10 +3743,7 @@
         </is>
       </c>
       <c r="D27">
-        <v>0.05429999999999999</v>
-      </c>
-      <c r="E27">
-        <v>0.0367</v>
+        <v>-0.138</v>
       </c>
       <c r="G27">
         <v>0</v>
@@ -3761,85 +3758,85 @@
         <v>0</v>
       </c>
       <c r="K27">
-        <v>45.1</v>
+        <v>-22.8</v>
       </c>
       <c r="L27">
-        <v>0.1933962264150944</v>
+        <v>-1.288135593220339</v>
       </c>
       <c r="M27">
-        <v>11.4</v>
+        <v>1.63</v>
       </c>
       <c r="N27">
-        <v>0.03517432891082999</v>
+        <v>0.08358974358974358</v>
       </c>
       <c r="O27">
-        <v>0.2527716186252771</v>
+        <v>-0.07149122807017542</v>
       </c>
       <c r="P27">
-        <v>11.4</v>
+        <v>-0</v>
       </c>
       <c r="Q27">
-        <v>0.03517432891082999</v>
+        <v>-0</v>
       </c>
       <c r="R27">
-        <v>0.2527716186252771</v>
+        <v>0</v>
       </c>
       <c r="S27">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="T27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U27">
-        <v>163.6</v>
+        <v>15.9</v>
       </c>
       <c r="V27">
-        <v>0.5047824745448934</v>
+        <v>0.8153846153846154</v>
       </c>
       <c r="W27">
-        <v>0.1129476584022039</v>
+        <v>-0.5560975609756098</v>
       </c>
       <c r="X27">
-        <v>0.05395428742998681</v>
+        <v>0.1097257435882222</v>
       </c>
       <c r="Y27">
-        <v>0.05899337097221705</v>
+        <v>-0.665823304563832</v>
       </c>
       <c r="Z27">
-        <v>0.1334630572883878</v>
+        <v>0.09378974141585417</v>
       </c>
       <c r="AA27">
         <v>0</v>
       </c>
       <c r="AB27">
-        <v>0.02474284710465689</v>
+        <v>0.04533178553846696</v>
       </c>
       <c r="AC27">
-        <v>-0.02474284710465689</v>
+        <v>-0.04533178553846696</v>
       </c>
       <c r="AD27">
-        <v>1831.9</v>
+        <v>183.8</v>
       </c>
       <c r="AE27">
         <v>0</v>
       </c>
       <c r="AF27">
-        <v>1831.9</v>
+        <v>183.8</v>
       </c>
       <c r="AG27">
-        <v>1668.3</v>
+        <v>167.9</v>
       </c>
       <c r="AH27">
-        <v>0.8496753246753247</v>
+        <v>0.9040826364977865</v>
       </c>
       <c r="AI27">
-        <v>0.7629737609329447</v>
+        <v>0.8665723715228665</v>
       </c>
       <c r="AJ27">
-        <v>0.8373318610720739</v>
+        <v>0.8959445037353255</v>
       </c>
       <c r="AK27">
-        <v>0.7456422633413784</v>
+        <v>0.8557594291539246</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -3856,7 +3853,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Butn Limited (ASX:BTN)</t>
+          <t>Propell Holdings Limited (ASX:PHL)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3864,23 +3861,8 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="G28">
-        <v>0</v>
-      </c>
-      <c r="H28">
-        <v>0</v>
-      </c>
-      <c r="I28">
-        <v>0</v>
-      </c>
-      <c r="J28">
-        <v>0</v>
-      </c>
       <c r="K28">
-        <v>-3.94</v>
-      </c>
-      <c r="L28">
-        <v>-3.947895791583167</v>
+        <v>-3.08</v>
       </c>
       <c r="M28">
         <v>-0</v>
@@ -3904,64 +3886,61 @@
         <v>0</v>
       </c>
       <c r="U28">
-        <v>11.6</v>
+        <v>0.266</v>
       </c>
       <c r="V28">
-        <v>0.2929292929292929</v>
+        <v>0.1171806167400881</v>
       </c>
       <c r="W28">
-        <v>6.293929712460064</v>
+        <v>-1.822485207100592</v>
       </c>
       <c r="X28">
-        <v>0.02780261183107584</v>
+        <v>0.05939013878272881</v>
       </c>
       <c r="Y28">
-        <v>6.266127100628988</v>
+        <v>-1.881875345883321</v>
       </c>
       <c r="Z28">
-        <v>0.04531420268797675</v>
+        <v>0</v>
       </c>
       <c r="AA28">
         <v>0</v>
       </c>
       <c r="AB28">
-        <v>0.02493862512216681</v>
+        <v>0.04617323867909294</v>
       </c>
       <c r="AC28">
-        <v>-0.02493862512216681</v>
+        <v>-0.04617323867909294</v>
       </c>
       <c r="AD28">
-        <v>35.1</v>
+        <v>3.91</v>
       </c>
       <c r="AE28">
         <v>0</v>
       </c>
       <c r="AF28">
-        <v>35.1</v>
+        <v>3.91</v>
       </c>
       <c r="AG28">
-        <v>23.5</v>
+        <v>3.644</v>
       </c>
       <c r="AH28">
-        <v>0.4698795180722892</v>
+        <v>0.6326860841423949</v>
       </c>
       <c r="AI28">
-        <v>0.9285714285714285</v>
+        <v>1.174879807692308</v>
       </c>
       <c r="AJ28">
-        <v>0.3724247226624406</v>
+        <v>0.616165032127156</v>
       </c>
       <c r="AK28">
-        <v>0.8969465648854962</v>
+        <v>1.190071848465055</v>
       </c>
       <c r="AL28">
         <v>0</v>
       </c>
       <c r="AM28">
-        <v>-0.008999999999999999</v>
-      </c>
-      <c r="AQ28">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -3972,7 +3951,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Resimac Group Limited (ASX:RMC)</t>
+          <t>QuickFee Limited (ASX:QFE)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -3981,13 +3960,10 @@
         </is>
       </c>
       <c r="D29">
-        <v>0.27</v>
-      </c>
-      <c r="E29">
-        <v>0.525</v>
+        <v>0.366</v>
       </c>
       <c r="G29">
-        <v>0</v>
+        <v>0.5438066465256798</v>
       </c>
       <c r="H29">
         <v>0</v>
@@ -3999,85 +3975,82 @@
         <v>0</v>
       </c>
       <c r="K29">
-        <v>80.59999999999999</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="L29">
-        <v>0.4167528438469493</v>
+        <v>-1.404833836858006</v>
       </c>
       <c r="M29">
-        <v>13.1</v>
+        <v>-0</v>
       </c>
       <c r="N29">
-        <v>0.02319405099150142</v>
+        <v>-0</v>
       </c>
       <c r="O29">
-        <v>0.1625310173697271</v>
+        <v>0</v>
       </c>
       <c r="P29">
-        <v>12.1</v>
+        <v>-0</v>
       </c>
       <c r="Q29">
-        <v>0.02142351274787535</v>
+        <v>-0</v>
       </c>
       <c r="R29">
-        <v>0.1501240694789082</v>
+        <v>0</v>
       </c>
       <c r="S29">
-        <v>1</v>
-      </c>
-      <c r="T29">
-        <v>0.07633587786259542</v>
+        <v>0</v>
       </c>
       <c r="U29">
-        <v>464.7</v>
+        <v>5.64</v>
       </c>
       <c r="V29">
-        <v>0.8227691218130312</v>
+        <v>0.5320754716981132</v>
       </c>
       <c r="W29">
-        <v>0.483503299340132</v>
+        <v>-0.5081967213114754</v>
       </c>
       <c r="X29">
-        <v>0.1266923129583227</v>
+        <v>0.05812138692448061</v>
       </c>
       <c r="Y29">
-        <v>0.3568109863818093</v>
+        <v>-0.5663181082359561</v>
       </c>
       <c r="Z29">
-        <v>0.02231941927963901</v>
+        <v>0.3229268292682927</v>
       </c>
       <c r="AA29">
         <v>0</v>
       </c>
       <c r="AB29">
-        <v>0.02495535437366287</v>
+        <v>0.04626069781341397</v>
       </c>
       <c r="AC29">
-        <v>-0.02495535437366287</v>
+        <v>-0.04626069781341397</v>
       </c>
       <c r="AD29">
-        <v>10679.3</v>
+        <v>16.2</v>
       </c>
       <c r="AE29">
         <v>0</v>
       </c>
       <c r="AF29">
-        <v>10679.3</v>
+        <v>16.2</v>
       </c>
       <c r="AG29">
-        <v>10214.6</v>
+        <v>10.56</v>
       </c>
       <c r="AH29">
-        <v>0.9497692122980053</v>
+        <v>0.6044776119402986</v>
       </c>
       <c r="AI29">
-        <v>0.9779489198816861</v>
+        <v>0.5912408759124088</v>
       </c>
       <c r="AJ29">
-        <v>0.9476037627326197</v>
+        <v>0.4990548204158791</v>
       </c>
       <c r="AK29">
-        <v>0.9769688390688066</v>
+        <v>0.4852941176470588</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -4103,13 +4076,13 @@
         </is>
       </c>
       <c r="D30">
-        <v>0.0924</v>
+        <v>0.121</v>
       </c>
       <c r="E30">
-        <v>0.148</v>
+        <v>0.155</v>
       </c>
       <c r="F30">
-        <v>0.0751</v>
+        <v>0.0245</v>
       </c>
       <c r="G30">
         <v>0</v>
@@ -4124,85 +4097,85 @@
         <v>0</v>
       </c>
       <c r="K30">
-        <v>2950.2</v>
+        <v>3200.6</v>
       </c>
       <c r="L30">
-        <v>0.2670323404024221</v>
+        <v>0.2731003882418192</v>
       </c>
       <c r="M30">
-        <v>880.8</v>
+        <v>1747.9</v>
       </c>
       <c r="N30">
-        <v>0.01602060415575345</v>
+        <v>0.0414419199044031</v>
       </c>
       <c r="O30">
-        <v>0.2985560300996543</v>
+        <v>0.546116353183778</v>
       </c>
       <c r="P30">
-        <v>880.8</v>
+        <v>1152.6</v>
       </c>
       <c r="Q30">
-        <v>0.01602060415575345</v>
+        <v>0.02732762565467991</v>
       </c>
       <c r="R30">
-        <v>0.2985560300996543</v>
+        <v>0.3601199775042179</v>
       </c>
       <c r="S30">
-        <v>0</v>
+        <v>595.3</v>
       </c>
       <c r="T30">
-        <v>0</v>
+        <v>0.3405801247210939</v>
       </c>
       <c r="U30">
-        <v>21301.6</v>
+        <v>34869.9</v>
       </c>
       <c r="V30">
-        <v>0.3874483441010418</v>
+        <v>0.8267495868611167</v>
       </c>
       <c r="W30">
-        <v>0.2006788607655209</v>
+        <v>0.1836248788016133</v>
       </c>
       <c r="X30">
-        <v>0.03686199827028597</v>
+        <v>0.07556479028335128</v>
       </c>
       <c r="Y30">
-        <v>0.163816862495235</v>
+        <v>0.108060088518262</v>
       </c>
       <c r="Z30">
-        <v>0.1370364765769967</v>
+        <v>0.0871210037481471</v>
       </c>
       <c r="AA30">
         <v>0</v>
       </c>
       <c r="AB30">
-        <v>0.02503224123449504</v>
+        <v>0.04670501601426072</v>
       </c>
       <c r="AC30">
-        <v>-0.02503224123449504</v>
+        <v>-0.04670501601426072</v>
       </c>
       <c r="AD30">
-        <v>139501.7</v>
+        <v>177050</v>
       </c>
       <c r="AE30">
         <v>0</v>
       </c>
       <c r="AF30">
-        <v>139501.7</v>
+        <v>177050</v>
       </c>
       <c r="AG30">
-        <v>118200.1</v>
+        <v>142180.1</v>
       </c>
       <c r="AH30">
-        <v>0.7173028302522253</v>
+        <v>0.8076100080692579</v>
       </c>
       <c r="AI30">
-        <v>0.8874983856632904</v>
+        <v>0.8966177683763598</v>
       </c>
       <c r="AJ30">
-        <v>0.6825301869218782</v>
+        <v>0.7712207605669863</v>
       </c>
       <c r="AK30">
-        <v>0.8698622424911892</v>
+        <v>0.8744464754013669</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -4219,7 +4192,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Pioneer Credit Limited (ASX:PNC)</t>
+          <t>Credit Corp Group Limited (ASX:CCP)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4228,7 +4201,13 @@
         </is>
       </c>
       <c r="D31">
-        <v>-0.0959</v>
+        <v>0.102</v>
+      </c>
+      <c r="E31">
+        <v>0.128</v>
+      </c>
+      <c r="F31">
+        <v>0.0407</v>
       </c>
       <c r="G31">
         <v>0</v>
@@ -4243,85 +4222,85 @@
         <v>0</v>
       </c>
       <c r="K31">
-        <v>-14.7</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="L31">
-        <v>-0.7033492822966507</v>
+        <v>0.2696192696192697</v>
       </c>
       <c r="M31">
-        <v>0.5590000000000001</v>
+        <v>34.4</v>
       </c>
       <c r="N31">
-        <v>0.01780254777070064</v>
+        <v>0.0395538691502817</v>
       </c>
       <c r="O31">
-        <v>-0.03802721088435375</v>
+        <v>0.4956772334293947</v>
       </c>
       <c r="P31">
-        <v>-0</v>
+        <v>34.4</v>
       </c>
       <c r="Q31">
-        <v>-0</v>
+        <v>0.0395538691502817</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>0.4956772334293947</v>
       </c>
       <c r="S31">
-        <v>0.5590000000000001</v>
+        <v>0</v>
       </c>
       <c r="T31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U31">
-        <v>7.78</v>
+        <v>20.5</v>
       </c>
       <c r="V31">
-        <v>0.2477707006369427</v>
+        <v>0.0235713464413016</v>
       </c>
       <c r="W31">
-        <v>-0.332579185520362</v>
+        <v>0.1387722455508898</v>
       </c>
       <c r="X31">
-        <v>0.05011300578410458</v>
+        <v>0.04895231137685896</v>
       </c>
       <c r="Y31">
-        <v>-0.3826921913044665</v>
+        <v>0.08981993417403086</v>
       </c>
       <c r="Z31">
-        <v>0.1131013582986092</v>
+        <v>0.5424657534246574</v>
       </c>
       <c r="AA31">
         <v>0</v>
       </c>
       <c r="AB31">
-        <v>0.02647971380201115</v>
+        <v>0.04719079530347903</v>
       </c>
       <c r="AC31">
-        <v>-0.02647971380201115</v>
+        <v>-0.04719079530347903</v>
       </c>
       <c r="AD31">
-        <v>155.5</v>
+        <v>108.8</v>
       </c>
       <c r="AE31">
         <v>0</v>
       </c>
       <c r="AF31">
-        <v>155.5</v>
+        <v>108.8</v>
       </c>
       <c r="AG31">
-        <v>147.72</v>
+        <v>88.3</v>
       </c>
       <c r="AH31">
-        <v>0.831995719636169</v>
+        <v>0.1111905978538579</v>
       </c>
       <c r="AI31">
-        <v>0.7913486005089059</v>
+        <v>0.1757389759328057</v>
       </c>
       <c r="AJ31">
-        <v>0.8246985261277355</v>
+        <v>0.09217118997912317</v>
       </c>
       <c r="AK31">
-        <v>0.7827469266638406</v>
+        <v>0.1475108586702305</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -4338,7 +4317,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Liberty Financial Group Limited (ASX:LFG)</t>
+          <t>Beforepay Group Limited (ASX:B4P)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4346,17 +4325,8 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D32">
-        <v>0.286</v>
-      </c>
-      <c r="E32">
-        <v>1.358</v>
-      </c>
-      <c r="F32">
-        <v>0.169</v>
-      </c>
       <c r="G32">
-        <v>0.0009636614535418582</v>
+        <v>0.02811671087533156</v>
       </c>
       <c r="H32">
         <v>0</v>
@@ -4368,85 +4338,82 @@
         <v>0</v>
       </c>
       <c r="K32">
-        <v>139.4</v>
+        <v>-20.1</v>
       </c>
       <c r="L32">
-        <v>0.3206071757129715</v>
+        <v>-5.331564986737401</v>
       </c>
       <c r="M32">
-        <v>136.2</v>
+        <v>-0</v>
       </c>
       <c r="N32">
-        <v>0.1107677293428757</v>
+        <v>-0</v>
       </c>
       <c r="O32">
-        <v>0.9770444763271161</v>
+        <v>0</v>
       </c>
       <c r="P32">
-        <v>136.2</v>
+        <v>-0</v>
       </c>
       <c r="Q32">
-        <v>0.1107677293428757</v>
+        <v>-0</v>
       </c>
       <c r="R32">
-        <v>0.9770444763271161</v>
+        <v>0</v>
       </c>
       <c r="S32">
         <v>0</v>
       </c>
-      <c r="T32">
-        <v>0</v>
-      </c>
       <c r="U32">
-        <v>374.3</v>
+        <v>19.5</v>
       </c>
       <c r="V32">
-        <v>0.3044079375406636</v>
+        <v>1.326530612244898</v>
       </c>
       <c r="W32">
-        <v>0.1957590226091841</v>
+        <v>2.02416918429003</v>
       </c>
       <c r="X32">
-        <v>0.0641940987046422</v>
+        <v>0.05466925215948681</v>
       </c>
       <c r="Y32">
-        <v>0.1315649239045419</v>
+        <v>1.969499932130544</v>
       </c>
       <c r="Z32">
-        <v>0.05059461472224161</v>
+        <v>0.4564164648910412</v>
       </c>
       <c r="AA32">
         <v>0</v>
       </c>
       <c r="AB32">
-        <v>0.02669510361726152</v>
+        <v>0.04791462607974341</v>
       </c>
       <c r="AC32">
-        <v>-0.02669510361726152</v>
+        <v>-0.04791462607974341</v>
       </c>
       <c r="AD32">
-        <v>9244.6</v>
+        <v>14.7</v>
       </c>
       <c r="AE32">
         <v>0</v>
       </c>
       <c r="AF32">
-        <v>9244.6</v>
+        <v>14.7</v>
       </c>
       <c r="AG32">
-        <v>8870.300000000001</v>
+        <v>-4.800000000000001</v>
       </c>
       <c r="AH32">
-        <v>0.8826067861984686</v>
+        <v>0.5</v>
       </c>
       <c r="AI32">
-        <v>0.9223386211713061</v>
+        <v>0.3951612903225806</v>
       </c>
       <c r="AJ32">
-        <v>0.8782562203586174</v>
+        <v>-0.484848484848485</v>
       </c>
       <c r="AK32">
-        <v>0.9193259195539296</v>
+        <v>-0.2711864406779662</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -4463,7 +4430,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Pepper Money Limited (ASX:PPM)</t>
+          <t>AMP Limited (ASX:AMP)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4472,28 +4439,28 @@
         </is>
       </c>
       <c r="D33">
-        <v>0.0196</v>
-      </c>
-      <c r="E33">
-        <v>0.584</v>
+        <v>-0.282</v>
+      </c>
+      <c r="F33">
+        <v>0.0445</v>
       </c>
       <c r="G33">
-        <v>0.05347222222222223</v>
+        <v>0.02780628907343473</v>
       </c>
       <c r="H33">
-        <v>0</v>
+        <v>0.02780628907343473</v>
       </c>
       <c r="I33">
-        <v>0</v>
+        <v>-0.006305057584644442</v>
       </c>
       <c r="J33">
-        <v>0</v>
+        <v>-0.006305057584644442</v>
       </c>
       <c r="K33">
-        <v>179.9</v>
+        <v>57.2</v>
       </c>
       <c r="L33">
-        <v>0.6246527777777778</v>
+        <v>0.02668657273490716</v>
       </c>
       <c r="M33">
         <v>-0</v>
@@ -4517,61 +4484,73 @@
         <v>0</v>
       </c>
       <c r="U33">
-        <v>627.3</v>
+        <v>1278.8</v>
       </c>
       <c r="V33">
-        <v>0.9087353324641461</v>
+        <v>0.4704930095658572</v>
       </c>
       <c r="W33">
-        <v>0.4998610725201446</v>
+        <v>0.01773038653482533</v>
       </c>
       <c r="X33">
-        <v>0.1105408537764406</v>
+        <v>0.09591258166444018</v>
       </c>
       <c r="Y33">
-        <v>0.3893202187437039</v>
+        <v>-0.07818219512961486</v>
       </c>
       <c r="Z33">
-        <v>0.05572647588088465</v>
+        <v>0.1050765014815449</v>
       </c>
       <c r="AA33">
-        <v>0</v>
+        <v>-0.0006625133926341173</v>
       </c>
       <c r="AB33">
-        <v>0.02694384199829537</v>
+        <v>0.04904053152906292</v>
       </c>
       <c r="AC33">
-        <v>-0.02694384199829537</v>
+        <v>-0.04970304492169704</v>
       </c>
       <c r="AD33">
-        <v>11020.4</v>
+        <v>19495.7</v>
       </c>
       <c r="AE33">
-        <v>0</v>
+        <v>377.5713021346345</v>
       </c>
       <c r="AF33">
-        <v>11020.4</v>
+        <v>19873.27130213464</v>
       </c>
       <c r="AG33">
-        <v>10393.1</v>
+        <v>18594.47130213464</v>
       </c>
       <c r="AH33">
-        <v>0.9410539079645112</v>
+        <v>0.8796880457213058</v>
       </c>
       <c r="AI33">
-        <v>0.9649918565349119</v>
+        <v>0.8630244737420384</v>
       </c>
       <c r="AJ33">
-        <v>0.937717667863652</v>
+        <v>0.8724690364872061</v>
       </c>
       <c r="AK33">
-        <v>0.9629571292238417</v>
+        <v>0.8549704505538959</v>
       </c>
       <c r="AL33">
-        <v>0</v>
+        <v>253.5</v>
       </c>
       <c r="AM33">
-        <v>0</v>
+        <v>253.5</v>
+      </c>
+      <c r="AN33">
+        <v>241.8821339950372</v>
+      </c>
+      <c r="AO33">
+        <v>0.1384615384615385</v>
+      </c>
+      <c r="AP33">
+        <v>230.7006365029111</v>
+      </c>
+      <c r="AQ33">
+        <v>0.1384615384615385</v>
       </c>
     </row>
     <row r="34">
@@ -4582,7 +4561,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>ThinkSmart Limited (AIM:TSL)</t>
+          <t>Butn Limited (ASX:BTN)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4590,29 +4569,23 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D34">
-        <v>-0.2</v>
-      </c>
-      <c r="E34">
-        <v>1.988</v>
-      </c>
       <c r="G34">
-        <v>-0.1034941763727121</v>
+        <v>0</v>
       </c>
       <c r="H34">
-        <v>-0.1034941763727121</v>
+        <v>0</v>
       </c>
       <c r="I34">
-        <v>-0.2196339434276207</v>
+        <v>0</v>
       </c>
       <c r="J34">
-        <v>-0.2195829173599557</v>
+        <v>0</v>
       </c>
       <c r="K34">
-        <v>99</v>
+        <v>-5.97</v>
       </c>
       <c r="L34">
-        <v>16.47254575707155</v>
+        <v>-4.738095238095238</v>
       </c>
       <c r="M34">
         <v>-0</v>
@@ -4621,7 +4594,7 @@
         <v>-0</v>
       </c>
       <c r="O34">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P34">
         <v>-0</v>
@@ -4630,79 +4603,70 @@
         <v>-0</v>
       </c>
       <c r="R34">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S34">
         <v>0</v>
       </c>
       <c r="U34">
-        <v>9.76</v>
+        <v>10.9</v>
       </c>
       <c r="V34">
-        <v>0.1287598944591029</v>
+        <v>0.7218543046357616</v>
       </c>
       <c r="W34">
-        <v>1.202916160388821</v>
+        <v>-2.211111111111111</v>
       </c>
       <c r="X34">
-        <v>0.02295383150287535</v>
+        <v>0.06492522774678272</v>
       </c>
       <c r="Y34">
-        <v>1.179962328885946</v>
+        <v>-2.276036338857894</v>
       </c>
       <c r="Z34">
-        <v>0.08382147838214785</v>
+        <v>0.04809160305343511</v>
       </c>
       <c r="AA34">
-        <v>-0.01840576476057648</v>
+        <v>0</v>
       </c>
       <c r="AB34">
-        <v>0.02294467315029232</v>
+        <v>0.05351181704965527</v>
       </c>
       <c r="AC34">
-        <v>-0.04135043791086879</v>
+        <v>-0.05351181704965527</v>
       </c>
       <c r="AD34">
-        <v>0.206</v>
+        <v>38.8</v>
       </c>
       <c r="AE34">
         <v>0</v>
       </c>
       <c r="AF34">
-        <v>0.206</v>
+        <v>38.8</v>
       </c>
       <c r="AG34">
-        <v>-9.554</v>
+        <v>27.9</v>
       </c>
       <c r="AH34">
-        <v>0.002710312343762334</v>
+        <v>0.7198515769944341</v>
       </c>
       <c r="AI34">
-        <v>0.001108086882618097</v>
+        <v>0.7578125</v>
       </c>
       <c r="AJ34">
-        <v>-0.144220028379072</v>
+        <v>0.6488372093023256</v>
       </c>
       <c r="AK34">
-        <v>-0.05423909711262249</v>
+        <v>0.6923076923076923</v>
       </c>
       <c r="AL34">
-        <v>0.153</v>
+        <v>0</v>
       </c>
       <c r="AM34">
-        <v>0.153</v>
-      </c>
-      <c r="AN34">
-        <v>-0.3311897106109324</v>
-      </c>
-      <c r="AO34">
-        <v>-8.627450980392158</v>
-      </c>
-      <c r="AP34">
-        <v>15.36012861736334</v>
+        <v>-0.016</v>
       </c>
       <c r="AQ34">
-        <v>-8.627450980392158</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="35">
@@ -4713,7 +4677,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Collection House Limited (ASX:CLH)</t>
+          <t>Challenger Limited (ASX:CGF)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -4722,115 +4686,124 @@
         </is>
       </c>
       <c r="D35">
-        <v>-0.109</v>
+        <v>-0.297</v>
+      </c>
+      <c r="E35">
+        <v>-0.0859</v>
+      </c>
+      <c r="F35">
+        <v>0.106</v>
       </c>
       <c r="G35">
-        <v>-0.1078853046594982</v>
+        <v>-0.6929065743944637</v>
       </c>
       <c r="H35">
-        <v>-0.1078853046594982</v>
+        <v>-0.6929065743944637</v>
       </c>
       <c r="I35">
-        <v>-0.1917562724014337</v>
+        <v>-0.7035755478662052</v>
       </c>
       <c r="J35">
-        <v>-0.1917562724014337</v>
+        <v>-0.4995329235053317</v>
       </c>
       <c r="K35">
-        <v>-24</v>
+        <v>174.8</v>
       </c>
       <c r="L35">
-        <v>-0.4301075268817204</v>
+        <v>0.5040369088811996</v>
       </c>
       <c r="M35">
-        <v>-0</v>
+        <v>93.27</v>
       </c>
       <c r="N35">
-        <v>-0</v>
+        <v>0.02638920325939339</v>
       </c>
       <c r="O35">
-        <v>0</v>
+        <v>0.5335812356979405</v>
       </c>
       <c r="P35">
-        <v>-0</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="Q35">
-        <v>-0</v>
+        <v>0.02605817111815301</v>
       </c>
       <c r="R35">
-        <v>0</v>
+        <v>0.5268878718535468</v>
       </c>
       <c r="S35">
-        <v>0</v>
+        <v>1.170000000000002</v>
+      </c>
+      <c r="T35">
+        <v>0.01254422643936959</v>
       </c>
       <c r="U35">
-        <v>5.46</v>
+        <v>505.1</v>
       </c>
       <c r="V35">
-        <v>0.4074626865671642</v>
+        <v>0.1429096876414667</v>
       </c>
       <c r="W35">
-        <v>-0.4752475247524752</v>
+        <v>0.06094202140640798</v>
       </c>
       <c r="X35">
-        <v>0.05094842931105315</v>
+        <v>0.05599983336229149</v>
       </c>
       <c r="Y35">
-        <v>-0.5261959540635284</v>
+        <v>0.004942188044116481</v>
       </c>
       <c r="Z35">
-        <v>0.2728206131129907</v>
+        <v>0.05138919759946655</v>
       </c>
       <c r="AA35">
-        <v>-0.0523150638048208</v>
+        <v>-0.0256705961134547</v>
       </c>
       <c r="AB35">
-        <v>0.02649754596411383</v>
+        <v>0.04716782615852642</v>
       </c>
       <c r="AC35">
-        <v>-0.07881260976893463</v>
+        <v>-0.07283842227198112</v>
       </c>
       <c r="AD35">
-        <v>68.40000000000001</v>
+        <v>4254.1</v>
       </c>
       <c r="AE35">
         <v>0</v>
       </c>
       <c r="AF35">
-        <v>68.40000000000001</v>
+        <v>4254.1</v>
       </c>
       <c r="AG35">
-        <v>62.94</v>
+        <v>3749</v>
       </c>
       <c r="AH35">
-        <v>0.8361858190709046</v>
+        <v>0.5462027348013097</v>
       </c>
       <c r="AI35">
-        <v>0.6965376782077394</v>
+        <v>0.6075549842902028</v>
       </c>
       <c r="AJ35">
-        <v>0.824469478648153</v>
+        <v>0.514732130598347</v>
       </c>
       <c r="AK35">
-        <v>0.6786715548846237</v>
+        <v>0.5770444365774446</v>
       </c>
       <c r="AL35">
-        <v>5.21</v>
+        <v>28.4</v>
       </c>
       <c r="AM35">
-        <v>5.21</v>
+        <v>28.4</v>
       </c>
       <c r="AN35">
-        <v>-11.36212624584718</v>
+        <v>-17.70328755722014</v>
       </c>
       <c r="AO35">
-        <v>-2.053742802303263</v>
+        <v>-8.591549295774648</v>
       </c>
       <c r="AP35">
-        <v>-10.45514950166113</v>
+        <v>-15.6013316687474</v>
       </c>
       <c r="AQ35">
-        <v>-2.053742802303263</v>
+        <v>-8.591549295774648</v>
       </c>
     </row>
     <row r="36">
@@ -4841,7 +4814,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>WT Financial Group Limited (ASX:WTL)</t>
+          <t>ClearView Wealth Limited (ASX:CVW)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -4850,115 +4823,121 @@
         </is>
       </c>
       <c r="D36">
-        <v>0.0204</v>
+        <v>-0.234</v>
+      </c>
+      <c r="E36">
+        <v>0.1</v>
       </c>
       <c r="G36">
-        <v>0.02515657620041754</v>
+        <v>-0.148817802503477</v>
       </c>
       <c r="H36">
-        <v>0.02515657620041754</v>
+        <v>-0.148817802503477</v>
       </c>
       <c r="I36">
-        <v>-0.02995824634655532</v>
+        <v>-0.1515994436717663</v>
       </c>
       <c r="J36">
-        <v>-0.02995824634655532</v>
+        <v>-0.1515994436717663</v>
       </c>
       <c r="K36">
-        <v>-2.46</v>
+        <v>14.6</v>
       </c>
       <c r="L36">
-        <v>-0.2567849686847599</v>
+        <v>0.2030598052851182</v>
       </c>
       <c r="M36">
-        <v>-0</v>
+        <v>4.61</v>
       </c>
       <c r="N36">
-        <v>-0</v>
+        <v>0.02222757955641273</v>
       </c>
       <c r="O36">
-        <v>0</v>
+        <v>0.3157534246575343</v>
       </c>
       <c r="P36">
-        <v>-0</v>
+        <v>4.61</v>
       </c>
       <c r="Q36">
-        <v>-0</v>
+        <v>0.02222757955641273</v>
       </c>
       <c r="R36">
-        <v>0</v>
+        <v>0.3157534246575343</v>
       </c>
       <c r="S36">
         <v>0</v>
       </c>
+      <c r="T36">
+        <v>0</v>
+      </c>
       <c r="U36">
-        <v>0.9340000000000001</v>
+        <v>103.9</v>
       </c>
       <c r="V36">
-        <v>0.05660606060606061</v>
+        <v>0.5009643201542913</v>
       </c>
       <c r="W36">
-        <v>-0.4248704663212435</v>
+        <v>0.04238026124818577</v>
       </c>
       <c r="X36">
-        <v>0.02350094567588271</v>
+        <v>0.05032768978129151</v>
       </c>
       <c r="Y36">
-        <v>-0.4483714119971263</v>
+        <v>-0.00794742853310574</v>
       </c>
       <c r="Z36">
-        <v>4.307553956834533</v>
+        <v>0.2230010545251535</v>
       </c>
       <c r="AA36">
-        <v>-0.1290467625899281</v>
+        <v>-0.03380683580423051</v>
       </c>
       <c r="AB36">
-        <v>0.02333431622412718</v>
+        <v>0.04600151213227386</v>
       </c>
       <c r="AC36">
-        <v>-0.1523810788140552</v>
+        <v>-0.07980834793650438</v>
       </c>
       <c r="AD36">
-        <v>1.69</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="AE36">
         <v>0</v>
       </c>
       <c r="AF36">
-        <v>1.69</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="AG36">
-        <v>0.7559999999999999</v>
+        <v>-34.30000000000001</v>
       </c>
       <c r="AH36">
-        <v>0.09290819131390873</v>
+        <v>0.2512635379061371</v>
       </c>
       <c r="AI36">
-        <v>0.2743506493506493</v>
+        <v>0.08227922922331245</v>
       </c>
       <c r="AJ36">
-        <v>0.04381084840055632</v>
+        <v>-0.1981513575967649</v>
       </c>
       <c r="AK36">
-        <v>0.1446613088404133</v>
+        <v>-0.04622641509433964</v>
       </c>
       <c r="AL36">
-        <v>0.424</v>
+        <v>6.01</v>
       </c>
       <c r="AM36">
-        <v>0.424</v>
+        <v>6.01</v>
       </c>
       <c r="AN36">
-        <v>7.012448132780083</v>
+        <v>-6.504672897196262</v>
       </c>
       <c r="AO36">
-        <v>-0.6768867924528301</v>
+        <v>-1.813643926788686</v>
       </c>
       <c r="AP36">
-        <v>3.136929460580912</v>
+        <v>3.205607476635515</v>
       </c>
       <c r="AQ36">
-        <v>-0.6768867924528301</v>
+        <v>-1.813643926788686</v>
       </c>
     </row>
     <row r="37">
@@ -4969,7 +4948,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>LawFinance Limited (ASX:LAW)</t>
+          <t>Payright Limited (ASX:PYR)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -4978,22 +4957,22 @@
         </is>
       </c>
       <c r="G37">
-        <v>4.031890660592255</v>
+        <v>-0.2446428571428572</v>
       </c>
       <c r="H37">
-        <v>4.031890660592255</v>
+        <v>-0.2446428571428572</v>
       </c>
       <c r="I37">
-        <v>3.16628701594533</v>
+        <v>-0.25</v>
       </c>
       <c r="J37">
-        <v>3.16628701594533</v>
+        <v>-0.25</v>
       </c>
       <c r="K37">
-        <v>-76.7</v>
+        <v>-8.720000000000001</v>
       </c>
       <c r="L37">
-        <v>17.47152619589977</v>
+        <v>-0.7785714285714287</v>
       </c>
       <c r="M37">
         <v>-0</v>
@@ -5017,73 +4996,73 @@
         <v>0</v>
       </c>
       <c r="U37">
-        <v>11</v>
+        <v>8.74</v>
       </c>
       <c r="V37">
-        <v>0.4910714285714286</v>
+        <v>2.312169312169313</v>
       </c>
       <c r="W37">
-        <v>-5.013071895424837</v>
+        <v>-0.6507462686567165</v>
       </c>
       <c r="X37">
-        <v>0.03778387168852358</v>
+        <v>0.1643019288430003</v>
       </c>
       <c r="Y37">
-        <v>-5.05085576711336</v>
+        <v>-0.8150481974997168</v>
       </c>
       <c r="Z37">
-        <v>-0.05006272094879689</v>
+        <v>0.243002820568453</v>
       </c>
       <c r="AA37">
-        <v>-0.1585129433230699</v>
+        <v>-0.06075070514211326</v>
       </c>
       <c r="AB37">
-        <v>0.02448902268308473</v>
+        <v>0.04771785419873967</v>
       </c>
       <c r="AC37">
-        <v>-0.1830019660061546</v>
+        <v>-0.1084685593408529</v>
       </c>
       <c r="AD37">
-        <v>60.6</v>
+        <v>67.2</v>
       </c>
       <c r="AE37">
         <v>0</v>
       </c>
       <c r="AF37">
-        <v>60.6</v>
+        <v>67.2</v>
       </c>
       <c r="AG37">
-        <v>49.6</v>
+        <v>58.46</v>
       </c>
       <c r="AH37">
-        <v>0.7301204819277108</v>
+        <v>0.9467455621301775</v>
       </c>
       <c r="AI37">
-        <v>1.059625808707816</v>
+        <v>0.9337223843268029</v>
       </c>
       <c r="AJ37">
-        <v>0.6888888888888889</v>
+        <v>0.9392673521850899</v>
       </c>
       <c r="AK37">
-        <v>1.073825503355705</v>
+        <v>0.9245611260477621</v>
       </c>
       <c r="AL37">
-        <v>16.6</v>
+        <v>6.71</v>
       </c>
       <c r="AM37">
-        <v>16.598</v>
+        <v>6.71</v>
       </c>
       <c r="AN37">
-        <v>-4.423357664233577</v>
+        <v>-24.52554744525547</v>
       </c>
       <c r="AO37">
-        <v>-0.8373493975903614</v>
+        <v>-0.4172876304023845</v>
       </c>
       <c r="AP37">
-        <v>-3.62043795620438</v>
+        <v>-21.33576642335766</v>
       </c>
       <c r="AQ37">
-        <v>-0.837450295216291</v>
+        <v>-0.4172876304023845</v>
       </c>
     </row>
     <row r="38">
@@ -5094,7 +5073,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Payright Limited (ASX:PYR)</t>
+          <t>Zip Co Limited (ASX:ZIP)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -5102,23 +5081,26 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D38">
+        <v>1.067</v>
+      </c>
       <c r="G38">
-        <v>-0.5147864184008762</v>
+        <v>-0.2326779026217229</v>
       </c>
       <c r="H38">
-        <v>-0.5147864184008762</v>
+        <v>-0.2326779026217229</v>
       </c>
       <c r="I38">
-        <v>-0.5213581599123767</v>
+        <v>-0.2661516853932585</v>
       </c>
       <c r="J38">
-        <v>-0.5213581599123767</v>
+        <v>-0.2661516853932585</v>
       </c>
       <c r="K38">
-        <v>-9.550000000000001</v>
+        <v>-761.4</v>
       </c>
       <c r="L38">
-        <v>-1.046002190580504</v>
+        <v>-1.782303370786517</v>
       </c>
       <c r="M38">
         <v>-0</v>
@@ -5142,73 +5124,73 @@
         <v>0</v>
       </c>
       <c r="U38">
-        <v>5.31</v>
+        <v>166.3</v>
       </c>
       <c r="V38">
-        <v>0.3636986301369863</v>
+        <v>0.6702942361950827</v>
       </c>
       <c r="W38">
-        <v>-1.89484126984127</v>
+        <v>-0.9039534607621987</v>
       </c>
       <c r="X38">
-        <v>0.03722078495972476</v>
+        <v>0.09832408730196868</v>
       </c>
       <c r="Y38">
-        <v>-1.932062054800995</v>
+        <v>-1.002277548064167</v>
       </c>
       <c r="Z38">
-        <v>0.3265379113018598</v>
+        <v>0.2666999625421401</v>
       </c>
       <c r="AA38">
-        <v>-0.1702432045779685</v>
+        <v>-0.07098264452490949</v>
       </c>
       <c r="AB38">
-        <v>0.02601344038696626</v>
+        <v>0.04774513723342082</v>
       </c>
       <c r="AC38">
-        <v>-0.1962566449649348</v>
+        <v>-0.1187277817583303</v>
       </c>
       <c r="AD38">
-        <v>38</v>
+        <v>1905.6</v>
       </c>
       <c r="AE38">
         <v>0</v>
       </c>
       <c r="AF38">
-        <v>38</v>
+        <v>1905.6</v>
       </c>
       <c r="AG38">
-        <v>32.69</v>
+        <v>1739.3</v>
       </c>
       <c r="AH38">
-        <v>0.7224334600760456</v>
+        <v>0.8848028973394624</v>
       </c>
       <c r="AI38">
-        <v>0.7392996108949417</v>
+        <v>0.8633562885103299</v>
       </c>
       <c r="AJ38">
-        <v>0.6912666525692535</v>
+        <v>0.8751635302405153</v>
       </c>
       <c r="AK38">
-        <v>0.7092644825341723</v>
+        <v>0.8522220588955852</v>
       </c>
       <c r="AL38">
-        <v>4.52</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="AM38">
-        <v>4.52</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="AN38">
-        <v>-8.085106382978724</v>
+        <v>-19.17102615694165</v>
       </c>
       <c r="AO38">
-        <v>-1.053097345132743</v>
+        <v>-1.518024032042724</v>
       </c>
       <c r="AP38">
-        <v>-6.955319148936169</v>
+        <v>-17.49798792756539</v>
       </c>
       <c r="AQ38">
-        <v>-1.053097345132743</v>
+        <v>-1.518024032042724</v>
       </c>
     </row>
     <row r="39">
@@ -5219,7 +5201,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Zip Co Limited (ASX:Z1P)</t>
+          <t>LawFinance Limited (ASX:LAW)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -5227,26 +5209,23 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D39">
-        <v>1.671</v>
-      </c>
       <c r="G39">
-        <v>-0.6540141081625798</v>
+        <v>-5</v>
       </c>
       <c r="H39">
-        <v>-0.6540141081625798</v>
+        <v>-5</v>
       </c>
       <c r="I39">
-        <v>-0.6963385959019147</v>
+        <v>-1.980582524271845</v>
       </c>
       <c r="J39">
-        <v>-0.6963385959019147</v>
+        <v>-1.980582524271845</v>
       </c>
       <c r="K39">
-        <v>-493.9</v>
+        <v>-12.8</v>
       </c>
       <c r="L39">
-        <v>-1.659052737655358</v>
+        <v>-6.213592233009709</v>
       </c>
       <c r="M39">
         <v>-0</v>
@@ -5270,73 +5249,73 @@
         <v>0</v>
       </c>
       <c r="U39">
-        <v>247.6</v>
+        <v>3.18</v>
       </c>
       <c r="V39">
-        <v>0.133556286746858</v>
+        <v>1.319502074688797</v>
       </c>
       <c r="W39">
-        <v>-3.483074753173483</v>
+        <v>3.878787878787879</v>
       </c>
       <c r="X39">
-        <v>0.02754383455939441</v>
+        <v>0.2075633186694753</v>
       </c>
       <c r="Y39">
-        <v>-3.510618587732878</v>
+        <v>3.671224560118404</v>
       </c>
       <c r="Z39">
-        <v>0.3564842533828284</v>
+        <v>0.04449244060475162</v>
       </c>
       <c r="AA39">
-        <v>-0.2482337444617412</v>
+        <v>-0.08812095032397407</v>
       </c>
       <c r="AB39">
-        <v>0.02390765135293326</v>
+        <v>0.05531030220541471</v>
       </c>
       <c r="AC39">
-        <v>-0.2721413958146744</v>
+        <v>-0.1434312525293888</v>
       </c>
       <c r="AD39">
-        <v>1555.8</v>
+        <v>58.8</v>
       </c>
       <c r="AE39">
         <v>0</v>
       </c>
       <c r="AF39">
-        <v>1555.8</v>
+        <v>58.8</v>
       </c>
       <c r="AG39">
-        <v>1308.2</v>
+        <v>55.62</v>
       </c>
       <c r="AH39">
-        <v>0.4562864768161422</v>
+        <v>0.9606273484724719</v>
       </c>
       <c r="AI39">
-        <v>0.6448644615767222</v>
+        <v>1.199755152009794</v>
       </c>
       <c r="AJ39">
-        <v>0.4137124063122608</v>
+        <v>0.9584697570222298</v>
       </c>
       <c r="AK39">
-        <v>0.6042494226327945</v>
+        <v>1.213615535675322</v>
       </c>
       <c r="AL39">
-        <v>7.81</v>
+        <v>8.32</v>
       </c>
       <c r="AM39">
-        <v>7.67</v>
+        <v>8.31</v>
       </c>
       <c r="AN39">
-        <v>-7.990755007704161</v>
+        <v>-14.9238578680203</v>
       </c>
       <c r="AO39">
-        <v>-26.54289372599232</v>
+        <v>-0.4903846153846154</v>
       </c>
       <c r="AP39">
-        <v>-6.719054956343093</v>
+        <v>-14.11675126903553</v>
       </c>
       <c r="AQ39">
-        <v>-27.02737940026076</v>
+        <v>-0.4909747292418772</v>
       </c>
     </row>
     <row r="40">
@@ -5347,7 +5326,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>NSX Limited (ASX:NSX)</t>
+          <t>Omni Bridgeway Limited (ASX:OBL)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -5356,25 +5335,25 @@
         </is>
       </c>
       <c r="D40">
-        <v>-0.0173</v>
+        <v>-0.138</v>
       </c>
       <c r="G40">
-        <v>-1.537313432835821</v>
+        <v>-1.757009345794393</v>
       </c>
       <c r="H40">
-        <v>-1.537313432835821</v>
+        <v>-1.757009345794393</v>
       </c>
       <c r="I40">
-        <v>-1.634328358208955</v>
+        <v>-1.957943925233645</v>
       </c>
       <c r="J40">
-        <v>-1.634328358208955</v>
+        <v>-1.957943925233645</v>
       </c>
       <c r="K40">
-        <v>-2.25</v>
+        <v>-31.4</v>
       </c>
       <c r="L40">
-        <v>-1.67910447761194</v>
+        <v>-1.467289719626168</v>
       </c>
       <c r="M40">
         <v>-0</v>
@@ -5398,73 +5377,73 @@
         <v>0</v>
       </c>
       <c r="U40">
-        <v>1.83</v>
+        <v>109.5</v>
       </c>
       <c r="V40">
-        <v>0.1180645161290323</v>
+        <v>0.1594582787243338</v>
       </c>
       <c r="W40">
-        <v>-0.5244755244755245</v>
+        <v>-0.1262057877813505</v>
       </c>
       <c r="X40">
-        <v>0.02356198656375395</v>
+        <v>0.04919680092909713</v>
       </c>
       <c r="Y40">
-        <v>-0.5480375110392784</v>
+        <v>-0.1754025887104476</v>
       </c>
       <c r="Z40">
-        <v>0.3418367346938775</v>
+        <v>0.1184283342556724</v>
       </c>
       <c r="AA40">
-        <v>-0.5586734693877551</v>
+        <v>-0.2318760376314333</v>
       </c>
       <c r="AB40">
-        <v>0.02315540907593699</v>
+        <v>0.04770141951398096</v>
       </c>
       <c r="AC40">
-        <v>-0.581828878463692</v>
+        <v>-0.2795774571454143</v>
       </c>
       <c r="AD40">
-        <v>1.76</v>
+        <v>111.6</v>
       </c>
       <c r="AE40">
         <v>0</v>
       </c>
       <c r="AF40">
-        <v>1.76</v>
+        <v>111.6</v>
       </c>
       <c r="AG40">
-        <v>-0.07000000000000006</v>
+        <v>2.099999999999994</v>
       </c>
       <c r="AH40">
-        <v>0.1019698725376593</v>
+        <v>0.1397970687711386</v>
       </c>
       <c r="AI40">
-        <v>0.2978003384094755</v>
+        <v>0.1796812107551119</v>
       </c>
       <c r="AJ40">
-        <v>-0.004536616979909272</v>
+        <v>0.003048780487804869</v>
       </c>
       <c r="AK40">
-        <v>-0.01715686274509805</v>
+        <v>0.004104769351055501</v>
       </c>
       <c r="AL40">
-        <v>0.099</v>
+        <v>0.963</v>
       </c>
       <c r="AM40">
-        <v>0.099</v>
+        <v>0.963</v>
       </c>
       <c r="AN40">
-        <v>-0.8543689320388349</v>
+        <v>-2.968085106382978</v>
       </c>
       <c r="AO40">
-        <v>-22.12121212121212</v>
+        <v>-43.50986500519211</v>
       </c>
       <c r="AP40">
-        <v>0.03398058252427187</v>
+        <v>-0.05585106382978708</v>
       </c>
       <c r="AQ40">
-        <v>-22.12121212121212</v>
+        <v>-43.50986500519211</v>
       </c>
     </row>
     <row r="41">
@@ -5475,7 +5454,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Openpay Group Ltd (ASX:OPY)</t>
+          <t>NSX Limited (ASX:NSX)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -5483,23 +5462,26 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D41">
+        <v>-0.105</v>
+      </c>
       <c r="G41">
-        <v>-2.186461538461538</v>
+        <v>-1.7890625</v>
       </c>
       <c r="H41">
-        <v>-2.205128205128205</v>
+        <v>-1.7890625</v>
       </c>
       <c r="I41">
-        <v>-2.215384615384616</v>
+        <v>-1.90625</v>
       </c>
       <c r="J41">
-        <v>-2.215384615384616</v>
+        <v>-1.90625</v>
       </c>
       <c r="K41">
-        <v>-47.3</v>
+        <v>-4.38</v>
       </c>
       <c r="L41">
-        <v>-2.425641025641025</v>
+        <v>-3.421875</v>
       </c>
       <c r="M41">
         <v>-0</v>
@@ -5523,73 +5505,73 @@
         <v>0</v>
       </c>
       <c r="U41">
-        <v>39</v>
+        <v>0.549</v>
       </c>
       <c r="V41">
-        <v>0.5660377358490566</v>
+        <v>0.0305</v>
       </c>
       <c r="W41">
-        <v>-0.9078694817658348</v>
+        <v>-1.055421686746988</v>
       </c>
       <c r="X41">
-        <v>0.02590951652660475</v>
+        <v>0.0486321944997291</v>
       </c>
       <c r="Y41">
-        <v>-0.9337789982924396</v>
+        <v>-1.104053881246717</v>
       </c>
       <c r="Z41">
-        <v>0.6037151702786376</v>
+        <v>0.3137254901960784</v>
       </c>
       <c r="AA41">
-        <v>-1.337461300309597</v>
+        <v>-0.5980392156862745</v>
       </c>
       <c r="AB41">
-        <v>0.02581426650483461</v>
+        <v>0.0481037016517875</v>
       </c>
       <c r="AC41">
-        <v>-1.363275566814432</v>
+        <v>-0.646142917338062</v>
       </c>
       <c r="AD41">
-        <v>37.3</v>
+        <v>1.37</v>
       </c>
       <c r="AE41">
         <v>0</v>
       </c>
       <c r="AF41">
-        <v>37.3</v>
+        <v>1.37</v>
       </c>
       <c r="AG41">
-        <v>-1.700000000000003</v>
+        <v>0.8210000000000001</v>
       </c>
       <c r="AH41">
-        <v>0.3512241054613935</v>
+        <v>0.07072792978833248</v>
       </c>
       <c r="AI41">
-        <v>0.4559902200488997</v>
+        <v>0.8925081433224755</v>
       </c>
       <c r="AJ41">
-        <v>-0.02529761904761909</v>
+        <v>0.04362148663726688</v>
       </c>
       <c r="AK41">
-        <v>-0.03971962616822437</v>
+        <v>0.832657200811359</v>
       </c>
       <c r="AL41">
-        <v>4.25</v>
+        <v>0.096</v>
       </c>
       <c r="AM41">
-        <v>4.165</v>
+        <v>0.096</v>
       </c>
       <c r="AN41">
-        <v>-0.8674418604651162</v>
+        <v>-0.5982532751091704</v>
       </c>
       <c r="AO41">
-        <v>-10.16470588235294</v>
+        <v>-25.41666666666666</v>
       </c>
       <c r="AP41">
-        <v>0.0395348837209303</v>
+        <v>-0.3585152838427948</v>
       </c>
       <c r="AQ41">
-        <v>-10.37214885954382</v>
+        <v>-25.41666666666666</v>
       </c>
     </row>
     <row r="42">
@@ -5600,121 +5582,252 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
+          <t>Openpay Group Ltd (ASX:OPY)</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D42">
+        <v>0.5770000000000001</v>
+      </c>
+      <c r="G42">
+        <v>-1.822881355932203</v>
+      </c>
+      <c r="H42">
+        <v>-1.877118644067796</v>
+      </c>
+      <c r="I42">
+        <v>-1.889830508474576</v>
+      </c>
+      <c r="J42">
+        <v>-1.889830508474576</v>
+      </c>
+      <c r="K42">
+        <v>-56.8</v>
+      </c>
+      <c r="L42">
+        <v>-2.406779661016949</v>
+      </c>
+      <c r="M42">
+        <v>-0</v>
+      </c>
+      <c r="N42">
+        <v>-0</v>
+      </c>
+      <c r="O42">
+        <v>0</v>
+      </c>
+      <c r="P42">
+        <v>-0</v>
+      </c>
+      <c r="Q42">
+        <v>-0</v>
+      </c>
+      <c r="R42">
+        <v>0</v>
+      </c>
+      <c r="S42">
+        <v>0</v>
+      </c>
+      <c r="U42">
+        <v>7.13</v>
+      </c>
+      <c r="V42">
+        <v>0.2574007220216606</v>
+      </c>
+      <c r="W42">
+        <v>-1.276404494382022</v>
+      </c>
+      <c r="X42">
+        <v>0.06191134663617765</v>
+      </c>
+      <c r="Y42">
+        <v>-1.3383158410182</v>
+      </c>
+      <c r="Z42">
+        <v>0.5514018691588786</v>
+      </c>
+      <c r="AA42">
+        <v>-1.042056074766355</v>
+      </c>
+      <c r="AB42">
+        <v>0.04783610106645901</v>
+      </c>
+      <c r="AC42">
+        <v>-1.089892175832814</v>
+      </c>
+      <c r="AD42">
+        <v>58.4</v>
+      </c>
+      <c r="AE42">
+        <v>0</v>
+      </c>
+      <c r="AF42">
+        <v>58.4</v>
+      </c>
+      <c r="AG42">
+        <v>51.27</v>
+      </c>
+      <c r="AH42">
+        <v>0.6782810685249709</v>
+      </c>
+      <c r="AI42">
+        <v>1.214137214137214</v>
+      </c>
+      <c r="AJ42">
+        <v>0.6492338862859314</v>
+      </c>
+      <c r="AK42">
+        <v>1.251403465950696</v>
+      </c>
+      <c r="AL42">
+        <v>12.2</v>
+      </c>
+      <c r="AM42">
+        <v>12.2</v>
+      </c>
+      <c r="AN42">
+        <v>-1.318284424379233</v>
+      </c>
+      <c r="AO42">
+        <v>-3.655737704918033</v>
+      </c>
+      <c r="AP42">
+        <v>-1.157336343115124</v>
+      </c>
+      <c r="AQ42">
+        <v>-3.655737704918033</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
           <t>Income Asset Management Group Limited (ASX:IAM)</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="G42">
-        <v>-3.447204968944099</v>
-      </c>
-      <c r="H42">
-        <v>-3.447204968944099</v>
-      </c>
-      <c r="I42">
-        <v>-3.478260869565217</v>
-      </c>
-      <c r="J42">
-        <v>-3.478260869565217</v>
-      </c>
-      <c r="K42">
-        <v>-11.5</v>
-      </c>
-      <c r="L42">
-        <v>-3.571428571428571</v>
-      </c>
-      <c r="M42">
-        <v>-0</v>
-      </c>
-      <c r="N42">
-        <v>-0</v>
-      </c>
-      <c r="O42">
-        <v>0</v>
-      </c>
-      <c r="P42">
-        <v>-0</v>
-      </c>
-      <c r="Q42">
-        <v>-0</v>
-      </c>
-      <c r="R42">
-        <v>0</v>
-      </c>
-      <c r="S42">
-        <v>0</v>
-      </c>
-      <c r="U42">
-        <v>4.52</v>
-      </c>
-      <c r="V42">
-        <v>0.07915936952714535</v>
-      </c>
-      <c r="W42">
-        <v>-1.372315035799523</v>
-      </c>
-      <c r="X42">
-        <v>0.02322337148228188</v>
-      </c>
-      <c r="Y42">
-        <v>-1.395538407281804</v>
-      </c>
-      <c r="Z42">
-        <v>0.5859872611464967</v>
-      </c>
-      <c r="AA42">
-        <v>-2.038216560509553</v>
-      </c>
-      <c r="AB42">
-        <v>0.02304355289090038</v>
-      </c>
-      <c r="AC42">
-        <v>-2.061260113400454</v>
-      </c>
-      <c r="AD42">
-        <v>2.96</v>
-      </c>
-      <c r="AE42">
-        <v>0</v>
-      </c>
-      <c r="AF42">
-        <v>2.96</v>
-      </c>
-      <c r="AG42">
-        <v>-1.56</v>
-      </c>
-      <c r="AH42">
-        <v>0.04928404928404928</v>
-      </c>
-      <c r="AI42">
-        <v>0.2502113271344041</v>
-      </c>
-      <c r="AJ42">
-        <v>-0.02808786460208858</v>
-      </c>
-      <c r="AK42">
-        <v>-0.213406292749658</v>
-      </c>
-      <c r="AL42">
-        <v>0.316</v>
-      </c>
-      <c r="AM42">
-        <v>0.316</v>
-      </c>
-      <c r="AN42">
-        <v>-0.2666666666666667</v>
-      </c>
-      <c r="AO42">
-        <v>-35.44303797468354</v>
-      </c>
-      <c r="AP42">
-        <v>0.1405405405405405</v>
-      </c>
-      <c r="AQ42">
-        <v>-35.44303797468354</v>
+      <c r="D43">
+        <v>0.408</v>
+      </c>
+      <c r="G43">
+        <v>-1.465618860510806</v>
+      </c>
+      <c r="H43">
+        <v>-1.465618860510806</v>
+      </c>
+      <c r="I43">
+        <v>-1.489194499017682</v>
+      </c>
+      <c r="J43">
+        <v>-1.489194499017682</v>
+      </c>
+      <c r="K43">
+        <v>-7.99</v>
+      </c>
+      <c r="L43">
+        <v>-1.569744597249509</v>
+      </c>
+      <c r="M43">
+        <v>-0</v>
+      </c>
+      <c r="N43">
+        <v>-0</v>
+      </c>
+      <c r="O43">
+        <v>0</v>
+      </c>
+      <c r="P43">
+        <v>-0</v>
+      </c>
+      <c r="Q43">
+        <v>-0</v>
+      </c>
+      <c r="R43">
+        <v>0</v>
+      </c>
+      <c r="S43">
+        <v>0</v>
+      </c>
+      <c r="U43">
+        <v>1.96</v>
+      </c>
+      <c r="V43">
+        <v>0.06901408450704226</v>
+      </c>
+      <c r="W43">
+        <v>-0.9007891770011275</v>
+      </c>
+      <c r="X43">
+        <v>0.04889643369061633</v>
+      </c>
+      <c r="Y43">
+        <v>-0.9496856106917438</v>
+      </c>
+      <c r="Z43">
+        <v>0.712785324184288</v>
+      </c>
+      <c r="AA43">
+        <v>-1.061475983755777</v>
+      </c>
+      <c r="AB43">
+        <v>0.04781121781184181</v>
+      </c>
+      <c r="AC43">
+        <v>-1.109287201567618</v>
+      </c>
+      <c r="AD43">
+        <v>3.31</v>
+      </c>
+      <c r="AE43">
+        <v>0</v>
+      </c>
+      <c r="AF43">
+        <v>3.31</v>
+      </c>
+      <c r="AG43">
+        <v>1.35</v>
+      </c>
+      <c r="AH43">
+        <v>0.1043834752444024</v>
+      </c>
+      <c r="AI43">
+        <v>0.2968609865470852</v>
+      </c>
+      <c r="AJ43">
+        <v>0.04537815126050421</v>
+      </c>
+      <c r="AK43">
+        <v>0.14689880304679</v>
+      </c>
+      <c r="AL43">
+        <v>0.504</v>
+      </c>
+      <c r="AM43">
+        <v>0.504</v>
+      </c>
+      <c r="AN43">
+        <v>-0.4436997319034853</v>
+      </c>
+      <c r="AO43">
+        <v>-15.03968253968254</v>
+      </c>
+      <c r="AP43">
+        <v>-0.1809651474530831</v>
+      </c>
+      <c r="AQ43">
+        <v>-15.03968253968254</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/australia/australia_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/australia/australia_financial_svcs_non_bank_insurance.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ43"/>
+  <dimension ref="A1:AQ45"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>43</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.07200000000000001</v>
+        <v>0.134</v>
       </c>
       <c r="E2">
-        <v>0.1185</v>
+        <v>0.08515</v>
       </c>
       <c r="F2">
-        <v>0.04005</v>
+        <v>0.0321</v>
       </c>
       <c r="G2">
-        <v>0.03736148910246911</v>
+        <v>0.108422916028702</v>
       </c>
       <c r="H2">
-        <v>0.03510384176339058</v>
+        <v>0.106165368057548</v>
       </c>
       <c r="I2">
-        <v>0.02195059470511513</v>
+        <v>0.1148113826917579</v>
       </c>
       <c r="J2">
-        <v>0.01899729054214386</v>
+        <v>0.1046067338996103</v>
       </c>
       <c r="K2">
-        <v>3482.649</v>
+        <v>3380.167</v>
       </c>
       <c r="L2">
-        <v>0.1761412529189137</v>
+        <v>0.1568786059991685</v>
       </c>
       <c r="M2">
-        <v>2752.8431</v>
+        <v>3988.1485</v>
       </c>
       <c r="N2">
-        <v>0.04222760796801993</v>
+        <v>0.05895825587157938</v>
       </c>
       <c r="O2">
-        <v>0.7904451754971575</v>
+        <v>1.179867296497481</v>
       </c>
       <c r="P2">
-        <v>2022.4281</v>
+        <v>2613.6745</v>
       </c>
       <c r="Q2">
-        <v>0.03102330857516267</v>
+        <v>0.03863890472885408</v>
       </c>
       <c r="R2">
-        <v>0.5807154553904226</v>
+        <v>0.7732382749136359</v>
       </c>
       <c r="S2">
-        <v>730.415</v>
+        <v>1374.474</v>
       </c>
       <c r="T2">
-        <v>0.2653311407395503</v>
+        <v>0.3446396241263333</v>
       </c>
       <c r="U2">
-        <v>43775.685</v>
+        <v>24989.328</v>
       </c>
       <c r="V2">
-        <v>0.6715030234420301</v>
+        <v>0.3694263627051056</v>
       </c>
       <c r="W2">
-        <v>0.06876876876876878</v>
+        <v>0.03775917823853909</v>
       </c>
       <c r="X2">
-        <v>0.06704965351188377</v>
+        <v>0.06363687649318238</v>
       </c>
       <c r="Y2">
-        <v>0.001719115256885007</v>
+        <v>-0.02587769825464329</v>
       </c>
       <c r="Z2">
-        <v>0.09343381337955699</v>
+        <v>0.08812791996195585</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.04626069781341397</v>
+        <v>0.04642117690259958</v>
       </c>
       <c r="AC2">
-        <v>-0.04518298311975139</v>
+        <v>-0.0442430630928432</v>
       </c>
       <c r="AD2">
-        <v>252711.26</v>
+        <v>188302.98</v>
       </c>
       <c r="AE2">
-        <v>377.8790852199358</v>
+        <v>0.1381566483232385</v>
       </c>
       <c r="AF2">
-        <v>253089.1390852199</v>
+        <v>188303.1181566483</v>
       </c>
       <c r="AG2">
-        <v>209313.4540852199</v>
+        <v>163313.7901566483</v>
       </c>
       <c r="AH2">
-        <v>0.7951782913126459</v>
+        <v>0.7357121893180002</v>
       </c>
       <c r="AI2">
-        <v>0.8719241912061345</v>
+        <v>0.8333398301170269</v>
       </c>
       <c r="AJ2">
-        <v>0.7625149828214868</v>
+        <v>0.7071165472004569</v>
       </c>
       <c r="AK2">
-        <v>0.8491783590004005</v>
+        <v>0.8126169824805478</v>
       </c>
       <c r="AL2">
-        <v>451.901</v>
+        <v>1494.714</v>
       </c>
       <c r="AM2">
-        <v>451.696</v>
+        <v>1489.002</v>
       </c>
       <c r="AN2">
-        <v>376.4443901559785</v>
+        <v>71.53784170366022</v>
       </c>
       <c r="AO2">
-        <v>1.067711733322122</v>
+        <v>1.654940677614581</v>
       </c>
       <c r="AP2">
-        <v>311.7980400816015</v>
+        <v>62.0442441657115</v>
       </c>
       <c r="AQ2">
-        <v>1.068196309021997</v>
+        <v>1.661289239369726</v>
       </c>
     </row>
     <row r="3">
@@ -716,7 +716,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ASX Limited (ASX:ASX)</t>
+          <t>WT Financial Group Limited (ASX:WTL)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -725,115 +725,106 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0304</v>
-      </c>
-      <c r="E3">
-        <v>0.0321</v>
-      </c>
-      <c r="F3">
-        <v>0.0429</v>
+        <v>0.8440000000000001</v>
       </c>
       <c r="G3">
-        <v>0.7009383378016085</v>
+        <v>0.03567415730337078</v>
       </c>
       <c r="H3">
-        <v>0.7009383378016085</v>
+        <v>0.03567415730337078</v>
       </c>
       <c r="I3">
-        <v>0.687265415549598</v>
+        <v>0.0351123595505618</v>
       </c>
       <c r="J3">
-        <v>0.4785727376959044</v>
+        <v>0.02981849611063095</v>
       </c>
       <c r="K3">
-        <v>350.4</v>
+        <v>2.76</v>
       </c>
       <c r="L3">
-        <v>0.4697050938337801</v>
+        <v>0.02584269662921348</v>
       </c>
       <c r="M3">
-        <v>303.6</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.03392444101773324</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>0.8664383561643837</v>
+        <v>-0</v>
       </c>
       <c r="P3">
-        <v>303.6</v>
+        <v>-0</v>
       </c>
       <c r="Q3">
-        <v>0.03392444101773324</v>
+        <v>-0</v>
       </c>
       <c r="R3">
-        <v>0.8664383561643837</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
       <c r="U3">
-        <v>3425.8</v>
+        <v>3.54</v>
       </c>
       <c r="V3">
-        <v>0.3828008894550412</v>
+        <v>0.1853403141361256</v>
       </c>
       <c r="W3">
-        <v>0.125089247465372</v>
+        <v>0.2</v>
       </c>
       <c r="X3">
-        <v>0.04816887954801183</v>
+        <v>0.05200154469671647</v>
       </c>
       <c r="Y3">
-        <v>0.07692036791736015</v>
+        <v>0.1479984553032835</v>
       </c>
       <c r="AB3">
-        <v>0.04809776206260877</v>
+        <v>0.04838096241155791</v>
       </c>
       <c r="AD3">
-        <v>46.6</v>
+        <v>5.41</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>46.6</v>
+        <v>5.41</v>
       </c>
       <c r="AG3">
-        <v>-3379.2</v>
+        <v>1.87</v>
       </c>
       <c r="AH3">
-        <v>0.005180137618248313</v>
+        <v>0.2207262341901265</v>
       </c>
       <c r="AI3">
-        <v>0.01746299419149335</v>
+        <v>0.2414100847835788</v>
       </c>
       <c r="AJ3">
-        <v>-0.6066677438466098</v>
+        <v>0.08917501192179303</v>
       </c>
       <c r="AK3">
-        <v>4.462168229235441</v>
+        <v>0.0990990990990991</v>
       </c>
       <c r="AL3">
-        <v>9.51</v>
+        <v>0.5</v>
       </c>
       <c r="AM3">
-        <v>9.51</v>
+        <v>0.5</v>
       </c>
       <c r="AN3">
-        <v>0.08911837827500478</v>
+        <v>1.41994750656168</v>
       </c>
       <c r="AO3">
-        <v>53.91167192429022</v>
+        <v>7.5</v>
       </c>
       <c r="AP3">
-        <v>-6.462421113023524</v>
+        <v>0.4908136482939633</v>
       </c>
       <c r="AQ3">
-        <v>53.91167192429022</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="4">
@@ -844,7 +835,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>WT Financial Group Limited (ASX:WTL)</t>
+          <t>ASX Limited (ASX:ASX)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -853,118 +844,115 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.556</v>
+        <v>0.0675</v>
       </c>
       <c r="E4">
-        <v>0.141</v>
+        <v>-0.0655</v>
+      </c>
+      <c r="F4">
+        <v>0.0321</v>
       </c>
       <c r="G4">
-        <v>0.03851640513552069</v>
+        <v>0.5452600042799058</v>
       </c>
       <c r="H4">
-        <v>0.03851640513552069</v>
+        <v>0.5452600042799058</v>
       </c>
       <c r="I4">
-        <v>0.03366619115549215</v>
+        <v>0.5375561737641772</v>
       </c>
       <c r="J4">
-        <v>0.02682904492700023</v>
+        <v>0.38131084772049</v>
       </c>
       <c r="K4">
-        <v>1.29</v>
+        <v>211.2</v>
       </c>
       <c r="L4">
-        <v>0.01840228245363766</v>
+        <v>0.2259790284613738</v>
       </c>
       <c r="M4">
-        <v>-0</v>
+        <v>304.4</v>
       </c>
       <c r="N4">
-        <v>-0</v>
+        <v>0.0365812623179349</v>
       </c>
       <c r="O4">
-        <v>-0</v>
+        <v>1.441287878787879</v>
       </c>
       <c r="P4">
-        <v>-0</v>
+        <v>304.4</v>
       </c>
       <c r="Q4">
-        <v>-0</v>
+        <v>0.0365812623179349</v>
       </c>
       <c r="R4">
-        <v>-0</v>
+        <v>1.441287878787879</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
       <c r="U4">
-        <v>2.33</v>
+        <v>671.3</v>
       </c>
       <c r="V4">
-        <v>0.1153465346534654</v>
+        <v>0.08067346055857327</v>
       </c>
       <c r="W4">
-        <v>0.2885906040268457</v>
+        <v>0.080552271253671</v>
       </c>
       <c r="X4">
-        <v>0.04964552938063471</v>
+        <v>0.04986562075120544</v>
       </c>
       <c r="Y4">
-        <v>0.238945074646211</v>
-      </c>
-      <c r="Z4">
-        <v>76.52838427947594</v>
-      </c>
-      <c r="AA4">
-        <v>2.053183460024798</v>
+        <v>0.03068665050246556</v>
       </c>
       <c r="AB4">
-        <v>0.04805214690345079</v>
-      </c>
-      <c r="AC4">
-        <v>2.005131313121348</v>
+        <v>0.04975762223024192</v>
       </c>
       <c r="AD4">
-        <v>4.67</v>
+        <v>52.3</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>4.67</v>
+        <v>52.3</v>
       </c>
       <c r="AG4">
-        <v>2.34</v>
+        <v>-619</v>
       </c>
       <c r="AH4">
-        <v>0.1877764374748693</v>
+        <v>0.006245894787126052</v>
       </c>
       <c r="AI4">
-        <v>0.2528424472116946</v>
+        <v>0.0211287520704561</v>
       </c>
       <c r="AJ4">
-        <v>0.1038154392191659</v>
+        <v>-0.0803666484900418</v>
       </c>
       <c r="AK4">
-        <v>0.1449814126394052</v>
+        <v>-0.3431263858093127</v>
       </c>
       <c r="AL4">
-        <v>0.412</v>
+        <v>221.7</v>
       </c>
       <c r="AM4">
-        <v>0.412</v>
+        <v>221.7</v>
       </c>
       <c r="AN4">
-        <v>1.729629629629629</v>
+        <v>0.1026295133437991</v>
       </c>
       <c r="AO4">
-        <v>5.728155339805825</v>
+        <v>2.266125394677492</v>
       </c>
       <c r="AP4">
-        <v>0.8666666666666666</v>
+        <v>-1.214678178963893</v>
       </c>
       <c r="AQ4">
-        <v>5.728155339805825</v>
+        <v>2.266125394677492</v>
       </c>
     </row>
     <row r="5">
@@ -975,7 +963,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>N1 Holdings Limited (ASX:N1H)</t>
+          <t>Litigation Capital Management Limited (AIM:LIT)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -984,43 +972,46 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.207</v>
+        <v>0.441</v>
+      </c>
+      <c r="E5">
+        <v>0.296</v>
       </c>
       <c r="G5">
-        <v>0.557312252964427</v>
+        <v>0.9195121951219511</v>
       </c>
       <c r="H5">
-        <v>0.557312252964427</v>
+        <v>0.9195121951219511</v>
       </c>
       <c r="I5">
-        <v>0.546772068511199</v>
+        <v>0.9178861788617887</v>
       </c>
       <c r="J5">
-        <v>0.546772068511199</v>
+        <v>0.6758098591549296</v>
       </c>
       <c r="K5">
-        <v>0.759</v>
+        <v>21</v>
       </c>
       <c r="L5">
-        <v>0.1</v>
+        <v>0.1707317073170732</v>
       </c>
       <c r="M5">
-        <v>0.0881</v>
+        <v>1.8045</v>
       </c>
       <c r="N5">
-        <v>0.009332627118644068</v>
+        <v>0.01190303430079156</v>
       </c>
       <c r="O5">
-        <v>0.1160737812911726</v>
+        <v>0.08592857142857142</v>
       </c>
       <c r="P5">
-        <v>0.0881</v>
+        <v>1.8045</v>
       </c>
       <c r="Q5">
-        <v>0.009332627118644068</v>
+        <v>0.01190303430079156</v>
       </c>
       <c r="R5">
-        <v>0.1160737812911726</v>
+        <v>0.08592857142857142</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1029,73 +1020,73 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>9.74</v>
+        <v>69.5</v>
       </c>
       <c r="V5">
-        <v>1.031779661016949</v>
+        <v>0.45844327176781</v>
       </c>
       <c r="W5">
-        <v>-0.6837837837837837</v>
+        <v>0.2046783625730994</v>
       </c>
       <c r="X5">
-        <v>0.08406019886214552</v>
+        <v>0.05215211677128741</v>
       </c>
       <c r="Y5">
-        <v>-0.7678439826459292</v>
+        <v>0.152526245801812</v>
       </c>
       <c r="Z5">
-        <v>0.9885386819484241</v>
+        <v>1.060344827586207</v>
       </c>
       <c r="AA5">
-        <v>0.5405053399322741</v>
+        <v>0.7165914885866927</v>
       </c>
       <c r="AB5">
-        <v>0.04776218254415802</v>
+        <v>0.04735945565836543</v>
       </c>
       <c r="AC5">
-        <v>0.4927431573881161</v>
+        <v>0.6692320329283273</v>
       </c>
       <c r="AD5">
-        <v>51.9</v>
+        <v>45.9</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>51.9</v>
+        <v>45.9</v>
       </c>
       <c r="AG5">
-        <v>42.16</v>
+        <v>-23.6</v>
       </c>
       <c r="AH5">
-        <v>0.8461036843821325</v>
+        <v>0.2324050632911392</v>
       </c>
       <c r="AI5">
-        <v>0.9917639639983948</v>
+        <v>0.2732142857142857</v>
       </c>
       <c r="AJ5">
-        <v>0.8170542635658915</v>
+        <v>-0.184375</v>
       </c>
       <c r="AK5">
-        <v>0.9898804911835835</v>
+        <v>-0.2395939086294416</v>
       </c>
       <c r="AL5">
-        <v>3.37</v>
+        <v>5.21</v>
       </c>
       <c r="AM5">
-        <v>3.37</v>
+        <v>5.092</v>
       </c>
       <c r="AN5">
-        <v>12.26950354609929</v>
+        <v>0.4058355437665783</v>
       </c>
       <c r="AO5">
-        <v>1.231454005934718</v>
+        <v>21.66986564299424</v>
       </c>
       <c r="AP5">
-        <v>9.96690307328605</v>
+        <v>-0.2086648983200708</v>
       </c>
       <c r="AQ5">
-        <v>1.231454005934718</v>
+        <v>22.172034564022</v>
       </c>
     </row>
     <row r="6">
@@ -1115,37 +1106,37 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.113</v>
+        <v>0.134</v>
       </c>
       <c r="E6">
-        <v>0.09179999999999999</v>
+        <v>0.106</v>
       </c>
       <c r="G6">
-        <v>0.2344637223974763</v>
+        <v>0.1958495460440986</v>
       </c>
       <c r="H6">
-        <v>0.2018927444794953</v>
+        <v>0.1958495460440986</v>
       </c>
       <c r="I6">
-        <v>0.2034700315457413</v>
+        <v>0.1815823605706874</v>
       </c>
       <c r="J6">
-        <v>0.1556802216154601</v>
+        <v>0.158827102727019</v>
       </c>
       <c r="K6">
-        <v>18.2</v>
+        <v>20.7</v>
       </c>
       <c r="L6">
-        <v>0.1435331230283912</v>
+        <v>0.1342412451361868</v>
       </c>
       <c r="M6">
-        <v>1.31</v>
+        <v>-0</v>
       </c>
       <c r="N6">
-        <v>0.003266018449264523</v>
+        <v>-0</v>
       </c>
       <c r="O6">
-        <v>0.07197802197802199</v>
+        <v>-0</v>
       </c>
       <c r="P6">
         <v>-0</v>
@@ -1157,79 +1148,76 @@
         <v>-0</v>
       </c>
       <c r="S6">
-        <v>1.31</v>
-      </c>
-      <c r="T6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U6">
-        <v>43.3</v>
+        <v>43.6</v>
       </c>
       <c r="V6">
-        <v>0.1079531288955373</v>
+        <v>0.1775244299674267</v>
       </c>
       <c r="W6">
-        <v>0.2749244712990936</v>
+        <v>0.2527472527472527</v>
       </c>
       <c r="X6">
-        <v>0.04904553196088826</v>
+        <v>0.05119249901587278</v>
       </c>
       <c r="Y6">
-        <v>0.2258789393382054</v>
+        <v>0.20155475373138</v>
       </c>
       <c r="Z6">
-        <v>2.929759704251387</v>
+        <v>1.631746031746031</v>
       </c>
       <c r="AA6">
-        <v>0.4561056400379007</v>
+        <v>0.2591654946085326</v>
       </c>
       <c r="AB6">
-        <v>0.04775560802956735</v>
+        <v>0.04883238444470751</v>
       </c>
       <c r="AC6">
-        <v>0.4083500320083333</v>
+        <v>0.2103331101638251</v>
       </c>
       <c r="AD6">
-        <v>55.9</v>
+        <v>43.8</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>55.9</v>
+        <v>43.8</v>
       </c>
       <c r="AG6">
-        <v>12.6</v>
+        <v>0.1999999999999957</v>
       </c>
       <c r="AH6">
-        <v>0.1223194748358862</v>
+        <v>0.1513476157567381</v>
       </c>
       <c r="AI6">
-        <v>0.4056603773584905</v>
+        <v>0.2965470548408937</v>
       </c>
       <c r="AJ6">
-        <v>0.03045685279187817</v>
+        <v>0.0008136696501220332</v>
       </c>
       <c r="AK6">
-        <v>0.1333333333333334</v>
+        <v>0.001921229586935598</v>
       </c>
       <c r="AL6">
-        <v>1.82</v>
+        <v>4.45</v>
       </c>
       <c r="AM6">
-        <v>1.82</v>
+        <v>4.45</v>
       </c>
       <c r="AN6">
-        <v>2.109433962264151</v>
+        <v>1.399361022364217</v>
       </c>
       <c r="AO6">
-        <v>14.17582417582418</v>
+        <v>6.292134831460674</v>
       </c>
       <c r="AP6">
-        <v>0.4754716981132076</v>
+        <v>0.00638977635782734</v>
       </c>
       <c r="AQ6">
-        <v>14.17582417582418</v>
+        <v>6.292134831460674</v>
       </c>
     </row>
     <row r="7">
@@ -1240,7 +1228,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Yellow Brick Road Holdings Limited (ASX:YBR)</t>
+          <t>Helia Group Limited (ASX:HLI)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1249,115 +1237,121 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.06900000000000001</v>
+        <v>0.0713</v>
+      </c>
+      <c r="E7">
+        <v>0.22</v>
       </c>
       <c r="G7">
-        <v>0.04692816635160681</v>
+        <v>0.5025232403718459</v>
       </c>
       <c r="H7">
-        <v>0.04692816635160681</v>
+        <v>0.5025232403718459</v>
       </c>
       <c r="I7">
-        <v>0.04673913043478261</v>
+        <v>0.9492695883134129</v>
       </c>
       <c r="J7">
-        <v>0.04673913043478261</v>
+        <v>0.6659001305744109</v>
       </c>
       <c r="K7">
-        <v>-1.69</v>
+        <v>184</v>
       </c>
       <c r="L7">
-        <v>-0.007986767485822307</v>
+        <v>0.4887118193891102</v>
       </c>
       <c r="M7">
-        <v>-0</v>
+        <v>184.5</v>
       </c>
       <c r="N7">
-        <v>-0</v>
+        <v>0.2068385650224215</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>1.002717391304348</v>
       </c>
       <c r="P7">
-        <v>-0</v>
+        <v>62.5</v>
       </c>
       <c r="Q7">
-        <v>-0</v>
+        <v>0.07006726457399103</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>0.3396739130434783</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>122</v>
+      </c>
+      <c r="T7">
+        <v>0.6612466124661247</v>
       </c>
       <c r="U7">
-        <v>6.95</v>
+        <v>19.3</v>
       </c>
       <c r="V7">
-        <v>0.337378640776699</v>
+        <v>0.02163677130044843</v>
       </c>
       <c r="W7">
-        <v>-0.05184049079754601</v>
+        <v>0.1932976152957243</v>
       </c>
       <c r="X7">
-        <v>0.04927678783344761</v>
+        <v>0.05090478438537088</v>
       </c>
       <c r="Y7">
-        <v>-0.1011172786309936</v>
+        <v>0.1423928309103535</v>
       </c>
       <c r="Z7">
-        <v>8.1793583301121</v>
+        <v>0.3531861802422115</v>
       </c>
       <c r="AA7">
-        <v>0.3822960958639351</v>
+        <v>0.2351867235403661</v>
       </c>
       <c r="AB7">
-        <v>0.04767362931276945</v>
+        <v>0.04851007491820674</v>
       </c>
       <c r="AC7">
-        <v>0.3346224665511656</v>
+        <v>0.1866766486221594</v>
       </c>
       <c r="AD7">
-        <v>3.6</v>
+        <v>125.8</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>3.6</v>
+        <v>125.8</v>
       </c>
       <c r="AG7">
-        <v>-3.35</v>
+        <v>106.5</v>
       </c>
       <c r="AH7">
-        <v>0.1487603305785124</v>
+        <v>0.1235999213990961</v>
       </c>
       <c r="AI7">
-        <v>0.1128526645768025</v>
+        <v>0.1452320480258601</v>
       </c>
       <c r="AJ7">
-        <v>-0.1942028985507246</v>
+        <v>0.1066599899849775</v>
       </c>
       <c r="AK7">
-        <v>-0.1342685370741483</v>
+        <v>0.1257527453064116</v>
       </c>
       <c r="AL7">
-        <v>0.256</v>
+        <v>25</v>
       </c>
       <c r="AM7">
-        <v>0.256</v>
+        <v>25</v>
       </c>
       <c r="AN7">
-        <v>0.3625377643504532</v>
+        <v>0.3513966480446927</v>
       </c>
       <c r="AO7">
-        <v>38.6328125</v>
+        <v>14.296</v>
       </c>
       <c r="AP7">
-        <v>-0.3373615307150051</v>
+        <v>0.2974860335195531</v>
       </c>
       <c r="AQ7">
-        <v>38.6328125</v>
+        <v>14.296</v>
       </c>
     </row>
     <row r="8">
@@ -1377,121 +1371,121 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.114</v>
+        <v>0.232</v>
       </c>
       <c r="E8">
-        <v>0.122</v>
+        <v>0.08259999999999999</v>
       </c>
       <c r="G8">
-        <v>0.6488408037094281</v>
+        <v>0.6552045944005742</v>
       </c>
       <c r="H8">
-        <v>0.6143740340030912</v>
+        <v>0.6231155778894472</v>
       </c>
       <c r="I8">
-        <v>0.6081916537867079</v>
+        <v>0.6173725771715721</v>
       </c>
       <c r="J8">
-        <v>0.4258541165567679</v>
+        <v>0.4417767651543755</v>
       </c>
       <c r="K8">
-        <v>35.6</v>
+        <v>31.7</v>
       </c>
       <c r="L8">
-        <v>0.2751159196290572</v>
+        <v>0.2275664034458004</v>
       </c>
       <c r="M8">
-        <v>17.7</v>
+        <v>27.17</v>
       </c>
       <c r="N8">
-        <v>0.0671217292377702</v>
+        <v>0.1438327157226046</v>
       </c>
       <c r="O8">
-        <v>0.497191011235955</v>
+        <v>0.8570977917981073</v>
       </c>
       <c r="P8">
-        <v>17.7</v>
+        <v>18.2</v>
       </c>
       <c r="Q8">
-        <v>0.0671217292377702</v>
+        <v>0.09634727368978295</v>
       </c>
       <c r="R8">
-        <v>0.497191011235955</v>
+        <v>0.5741324921135647</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>8.970000000000002</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>0.3301435406698565</v>
       </c>
       <c r="U8">
-        <v>84.40000000000001</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="V8">
-        <v>0.3200606750094805</v>
+        <v>0.5140285865537321</v>
       </c>
       <c r="W8">
-        <v>0.1411018628616726</v>
+        <v>0.1247049567269866</v>
       </c>
       <c r="X8">
-        <v>0.05540520824237007</v>
+        <v>0.06663332091339989</v>
       </c>
       <c r="Y8">
-        <v>0.08569665461930255</v>
+        <v>0.05807163581358674</v>
       </c>
       <c r="Z8">
-        <v>0.3340216830149716</v>
+        <v>0.3133858267716536</v>
       </c>
       <c r="AA8">
-        <v>0.1422445087311455</v>
+        <v>0.1384465767964106</v>
       </c>
       <c r="AB8">
-        <v>0.04366330535543526</v>
+        <v>0.04535628573658662</v>
       </c>
       <c r="AC8">
-        <v>0.09858120337571023</v>
+        <v>0.09309029105982403</v>
       </c>
       <c r="AD8">
-        <v>293.4</v>
+        <v>411.9</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>293.4</v>
+        <v>411.9</v>
       </c>
       <c r="AG8">
-        <v>209</v>
+        <v>314.8</v>
       </c>
       <c r="AH8">
-        <v>0.5266558966074314</v>
+        <v>0.6855858854860186</v>
       </c>
       <c r="AI8">
-        <v>0.5357925493060629</v>
+        <v>0.6213606878865591</v>
       </c>
       <c r="AJ8">
-        <v>0.4421408927438121</v>
+        <v>0.6249751836410562</v>
       </c>
       <c r="AK8">
-        <v>0.4512089810017271</v>
+        <v>0.5563803464121597</v>
       </c>
       <c r="AL8">
-        <v>24.2</v>
+        <v>38.8</v>
       </c>
       <c r="AM8">
-        <v>24.2</v>
+        <v>38.8</v>
       </c>
       <c r="AN8">
-        <v>3.690566037735849</v>
+        <v>4.745391705069125</v>
       </c>
       <c r="AO8">
-        <v>3.25206611570248</v>
+        <v>2.216494845360825</v>
       </c>
       <c r="AP8">
-        <v>2.628930817610063</v>
+        <v>3.626728110599078</v>
       </c>
       <c r="AQ8">
-        <v>3.25206611570248</v>
+        <v>2.216494845360825</v>
       </c>
     </row>
     <row r="9">
@@ -1502,7 +1496,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Litigation Capital Management Limited (AIM:LIT)</t>
+          <t>Findi Limited (ASX:FND)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1511,25 +1505,25 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.8490000000000001</v>
+        <v>0.6679999999999999</v>
       </c>
       <c r="G9">
-        <v>0.3975535168195719</v>
+        <v>0.2588082901554404</v>
       </c>
       <c r="H9">
-        <v>0.3975535168195719</v>
+        <v>0.2588082901554404</v>
       </c>
       <c r="I9">
-        <v>0.3914373088685015</v>
+        <v>0.1318652849740932</v>
       </c>
       <c r="J9">
-        <v>0.2435846297034969</v>
+        <v>0.1318652849740932</v>
       </c>
       <c r="K9">
-        <v>4.58</v>
+        <v>2.16</v>
       </c>
       <c r="L9">
-        <v>0.1400611620795107</v>
+        <v>0.05595854922279793</v>
       </c>
       <c r="M9">
         <v>-0</v>
@@ -1553,73 +1547,73 @@
         <v>0</v>
       </c>
       <c r="U9">
-        <v>34.4</v>
+        <v>1.84</v>
       </c>
       <c r="V9">
-        <v>0.3429710867397807</v>
+        <v>0.0696969696969697</v>
       </c>
       <c r="W9">
-        <v>0.06876876876876878</v>
+        <v>0.2097087378640777</v>
       </c>
       <c r="X9">
-        <v>0.0512489541308601</v>
+        <v>0.06275812729443339</v>
       </c>
       <c r="Y9">
-        <v>0.01751981463790868</v>
+        <v>0.1469506105696443</v>
       </c>
       <c r="Z9">
-        <v>0.4873323397913563</v>
+        <v>1.026677660451632</v>
       </c>
       <c r="AA9">
-        <v>0.1187066675306162</v>
+        <v>0.1353831422719898</v>
       </c>
       <c r="AB9">
-        <v>0.04713416677464732</v>
+        <v>0.04691080340273043</v>
       </c>
       <c r="AC9">
-        <v>0.07157250075596891</v>
+        <v>0.08847233886925934</v>
       </c>
       <c r="AD9">
-        <v>47.8</v>
+        <v>44.3</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>47.8</v>
+        <v>44.3</v>
       </c>
       <c r="AG9">
-        <v>13.4</v>
+        <v>42.45999999999999</v>
       </c>
       <c r="AH9">
-        <v>0.3227548953409858</v>
+        <v>0.6265912305516267</v>
       </c>
       <c r="AI9">
-        <v>0.4245115452930728</v>
+        <v>0.7445378151260503</v>
       </c>
       <c r="AJ9">
-        <v>0.1178540017590149</v>
+        <v>0.6166134185303515</v>
       </c>
       <c r="AK9">
-        <v>0.1713554987212276</v>
+        <v>0.7363857093305584</v>
       </c>
       <c r="AL9">
-        <v>3.02</v>
+        <v>4.25</v>
       </c>
       <c r="AM9">
-        <v>3.019</v>
+        <v>2.93</v>
       </c>
       <c r="AN9">
-        <v>3.676923076923077</v>
+        <v>3.661157024793388</v>
       </c>
       <c r="AO9">
-        <v>4.23841059602649</v>
+        <v>1.197647058823529</v>
       </c>
       <c r="AP9">
-        <v>1.030769230769231</v>
+        <v>3.509090909090909</v>
       </c>
       <c r="AQ9">
-        <v>4.23981450811527</v>
+        <v>1.737201365187713</v>
       </c>
     </row>
     <row r="10">
@@ -1630,7 +1624,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Earlypay Limited (ASX:EPY)</t>
+          <t>Challenger Limited (ASX:CGF)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1639,124 +1633,124 @@
         </is>
       </c>
       <c r="D10">
-        <v>0.061</v>
+        <v>-0.03700000000000001</v>
       </c>
       <c r="E10">
-        <v>0.392</v>
+        <v>-0.0227</v>
       </c>
       <c r="F10">
-        <v>0.0394</v>
+        <v>0.0926</v>
       </c>
       <c r="G10">
-        <v>0.4974393530997305</v>
+        <v>0.4336540896429476</v>
       </c>
       <c r="H10">
-        <v>0.4932614555256065</v>
+        <v>0.4336540896429476</v>
       </c>
       <c r="I10">
-        <v>0.4636118598382749</v>
+        <v>0.4311851101544695</v>
       </c>
       <c r="J10">
-        <v>0.4009138749839558</v>
+        <v>0.3122320171505293</v>
       </c>
       <c r="K10">
-        <v>9.109999999999999</v>
+        <v>191.3</v>
       </c>
       <c r="L10">
-        <v>0.2455525606469003</v>
+        <v>0.1211066092681692</v>
       </c>
       <c r="M10">
-        <v>4.52</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="N10">
-        <v>0.1147208121827411</v>
+        <v>0.0309580207922095</v>
       </c>
       <c r="O10">
-        <v>0.4961580680570801</v>
+        <v>0.4918975431259801</v>
       </c>
       <c r="P10">
-        <v>4.52</v>
+        <v>81.5</v>
       </c>
       <c r="Q10">
-        <v>0.1147208121827411</v>
+        <v>0.02681273851822608</v>
       </c>
       <c r="R10">
-        <v>0.4961580680570801</v>
+        <v>0.4260324098274961</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>12.59999999999999</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>0.1339001062699255</v>
       </c>
       <c r="U10">
-        <v>36.3</v>
+        <v>394.9</v>
       </c>
       <c r="V10">
-        <v>0.9213197969543147</v>
+        <v>0.129918410317147</v>
       </c>
       <c r="W10">
-        <v>0.2075170842824601</v>
+        <v>0.06961679828232469</v>
       </c>
       <c r="X10">
-        <v>0.08168583656895653</v>
+        <v>0.06040732854223071</v>
       </c>
       <c r="Y10">
-        <v>0.1258312477135036</v>
+        <v>0.009209469740093977</v>
       </c>
       <c r="Z10">
-        <v>0.2542837559972584</v>
+        <v>0.2590612392167153</v>
       </c>
       <c r="AA10">
-        <v>0.1019458859623356</v>
+        <v>0.08088721328615082</v>
       </c>
       <c r="AB10">
-        <v>0.0455398095193086</v>
+        <v>0.04659253854344078</v>
       </c>
       <c r="AC10">
-        <v>0.05640607644302698</v>
+        <v>0.03429467474271004</v>
       </c>
       <c r="AD10">
-        <v>202.3</v>
+        <v>4174</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>202.3</v>
+        <v>4174</v>
       </c>
       <c r="AG10">
-        <v>166</v>
+        <v>3779.1</v>
       </c>
       <c r="AH10">
-        <v>0.8369880016549441</v>
+        <v>0.578629255850061</v>
       </c>
       <c r="AI10">
-        <v>0.7753928708317362</v>
+        <v>0.6009560009214466</v>
       </c>
       <c r="AJ10">
-        <v>0.8081791626095424</v>
+        <v>0.5542258788332087</v>
       </c>
       <c r="AK10">
-        <v>0.7390917186108638</v>
+        <v>0.5769001786068665</v>
       </c>
       <c r="AL10">
-        <v>6.71</v>
+        <v>362.9</v>
       </c>
       <c r="AM10">
-        <v>6.71</v>
+        <v>362.9</v>
       </c>
       <c r="AN10">
-        <v>11.05464480874317</v>
+        <v>6.093430656934307</v>
       </c>
       <c r="AO10">
-        <v>2.563338301043219</v>
+        <v>1.876825571782861</v>
       </c>
       <c r="AP10">
-        <v>9.071038251366121</v>
+        <v>5.516934306569343</v>
       </c>
       <c r="AQ10">
-        <v>2.563338301043219</v>
+        <v>1.876825571782861</v>
       </c>
     </row>
     <row r="11">
@@ -1767,7 +1761,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Helia Group Limited (ASX:HLI)</t>
+          <t>FleetPartners Group Limited (ASX:FPR)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1776,121 +1770,121 @@
         </is>
       </c>
       <c r="D11">
-        <v>-0.123</v>
+        <v>-0.00402</v>
       </c>
       <c r="E11">
-        <v>-0.00461</v>
+        <v>0.0877</v>
       </c>
       <c r="G11">
-        <v>1.151079136690648</v>
+        <v>0.4567895580490039</v>
       </c>
       <c r="H11">
-        <v>1.151079136690648</v>
+        <v>0.4444698877948248</v>
       </c>
       <c r="I11">
-        <v>0.8644161593801881</v>
+        <v>0.1829631325852988</v>
       </c>
       <c r="J11">
-        <v>0.6087437742114</v>
+        <v>0.129135922189084</v>
       </c>
       <c r="K11">
-        <v>105</v>
+        <v>52.3</v>
       </c>
       <c r="L11">
-        <v>0.5810736026563365</v>
+        <v>0.1197618502404397</v>
       </c>
       <c r="M11">
-        <v>150.5</v>
+        <v>51.8</v>
       </c>
       <c r="N11">
-        <v>0.2317523868186018</v>
+        <v>0.1039117352056168</v>
       </c>
       <c r="O11">
-        <v>1.433333333333333</v>
+        <v>0.9904397705544933</v>
       </c>
       <c r="P11">
-        <v>81.59999999999999</v>
+        <v>-0</v>
       </c>
       <c r="Q11">
-        <v>0.1256544502617801</v>
+        <v>-0</v>
       </c>
       <c r="R11">
-        <v>0.7771428571428571</v>
+        <v>-0</v>
       </c>
       <c r="S11">
-        <v>68.90000000000001</v>
+        <v>51.8</v>
       </c>
       <c r="T11">
-        <v>0.4578073089700997</v>
+        <v>1</v>
       </c>
       <c r="U11">
-        <v>13.1</v>
+        <v>56.5</v>
       </c>
       <c r="V11">
-        <v>0.02017246689251617</v>
+        <v>0.1133400200601805</v>
       </c>
       <c r="W11">
-        <v>0.09680095879044896</v>
+        <v>0.1308154077038519</v>
       </c>
       <c r="X11">
-        <v>0.04947815899443358</v>
+        <v>0.06363687649318238</v>
       </c>
       <c r="Y11">
-        <v>0.04732279979601538</v>
+        <v>0.06717853121066954</v>
       </c>
       <c r="Z11">
-        <v>0.1558887470237068</v>
+        <v>0.5285645122246428</v>
       </c>
       <c r="AA11">
-        <v>0.09489630422029743</v>
+        <v>0.06825666572255265</v>
       </c>
       <c r="AB11">
-        <v>0.04760616483712501</v>
+        <v>0.04302976092962453</v>
       </c>
       <c r="AC11">
-        <v>0.04729013938317243</v>
+        <v>0.02522690479292812</v>
       </c>
       <c r="AD11">
-        <v>133.5</v>
+        <v>893.3</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>133.5</v>
+        <v>893.3</v>
       </c>
       <c r="AG11">
-        <v>120.4</v>
+        <v>836.8</v>
       </c>
       <c r="AH11">
-        <v>0.1705198620513476</v>
+        <v>0.6418307228050008</v>
       </c>
       <c r="AI11">
-        <v>0.122996130458817</v>
+        <v>0.6853087840429612</v>
       </c>
       <c r="AJ11">
-        <v>0.1564042608469733</v>
+        <v>0.6266756534112184</v>
       </c>
       <c r="AK11">
-        <v>0.1122820106313532</v>
+        <v>0.6710505212510024</v>
       </c>
       <c r="AL11">
-        <v>7.08</v>
+        <v>4.54</v>
       </c>
       <c r="AM11">
-        <v>7.08</v>
+        <v>4.54</v>
       </c>
       <c r="AN11">
-        <v>0.8514030612244897</v>
+        <v>4.602266872746007</v>
       </c>
       <c r="AO11">
-        <v>22.06214689265537</v>
+        <v>17.59911894273128</v>
       </c>
       <c r="AP11">
-        <v>0.7678571428571428</v>
+        <v>4.311179804224627</v>
       </c>
       <c r="AQ11">
-        <v>22.06214689265537</v>
+        <v>17.59911894273128</v>
       </c>
     </row>
     <row r="12">
@@ -1901,7 +1895,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Eclipx Group Limited (ASX:ECX)</t>
+          <t>Charter Hall Social Infrastructure REIT (ASX:CQE)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1910,121 +1904,118 @@
         </is>
       </c>
       <c r="D12">
-        <v>0.0228</v>
+        <v>0.0916</v>
       </c>
       <c r="E12">
-        <v>0.138</v>
+        <v>-0.107</v>
+      </c>
+      <c r="F12">
+        <v>0.0145</v>
       </c>
       <c r="G12">
-        <v>0.4840559761413168</v>
+        <v>0</v>
       </c>
       <c r="H12">
-        <v>0.4712089928882772</v>
+        <v>0</v>
       </c>
       <c r="I12">
-        <v>0.2284927735719202</v>
+        <v>0.7175283732660782</v>
       </c>
       <c r="J12">
-        <v>0.1596089227156795</v>
+        <v>0.7175283732660782</v>
       </c>
       <c r="K12">
-        <v>66.59999999999999</v>
+        <v>39.1</v>
       </c>
       <c r="L12">
-        <v>0.1527873365450791</v>
+        <v>0.4930643127364439</v>
       </c>
       <c r="M12">
-        <v>51.7</v>
+        <v>36</v>
       </c>
       <c r="N12">
-        <v>0.1457569777276572</v>
+        <v>0.04766318019330068</v>
       </c>
       <c r="O12">
-        <v>0.7762762762762764</v>
+        <v>0.9207161125319693</v>
       </c>
       <c r="P12">
-        <v>-0</v>
+        <v>36</v>
       </c>
       <c r="Q12">
-        <v>-0</v>
+        <v>0.04766318019330068</v>
       </c>
       <c r="R12">
-        <v>-0</v>
+        <v>0.9207161125319693</v>
       </c>
       <c r="S12">
-        <v>51.7</v>
+        <v>0</v>
       </c>
       <c r="T12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U12">
-        <v>65.40000000000001</v>
+        <v>9.65</v>
       </c>
       <c r="V12">
-        <v>0.1843811671835354</v>
+        <v>0.01277638024625977</v>
       </c>
       <c r="W12">
-        <v>0.1597122302158273</v>
+        <v>0.03801652892561984</v>
       </c>
       <c r="X12">
-        <v>0.06234951859459027</v>
+        <v>0.05483766166121605</v>
       </c>
       <c r="Y12">
-        <v>0.09736271162123704</v>
+        <v>-0.01682113273559621</v>
       </c>
       <c r="Z12">
-        <v>0.4623462028001697</v>
+        <v>0.05655116347065829</v>
       </c>
       <c r="AA12">
-        <v>0.07379457935062017</v>
+        <v>0.0405770643314055</v>
       </c>
       <c r="AB12">
-        <v>0.04601080906108601</v>
+        <v>0.04564734244002926</v>
       </c>
       <c r="AC12">
-        <v>0.02778377028953416</v>
+        <v>-0.005070278108623753</v>
       </c>
       <c r="AD12">
-        <v>771.6</v>
+        <v>491.7</v>
       </c>
       <c r="AE12">
         <v>0</v>
       </c>
       <c r="AF12">
-        <v>771.6</v>
+        <v>491.7</v>
       </c>
       <c r="AG12">
-        <v>706.2</v>
+        <v>482.05</v>
       </c>
       <c r="AH12">
-        <v>0.6850750244162301</v>
+        <v>0.3943063352044908</v>
       </c>
       <c r="AI12">
-        <v>0.6586989926583575</v>
+        <v>0.3314682486180396</v>
       </c>
       <c r="AJ12">
-        <v>0.6656612310302573</v>
+        <v>0.3895825756657373</v>
       </c>
       <c r="AK12">
-        <v>0.6385171790235081</v>
+        <v>0.3270907548770144</v>
       </c>
       <c r="AL12">
-        <v>3.92</v>
+        <v>19.1</v>
       </c>
       <c r="AM12">
-        <v>3.92</v>
-      </c>
-      <c r="AN12">
-        <v>3.756572541382668</v>
+        <v>19.1</v>
       </c>
       <c r="AO12">
-        <v>25.40816326530612</v>
-      </c>
-      <c r="AP12">
-        <v>3.438169425511198</v>
+        <v>2.979057591623036</v>
       </c>
       <c r="AQ12">
-        <v>25.40816326530612</v>
+        <v>2.979057591623036</v>
       </c>
     </row>
     <row r="13">
@@ -2035,7 +2026,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Australian Finance Group Limited (ASX:AFG)</t>
+          <t>Tyro Payments Limited (ASX:TYR)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2044,112 +2035,118 @@
         </is>
       </c>
       <c r="D13">
-        <v>0.09619999999999999</v>
-      </c>
-      <c r="E13">
-        <v>-0.00142</v>
+        <v>0.245</v>
+      </c>
+      <c r="F13">
+        <v>0.61</v>
       </c>
       <c r="G13">
-        <v>0.0001564210855623338</v>
+        <v>0.07550392893747865</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>0.07550392893747865</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>0.01434916296549368</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>0.01434916296549368</v>
       </c>
       <c r="K13">
-        <v>26.7</v>
+        <v>4</v>
       </c>
       <c r="L13">
-        <v>0.04176442984514313</v>
+        <v>0.01366586949094636</v>
       </c>
       <c r="M13">
-        <v>26.7</v>
+        <v>-0</v>
       </c>
       <c r="N13">
-        <v>0.09988776655443321</v>
+        <v>-0</v>
       </c>
       <c r="O13">
-        <v>1</v>
+        <v>-0</v>
       </c>
       <c r="P13">
-        <v>26.7</v>
+        <v>-0</v>
       </c>
       <c r="Q13">
-        <v>0.09988776655443321</v>
+        <v>-0</v>
       </c>
       <c r="R13">
-        <v>1</v>
+        <v>-0</v>
       </c>
       <c r="S13">
         <v>0</v>
       </c>
-      <c r="T13">
-        <v>0</v>
-      </c>
       <c r="U13">
-        <v>58.3</v>
+        <v>28.4</v>
       </c>
       <c r="V13">
-        <v>0.2181069958847736</v>
+        <v>0.07219115404168785</v>
       </c>
       <c r="W13">
-        <v>0.1754270696452037</v>
+        <v>0.03636363636363636</v>
       </c>
       <c r="X13">
-        <v>0.131930624081409</v>
+        <v>0.05025430699646323</v>
       </c>
       <c r="Y13">
-        <v>0.0434964455637947</v>
+        <v>-0.01389067063282687</v>
       </c>
       <c r="Z13">
-        <v>0.2395817718482986</v>
+        <v>2.969463325555443</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>0.04260931317845187</v>
       </c>
       <c r="AB13">
-        <v>0.04025858943383417</v>
+        <v>0.04946810421556082</v>
       </c>
       <c r="AC13">
-        <v>-0.04025858943383417</v>
+        <v>-0.006858791037108958</v>
       </c>
       <c r="AD13">
-        <v>3427.8</v>
+        <v>22.3</v>
       </c>
       <c r="AE13">
         <v>0</v>
       </c>
       <c r="AF13">
-        <v>3427.8</v>
+        <v>22.3</v>
       </c>
       <c r="AG13">
-        <v>3369.5</v>
+        <v>-6.099999999999998</v>
       </c>
       <c r="AH13">
-        <v>0.9276609564017212</v>
+        <v>0.05364445513591533</v>
       </c>
       <c r="AI13">
-        <v>0.9603563723979491</v>
+        <v>0.1586059743954481</v>
       </c>
       <c r="AJ13">
-        <v>0.926501319841619</v>
+        <v>-0.01575006454944487</v>
       </c>
       <c r="AK13">
-        <v>0.959698091711763</v>
+        <v>-0.05436720142602493</v>
       </c>
       <c r="AL13">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AM13">
-        <v>-0.178</v>
+        <v>2.47</v>
+      </c>
+      <c r="AN13">
+        <v>1.009049773755656</v>
+      </c>
+      <c r="AO13">
+        <v>1.700404858299595</v>
+      </c>
+      <c r="AP13">
+        <v>-0.2760180995475112</v>
       </c>
       <c r="AQ13">
-        <v>-0</v>
+        <v>1.700404858299595</v>
       </c>
     </row>
     <row r="14">
@@ -2160,7 +2157,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Liberty Financial Group Limited (ASX:LFG)</t>
+          <t>Earlypay Limited (ASX:EPY)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2169,112 +2166,121 @@
         </is>
       </c>
       <c r="D14">
-        <v>0.234</v>
-      </c>
-      <c r="E14">
-        <v>0.6679999999999999</v>
+        <v>0.055</v>
       </c>
       <c r="F14">
-        <v>0.0998</v>
+        <v>-0.141</v>
       </c>
       <c r="G14">
-        <v>-0.001057916861279776</v>
+        <v>0.1902948402948403</v>
       </c>
       <c r="H14">
-        <v>0</v>
+        <v>0.1810810810810811</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>0.1791154791154791</v>
       </c>
       <c r="J14">
-        <v>0</v>
+        <v>0.1791154791154791</v>
       </c>
       <c r="K14">
+        <v>-5.15</v>
+      </c>
+      <c r="L14">
+        <v>-0.1265356265356265</v>
+      </c>
+      <c r="M14">
+        <v>3.44</v>
+      </c>
+      <c r="N14">
+        <v>0.0669260700389105</v>
+      </c>
+      <c r="O14">
+        <v>-0.6679611650485436</v>
+      </c>
+      <c r="P14">
+        <v>3.44</v>
+      </c>
+      <c r="Q14">
+        <v>0.0669260700389105</v>
+      </c>
+      <c r="R14">
+        <v>-0.6679611650485436</v>
+      </c>
+      <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="T14">
+        <v>0</v>
+      </c>
+      <c r="U14">
+        <v>35.3</v>
+      </c>
+      <c r="V14">
+        <v>0.6867704280155642</v>
+      </c>
+      <c r="W14">
+        <v>-0.0878839590443686</v>
+      </c>
+      <c r="X14">
+        <v>0.07781442756129371</v>
+      </c>
+      <c r="Y14">
+        <v>-0.1656983866056623</v>
+      </c>
+      <c r="Z14">
+        <v>0.1980535279805353</v>
+      </c>
+      <c r="AA14">
+        <v>0.03547445255474452</v>
+      </c>
+      <c r="AB14">
+        <v>0.04471572133046427</v>
+      </c>
+      <c r="AC14">
+        <v>-0.009241268775719749</v>
+      </c>
+      <c r="AD14">
+        <v>186.6</v>
+      </c>
+      <c r="AE14">
+        <v>0</v>
+      </c>
+      <c r="AF14">
+        <v>186.6</v>
+      </c>
+      <c r="AG14">
         <v>151.3</v>
       </c>
-      <c r="L14">
-        <v>0.3533395609528258</v>
-      </c>
-      <c r="M14">
-        <v>94.90000000000001</v>
-      </c>
-      <c r="N14">
-        <v>0.1152678246082837</v>
-      </c>
-      <c r="O14">
-        <v>0.627230667547918</v>
-      </c>
-      <c r="P14">
-        <v>94.90000000000001</v>
-      </c>
-      <c r="Q14">
-        <v>0.1152678246082837</v>
-      </c>
-      <c r="R14">
-        <v>0.627230667547918</v>
-      </c>
-      <c r="S14">
-        <v>0</v>
-      </c>
-      <c r="T14">
-        <v>0</v>
-      </c>
-      <c r="U14">
-        <v>376.8</v>
-      </c>
-      <c r="V14">
-        <v>0.4576703510263574</v>
-      </c>
-      <c r="W14">
-        <v>0.1945480262311945</v>
-      </c>
-      <c r="X14">
-        <v>0.1187607987523245</v>
-      </c>
-      <c r="Y14">
-        <v>0.07578722747887007</v>
-      </c>
-      <c r="Z14">
-        <v>0.04451883889212342</v>
-      </c>
-      <c r="AA14">
-        <v>0</v>
-      </c>
-      <c r="AB14">
-        <v>0.04036342041728781</v>
-      </c>
-      <c r="AC14">
-        <v>-0.04036342041728781</v>
-      </c>
-      <c r="AD14">
-        <v>8898.5</v>
-      </c>
-      <c r="AE14">
-        <v>0</v>
-      </c>
-      <c r="AF14">
-        <v>8898.5</v>
-      </c>
-      <c r="AG14">
-        <v>8521.700000000001</v>
-      </c>
       <c r="AH14">
-        <v>0.9153140364952993</v>
+        <v>0.7840336134453781</v>
       </c>
       <c r="AI14">
-        <v>0.9204551331781743</v>
+        <v>0.7923566878980891</v>
       </c>
       <c r="AJ14">
-        <v>0.9118994114499733</v>
+        <v>0.7464232856438086</v>
       </c>
       <c r="AK14">
-        <v>0.9172290570140033</v>
+        <v>0.7557442557442557</v>
       </c>
       <c r="AL14">
-        <v>0</v>
+        <v>12.8</v>
       </c>
       <c r="AM14">
-        <v>0</v>
+        <v>12.8</v>
+      </c>
+      <c r="AN14">
+        <v>25.31886024423338</v>
+      </c>
+      <c r="AO14">
+        <v>0.5695312499999999</v>
+      </c>
+      <c r="AP14">
+        <v>20.5291723202171</v>
+      </c>
+      <c r="AQ14">
+        <v>0.5695312499999999</v>
       </c>
     </row>
     <row r="15">
@@ -2285,7 +2291,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Latitude Group Holdings Limited (ASX:LFS)</t>
+          <t>Zip Co Limited (ASX:ZIP)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2293,107 +2299,116 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="F15">
-        <v>0.0161</v>
+      <c r="D15">
+        <v>0.7759999999999999</v>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>0.2095795405288253</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>0.2095795405288253</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>0.1426094495015171</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>0.1426094495015171</v>
       </c>
       <c r="K15">
-        <v>70.3</v>
+        <v>-250.9</v>
       </c>
       <c r="L15">
-        <v>0.1467028380634391</v>
+        <v>-0.5437798006068487</v>
       </c>
       <c r="M15">
-        <v>110.2</v>
+        <v>-0</v>
       </c>
       <c r="N15">
-        <v>0.1195487090475157</v>
+        <v>-0</v>
       </c>
       <c r="O15">
-        <v>1.567567567567568</v>
+        <v>0</v>
       </c>
       <c r="P15">
-        <v>110.2</v>
+        <v>-0</v>
       </c>
       <c r="Q15">
-        <v>0.1195487090475157</v>
+        <v>-0</v>
       </c>
       <c r="R15">
-        <v>1.567567567567568</v>
+        <v>0</v>
       </c>
       <c r="S15">
         <v>0</v>
       </c>
-      <c r="T15">
-        <v>0</v>
-      </c>
       <c r="U15">
-        <v>262</v>
+        <v>101.1</v>
       </c>
       <c r="V15">
-        <v>0.2842265133434584</v>
+        <v>0.2831932773109244</v>
       </c>
       <c r="W15">
-        <v>0.07104598281960586</v>
+        <v>-0.8338318378198738</v>
       </c>
       <c r="X15">
-        <v>0.07684211323740416</v>
+        <v>0.09201499296479845</v>
       </c>
       <c r="Y15">
-        <v>-0.005796130417798293</v>
+        <v>-0.9258468307846722</v>
       </c>
       <c r="Z15">
-        <v>0.1012102139523095</v>
+        <v>0.2445539831451741</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>0.03487570890973658</v>
       </c>
       <c r="AB15">
-        <v>0.0412186718258552</v>
+        <v>0.04589551575849769</v>
       </c>
       <c r="AC15">
-        <v>-0.0412186718258552</v>
+        <v>-0.01101980684876112</v>
       </c>
       <c r="AD15">
-        <v>4049.7</v>
+        <v>1953.4</v>
       </c>
       <c r="AE15">
         <v>0</v>
       </c>
       <c r="AF15">
-        <v>4049.7</v>
+        <v>1953.4</v>
       </c>
       <c r="AG15">
-        <v>3787.7</v>
+        <v>1852.3</v>
       </c>
       <c r="AH15">
-        <v>0.8145831238056924</v>
+        <v>0.8454813019390581</v>
       </c>
       <c r="AI15">
-        <v>0.7924118498806402</v>
+        <v>0.9260453209443443</v>
       </c>
       <c r="AJ15">
-        <v>0.8042679689988321</v>
+        <v>0.8384103562214276</v>
       </c>
       <c r="AK15">
-        <v>0.7811945716289237</v>
+        <v>0.9223223621968829</v>
       </c>
       <c r="AL15">
-        <v>0</v>
+        <v>161.6</v>
       </c>
       <c r="AM15">
-        <v>0</v>
+        <v>161.6</v>
+      </c>
+      <c r="AN15">
+        <v>20.20062047569803</v>
+      </c>
+      <c r="AO15">
+        <v>0.4071782178217822</v>
+      </c>
+      <c r="AP15">
+        <v>19.15511892450879</v>
+      </c>
+      <c r="AQ15">
+        <v>0.4071782178217822</v>
       </c>
     </row>
     <row r="16">
@@ -2404,7 +2419,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>FSA Group Limited (ASX:FSA)</t>
+          <t>Rural Funds Group (ASX:RFF)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2413,109 +2428,121 @@
         </is>
       </c>
       <c r="D16">
-        <v>-0.0416</v>
+        <v>0.135</v>
       </c>
       <c r="E16">
-        <v>0.0264</v>
+        <v>0.309</v>
       </c>
       <c r="G16">
-        <v>0</v>
+        <v>0.5564024390243902</v>
       </c>
       <c r="H16">
-        <v>0</v>
+        <v>0.5564024390243902</v>
       </c>
       <c r="I16">
-        <v>0</v>
+        <v>0.4314024390243903</v>
       </c>
       <c r="J16">
-        <v>0</v>
+        <v>0.4314024390243903</v>
       </c>
       <c r="K16">
-        <v>11.9</v>
+        <v>74.5</v>
       </c>
       <c r="L16">
-        <v>0.2967581047381546</v>
+        <v>1.135670731707317</v>
       </c>
       <c r="M16">
-        <v>9</v>
+        <v>29.8</v>
       </c>
       <c r="N16">
-        <v>0.1012373453318335</v>
+        <v>0.05330948121645796</v>
       </c>
       <c r="O16">
-        <v>0.7563025210084033</v>
+        <v>0.4</v>
       </c>
       <c r="P16">
-        <v>5.63</v>
+        <v>29.8</v>
       </c>
       <c r="Q16">
-        <v>0.06332958380202475</v>
+        <v>0.05330948121645796</v>
       </c>
       <c r="R16">
-        <v>0.473109243697479</v>
+        <v>0.4</v>
       </c>
       <c r="S16">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="T16">
-        <v>0.3744444444444445</v>
+        <v>0</v>
       </c>
       <c r="U16">
-        <v>24.8</v>
+        <v>3.83</v>
       </c>
       <c r="V16">
-        <v>0.2789651293588301</v>
+        <v>0.006851520572450805</v>
       </c>
       <c r="W16">
-        <v>0.2203703703703704</v>
+        <v>0.1201806743023068</v>
       </c>
       <c r="X16">
-        <v>0.07404458735745217</v>
+        <v>0.05569979511526547</v>
       </c>
       <c r="Y16">
-        <v>0.1463257830129182</v>
+        <v>0.06448087918704136</v>
       </c>
       <c r="Z16">
-        <v>0.1143293769476623</v>
+        <v>0.07036512635688848</v>
       </c>
       <c r="AA16">
-        <v>0</v>
+        <v>0.0303556871326211</v>
       </c>
       <c r="AB16">
-        <v>0.04135441507946873</v>
+        <v>0.04524114076459651</v>
       </c>
       <c r="AC16">
-        <v>-0.04135441507946873</v>
+        <v>-0.01488545363197541</v>
       </c>
       <c r="AD16">
-        <v>352.5</v>
+        <v>426.4</v>
       </c>
       <c r="AE16">
         <v>0</v>
       </c>
       <c r="AF16">
-        <v>352.5</v>
+        <v>426.4</v>
       </c>
       <c r="AG16">
-        <v>327.7</v>
+        <v>422.57</v>
       </c>
       <c r="AH16">
-        <v>0.7985953783416403</v>
+        <v>0.4327176781002638</v>
       </c>
       <c r="AI16">
-        <v>0.8418915691425842</v>
+        <v>0.3921280117711973</v>
       </c>
       <c r="AJ16">
-        <v>0.7866058569371098</v>
+        <v>0.4305041922634147</v>
       </c>
       <c r="AK16">
-        <v>0.831937039857832</v>
+        <v>0.3899794198805799</v>
       </c>
       <c r="AL16">
-        <v>0</v>
+        <v>5.56</v>
       </c>
       <c r="AM16">
-        <v>0</v>
+        <v>5.56</v>
+      </c>
+      <c r="AN16">
+        <v>11.68219178082192</v>
+      </c>
+      <c r="AO16">
+        <v>5.089928057553958</v>
+      </c>
+      <c r="AP16">
+        <v>11.5772602739726</v>
+      </c>
+      <c r="AQ16">
+        <v>5.089928057553958</v>
       </c>
     </row>
     <row r="17">
@@ -2526,7 +2553,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>MyState Limited (ASX:MYS)</t>
+          <t>AMP Limited (ASX:AMP)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2535,109 +2562,124 @@
         </is>
       </c>
       <c r="D17">
-        <v>0.0257</v>
+        <v>-0.315</v>
       </c>
       <c r="E17">
-        <v>0.0126</v>
+        <v>-0.191</v>
+      </c>
+      <c r="F17">
+        <v>0.1</v>
       </c>
       <c r="G17">
-        <v>0</v>
+        <v>0.205903567663541</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>0.205903567663541</v>
       </c>
       <c r="I17">
-        <v>0</v>
+        <v>0.2976197081506963</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>0.2976197081506963</v>
       </c>
       <c r="K17">
-        <v>22.1</v>
+        <v>119.1</v>
       </c>
       <c r="L17">
-        <v>0.2271325796505653</v>
+        <v>0.06608222826388503</v>
       </c>
       <c r="M17">
-        <v>16.9</v>
+        <v>408.6</v>
       </c>
       <c r="N17">
-        <v>0.05817555938037865</v>
+        <v>0.2342352671405641</v>
       </c>
       <c r="O17">
-        <v>0.764705882352941</v>
+        <v>3.430730478589421</v>
       </c>
       <c r="P17">
-        <v>16.9</v>
+        <v>49.9</v>
       </c>
       <c r="Q17">
-        <v>0.05817555938037865</v>
+        <v>0.02860582435221279</v>
       </c>
       <c r="R17">
-        <v>0.764705882352941</v>
+        <v>0.418975650713686</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>358.7</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>0.8778756730298581</v>
       </c>
       <c r="U17">
-        <v>82.09999999999999</v>
+        <v>1107.5</v>
       </c>
       <c r="V17">
-        <v>0.2826161790017211</v>
+        <v>0.6348887869754644</v>
       </c>
       <c r="W17">
-        <v>0.07099261162865403</v>
+        <v>0.03775917823853909</v>
       </c>
       <c r="X17">
-        <v>0.06863554367731156</v>
+        <v>0.1374751095522118</v>
       </c>
       <c r="Y17">
-        <v>0.002357067951342467</v>
+        <v>-0.09971593131367268</v>
       </c>
       <c r="Z17">
-        <v>0.08940549480841679</v>
+        <v>0.08452415009215444</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>0.02515605288211266</v>
       </c>
       <c r="AB17">
-        <v>0.04169654666632749</v>
+        <v>0.04642117690259958</v>
       </c>
       <c r="AC17">
-        <v>-0.04169654666632749</v>
+        <v>-0.02126512402048692</v>
       </c>
       <c r="AD17">
-        <v>911.4</v>
+        <v>19827.6</v>
       </c>
       <c r="AE17">
         <v>0</v>
       </c>
       <c r="AF17">
-        <v>911.4</v>
+        <v>19827.6</v>
       </c>
       <c r="AG17">
-        <v>829.3</v>
+        <v>18720.1</v>
       </c>
       <c r="AH17">
-        <v>0.7582993593476994</v>
+        <v>0.9191359169293528</v>
       </c>
       <c r="AI17">
-        <v>0.7547201059953628</v>
+        <v>0.8811561741727328</v>
       </c>
       <c r="AJ17">
-        <v>0.7405786747633506</v>
+        <v>0.9147597058320506</v>
       </c>
       <c r="AK17">
-        <v>0.7368280764104842</v>
+        <v>0.8750040898744058</v>
       </c>
       <c r="AL17">
-        <v>0</v>
+        <v>619.6</v>
       </c>
       <c r="AM17">
-        <v>0</v>
+        <v>619.6</v>
+      </c>
+      <c r="AN17">
+        <v>36.50819370281716</v>
+      </c>
+      <c r="AO17">
+        <v>0.8657198192382182</v>
+      </c>
+      <c r="AP17">
+        <v>34.4689744061867</v>
+      </c>
+      <c r="AQ17">
+        <v>0.8657198192382182</v>
       </c>
     </row>
     <row r="18">
@@ -2648,7 +2690,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Auswide Bank Ltd (ASX:ABA)</t>
+          <t>Australian Finance Group Limited (ASX:AFG)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2657,13 +2699,16 @@
         </is>
       </c>
       <c r="D18">
-        <v>0.075</v>
+        <v>0.106</v>
       </c>
       <c r="E18">
-        <v>0.115</v>
+        <v>0.0228</v>
+      </c>
+      <c r="F18">
+        <v>0.027</v>
       </c>
       <c r="G18">
-        <v>0</v>
+        <v>0.001547941088067328</v>
       </c>
       <c r="H18">
         <v>0</v>
@@ -2675,28 +2720,28 @@
         <v>0</v>
       </c>
       <c r="K18">
-        <v>18</v>
+        <v>24.8</v>
       </c>
       <c r="L18">
-        <v>0.274390243902439</v>
+        <v>0.03727081454764052</v>
       </c>
       <c r="M18">
-        <v>9.92</v>
+        <v>29.1</v>
       </c>
       <c r="N18">
-        <v>0.05414847161572053</v>
+        <v>0.1010767627648489</v>
       </c>
       <c r="O18">
-        <v>0.5511111111111111</v>
+        <v>1.173387096774194</v>
       </c>
       <c r="P18">
-        <v>9.92</v>
+        <v>29.1</v>
       </c>
       <c r="Q18">
-        <v>0.05414847161572053</v>
+        <v>0.1010767627648489</v>
       </c>
       <c r="R18">
-        <v>0.5511111111111111</v>
+        <v>1.173387096774194</v>
       </c>
       <c r="S18">
         <v>0</v>
@@ -2705,61 +2750,64 @@
         <v>0</v>
       </c>
       <c r="U18">
-        <v>123</v>
+        <v>40</v>
       </c>
       <c r="V18">
-        <v>0.6713973799126638</v>
+        <v>0.1389371309482459</v>
       </c>
       <c r="W18">
-        <v>0.09360374414976598</v>
+        <v>0.1952755905511811</v>
       </c>
       <c r="X18">
-        <v>0.06704965351188377</v>
+        <v>0.1321821103490175</v>
       </c>
       <c r="Y18">
-        <v>0.02655409063788221</v>
+        <v>0.06309348020216357</v>
       </c>
       <c r="Z18">
-        <v>0.1097907949790795</v>
+        <v>0.192612748219765</v>
       </c>
       <c r="AA18">
         <v>0</v>
       </c>
       <c r="AB18">
-        <v>0.04182442820375208</v>
+        <v>0.0401474948849086</v>
       </c>
       <c r="AC18">
-        <v>-0.04182442820375208</v>
+        <v>-0.0401474948849086</v>
       </c>
       <c r="AD18">
-        <v>530.3</v>
+        <v>3074.8</v>
       </c>
       <c r="AE18">
         <v>0</v>
       </c>
       <c r="AF18">
-        <v>530.3</v>
+        <v>3074.8</v>
       </c>
       <c r="AG18">
-        <v>407.3</v>
+        <v>3034.8</v>
       </c>
       <c r="AH18">
-        <v>0.7432375613174491</v>
+        <v>0.9143842745412912</v>
       </c>
       <c r="AI18">
-        <v>0.731852056306928</v>
+        <v>0.9585385622545046</v>
       </c>
       <c r="AJ18">
-        <v>0.6897544453852666</v>
+        <v>0.9133535979775483</v>
       </c>
       <c r="AK18">
-        <v>0.6770279255319149</v>
+        <v>0.9580150262011491</v>
       </c>
       <c r="AL18">
         <v>0</v>
       </c>
       <c r="AM18">
-        <v>0</v>
+        <v>-4.11</v>
+      </c>
+      <c r="AQ18">
+        <v>-0</v>
       </c>
     </row>
     <row r="19">
@@ -2770,7 +2818,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Cash Converters International Limited (ASX:CCV)</t>
+          <t>Latitude Group Holdings Limited (ASX:LFS)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2778,12 +2826,6 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D19">
-        <v>-0.0227</v>
-      </c>
-      <c r="E19">
-        <v>-0.115</v>
-      </c>
       <c r="G19">
         <v>0</v>
       </c>
@@ -2797,85 +2839,85 @@
         <v>0</v>
       </c>
       <c r="K19">
-        <v>7.7</v>
+        <v>-72.7</v>
       </c>
       <c r="L19">
-        <v>0.04785581106277191</v>
+        <v>-0.2400132056784418</v>
       </c>
       <c r="M19">
-        <v>9.720000000000001</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="N19">
-        <v>0.09681274900398407</v>
+        <v>0.09798934108527133</v>
       </c>
       <c r="O19">
-        <v>1.262337662337662</v>
+        <v>-1.112792297111417</v>
       </c>
       <c r="P19">
-        <v>8.65</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="Q19">
-        <v>0.08615537848605577</v>
+        <v>0.09798934108527133</v>
       </c>
       <c r="R19">
-        <v>1.123376623376623</v>
+        <v>-1.112792297111417</v>
       </c>
       <c r="S19">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="T19">
-        <v>0.110082304526749</v>
+        <v>0</v>
       </c>
       <c r="U19">
-        <v>40</v>
+        <v>180.2</v>
       </c>
       <c r="V19">
-        <v>0.398406374501992</v>
+        <v>0.218265503875969</v>
       </c>
       <c r="W19">
-        <v>0.03231221149811162</v>
+        <v>-0.06870806161988471</v>
       </c>
       <c r="X19">
-        <v>0.05410953281334133</v>
+        <v>0.08582705551163194</v>
       </c>
       <c r="Y19">
-        <v>-0.02179732131522971</v>
+        <v>-0.1545351171315167</v>
       </c>
       <c r="Z19">
-        <v>0.7945679012345679</v>
+        <v>0.0697395989224783</v>
       </c>
       <c r="AA19">
         <v>0</v>
       </c>
       <c r="AB19">
-        <v>0.04407957905546031</v>
+        <v>0.04110741198359256</v>
       </c>
       <c r="AC19">
-        <v>-0.04407957905546031</v>
+        <v>-0.04110741198359256</v>
       </c>
       <c r="AD19">
-        <v>91.8</v>
+        <v>3855</v>
       </c>
       <c r="AE19">
         <v>0</v>
       </c>
       <c r="AF19">
-        <v>91.8</v>
+        <v>3855</v>
       </c>
       <c r="AG19">
-        <v>51.8</v>
+        <v>3674.8</v>
       </c>
       <c r="AH19">
-        <v>0.477627471383975</v>
+        <v>0.8236123573900781</v>
       </c>
       <c r="AI19">
-        <v>0.2969912649627952</v>
+        <v>0.8161839430894309</v>
       </c>
       <c r="AJ19">
-        <v>0.3403416557161629</v>
+        <v>0.8165496400319971</v>
       </c>
       <c r="AK19">
-        <v>0.1924934968413229</v>
+        <v>0.8088928021131412</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -2892,7 +2934,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Prospa Group Limited (ASX:PGL)</t>
+          <t>Resimac Group Limited (ASX:RMC)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2901,10 +2943,13 @@
         </is>
       </c>
       <c r="D20">
-        <v>0.221</v>
+        <v>0.103</v>
       </c>
       <c r="E20">
-        <v>0.412</v>
+        <v>0.213</v>
+      </c>
+      <c r="F20">
+        <v>0.135</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -2913,103 +2958,97 @@
         <v>0</v>
       </c>
       <c r="I20">
-        <v>0.001807010331917303</v>
+        <v>0</v>
       </c>
       <c r="J20">
-        <v>0.001807010331917303</v>
+        <v>0</v>
       </c>
       <c r="K20">
-        <v>4.63</v>
+        <v>44.2</v>
       </c>
       <c r="L20">
-        <v>0.07004538577912255</v>
+        <v>0.3112676056338028</v>
       </c>
       <c r="M20">
-        <v>0.298</v>
+        <v>24.86</v>
       </c>
       <c r="N20">
-        <v>0.00438880706921944</v>
+        <v>0.08725868725868727</v>
       </c>
       <c r="O20">
-        <v>0.06436285097192225</v>
+        <v>0.5624434389140271</v>
       </c>
       <c r="P20">
-        <v>-0</v>
+        <v>21.4</v>
       </c>
       <c r="Q20">
-        <v>-0</v>
+        <v>0.07511407511407511</v>
       </c>
       <c r="R20">
-        <v>-0</v>
+        <v>0.4841628959276018</v>
       </c>
       <c r="S20">
-        <v>0.298</v>
+        <v>3.460000000000001</v>
       </c>
       <c r="T20">
-        <v>1</v>
+        <v>0.1391794046661304</v>
       </c>
       <c r="U20">
-        <v>72.90000000000001</v>
+        <v>722.4</v>
       </c>
       <c r="V20">
-        <v>1.073637702503682</v>
+        <v>2.535626535626536</v>
       </c>
       <c r="W20">
-        <v>0.04957173447537472</v>
+        <v>0.1696737044145873</v>
       </c>
       <c r="X20">
-        <v>0.09128765093709723</v>
+        <v>0.3107043357702532</v>
       </c>
       <c r="Y20">
-        <v>-0.04171591646172251</v>
+        <v>-0.1410306313556659</v>
       </c>
       <c r="Z20">
-        <v>0.2143961444583828</v>
+        <v>0.01311257421994035</v>
       </c>
       <c r="AA20">
-        <v>0.0003874160481595324</v>
+        <v>0</v>
       </c>
       <c r="AB20">
-        <v>0.04544214113374451</v>
+        <v>0.04349732316415341</v>
       </c>
       <c r="AC20">
-        <v>-0.04505472508558497</v>
+        <v>-0.04349732316415341</v>
       </c>
       <c r="AD20">
-        <v>448.1</v>
+        <v>9637.799999999999</v>
       </c>
       <c r="AE20">
-        <v>0.3077830853013312</v>
+        <v>0</v>
       </c>
       <c r="AF20">
-        <v>448.4077830853013</v>
+        <v>9637.799999999999</v>
       </c>
       <c r="AG20">
-        <v>375.5077830853013</v>
+        <v>8915.4</v>
       </c>
       <c r="AH20">
-        <v>0.8684892960662923</v>
+        <v>0.9712880566781219</v>
       </c>
       <c r="AI20">
-        <v>0.8235103280701037</v>
+        <v>0.9721109911945371</v>
       </c>
       <c r="AJ20">
-        <v>0.8468678210212255</v>
+        <v>0.969033618468963</v>
       </c>
       <c r="AK20">
-        <v>0.7962289778779624</v>
+        <v>0.969919167963098</v>
       </c>
       <c r="AL20">
         <v>0</v>
       </c>
       <c r="AM20">
         <v>0</v>
-      </c>
-      <c r="AN20">
-        <v>2475.690607734807</v>
-      </c>
-      <c r="AP20">
-        <v>2074.628635830394</v>
       </c>
     </row>
     <row r="21">
@@ -3020,7 +3059,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Resimac Group Limited (ASX:RMC)</t>
+          <t>Pepper Money Limited (ASX:PPM)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3028,17 +3067,11 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D21">
-        <v>0.175</v>
-      </c>
-      <c r="E21">
-        <v>0.453</v>
-      </c>
       <c r="F21">
-        <v>0.03700000000000001</v>
+        <v>-0.001</v>
       </c>
       <c r="G21">
-        <v>0</v>
+        <v>0.05555555555555555</v>
       </c>
       <c r="H21">
         <v>0</v>
@@ -3050,85 +3083,85 @@
         <v>0</v>
       </c>
       <c r="K21">
-        <v>70.40000000000001</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="L21">
-        <v>0.3878787878787879</v>
+        <v>0.2781207133058984</v>
       </c>
       <c r="M21">
-        <v>26.76</v>
+        <v>30.6</v>
       </c>
       <c r="N21">
-        <v>0.09502840909090909</v>
+        <v>0.08299430431244915</v>
       </c>
       <c r="O21">
-        <v>0.3801136363636364</v>
+        <v>0.3773119605425401</v>
       </c>
       <c r="P21">
-        <v>21.3</v>
+        <v>30.6</v>
       </c>
       <c r="Q21">
-        <v>0.07563920454545454</v>
+        <v>0.08299430431244915</v>
       </c>
       <c r="R21">
-        <v>0.3025568181818182</v>
+        <v>0.3773119605425401</v>
       </c>
       <c r="S21">
-        <v>5.460000000000001</v>
+        <v>0</v>
       </c>
       <c r="T21">
-        <v>0.2040358744394619</v>
+        <v>0</v>
       </c>
       <c r="U21">
-        <v>642.7</v>
+        <v>739.2</v>
       </c>
       <c r="V21">
-        <v>2.282315340909091</v>
+        <v>2.004882017900732</v>
       </c>
       <c r="W21">
-        <v>0.292358803986711</v>
+        <v>0.1557518724793547</v>
       </c>
       <c r="X21">
-        <v>0.3087310996499874</v>
+        <v>0.309427450940139</v>
       </c>
       <c r="Y21">
-        <v>-0.01637229566327636</v>
+        <v>-0.1536755784607843</v>
       </c>
       <c r="Z21">
-        <v>0.01739372101046499</v>
+        <v>0.02283977692837897</v>
       </c>
       <c r="AA21">
         <v>0</v>
       </c>
       <c r="AB21">
-        <v>0.04511023954668489</v>
+        <v>0.04349821551619518</v>
       </c>
       <c r="AC21">
-        <v>-0.04511023954668489</v>
+        <v>-0.04349821551619518</v>
       </c>
       <c r="AD21">
-        <v>11230.4</v>
+        <v>12411.6</v>
       </c>
       <c r="AE21">
         <v>0</v>
       </c>
       <c r="AF21">
-        <v>11230.4</v>
+        <v>12411.6</v>
       </c>
       <c r="AG21">
-        <v>10587.7</v>
+        <v>11672.4</v>
       </c>
       <c r="AH21">
-        <v>0.9755385684503127</v>
+        <v>0.9711509119504237</v>
       </c>
       <c r="AI21">
-        <v>0.9773298871280752</v>
+        <v>0.955105809926895</v>
       </c>
       <c r="AJ21">
-        <v>0.9740921678488955</v>
+        <v>0.9693798739317836</v>
       </c>
       <c r="AK21">
-        <v>0.9759867996533987</v>
+        <v>0.9523980482710227</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3145,7 +3178,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Pepper Money Limited (ASX:PPM)</t>
+          <t>Cash Converters International Limited (ASX:CCV)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3154,16 +3187,10 @@
         </is>
       </c>
       <c r="D22">
-        <v>0.0291</v>
-      </c>
-      <c r="E22">
-        <v>0.176</v>
-      </c>
-      <c r="F22">
-        <v>-0.018</v>
+        <v>0.0282</v>
       </c>
       <c r="G22">
-        <v>0.04937458854509546</v>
+        <v>0</v>
       </c>
       <c r="H22">
         <v>0</v>
@@ -3175,85 +3202,85 @@
         <v>0</v>
       </c>
       <c r="K22">
-        <v>101.2</v>
+        <v>-64.7</v>
       </c>
       <c r="L22">
-        <v>0.3331138907175774</v>
+        <v>-0.3390985324947589</v>
       </c>
       <c r="M22">
-        <v>27.3</v>
+        <v>9.25</v>
       </c>
       <c r="N22">
-        <v>0.0643412679707754</v>
+        <v>0.1014254385964912</v>
       </c>
       <c r="O22">
-        <v>0.2697628458498024</v>
+        <v>-0.142967542503864</v>
       </c>
       <c r="P22">
-        <v>27.3</v>
+        <v>8.35</v>
       </c>
       <c r="Q22">
-        <v>0.0643412679707754</v>
+        <v>0.09155701754385964</v>
       </c>
       <c r="R22">
-        <v>0.2697628458498024</v>
+        <v>-0.1290571870170015</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>0.9000000000000004</v>
       </c>
       <c r="T22">
-        <v>0</v>
+        <v>0.09729729729729733</v>
       </c>
       <c r="U22">
-        <v>872.2</v>
+        <v>47.6</v>
       </c>
       <c r="V22">
-        <v>2.055621022861183</v>
+        <v>0.5219298245614035</v>
       </c>
       <c r="W22">
-        <v>0.2531265632816408</v>
+        <v>-0.2977450529222274</v>
       </c>
       <c r="X22">
-        <v>0.2501683360892432</v>
+        <v>0.06111456009502521</v>
       </c>
       <c r="Y22">
-        <v>0.002958227192397633</v>
+        <v>-0.3588596130172526</v>
       </c>
       <c r="Z22">
-        <v>0.02814813442170316</v>
+        <v>0.98860103626943</v>
       </c>
       <c r="AA22">
         <v>0</v>
       </c>
       <c r="AB22">
-        <v>0.04513153474139155</v>
+        <v>0.04353233647983229</v>
       </c>
       <c r="AC22">
-        <v>-0.04513153474139155</v>
+        <v>-0.04353233647983229</v>
       </c>
       <c r="AD22">
-        <v>13118.7</v>
+        <v>133.6</v>
       </c>
       <c r="AE22">
         <v>0</v>
       </c>
       <c r="AF22">
-        <v>13118.7</v>
+        <v>133.6</v>
       </c>
       <c r="AG22">
-        <v>12246.5</v>
+        <v>86</v>
       </c>
       <c r="AH22">
-        <v>0.968670161707155</v>
+        <v>0.594306049822064</v>
       </c>
       <c r="AI22">
-        <v>0.9618238338929864</v>
+        <v>0.4929889298892989</v>
       </c>
       <c r="AJ22">
-        <v>0.966513558733466</v>
+        <v>0.4853273137697517</v>
       </c>
       <c r="AK22">
-        <v>0.9592158029951751</v>
+        <v>0.3849597135183527</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -3270,7 +3297,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>MoneyMe Limited (ASX:MME)</t>
+          <t>Humm Group Limited (ASX:HUM)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3279,10 +3306,10 @@
         </is>
       </c>
       <c r="D23">
-        <v>-0.00642</v>
+        <v>-0.0357</v>
       </c>
       <c r="G23">
-        <v>0.8539325842696629</v>
+        <v>0</v>
       </c>
       <c r="H23">
         <v>0</v>
@@ -3294,82 +3321,85 @@
         <v>0</v>
       </c>
       <c r="K23">
-        <v>-34.7</v>
+        <v>1.93</v>
       </c>
       <c r="L23">
-        <v>-6.498127340823971</v>
+        <v>0.01168988491823138</v>
       </c>
       <c r="M23">
-        <v>-0</v>
+        <v>9.58</v>
       </c>
       <c r="N23">
-        <v>-0</v>
+        <v>0.05665286812536961</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>4.963730569948186</v>
       </c>
       <c r="P23">
-        <v>-0</v>
+        <v>9.58</v>
       </c>
       <c r="Q23">
-        <v>-0</v>
+        <v>0.05665286812536961</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>4.963730569948186</v>
       </c>
       <c r="S23">
         <v>0</v>
       </c>
+      <c r="T23">
+        <v>0</v>
+      </c>
       <c r="U23">
-        <v>55.6</v>
+        <v>223.7</v>
       </c>
       <c r="V23">
-        <v>1.177966101694915</v>
+        <v>1.322885866351271</v>
       </c>
       <c r="W23">
-        <v>-1.149006622516556</v>
+        <v>0.00446242774566474</v>
       </c>
       <c r="X23">
-        <v>0.1779506371746427</v>
+        <v>0.1721374803636257</v>
       </c>
       <c r="Y23">
-        <v>-1.326957259691199</v>
+        <v>-0.167675052617961</v>
       </c>
       <c r="Z23">
-        <v>0.02257928118393234</v>
+        <v>0.07253635604762533</v>
       </c>
       <c r="AA23">
         <v>0</v>
       </c>
       <c r="AB23">
-        <v>0.04518298311975139</v>
+        <v>0.04369640319145942</v>
       </c>
       <c r="AC23">
-        <v>-0.04518298311975139</v>
+        <v>-0.04369640319145942</v>
       </c>
       <c r="AD23">
-        <v>937.7</v>
+        <v>2682.1</v>
       </c>
       <c r="AE23">
         <v>0</v>
       </c>
       <c r="AF23">
-        <v>937.7</v>
+        <v>2682.1</v>
       </c>
       <c r="AG23">
-        <v>882.1</v>
+        <v>2458.4</v>
       </c>
       <c r="AH23">
-        <v>0.9520763529292313</v>
+        <v>0.9406916386083053</v>
       </c>
       <c r="AI23">
-        <v>0.9371377173695783</v>
+        <v>0.8655285917129212</v>
       </c>
       <c r="AJ23">
-        <v>0.94920908210481</v>
+        <v>0.9356422454804948</v>
       </c>
       <c r="AK23">
-        <v>0.9334391534391535</v>
+        <v>0.8550659107509304</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -3386,7 +3416,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Plenti Group Limited (ASX:PLT)</t>
+          <t>Pioneer Credit Limited (ASX:PNC)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3394,8 +3424,14 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D24">
+        <v>-0.08439999999999999</v>
+      </c>
+      <c r="E24">
+        <v>-0.607</v>
+      </c>
       <c r="G24">
-        <v>0.1270833333333333</v>
+        <v>0</v>
       </c>
       <c r="H24">
         <v>0</v>
@@ -3407,10 +3443,10 @@
         <v>0</v>
       </c>
       <c r="K24">
-        <v>2.41</v>
+        <v>0.11</v>
       </c>
       <c r="L24">
-        <v>0.05020833333333333</v>
+        <v>0.003343465045592705</v>
       </c>
       <c r="M24">
         <v>-0</v>
@@ -3434,55 +3470,55 @@
         <v>0</v>
       </c>
       <c r="U24">
-        <v>72.90000000000001</v>
+        <v>5.6</v>
       </c>
       <c r="V24">
-        <v>1.35</v>
+        <v>0.1824104234527687</v>
       </c>
       <c r="W24">
-        <v>0.08397212543554007</v>
+        <v>0.003886925795053003</v>
       </c>
       <c r="X24">
-        <v>0.1722642137500369</v>
+        <v>0.09591333434811125</v>
       </c>
       <c r="Y24">
-        <v>-0.08829208831449682</v>
+        <v>-0.09202640855305824</v>
       </c>
       <c r="Z24">
-        <v>0.07433792783026173</v>
+        <v>0.1676860346585117</v>
       </c>
       <c r="AA24">
         <v>0</v>
       </c>
       <c r="AB24">
-        <v>0.04518944947444156</v>
+        <v>0.0442430630928432</v>
       </c>
       <c r="AC24">
-        <v>-0.04518944947444156</v>
+        <v>-0.0442430630928432</v>
       </c>
       <c r="AD24">
-        <v>1025.8</v>
+        <v>183.5</v>
       </c>
       <c r="AE24">
         <v>0</v>
       </c>
       <c r="AF24">
-        <v>1025.8</v>
+        <v>183.5</v>
       </c>
       <c r="AG24">
-        <v>952.9</v>
+        <v>177.9</v>
       </c>
       <c r="AH24">
-        <v>0.9499907390257455</v>
+        <v>0.8566760037348273</v>
       </c>
       <c r="AI24">
-        <v>0.9552989383497859</v>
+        <v>0.8680227057710501</v>
       </c>
       <c r="AJ24">
-        <v>0.9463700466779223</v>
+        <v>0.8528283796740173</v>
       </c>
       <c r="AK24">
-        <v>0.9520431611549606</v>
+        <v>0.8644314868804664</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -3499,7 +3535,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Humm Group Limited (ASX:HUM)</t>
+          <t>Prospa Group Limited (ASX:PGL)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3508,7 +3544,7 @@
         </is>
       </c>
       <c r="D25">
-        <v>-0.00345</v>
+        <v>0.221</v>
       </c>
       <c r="G25">
         <v>0</v>
@@ -3517,97 +3553,103 @@
         <v>0</v>
       </c>
       <c r="I25">
-        <v>0</v>
+        <v>0.0009224112571765662</v>
       </c>
       <c r="J25">
-        <v>0</v>
+        <v>0.0009224112571765662</v>
       </c>
       <c r="K25">
-        <v>-117.3</v>
+        <v>-29.9</v>
       </c>
       <c r="L25">
-        <v>-0.5812685827552031</v>
+        <v>-0.256872852233677</v>
       </c>
       <c r="M25">
-        <v>9.917000000000002</v>
+        <v>0.572</v>
       </c>
       <c r="N25">
-        <v>0.05165104166666667</v>
+        <v>0.01345882352941176</v>
       </c>
       <c r="O25">
-        <v>-0.08454390451832909</v>
+        <v>-0.01913043478260869</v>
       </c>
       <c r="P25">
-        <v>9.710000000000001</v>
+        <v>-0</v>
       </c>
       <c r="Q25">
-        <v>0.05057291666666667</v>
+        <v>-0</v>
       </c>
       <c r="R25">
-        <v>-0.08277919863597615</v>
+        <v>0</v>
       </c>
       <c r="S25">
-        <v>0.2070000000000007</v>
+        <v>0.572</v>
       </c>
       <c r="T25">
-        <v>0.0208732479580519</v>
+        <v>1</v>
       </c>
       <c r="U25">
-        <v>193.6</v>
+        <v>64.5</v>
       </c>
       <c r="V25">
-        <v>1.008333333333333</v>
+        <v>1.517647058823529</v>
       </c>
       <c r="W25">
-        <v>-0.20611491829204</v>
+        <v>-0.3187633262260128</v>
       </c>
       <c r="X25">
-        <v>0.1194550851483329</v>
+        <v>0.1448178260631393</v>
       </c>
       <c r="Y25">
-        <v>-0.325570003440373</v>
+        <v>-0.4635811522891521</v>
       </c>
       <c r="Z25">
-        <v>0.09017382367398007</v>
+        <v>0.2481145444054258</v>
       </c>
       <c r="AA25">
-        <v>0</v>
+        <v>0.0002288636488287998</v>
       </c>
       <c r="AB25">
-        <v>0.0452946215896485</v>
+        <v>0.04552706688147462</v>
       </c>
       <c r="AC25">
-        <v>-0.0452946215896485</v>
+        <v>-0.04529820323264582</v>
       </c>
       <c r="AD25">
-        <v>2095.6</v>
+        <v>523.4</v>
       </c>
       <c r="AE25">
-        <v>0</v>
+        <v>0.1381566483232385</v>
       </c>
       <c r="AF25">
-        <v>2095.6</v>
+        <v>523.5381566483233</v>
       </c>
       <c r="AG25">
-        <v>1902</v>
+        <v>459.0381566483233</v>
       </c>
       <c r="AH25">
-        <v>0.9160692428746284</v>
+        <v>0.924916722484479</v>
       </c>
       <c r="AI25">
-        <v>0.8289229065305961</v>
+        <v>0.8942672265258861</v>
       </c>
       <c r="AJ25">
-        <v>0.9083094555873925</v>
+        <v>0.91526068468246</v>
       </c>
       <c r="AK25">
-        <v>0.8147354893981581</v>
+        <v>0.8811759146262967</v>
       </c>
       <c r="AL25">
         <v>0</v>
       </c>
       <c r="AM25">
         <v>0</v>
+      </c>
+      <c r="AN25">
+        <v>3877.037037037036</v>
+      </c>
+      <c r="AP25">
+        <v>3400.282641839431</v>
       </c>
     </row>
     <row r="26">
@@ -3618,7 +3660,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Wisr Limited (ASX:WZR)</t>
+          <t>Plenti Group Limited (ASX:PLT)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3626,11 +3668,8 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D26">
-        <v>0.861</v>
-      </c>
       <c r="G26">
-        <v>0</v>
+        <v>0.1715962441314554</v>
       </c>
       <c r="H26">
         <v>0</v>
@@ -3642,10 +3681,10 @@
         <v>0</v>
       </c>
       <c r="K26">
-        <v>-13.7</v>
+        <v>-10</v>
       </c>
       <c r="L26">
-        <v>-0.8203592814371258</v>
+        <v>-0.2347417840375587</v>
       </c>
       <c r="M26">
         <v>-0</v>
@@ -3669,55 +3708,55 @@
         <v>0</v>
       </c>
       <c r="U26">
-        <v>49.3</v>
+        <v>91.7</v>
       </c>
       <c r="V26">
-        <v>0.8772241992882561</v>
+        <v>1.106151990349819</v>
       </c>
       <c r="W26">
-        <v>-0.2527675276752767</v>
+        <v>-0.2083333333333333</v>
       </c>
       <c r="X26">
-        <v>0.110897630231807</v>
+        <v>0.1726789670843011</v>
       </c>
       <c r="Y26">
-        <v>-0.3636651579070838</v>
+        <v>-0.3810123004176345</v>
       </c>
       <c r="Z26">
-        <v>0.05951532430506059</v>
+        <v>0.04256169447497252</v>
       </c>
       <c r="AA26">
         <v>0</v>
       </c>
       <c r="AB26">
-        <v>0.04532675640776436</v>
+        <v>0.04545275657686561</v>
       </c>
       <c r="AC26">
-        <v>-0.04532675640776436</v>
+        <v>-0.04545275657686561</v>
       </c>
       <c r="AD26">
-        <v>539.8</v>
+        <v>1320.7</v>
       </c>
       <c r="AE26">
         <v>0</v>
       </c>
       <c r="AF26">
-        <v>539.8</v>
+        <v>1320.7</v>
       </c>
       <c r="AG26">
-        <v>490.4999999999999</v>
+        <v>1229</v>
       </c>
       <c r="AH26">
-        <v>0.9057046979865772</v>
+        <v>0.9409375890567112</v>
       </c>
       <c r="AI26">
-        <v>0.9096730704415233</v>
+        <v>0.9738957304033625</v>
       </c>
       <c r="AJ26">
-        <v>0.8972013901591367</v>
+        <v>0.9368092080189038</v>
       </c>
       <c r="AK26">
-        <v>0.9014886969307113</v>
+        <v>0.9720025308446694</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -3734,7 +3773,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Pioneer Credit Limited (ASX:PNC)</t>
+          <t>Wisr Limited (ASX:WZR)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3743,7 +3782,7 @@
         </is>
       </c>
       <c r="D27">
-        <v>-0.138</v>
+        <v>0.7390000000000001</v>
       </c>
       <c r="G27">
         <v>0</v>
@@ -3758,19 +3797,19 @@
         <v>0</v>
       </c>
       <c r="K27">
-        <v>-22.8</v>
+        <v>-8.75</v>
       </c>
       <c r="L27">
-        <v>-1.288135593220339</v>
+        <v>-0.5608974358974359</v>
       </c>
       <c r="M27">
-        <v>1.63</v>
+        <v>-0</v>
       </c>
       <c r="N27">
-        <v>0.08358974358974358</v>
+        <v>-0</v>
       </c>
       <c r="O27">
-        <v>-0.07149122807017542</v>
+        <v>0</v>
       </c>
       <c r="P27">
         <v>-0</v>
@@ -3782,61 +3821,58 @@
         <v>0</v>
       </c>
       <c r="S27">
-        <v>1.63</v>
-      </c>
-      <c r="T27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U27">
-        <v>15.9</v>
+        <v>35.7</v>
       </c>
       <c r="V27">
-        <v>0.8153846153846154</v>
+        <v>0.8004484304932736</v>
       </c>
       <c r="W27">
-        <v>-0.5560975609756098</v>
+        <v>-0.1632462686567164</v>
       </c>
       <c r="X27">
-        <v>0.1097257435882222</v>
+        <v>0.1570243904830012</v>
       </c>
       <c r="Y27">
-        <v>-0.665823304563832</v>
+        <v>-0.3202706591397175</v>
       </c>
       <c r="Z27">
-        <v>0.09378974141585417</v>
+        <v>0.02867120014703179</v>
       </c>
       <c r="AA27">
         <v>0</v>
       </c>
       <c r="AB27">
-        <v>0.04533178553846696</v>
+        <v>0.04549007495567537</v>
       </c>
       <c r="AC27">
-        <v>-0.04533178553846696</v>
+        <v>-0.04549007495567537</v>
       </c>
       <c r="AD27">
-        <v>183.8</v>
+        <v>620</v>
       </c>
       <c r="AE27">
         <v>0</v>
       </c>
       <c r="AF27">
-        <v>183.8</v>
+        <v>620</v>
       </c>
       <c r="AG27">
-        <v>167.9</v>
+        <v>584.3</v>
       </c>
       <c r="AH27">
-        <v>0.9040826364977865</v>
+        <v>0.9328919650917845</v>
       </c>
       <c r="AI27">
-        <v>0.8665723715228665</v>
+        <v>0.9319104163535248</v>
       </c>
       <c r="AJ27">
-        <v>0.8959445037353255</v>
+        <v>0.9290825250437271</v>
       </c>
       <c r="AK27">
-        <v>0.8557594291539246</v>
+        <v>0.9280495552731894</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -3853,7 +3889,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Propell Holdings Limited (ASX:PHL)</t>
+          <t>Liberty Financial Group Limited (ASX:LFG)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3861,80 +3897,107 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D28">
+        <v>0.153</v>
+      </c>
+      <c r="E28">
+        <v>0.516</v>
+      </c>
+      <c r="F28">
+        <v>0.0232</v>
+      </c>
+      <c r="G28">
+        <v>0.001119598949629983</v>
+      </c>
+      <c r="H28">
+        <v>0</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
       <c r="K28">
-        <v>-3.08</v>
+        <v>120.8</v>
+      </c>
+      <c r="L28">
+        <v>0.2883743136786823</v>
       </c>
       <c r="M28">
-        <v>-0</v>
+        <v>99.3</v>
       </c>
       <c r="N28">
-        <v>-0</v>
+        <v>0.1183975199713843</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>0.8220198675496688</v>
       </c>
       <c r="P28">
-        <v>-0</v>
+        <v>99.3</v>
       </c>
       <c r="Q28">
-        <v>-0</v>
+        <v>0.1183975199713843</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>0.8220198675496688</v>
       </c>
       <c r="S28">
         <v>0</v>
       </c>
+      <c r="T28">
+        <v>0</v>
+      </c>
       <c r="U28">
-        <v>0.266</v>
+        <v>811.9</v>
       </c>
       <c r="V28">
-        <v>0.1171806167400881</v>
+        <v>0.9680457851436747</v>
       </c>
       <c r="W28">
-        <v>-1.822485207100592</v>
+        <v>0.1568423786029603</v>
       </c>
       <c r="X28">
-        <v>0.05939013878272881</v>
+        <v>0.1367806465644223</v>
       </c>
       <c r="Y28">
-        <v>-1.881875345883321</v>
+        <v>0.02006173203853792</v>
       </c>
       <c r="Z28">
-        <v>0</v>
+        <v>0.04521365584086174</v>
       </c>
       <c r="AA28">
         <v>0</v>
       </c>
       <c r="AB28">
-        <v>0.04617323867909294</v>
+        <v>0.04555663150226114</v>
       </c>
       <c r="AC28">
-        <v>-0.04617323867909294</v>
+        <v>-0.04555663150226114</v>
       </c>
       <c r="AD28">
-        <v>3.91</v>
+        <v>9457.5</v>
       </c>
       <c r="AE28">
         <v>0</v>
       </c>
       <c r="AF28">
-        <v>3.91</v>
+        <v>9457.5</v>
       </c>
       <c r="AG28">
-        <v>3.644</v>
+        <v>8645.6</v>
       </c>
       <c r="AH28">
-        <v>0.6326860841423949</v>
+        <v>0.9185427633495852</v>
       </c>
       <c r="AI28">
-        <v>1.174879807692308</v>
+        <v>0.9239087960611153</v>
       </c>
       <c r="AJ28">
-        <v>0.616165032127156</v>
+        <v>0.9115696466792488</v>
       </c>
       <c r="AK28">
-        <v>1.190071848465055</v>
+        <v>0.9173537057668842</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -3951,7 +4014,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>QuickFee Limited (ASX:QFE)</t>
+          <t>Macquarie Group Limited (ASX:MQG)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -3960,10 +4023,16 @@
         </is>
       </c>
       <c r="D29">
-        <v>0.366</v>
+        <v>0.115</v>
+      </c>
+      <c r="E29">
+        <v>0.104</v>
+      </c>
+      <c r="F29">
+        <v>-0.0101</v>
       </c>
       <c r="G29">
-        <v>0.5438066465256798</v>
+        <v>0</v>
       </c>
       <c r="H29">
         <v>0</v>
@@ -3975,82 +4044,85 @@
         <v>0</v>
       </c>
       <c r="K29">
-        <v>-9.300000000000001</v>
+        <v>2769.6</v>
       </c>
       <c r="L29">
-        <v>-1.404833836858006</v>
+        <v>0.2328843146158115</v>
       </c>
       <c r="M29">
-        <v>-0</v>
+        <v>2528.2</v>
       </c>
       <c r="N29">
-        <v>-0</v>
+        <v>0.05509873618554251</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>0.9128393991912189</v>
       </c>
       <c r="P29">
-        <v>-0</v>
+        <v>1714.5</v>
       </c>
       <c r="Q29">
-        <v>-0</v>
+        <v>0.03736523344281016</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>0.6190424610051993</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>813.6999999999998</v>
+      </c>
+      <c r="T29">
+        <v>0.3218495372201566</v>
       </c>
       <c r="U29">
-        <v>5.64</v>
+        <v>19092.1</v>
       </c>
       <c r="V29">
-        <v>0.5320754716981132</v>
+        <v>0.4160867736444886</v>
       </c>
       <c r="W29">
-        <v>-0.5081967213114754</v>
+        <v>0.1371849738468854</v>
       </c>
       <c r="X29">
-        <v>0.05812138692448061</v>
+        <v>0.06897834241429714</v>
       </c>
       <c r="Y29">
-        <v>-0.5663181082359561</v>
+        <v>0.06820663143258827</v>
       </c>
       <c r="Z29">
-        <v>0.3229268292682927</v>
+        <v>0.07324432203457683</v>
       </c>
       <c r="AA29">
         <v>0</v>
       </c>
       <c r="AB29">
-        <v>0.04626069781341397</v>
+        <v>0.04584358619249825</v>
       </c>
       <c r="AC29">
-        <v>-0.04626069781341397</v>
+        <v>-0.04584358619249825</v>
       </c>
       <c r="AD29">
-        <v>16.2</v>
+        <v>114005.3</v>
       </c>
       <c r="AE29">
         <v>0</v>
       </c>
       <c r="AF29">
-        <v>16.2</v>
+        <v>114005.3</v>
       </c>
       <c r="AG29">
-        <v>10.56</v>
+        <v>94913.20000000001</v>
       </c>
       <c r="AH29">
-        <v>0.6044776119402986</v>
+        <v>0.713022436647149</v>
       </c>
       <c r="AI29">
-        <v>0.5912408759124088</v>
+        <v>0.8420585750076817</v>
       </c>
       <c r="AJ29">
-        <v>0.4990548204158791</v>
+        <v>0.6741085284531539</v>
       </c>
       <c r="AK29">
-        <v>0.4852941176470588</v>
+        <v>0.8161297784029986</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -4067,7 +4139,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Macquarie Group Limited (ASX:MQG)</t>
+          <t>Butn Limited (ASX:BTN)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4075,15 +4147,6 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D30">
-        <v>0.121</v>
-      </c>
-      <c r="E30">
-        <v>0.155</v>
-      </c>
-      <c r="F30">
-        <v>0.0245</v>
-      </c>
       <c r="G30">
         <v>0</v>
       </c>
@@ -4097,91 +4160,91 @@
         <v>0</v>
       </c>
       <c r="K30">
-        <v>3200.6</v>
+        <v>-4.35</v>
       </c>
       <c r="L30">
-        <v>0.2731003882418192</v>
+        <v>-1.208333333333333</v>
       </c>
       <c r="M30">
-        <v>1747.9</v>
+        <v>-0</v>
       </c>
       <c r="N30">
-        <v>0.0414419199044031</v>
+        <v>-0</v>
       </c>
       <c r="O30">
-        <v>0.546116353183778</v>
+        <v>0</v>
       </c>
       <c r="P30">
-        <v>1152.6</v>
+        <v>-0</v>
       </c>
       <c r="Q30">
-        <v>0.02732762565467991</v>
+        <v>-0</v>
       </c>
       <c r="R30">
-        <v>0.3601199775042179</v>
+        <v>0</v>
       </c>
       <c r="S30">
-        <v>595.3</v>
-      </c>
-      <c r="T30">
-        <v>0.3405801247210939</v>
+        <v>0</v>
       </c>
       <c r="U30">
-        <v>34869.9</v>
+        <v>9.76</v>
       </c>
       <c r="V30">
-        <v>0.8267495868611167</v>
+        <v>1.086859688195991</v>
       </c>
       <c r="W30">
-        <v>0.1836248788016133</v>
+        <v>-0.3508064516129032</v>
       </c>
       <c r="X30">
-        <v>0.07556479028335128</v>
+        <v>0.09524755620585107</v>
       </c>
       <c r="Y30">
-        <v>0.108060088518262</v>
+        <v>-0.4460540078187543</v>
       </c>
       <c r="Z30">
-        <v>0.0871210037481471</v>
+        <v>0.08933002481389579</v>
       </c>
       <c r="AA30">
         <v>0</v>
       </c>
       <c r="AB30">
-        <v>0.04670501601426072</v>
+        <v>0.04585191943646642</v>
       </c>
       <c r="AC30">
-        <v>-0.04670501601426072</v>
+        <v>-0.04585191943646642</v>
       </c>
       <c r="AD30">
-        <v>177050</v>
+        <v>52.9</v>
       </c>
       <c r="AE30">
         <v>0</v>
       </c>
       <c r="AF30">
-        <v>177050</v>
+        <v>52.9</v>
       </c>
       <c r="AG30">
-        <v>142180.1</v>
+        <v>43.14</v>
       </c>
       <c r="AH30">
-        <v>0.8076100080692579</v>
+        <v>0.8548804137039432</v>
       </c>
       <c r="AI30">
-        <v>0.8966177683763598</v>
+        <v>0.8357030015797788</v>
       </c>
       <c r="AJ30">
-        <v>0.7712207605669863</v>
+        <v>0.8277052954719877</v>
       </c>
       <c r="AK30">
-        <v>0.8744464754013669</v>
+        <v>0.8057527082555099</v>
       </c>
       <c r="AL30">
         <v>0</v>
       </c>
       <c r="AM30">
-        <v>0</v>
+        <v>-0.164</v>
+      </c>
+      <c r="AQ30">
+        <v>-0</v>
       </c>
     </row>
     <row r="31">
@@ -4192,7 +4255,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Credit Corp Group Limited (ASX:CCP)</t>
+          <t>Propell Holdings Limited (ASX:PHL)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4200,107 +4263,80 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D31">
-        <v>0.102</v>
-      </c>
-      <c r="E31">
-        <v>0.128</v>
-      </c>
-      <c r="F31">
-        <v>0.0407</v>
-      </c>
-      <c r="G31">
-        <v>0</v>
-      </c>
-      <c r="H31">
-        <v>0</v>
-      </c>
-      <c r="I31">
-        <v>0</v>
-      </c>
-      <c r="J31">
-        <v>0</v>
-      </c>
       <c r="K31">
-        <v>69.40000000000001</v>
-      </c>
-      <c r="L31">
-        <v>0.2696192696192697</v>
+        <v>-2.98</v>
       </c>
       <c r="M31">
-        <v>34.4</v>
+        <v>-0</v>
       </c>
       <c r="N31">
-        <v>0.0395538691502817</v>
+        <v>-0</v>
       </c>
       <c r="O31">
-        <v>0.4956772334293947</v>
+        <v>0</v>
       </c>
       <c r="P31">
-        <v>34.4</v>
+        <v>-0</v>
       </c>
       <c r="Q31">
-        <v>0.0395538691502817</v>
+        <v>-0</v>
       </c>
       <c r="R31">
-        <v>0.4956772334293947</v>
+        <v>0</v>
       </c>
       <c r="S31">
         <v>0</v>
       </c>
-      <c r="T31">
-        <v>0</v>
-      </c>
       <c r="U31">
-        <v>20.5</v>
+        <v>0.43</v>
       </c>
       <c r="V31">
-        <v>0.0235713464413016</v>
+        <v>0.474090407938258</v>
       </c>
       <c r="W31">
-        <v>0.1387722455508898</v>
+        <v>5.120274914089348</v>
       </c>
       <c r="X31">
-        <v>0.04895231137685896</v>
+        <v>0.09139565371735231</v>
       </c>
       <c r="Y31">
-        <v>0.08981993417403086</v>
+        <v>5.028879260371995</v>
       </c>
       <c r="Z31">
-        <v>0.5424657534246574</v>
+        <v>0</v>
       </c>
       <c r="AA31">
         <v>0</v>
       </c>
       <c r="AB31">
-        <v>0.04719079530347903</v>
+        <v>0.04590452129060524</v>
       </c>
       <c r="AC31">
-        <v>-0.04719079530347903</v>
+        <v>-0.04590452129060524</v>
       </c>
       <c r="AD31">
-        <v>108.8</v>
+        <v>4.89</v>
       </c>
       <c r="AE31">
         <v>0</v>
       </c>
       <c r="AF31">
-        <v>108.8</v>
+        <v>4.89</v>
       </c>
       <c r="AG31">
-        <v>88.3</v>
+        <v>4.46</v>
       </c>
       <c r="AH31">
-        <v>0.1111905978538579</v>
+        <v>0.843539761945834</v>
       </c>
       <c r="AI31">
-        <v>0.1757389759328057</v>
+        <v>2.928143712574851</v>
       </c>
       <c r="AJ31">
-        <v>0.09217118997912317</v>
+        <v>0.8310042854481088</v>
       </c>
       <c r="AK31">
-        <v>0.1475108586702305</v>
+        <v>3.596774193548388</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -4317,7 +4353,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Beforepay Group Limited (ASX:B4P)</t>
+          <t>FSA Group Limited (ASX:FSA)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4325,8 +4361,14 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D32">
+        <v>-0.0379</v>
+      </c>
+      <c r="E32">
+        <v>0.00611</v>
+      </c>
       <c r="G32">
-        <v>0.02811671087533156</v>
+        <v>0</v>
       </c>
       <c r="H32">
         <v>0</v>
@@ -4338,82 +4380,85 @@
         <v>0</v>
       </c>
       <c r="K32">
-        <v>-20.1</v>
+        <v>8.65</v>
       </c>
       <c r="L32">
-        <v>-5.331564986737401</v>
+        <v>0.2376373626373627</v>
       </c>
       <c r="M32">
-        <v>-0</v>
+        <v>6.372</v>
       </c>
       <c r="N32">
-        <v>-0</v>
+        <v>0.07984962406015038</v>
       </c>
       <c r="O32">
-        <v>0</v>
+        <v>0.7366473988439306</v>
       </c>
       <c r="P32">
-        <v>-0</v>
+        <v>5.7</v>
       </c>
       <c r="Q32">
-        <v>-0</v>
+        <v>0.07142857142857144</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>0.6589595375722543</v>
       </c>
       <c r="S32">
-        <v>0</v>
+        <v>0.6719999999999997</v>
+      </c>
+      <c r="T32">
+        <v>0.1054613935969868</v>
       </c>
       <c r="U32">
-        <v>19.5</v>
+        <v>10.9</v>
       </c>
       <c r="V32">
-        <v>1.326530612244898</v>
+        <v>0.1365914786967419</v>
       </c>
       <c r="W32">
-        <v>2.02416918429003</v>
+        <v>0.148881239242685</v>
       </c>
       <c r="X32">
-        <v>0.05466925215948681</v>
+        <v>0.08841583002505821</v>
       </c>
       <c r="Y32">
-        <v>1.969499932130544</v>
+        <v>0.06046540921762683</v>
       </c>
       <c r="Z32">
-        <v>0.4564164648910412</v>
+        <v>0.09290928582367654</v>
       </c>
       <c r="AA32">
         <v>0</v>
       </c>
       <c r="AB32">
-        <v>0.04791462607974341</v>
+        <v>0.04595121693656019</v>
       </c>
       <c r="AC32">
-        <v>-0.04791462607974341</v>
+        <v>-0.04595121693656019</v>
       </c>
       <c r="AD32">
-        <v>14.7</v>
+        <v>399.4</v>
       </c>
       <c r="AE32">
         <v>0</v>
       </c>
       <c r="AF32">
-        <v>14.7</v>
+        <v>399.4</v>
       </c>
       <c r="AG32">
-        <v>-4.800000000000001</v>
+        <v>388.5</v>
       </c>
       <c r="AH32">
-        <v>0.5</v>
+        <v>0.8334724540901502</v>
       </c>
       <c r="AI32">
-        <v>0.3951612903225806</v>
+        <v>0.8556126820908312</v>
       </c>
       <c r="AJ32">
-        <v>-0.484848484848485</v>
+        <v>0.8295964125560538</v>
       </c>
       <c r="AK32">
-        <v>-0.2711864406779662</v>
+        <v>0.8521605615266507</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -4430,7 +4475,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>AMP Limited (ASX:AMP)</t>
+          <t>QuickFee Limited (ASX:QFE)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4439,28 +4484,25 @@
         </is>
       </c>
       <c r="D33">
-        <v>-0.282</v>
-      </c>
-      <c r="F33">
-        <v>0.0445</v>
+        <v>0.22</v>
       </c>
       <c r="G33">
-        <v>0.02780628907343473</v>
+        <v>0.3209417596034696</v>
       </c>
       <c r="H33">
-        <v>0.02780628907343473</v>
+        <v>0</v>
       </c>
       <c r="I33">
-        <v>-0.006305057584644442</v>
+        <v>0</v>
       </c>
       <c r="J33">
-        <v>-0.006305057584644442</v>
+        <v>0</v>
       </c>
       <c r="K33">
-        <v>57.2</v>
+        <v>-5.38</v>
       </c>
       <c r="L33">
-        <v>0.02668657273490716</v>
+        <v>-0.6666666666666666</v>
       </c>
       <c r="M33">
         <v>-0</v>
@@ -4469,7 +4511,7 @@
         <v>-0</v>
       </c>
       <c r="O33">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P33">
         <v>-0</v>
@@ -4478,79 +4520,67 @@
         <v>-0</v>
       </c>
       <c r="R33">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S33">
         <v>0</v>
       </c>
       <c r="U33">
-        <v>1278.8</v>
+        <v>2.25</v>
       </c>
       <c r="V33">
-        <v>0.4704930095658572</v>
+        <v>0.2391073326248672</v>
       </c>
       <c r="W33">
-        <v>0.01773038653482533</v>
+        <v>-0.4803571428571429</v>
       </c>
       <c r="X33">
-        <v>0.09591258166444018</v>
+        <v>0.06948644972858579</v>
       </c>
       <c r="Y33">
-        <v>-0.07818219512961486</v>
+        <v>-0.5498435925857287</v>
       </c>
       <c r="Z33">
-        <v>0.1050765014815449</v>
+        <v>0.3708639705882353</v>
       </c>
       <c r="AA33">
-        <v>-0.0006625133926341173</v>
+        <v>0</v>
       </c>
       <c r="AB33">
-        <v>0.04904053152906292</v>
+        <v>0.04648520478736882</v>
       </c>
       <c r="AC33">
-        <v>-0.04970304492169704</v>
+        <v>-0.04648520478736882</v>
       </c>
       <c r="AD33">
-        <v>19495.7</v>
+        <v>24</v>
       </c>
       <c r="AE33">
-        <v>377.5713021346345</v>
+        <v>0</v>
       </c>
       <c r="AF33">
-        <v>19873.27130213464</v>
+        <v>24</v>
       </c>
       <c r="AG33">
-        <v>18594.47130213464</v>
+        <v>21.75</v>
       </c>
       <c r="AH33">
-        <v>0.8796880457213058</v>
+        <v>0.7183478000598624</v>
       </c>
       <c r="AI33">
-        <v>0.8630244737420384</v>
+        <v>0.8013355592654424</v>
       </c>
       <c r="AJ33">
-        <v>0.8724690364872061</v>
+        <v>0.69801026957638</v>
       </c>
       <c r="AK33">
-        <v>0.8549704505538959</v>
+        <v>0.7851985559566788</v>
       </c>
       <c r="AL33">
-        <v>253.5</v>
+        <v>0</v>
       </c>
       <c r="AM33">
-        <v>253.5</v>
-      </c>
-      <c r="AN33">
-        <v>241.8821339950372</v>
-      </c>
-      <c r="AO33">
-        <v>0.1384615384615385</v>
-      </c>
-      <c r="AP33">
-        <v>230.7006365029111</v>
-      </c>
-      <c r="AQ33">
-        <v>0.1384615384615385</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -4561,7 +4591,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Butn Limited (ASX:BTN)</t>
+          <t>Credit Corp Group Limited (ASX:CCP)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4569,6 +4599,15 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D34">
+        <v>0.08900000000000001</v>
+      </c>
+      <c r="E34">
+        <v>0.0726</v>
+      </c>
+      <c r="F34">
+        <v>0.0532</v>
+      </c>
       <c r="G34">
         <v>0</v>
       </c>
@@ -4582,91 +4621,91 @@
         <v>0</v>
       </c>
       <c r="K34">
-        <v>-5.97</v>
+        <v>60.7</v>
       </c>
       <c r="L34">
-        <v>-4.738095238095238</v>
+        <v>0.2310620479634564</v>
       </c>
       <c r="M34">
-        <v>-0</v>
+        <v>26.7</v>
       </c>
       <c r="N34">
-        <v>-0</v>
+        <v>0.03550059832469087</v>
       </c>
       <c r="O34">
-        <v>0</v>
+        <v>0.4398682042833608</v>
       </c>
       <c r="P34">
-        <v>-0</v>
+        <v>26.7</v>
       </c>
       <c r="Q34">
-        <v>-0</v>
+        <v>0.03550059832469087</v>
       </c>
       <c r="R34">
-        <v>0</v>
+        <v>0.4398682042833608</v>
       </c>
       <c r="S34">
         <v>0</v>
       </c>
+      <c r="T34">
+        <v>0</v>
+      </c>
       <c r="U34">
-        <v>10.9</v>
+        <v>43.8</v>
       </c>
       <c r="V34">
-        <v>0.7218543046357616</v>
+        <v>0.05823693657758276</v>
       </c>
       <c r="W34">
-        <v>-2.211111111111111</v>
+        <v>0.118949637468156</v>
       </c>
       <c r="X34">
-        <v>0.06492522774678272</v>
+        <v>0.05214890057149628</v>
       </c>
       <c r="Y34">
-        <v>-2.276036338857894</v>
+        <v>0.0668007368966597</v>
       </c>
       <c r="Z34">
-        <v>0.04809160305343511</v>
+        <v>0.4392616658501227</v>
       </c>
       <c r="AA34">
         <v>0</v>
       </c>
       <c r="AB34">
-        <v>0.05351181704965527</v>
+        <v>0.04830657174050265</v>
       </c>
       <c r="AC34">
-        <v>-0.05351181704965527</v>
+        <v>-0.04830657174050265</v>
       </c>
       <c r="AD34">
-        <v>38.8</v>
+        <v>227.4</v>
       </c>
       <c r="AE34">
         <v>0</v>
       </c>
       <c r="AF34">
-        <v>38.8</v>
+        <v>227.4</v>
       </c>
       <c r="AG34">
-        <v>27.9</v>
+        <v>183.6</v>
       </c>
       <c r="AH34">
-        <v>0.7198515769944341</v>
+        <v>0.2321592649310873</v>
       </c>
       <c r="AI34">
-        <v>0.7578125</v>
+        <v>0.2947886958776251</v>
       </c>
       <c r="AJ34">
-        <v>0.6488372093023256</v>
+        <v>0.1962167361333761</v>
       </c>
       <c r="AK34">
-        <v>0.6923076923076923</v>
+        <v>0.2523364485981309</v>
       </c>
       <c r="AL34">
         <v>0</v>
       </c>
       <c r="AM34">
-        <v>-0.016</v>
-      </c>
-      <c r="AQ34">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -4677,7 +4716,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Challenger Limited (ASX:CGF)</t>
+          <t>Australian Bond Exchange Holdings Limited (ASX:ABE)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -4685,125 +4724,101 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D35">
-        <v>-0.297</v>
-      </c>
-      <c r="E35">
-        <v>-0.0859</v>
-      </c>
-      <c r="F35">
-        <v>0.106</v>
-      </c>
       <c r="G35">
-        <v>-0.6929065743944637</v>
+        <v>0.02398753894080997</v>
       </c>
       <c r="H35">
-        <v>-0.6929065743944637</v>
+        <v>0</v>
       </c>
       <c r="I35">
-        <v>-0.7035755478662052</v>
+        <v>0</v>
       </c>
       <c r="J35">
-        <v>-0.4995329235053317</v>
+        <v>0</v>
       </c>
       <c r="K35">
-        <v>174.8</v>
+        <v>-3.35</v>
       </c>
       <c r="L35">
-        <v>0.5040369088811996</v>
+        <v>-1.043613707165109</v>
       </c>
       <c r="M35">
-        <v>93.27</v>
+        <v>-0</v>
       </c>
       <c r="N35">
-        <v>0.02638920325939339</v>
+        <v>-0</v>
       </c>
       <c r="O35">
-        <v>0.5335812356979405</v>
+        <v>0</v>
       </c>
       <c r="P35">
-        <v>92.09999999999999</v>
+        <v>-0</v>
       </c>
       <c r="Q35">
-        <v>0.02605817111815301</v>
+        <v>-0</v>
       </c>
       <c r="R35">
-        <v>0.5268878718535468</v>
+        <v>0</v>
       </c>
       <c r="S35">
-        <v>1.170000000000002</v>
-      </c>
-      <c r="T35">
-        <v>0.01254422643936959</v>
+        <v>0</v>
       </c>
       <c r="U35">
-        <v>505.1</v>
+        <v>3.9</v>
       </c>
       <c r="V35">
-        <v>0.1429096876414667</v>
+        <v>0.819327731092437</v>
       </c>
       <c r="W35">
-        <v>0.06094202140640798</v>
+        <v>-0.3772522522522522</v>
       </c>
       <c r="X35">
-        <v>0.05599983336229149</v>
+        <v>0.05205298294385964</v>
       </c>
       <c r="Y35">
-        <v>0.004942188044116481</v>
+        <v>-0.4293052351961119</v>
       </c>
       <c r="Z35">
-        <v>0.05138919759946655</v>
+        <v>1.211320754716981</v>
       </c>
       <c r="AA35">
-        <v>-0.0256705961134547</v>
+        <v>0</v>
       </c>
       <c r="AB35">
-        <v>0.04716782615852642</v>
+        <v>0.0487746551812332</v>
       </c>
       <c r="AC35">
-        <v>-0.07283842227198112</v>
+        <v>-0.0487746551812332</v>
       </c>
       <c r="AD35">
-        <v>4254.1</v>
+        <v>1.38</v>
       </c>
       <c r="AE35">
         <v>0</v>
       </c>
       <c r="AF35">
-        <v>4254.1</v>
+        <v>1.38</v>
       </c>
       <c r="AG35">
-        <v>3749</v>
+        <v>-2.52</v>
       </c>
       <c r="AH35">
-        <v>0.5462027348013097</v>
+        <v>0.2247557003257329</v>
       </c>
       <c r="AI35">
-        <v>0.6075549842902028</v>
+        <v>0.1994219653179191</v>
       </c>
       <c r="AJ35">
-        <v>0.514732130598347</v>
+        <v>-1.125</v>
       </c>
       <c r="AK35">
-        <v>0.5770444365774446</v>
+        <v>-0.8344370860927153</v>
       </c>
       <c r="AL35">
-        <v>28.4</v>
+        <v>0</v>
       </c>
       <c r="AM35">
-        <v>28.4</v>
-      </c>
-      <c r="AN35">
-        <v>-17.70328755722014</v>
-      </c>
-      <c r="AO35">
-        <v>-8.591549295774648</v>
-      </c>
-      <c r="AP35">
-        <v>-15.6013316687474</v>
-      </c>
-      <c r="AQ35">
-        <v>-8.591549295774648</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -4814,7 +4829,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>ClearView Wealth Limited (ASX:CVW)</t>
+          <t>Beforepay Group Limited (ASX:B4P)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -4822,122 +4837,101 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D36">
-        <v>-0.234</v>
-      </c>
-      <c r="E36">
-        <v>0.1</v>
-      </c>
       <c r="G36">
-        <v>-0.148817802503477</v>
+        <v>0.002367531003382187</v>
       </c>
       <c r="H36">
-        <v>-0.148817802503477</v>
+        <v>0</v>
       </c>
       <c r="I36">
-        <v>-0.1515994436717663</v>
+        <v>0</v>
       </c>
       <c r="J36">
-        <v>-0.1515994436717663</v>
+        <v>0</v>
       </c>
       <c r="K36">
-        <v>14.6</v>
+        <v>-4.42</v>
       </c>
       <c r="L36">
-        <v>0.2030598052851182</v>
+        <v>-0.4983089064261556</v>
       </c>
       <c r="M36">
-        <v>4.61</v>
+        <v>-0</v>
       </c>
       <c r="N36">
-        <v>0.02222757955641273</v>
+        <v>-0</v>
       </c>
       <c r="O36">
-        <v>0.3157534246575343</v>
+        <v>0</v>
       </c>
       <c r="P36">
-        <v>4.61</v>
+        <v>-0</v>
       </c>
       <c r="Q36">
-        <v>0.02222757955641273</v>
+        <v>-0</v>
       </c>
       <c r="R36">
-        <v>0.3157534246575343</v>
+        <v>0</v>
       </c>
       <c r="S36">
         <v>0</v>
       </c>
-      <c r="T36">
-        <v>0</v>
-      </c>
       <c r="U36">
-        <v>103.9</v>
+        <v>14.5</v>
       </c>
       <c r="V36">
-        <v>0.5009643201542913</v>
+        <v>1.098484848484849</v>
       </c>
       <c r="W36">
-        <v>0.04238026124818577</v>
+        <v>-0.1964444444444444</v>
       </c>
       <c r="X36">
-        <v>0.05032768978129151</v>
+        <v>0.06290418799035834</v>
       </c>
       <c r="Y36">
-        <v>-0.00794742853310574</v>
+        <v>-0.2593486324348028</v>
       </c>
       <c r="Z36">
-        <v>0.2230010545251535</v>
+        <v>0.5011299435028247</v>
       </c>
       <c r="AA36">
-        <v>-0.03380683580423051</v>
+        <v>0</v>
       </c>
       <c r="AB36">
-        <v>0.04600151213227386</v>
+        <v>0.05013814610878455</v>
       </c>
       <c r="AC36">
-        <v>-0.07980834793650438</v>
+        <v>-0.05013814610878455</v>
       </c>
       <c r="AD36">
-        <v>69.59999999999999</v>
+        <v>22.4</v>
       </c>
       <c r="AE36">
         <v>0</v>
       </c>
       <c r="AF36">
-        <v>69.59999999999999</v>
+        <v>22.4</v>
       </c>
       <c r="AG36">
-        <v>-34.30000000000001</v>
+        <v>7.899999999999999</v>
       </c>
       <c r="AH36">
-        <v>0.2512635379061371</v>
+        <v>0.6292134831460675</v>
       </c>
       <c r="AI36">
-        <v>0.08227922922331245</v>
+        <v>0.5558312655086849</v>
       </c>
       <c r="AJ36">
-        <v>-0.1981513575967649</v>
+        <v>0.3744075829383886</v>
       </c>
       <c r="AK36">
-        <v>-0.04622641509433964</v>
+        <v>0.3062015503875969</v>
       </c>
       <c r="AL36">
-        <v>6.01</v>
+        <v>0</v>
       </c>
       <c r="AM36">
-        <v>6.01</v>
-      </c>
-      <c r="AN36">
-        <v>-6.504672897196262</v>
-      </c>
-      <c r="AO36">
-        <v>-1.813643926788686</v>
-      </c>
-      <c r="AP36">
-        <v>3.205607476635515</v>
-      </c>
-      <c r="AQ36">
-        <v>-1.813643926788686</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -4948,7 +4942,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Payright Limited (ASX:PYR)</t>
+          <t>MoneyMe Limited (ASX:MME)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -4956,23 +4950,32 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D37">
+        <v>0.574</v>
+      </c>
+      <c r="E37">
+        <v>0.763</v>
+      </c>
+      <c r="F37">
+        <v>0.12</v>
+      </c>
       <c r="G37">
-        <v>-0.2446428571428572</v>
+        <v>0.1133200795228628</v>
       </c>
       <c r="H37">
-        <v>-0.2446428571428572</v>
+        <v>0</v>
       </c>
       <c r="I37">
-        <v>-0.25</v>
+        <v>0</v>
       </c>
       <c r="J37">
-        <v>-0.25</v>
+        <v>0</v>
       </c>
       <c r="K37">
-        <v>-8.720000000000001</v>
+        <v>8.18</v>
       </c>
       <c r="L37">
-        <v>-0.7785714285714287</v>
+        <v>0.162624254473161</v>
       </c>
       <c r="M37">
         <v>-0</v>
@@ -4981,7 +4984,7 @@
         <v>-0</v>
       </c>
       <c r="O37">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P37">
         <v>-0</v>
@@ -4990,79 +4993,67 @@
         <v>-0</v>
       </c>
       <c r="R37">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S37">
         <v>0</v>
       </c>
       <c r="U37">
-        <v>8.74</v>
+        <v>61</v>
       </c>
       <c r="V37">
-        <v>2.312169312169313</v>
+        <v>1.355555555555556</v>
       </c>
       <c r="W37">
-        <v>-0.6507462686567165</v>
+        <v>0.1300476947535771</v>
       </c>
       <c r="X37">
-        <v>0.1643019288430003</v>
+        <v>0.1774079836917407</v>
       </c>
       <c r="Y37">
-        <v>-0.8150481974997168</v>
+        <v>-0.04736028893816355</v>
       </c>
       <c r="Z37">
-        <v>0.243002820568453</v>
+        <v>0.05581446959609409</v>
       </c>
       <c r="AA37">
-        <v>-0.06075070514211326</v>
+        <v>0</v>
       </c>
       <c r="AB37">
-        <v>0.04771785419873967</v>
+        <v>0.05029822687286678</v>
       </c>
       <c r="AC37">
-        <v>-0.1084685593408529</v>
+        <v>-0.05029822687286678</v>
       </c>
       <c r="AD37">
-        <v>67.2</v>
+        <v>744.5</v>
       </c>
       <c r="AE37">
         <v>0</v>
       </c>
       <c r="AF37">
-        <v>67.2</v>
+        <v>744.5</v>
       </c>
       <c r="AG37">
-        <v>58.46</v>
+        <v>683.5</v>
       </c>
       <c r="AH37">
-        <v>0.9467455621301775</v>
+        <v>0.9430018999366688</v>
       </c>
       <c r="AI37">
-        <v>0.9337223843268029</v>
+        <v>0.8707602339181286</v>
       </c>
       <c r="AJ37">
-        <v>0.9392673521850899</v>
+        <v>0.938229238160604</v>
       </c>
       <c r="AK37">
-        <v>0.9245611260477621</v>
+        <v>0.860831234256927</v>
       </c>
       <c r="AL37">
-        <v>6.71</v>
+        <v>0</v>
       </c>
       <c r="AM37">
-        <v>6.71</v>
-      </c>
-      <c r="AN37">
-        <v>-24.52554744525547</v>
-      </c>
-      <c r="AO37">
-        <v>-0.4172876304023845</v>
-      </c>
-      <c r="AP37">
-        <v>-21.33576642335766</v>
-      </c>
-      <c r="AQ37">
-        <v>-0.4172876304023845</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -5073,7 +5064,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Zip Co Limited (ASX:ZIP)</t>
+          <t>EML Payments Limited (ASX:EML)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -5082,25 +5073,25 @@
         </is>
       </c>
       <c r="D38">
-        <v>1.067</v>
+        <v>0.29</v>
       </c>
       <c r="G38">
-        <v>-0.2326779026217229</v>
+        <v>0.05419621749408984</v>
       </c>
       <c r="H38">
-        <v>-0.2326779026217229</v>
+        <v>0.05419621749408984</v>
       </c>
       <c r="I38">
-        <v>-0.2661516853932585</v>
+        <v>-0.004178486997635934</v>
       </c>
       <c r="J38">
-        <v>-0.2661516853932585</v>
+        <v>-0.004178486997635934</v>
       </c>
       <c r="K38">
-        <v>-761.4</v>
+        <v>-189.6</v>
       </c>
       <c r="L38">
-        <v>-1.782303370786517</v>
+        <v>-1.120567375886525</v>
       </c>
       <c r="M38">
         <v>-0</v>
@@ -5124,73 +5115,73 @@
         <v>0</v>
       </c>
       <c r="U38">
-        <v>166.3</v>
+        <v>47.5</v>
       </c>
       <c r="V38">
-        <v>0.6702942361950827</v>
+        <v>0.2354982647496282</v>
       </c>
       <c r="W38">
-        <v>-0.9039534607621987</v>
+        <v>-0.6294820717131474</v>
       </c>
       <c r="X38">
-        <v>0.09832408730196868</v>
+        <v>0.05232536734128973</v>
       </c>
       <c r="Y38">
-        <v>-1.002277548064167</v>
+        <v>-0.6818074390544371</v>
       </c>
       <c r="Z38">
-        <v>0.2666999625421401</v>
+        <v>1.730061349693252</v>
       </c>
       <c r="AA38">
-        <v>-0.07098264452490949</v>
+        <v>-0.007229038854805727</v>
       </c>
       <c r="AB38">
-        <v>0.04774513723342082</v>
+        <v>0.04867882032449734</v>
       </c>
       <c r="AC38">
-        <v>-0.1187277817583303</v>
+        <v>-0.05590785917930307</v>
       </c>
       <c r="AD38">
-        <v>1905.6</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="AE38">
         <v>0</v>
       </c>
       <c r="AF38">
-        <v>1905.6</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="AG38">
-        <v>1739.3</v>
+        <v>18.09999999999999</v>
       </c>
       <c r="AH38">
-        <v>0.8848028973394624</v>
+        <v>0.2454171343060232</v>
       </c>
       <c r="AI38">
-        <v>0.8633562885103299</v>
+        <v>0.3608360836083608</v>
       </c>
       <c r="AJ38">
-        <v>0.8751635302405153</v>
+        <v>0.08234758871701545</v>
       </c>
       <c r="AK38">
-        <v>0.8522220588955852</v>
+        <v>0.1347728965003722</v>
       </c>
       <c r="AL38">
-        <v>74.90000000000001</v>
+        <v>2.08</v>
       </c>
       <c r="AM38">
-        <v>74.90000000000001</v>
+        <v>2.08</v>
       </c>
       <c r="AN38">
-        <v>-19.17102615694165</v>
+        <v>7.153762268266084</v>
       </c>
       <c r="AO38">
-        <v>-1.518024032042724</v>
+        <v>-0.3399038461538461</v>
       </c>
       <c r="AP38">
-        <v>-17.49798792756539</v>
+        <v>1.973827699018538</v>
       </c>
       <c r="AQ38">
-        <v>-1.518024032042724</v>
+        <v>-0.3399038461538461</v>
       </c>
     </row>
     <row r="39">
@@ -5201,7 +5192,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>LawFinance Limited (ASX:LAW)</t>
+          <t>Income Asset Management Group Limited (ASX:IAM)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -5209,23 +5200,26 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D39">
+        <v>0.753</v>
+      </c>
       <c r="G39">
-        <v>-5</v>
+        <v>-0.2776572668112798</v>
       </c>
       <c r="H39">
-        <v>-5</v>
+        <v>-0.2776572668112798</v>
       </c>
       <c r="I39">
-        <v>-1.980582524271845</v>
+        <v>-0.2841648590021692</v>
       </c>
       <c r="J39">
-        <v>-1.980582524271845</v>
+        <v>-0.2841648590021692</v>
       </c>
       <c r="K39">
-        <v>-12.8</v>
+        <v>-4.17</v>
       </c>
       <c r="L39">
-        <v>-6.213592233009709</v>
+        <v>-0.4522776572668112</v>
       </c>
       <c r="M39">
         <v>-0</v>
@@ -5249,73 +5243,73 @@
         <v>0</v>
       </c>
       <c r="U39">
-        <v>3.18</v>
+        <v>6.18</v>
       </c>
       <c r="V39">
-        <v>1.319502074688797</v>
+        <v>0.3886792452830188</v>
       </c>
       <c r="W39">
-        <v>3.878787878787879</v>
+        <v>-0.5318877551020408</v>
       </c>
       <c r="X39">
-        <v>0.2075633186694753</v>
+        <v>0.05245087201060614</v>
       </c>
       <c r="Y39">
-        <v>3.671224560118404</v>
+        <v>-0.5843386271126469</v>
       </c>
       <c r="Z39">
-        <v>0.04449244060475162</v>
+        <v>1.020588886429046</v>
       </c>
       <c r="AA39">
-        <v>-0.08812095032397407</v>
+        <v>-0.2900154970112906</v>
       </c>
       <c r="AB39">
-        <v>0.05531030220541471</v>
+        <v>0.04863636141437588</v>
       </c>
       <c r="AC39">
-        <v>-0.1434312525293888</v>
+        <v>-0.3386518584256665</v>
       </c>
       <c r="AD39">
-        <v>58.8</v>
+        <v>5.43</v>
       </c>
       <c r="AE39">
         <v>0</v>
       </c>
       <c r="AF39">
-        <v>58.8</v>
+        <v>5.43</v>
       </c>
       <c r="AG39">
-        <v>55.62</v>
+        <v>-0.75</v>
       </c>
       <c r="AH39">
-        <v>0.9606273484724719</v>
+        <v>0.2545710267229255</v>
       </c>
       <c r="AI39">
-        <v>1.199755152009794</v>
+        <v>0.480106100795756</v>
       </c>
       <c r="AJ39">
-        <v>0.9584697570222298</v>
+        <v>-0.0495049504950495</v>
       </c>
       <c r="AK39">
-        <v>1.213615535675322</v>
+        <v>-0.1461988304093567</v>
       </c>
       <c r="AL39">
-        <v>8.32</v>
+        <v>1.45</v>
       </c>
       <c r="AM39">
-        <v>8.31</v>
+        <v>1.45</v>
       </c>
       <c r="AN39">
-        <v>-14.9238578680203</v>
+        <v>-2.12109375</v>
       </c>
       <c r="AO39">
-        <v>-0.4903846153846154</v>
+        <v>-1.806896551724138</v>
       </c>
       <c r="AP39">
-        <v>-14.11675126903553</v>
+        <v>0.29296875</v>
       </c>
       <c r="AQ39">
-        <v>-0.4909747292418772</v>
+        <v>-1.806896551724138</v>
       </c>
     </row>
     <row r="40">
@@ -5335,34 +5329,34 @@
         </is>
       </c>
       <c r="D40">
-        <v>-0.138</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="G40">
-        <v>-1.757009345794393</v>
+        <v>-4.104895104895105</v>
       </c>
       <c r="H40">
-        <v>-1.757009345794393</v>
+        <v>-4.104895104895105</v>
       </c>
       <c r="I40">
-        <v>-1.957943925233645</v>
+        <v>-4.335664335664336</v>
       </c>
       <c r="J40">
-        <v>-1.957943925233645</v>
+        <v>-4.335664335664336</v>
       </c>
       <c r="K40">
-        <v>-31.4</v>
+        <v>-21.1</v>
       </c>
       <c r="L40">
-        <v>-1.467289719626168</v>
+        <v>-1.475524475524476</v>
       </c>
       <c r="M40">
-        <v>-0</v>
+        <v>1.1</v>
       </c>
       <c r="N40">
-        <v>-0</v>
+        <v>0.004245465071401004</v>
       </c>
       <c r="O40">
-        <v>0</v>
+        <v>-0.05213270142180095</v>
       </c>
       <c r="P40">
         <v>-0</v>
@@ -5374,76 +5368,79 @@
         <v>0</v>
       </c>
       <c r="S40">
-        <v>0</v>
+        <v>1.1</v>
+      </c>
+      <c r="T40">
+        <v>1</v>
       </c>
       <c r="U40">
-        <v>109.5</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="V40">
-        <v>0.1594582787243338</v>
+        <v>0.3006561173292165</v>
       </c>
       <c r="W40">
-        <v>-0.1262057877813505</v>
+        <v>-0.09311562224183584</v>
       </c>
       <c r="X40">
-        <v>0.04919680092909713</v>
+        <v>0.05376988691882638</v>
       </c>
       <c r="Y40">
-        <v>-0.1754025887104476</v>
+        <v>-0.1468855091606622</v>
       </c>
       <c r="Z40">
-        <v>0.1184283342556724</v>
+        <v>0.08778391651319829</v>
       </c>
       <c r="AA40">
-        <v>-0.2318760376314333</v>
+        <v>-0.3806015960712094</v>
       </c>
       <c r="AB40">
-        <v>0.04770141951398096</v>
+        <v>0.04761229523007889</v>
       </c>
       <c r="AC40">
-        <v>-0.2795774571454143</v>
+        <v>-0.4282138913012882</v>
       </c>
       <c r="AD40">
-        <v>111.6</v>
+        <v>132.8</v>
       </c>
       <c r="AE40">
         <v>0</v>
       </c>
       <c r="AF40">
-        <v>111.6</v>
+        <v>132.8</v>
       </c>
       <c r="AG40">
-        <v>2.099999999999994</v>
+        <v>54.90000000000001</v>
       </c>
       <c r="AH40">
-        <v>0.1397970687711386</v>
+        <v>0.3388619545802501</v>
       </c>
       <c r="AI40">
-        <v>0.1796812107551119</v>
+        <v>0.2028100183262065</v>
       </c>
       <c r="AJ40">
-        <v>0.003048780487804869</v>
+        <v>0.1748407643312102</v>
       </c>
       <c r="AK40">
-        <v>0.004104769351055501</v>
+        <v>0.0951638065522621</v>
       </c>
       <c r="AL40">
-        <v>0.963</v>
+        <v>0.726</v>
       </c>
       <c r="AM40">
-        <v>0.963</v>
+        <v>0.726</v>
       </c>
       <c r="AN40">
-        <v>-2.968085106382978</v>
+        <v>-2.262350936967632</v>
       </c>
       <c r="AO40">
-        <v>-43.50986500519211</v>
+        <v>-85.39944903581268</v>
       </c>
       <c r="AP40">
-        <v>-0.05585106382978708</v>
+        <v>-0.9352640545144805</v>
       </c>
       <c r="AQ40">
-        <v>-43.50986500519211</v>
+        <v>-85.39944903581268</v>
       </c>
     </row>
     <row r="41">
@@ -5454,7 +5451,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>NSX Limited (ASX:NSX)</t>
+          <t>Change Financial Limited (ASX:CCA)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -5463,25 +5460,25 @@
         </is>
       </c>
       <c r="D41">
-        <v>-0.105</v>
+        <v>0.519</v>
       </c>
       <c r="G41">
-        <v>-1.7890625</v>
+        <v>-0.2296211251435132</v>
       </c>
       <c r="H41">
-        <v>-1.7890625</v>
+        <v>-0.2847301951779563</v>
       </c>
       <c r="I41">
-        <v>-1.90625</v>
+        <v>-0.2916188289322618</v>
       </c>
       <c r="J41">
-        <v>-1.90625</v>
+        <v>-0.2916188289322618</v>
       </c>
       <c r="K41">
-        <v>-4.38</v>
+        <v>-2.92</v>
       </c>
       <c r="L41">
-        <v>-3.421875</v>
+        <v>-0.3352468427095293</v>
       </c>
       <c r="M41">
         <v>-0</v>
@@ -5505,73 +5502,73 @@
         <v>0</v>
       </c>
       <c r="U41">
-        <v>0.549</v>
+        <v>5.35</v>
       </c>
       <c r="V41">
-        <v>0.0305</v>
+        <v>0.2316017316017316</v>
       </c>
       <c r="W41">
-        <v>-1.055421686746988</v>
+        <v>-0.874251497005988</v>
       </c>
       <c r="X41">
-        <v>0.0486321944997291</v>
+        <v>0.0498625536461013</v>
       </c>
       <c r="Y41">
-        <v>-1.104053881246717</v>
+        <v>-0.9241140506520893</v>
       </c>
       <c r="Z41">
-        <v>0.3137254901960784</v>
+        <v>2.782747603833866</v>
       </c>
       <c r="AA41">
-        <v>-0.5980392156862745</v>
+        <v>-0.8115015974440895</v>
       </c>
       <c r="AB41">
-        <v>0.0481037016517875</v>
+        <v>0.04977906632918488</v>
       </c>
       <c r="AC41">
-        <v>-0.646142917338062</v>
+        <v>-0.8612806637732744</v>
       </c>
       <c r="AD41">
-        <v>1.37</v>
+        <v>0.136</v>
       </c>
       <c r="AE41">
         <v>0</v>
       </c>
       <c r="AF41">
-        <v>1.37</v>
+        <v>0.136</v>
       </c>
       <c r="AG41">
-        <v>0.8210000000000001</v>
+        <v>-5.214</v>
       </c>
       <c r="AH41">
-        <v>0.07072792978833248</v>
+        <v>0.00585298674470649</v>
       </c>
       <c r="AI41">
-        <v>0.8925081433224755</v>
+        <v>0.01585820895522388</v>
       </c>
       <c r="AJ41">
-        <v>0.04362148663726688</v>
+        <v>-0.2915129151291512</v>
       </c>
       <c r="AK41">
-        <v>0.832657200811359</v>
+        <v>-1.616243025418475</v>
       </c>
       <c r="AL41">
-        <v>0.096</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="AM41">
-        <v>0.096</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="AN41">
-        <v>-0.5982532751091704</v>
+        <v>-0.05483870967741936</v>
       </c>
       <c r="AO41">
-        <v>-25.41666666666666</v>
+        <v>-29.19540229885058</v>
       </c>
       <c r="AP41">
-        <v>-0.3585152838427948</v>
+        <v>2.102419354838709</v>
       </c>
       <c r="AQ41">
-        <v>-25.41666666666666</v>
+        <v>-29.19540229885058</v>
       </c>
     </row>
     <row r="42">
@@ -5582,7 +5579,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Openpay Group Ltd (ASX:OPY)</t>
+          <t>NSX Limited (ASX:NSX)</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -5591,25 +5588,25 @@
         </is>
       </c>
       <c r="D42">
-        <v>0.5770000000000001</v>
+        <v>-0.05309999999999999</v>
       </c>
       <c r="G42">
-        <v>-1.822881355932203</v>
+        <v>-1.6</v>
       </c>
       <c r="H42">
-        <v>-1.877118644067796</v>
+        <v>-1.6</v>
       </c>
       <c r="I42">
-        <v>-1.889830508474576</v>
+        <v>-1.676923076923077</v>
       </c>
       <c r="J42">
-        <v>-1.889830508474576</v>
+        <v>-1.676923076923077</v>
       </c>
       <c r="K42">
-        <v>-56.8</v>
+        <v>-2.27</v>
       </c>
       <c r="L42">
-        <v>-2.406779661016949</v>
+        <v>-1.746153846153846</v>
       </c>
       <c r="M42">
         <v>-0</v>
@@ -5633,73 +5630,73 @@
         <v>0</v>
       </c>
       <c r="U42">
-        <v>7.13</v>
+        <v>1.37</v>
       </c>
       <c r="V42">
-        <v>0.2574007220216606</v>
+        <v>0.1838926174496645</v>
       </c>
       <c r="W42">
-        <v>-1.276404494382022</v>
+        <v>-13.75757575757576</v>
       </c>
       <c r="X42">
-        <v>0.06191134663617765</v>
+        <v>0.05077364525752664</v>
       </c>
       <c r="Y42">
-        <v>-1.3383158410182</v>
+        <v>-13.80834940283328</v>
       </c>
       <c r="Z42">
-        <v>0.5514018691588786</v>
+        <v>1.318458417849899</v>
       </c>
       <c r="AA42">
-        <v>-1.042056074766355</v>
+        <v>-2.210953346855984</v>
       </c>
       <c r="AB42">
-        <v>0.04783610106645901</v>
+        <v>0.04930534754819363</v>
       </c>
       <c r="AC42">
-        <v>-1.089892175832814</v>
+        <v>-2.260258694404178</v>
       </c>
       <c r="AD42">
-        <v>58.4</v>
+        <v>0.924</v>
       </c>
       <c r="AE42">
         <v>0</v>
       </c>
       <c r="AF42">
-        <v>58.4</v>
+        <v>0.924</v>
       </c>
       <c r="AG42">
-        <v>51.27</v>
+        <v>-0.4460000000000001</v>
       </c>
       <c r="AH42">
-        <v>0.6782810685249709</v>
+        <v>0.110341533317411</v>
       </c>
       <c r="AI42">
-        <v>1.214137214137214</v>
+        <v>0.4173441734417345</v>
       </c>
       <c r="AJ42">
-        <v>0.6492338862859314</v>
+        <v>-0.06367789834380355</v>
       </c>
       <c r="AK42">
-        <v>1.251403465950696</v>
+        <v>-0.528436018957346</v>
       </c>
       <c r="AL42">
-        <v>12.2</v>
+        <v>0.062</v>
       </c>
       <c r="AM42">
-        <v>12.2</v>
+        <v>0.062</v>
       </c>
       <c r="AN42">
-        <v>-1.318284424379233</v>
+        <v>-0.4442307692307693</v>
       </c>
       <c r="AO42">
-        <v>-3.655737704918033</v>
+        <v>-35.16129032258065</v>
       </c>
       <c r="AP42">
-        <v>-1.157336343115124</v>
+        <v>0.2144230769230769</v>
       </c>
       <c r="AQ42">
-        <v>-3.655737704918033</v>
+        <v>-35.16129032258065</v>
       </c>
     </row>
     <row r="43">
@@ -5710,7 +5707,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Income Asset Management Group Limited (ASX:IAM)</t>
+          <t>EonX Technologies Inc. (CNSX:EONX)</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -5718,26 +5715,23 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D43">
-        <v>0.408</v>
-      </c>
       <c r="G43">
-        <v>-1.465618860510806</v>
+        <v>-0.04161979752530934</v>
       </c>
       <c r="H43">
-        <v>-1.465618860510806</v>
+        <v>-0.5523059617547806</v>
       </c>
       <c r="I43">
-        <v>-1.489194499017682</v>
+        <v>-0.4949381327334083</v>
       </c>
       <c r="J43">
-        <v>-1.489194499017682</v>
+        <v>-0.4949381327334083</v>
       </c>
       <c r="K43">
-        <v>-7.99</v>
+        <v>-4.37</v>
       </c>
       <c r="L43">
-        <v>-1.569744597249509</v>
+        <v>-0.4915635545556805</v>
       </c>
       <c r="M43">
         <v>-0</v>
@@ -5761,73 +5755,299 @@
         <v>0</v>
       </c>
       <c r="U43">
-        <v>1.96</v>
+        <v>0.985</v>
       </c>
       <c r="V43">
-        <v>0.06901408450704226</v>
+        <v>0.4668246445497631</v>
       </c>
       <c r="W43">
-        <v>-0.9007891770011275</v>
+        <v>2.913333333333334</v>
       </c>
       <c r="X43">
-        <v>0.04889643369061633</v>
+        <v>0.0675072458274322</v>
       </c>
       <c r="Y43">
-        <v>-0.9496856106917438</v>
+        <v>2.845826087505901</v>
       </c>
       <c r="Z43">
-        <v>0.712785324184288</v>
+        <v>6.006756756756757</v>
       </c>
       <c r="AA43">
-        <v>-1.061475983755777</v>
+        <v>-2.972972972972973</v>
       </c>
       <c r="AB43">
-        <v>0.04781121781184181</v>
+        <v>0.0808940271504866</v>
       </c>
       <c r="AC43">
-        <v>-1.109287201567618</v>
+        <v>-3.05386700012346</v>
       </c>
       <c r="AD43">
-        <v>3.31</v>
+        <v>4.84</v>
       </c>
       <c r="AE43">
         <v>0</v>
       </c>
       <c r="AF43">
-        <v>3.31</v>
+        <v>4.84</v>
       </c>
       <c r="AG43">
-        <v>1.35</v>
+        <v>3.855</v>
       </c>
       <c r="AH43">
-        <v>0.1043834752444024</v>
+        <v>0.6964028776978418</v>
       </c>
       <c r="AI43">
-        <v>0.2968609865470852</v>
+        <v>8.491228070175435</v>
       </c>
       <c r="AJ43">
-        <v>0.04537815126050421</v>
+        <v>0.6462699077954737</v>
       </c>
       <c r="AK43">
-        <v>0.14689880304679</v>
+        <v>-9.289156626506033</v>
       </c>
       <c r="AL43">
-        <v>0.504</v>
+        <v>0.549</v>
       </c>
       <c r="AM43">
-        <v>0.504</v>
+        <v>0.549</v>
       </c>
       <c r="AN43">
-        <v>-0.4436997319034853</v>
+        <v>-1.12037037037037</v>
       </c>
       <c r="AO43">
-        <v>-15.03968253968254</v>
+        <v>-8.014571948998178</v>
       </c>
       <c r="AP43">
-        <v>-0.1809651474530831</v>
+        <v>-0.892361111111111</v>
       </c>
       <c r="AQ43">
-        <v>-15.03968253968254</v>
+        <v>-8.014571948998178</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Banxa Holdings Inc. (TSXV:BNXA)</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D44">
+        <v>0.254</v>
+      </c>
+      <c r="G44">
+        <v>-0.1220560747663551</v>
+      </c>
+      <c r="H44">
+        <v>-0.1220560747663551</v>
+      </c>
+      <c r="I44">
+        <v>-0.1274766355140187</v>
+      </c>
+      <c r="J44">
+        <v>-0.1274766355140187</v>
+      </c>
+      <c r="K44">
+        <v>-6.23</v>
+      </c>
+      <c r="L44">
+        <v>-0.1164485981308411</v>
+      </c>
+      <c r="M44">
+        <v>-0</v>
+      </c>
+      <c r="N44">
+        <v>-0</v>
+      </c>
+      <c r="O44">
+        <v>0</v>
+      </c>
+      <c r="P44">
+        <v>-0</v>
+      </c>
+      <c r="Q44">
+        <v>-0</v>
+      </c>
+      <c r="R44">
+        <v>0</v>
+      </c>
+      <c r="S44">
+        <v>0</v>
+      </c>
+      <c r="U44">
+        <v>5.5</v>
+      </c>
+      <c r="V44">
+        <v>0.2380952380952381</v>
+      </c>
+      <c r="W44">
+        <v>-1.214424951267057</v>
+      </c>
+      <c r="X44">
+        <v>0.05194379336814969</v>
+      </c>
+      <c r="Y44">
+        <v>-1.266368744635206</v>
+      </c>
+      <c r="AB44">
+        <v>0.04992742069237387</v>
+      </c>
+      <c r="AD44">
+        <v>6.37</v>
+      </c>
+      <c r="AE44">
+        <v>0</v>
+      </c>
+      <c r="AF44">
+        <v>6.37</v>
+      </c>
+      <c r="AG44">
+        <v>0.8700000000000001</v>
+      </c>
+      <c r="AH44">
+        <v>0.2161520190023753</v>
+      </c>
+      <c r="AI44">
+        <v>1.3</v>
+      </c>
+      <c r="AJ44">
+        <v>0.0362953692115144</v>
+      </c>
+      <c r="AK44">
+        <v>-1.45</v>
+      </c>
+      <c r="AL44">
+        <v>1.28</v>
+      </c>
+      <c r="AM44">
+        <v>1.28</v>
+      </c>
+      <c r="AN44">
+        <v>-0.9754977029096478</v>
+      </c>
+      <c r="AO44">
+        <v>-5.328125</v>
+      </c>
+      <c r="AP44">
+        <v>-0.1332312404287902</v>
+      </c>
+      <c r="AQ44">
+        <v>-5.328125</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>333D Limited (ASX:T3D)</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D45">
+        <v>-0.452</v>
+      </c>
+      <c r="G45">
+        <v>0</v>
+      </c>
+      <c r="H45">
+        <v>0</v>
+      </c>
+      <c r="I45">
+        <v>-31.25</v>
+      </c>
+      <c r="J45">
+        <v>-31.25</v>
+      </c>
+      <c r="K45">
+        <v>-0.483</v>
+      </c>
+      <c r="L45">
+        <v>-30.1875</v>
+      </c>
+      <c r="M45">
+        <v>-0</v>
+      </c>
+      <c r="N45">
+        <v>-0</v>
+      </c>
+      <c r="O45">
+        <v>0</v>
+      </c>
+      <c r="P45">
+        <v>-0</v>
+      </c>
+      <c r="Q45">
+        <v>-0</v>
+      </c>
+      <c r="R45">
+        <v>0</v>
+      </c>
+      <c r="S45">
+        <v>0</v>
+      </c>
+      <c r="U45">
+        <v>0.043</v>
+      </c>
+      <c r="V45">
+        <v>0.02287234042553191</v>
+      </c>
+      <c r="W45">
+        <v>-9.288461538461538</v>
+      </c>
+      <c r="X45">
+        <v>0.04981714963548235</v>
+      </c>
+      <c r="Y45">
+        <v>-9.33827868809702</v>
+      </c>
+      <c r="AB45">
+        <v>0.04981714963548235</v>
+      </c>
+      <c r="AD45">
+        <v>0</v>
+      </c>
+      <c r="AE45">
+        <v>0</v>
+      </c>
+      <c r="AF45">
+        <v>0</v>
+      </c>
+      <c r="AG45">
+        <v>-0.043</v>
+      </c>
+      <c r="AH45">
+        <v>0</v>
+      </c>
+      <c r="AI45">
+        <v>-0</v>
+      </c>
+      <c r="AJ45">
+        <v>-0.02340772999455634</v>
+      </c>
+      <c r="AK45">
+        <v>0.1339563862928349</v>
+      </c>
+      <c r="AL45">
+        <v>0</v>
+      </c>
+      <c r="AM45">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/australia/australia_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/australia/australia_financial_svcs_non_bank_insurance.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ7"/>
+  <dimension ref="A1:AQ38"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>36</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.05599999999999999</v>
+        <v>0.129</v>
       </c>
       <c r="E2">
-        <v>0.01393</v>
+        <v>-0.04305</v>
       </c>
       <c r="F2">
-        <v>0.1</v>
+        <v>0.233</v>
       </c>
       <c r="G2">
-        <v>0.1642867305995845</v>
+        <v>0.1748615929616746</v>
       </c>
       <c r="H2">
-        <v>0.1622662986255371</v>
+        <v>0.1728684586529848</v>
       </c>
       <c r="I2">
-        <v>0.1686520019350616</v>
+        <v>0.1657419467656994</v>
       </c>
       <c r="J2">
-        <v>0.1295315851806725</v>
+        <v>0.1402967186369953</v>
       </c>
       <c r="K2">
-        <v>3074.1</v>
+        <v>3346.839</v>
       </c>
       <c r="L2">
-        <v>0.1749580262371589</v>
+        <v>0.1526091747285836</v>
       </c>
       <c r="M2">
-        <v>3481.18</v>
+        <v>3800.2674</v>
       </c>
       <c r="N2">
-        <v>0.05523850024356999</v>
+        <v>0.05369974993220884</v>
       </c>
       <c r="O2">
-        <v>1.132422497641586</v>
+        <v>1.135479597315557</v>
       </c>
       <c r="P2">
-        <v>2151.14</v>
+        <v>2331.2944</v>
       </c>
       <c r="Q2">
-        <v>0.03413375562710148</v>
+        <v>0.03294239934230914</v>
       </c>
       <c r="R2">
-        <v>0.699762532123223</v>
+        <v>0.6965660433621098</v>
       </c>
       <c r="S2">
-        <v>1330.04</v>
+        <v>1468.973</v>
       </c>
       <c r="T2">
-        <v>0.3820658512343516</v>
+        <v>0.3865446415691696</v>
       </c>
       <c r="U2">
-        <v>15334.8</v>
+        <v>17781.016</v>
       </c>
       <c r="V2">
-        <v>0.2433288004455665</v>
+        <v>0.2512549808312447</v>
       </c>
       <c r="W2">
-        <v>0.1223824350236364</v>
+        <v>0.03951328705795375</v>
       </c>
       <c r="X2">
-        <v>0.07046262752305171</v>
+        <v>0.06934296061424187</v>
       </c>
       <c r="Y2">
-        <v>0.05191980750058468</v>
+        <v>-0.02982967355628812</v>
       </c>
       <c r="Z2">
-        <v>0.1223785477973185</v>
+        <v>0.1185500115188863</v>
       </c>
       <c r="AA2">
-        <v>0.1285278785567077</v>
+        <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.04992379000309694</v>
+        <v>0.05159983756333533</v>
       </c>
       <c r="AC2">
-        <v>0.07860408855361078</v>
+        <v>-0.04737804051237557</v>
       </c>
       <c r="AD2">
-        <v>143759.3</v>
+        <v>183443.938</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>143759.3</v>
+        <v>183443.938</v>
       </c>
       <c r="AG2">
-        <v>128424.5</v>
+        <v>165662.922</v>
       </c>
       <c r="AH2">
-        <v>0.6952275894887422</v>
+        <v>0.7216158097626166</v>
       </c>
       <c r="AI2">
-        <v>0.8258122738497825</v>
+        <v>0.8349434673389134</v>
       </c>
       <c r="AJ2">
-        <v>0.6708152820595324</v>
+        <v>0.7006797294028198</v>
       </c>
       <c r="AK2">
-        <v>0.808985968282965</v>
+        <v>0.820409155580914</v>
       </c>
       <c r="AL2">
-        <v>1900.2</v>
+        <v>2131.233</v>
       </c>
       <c r="AM2">
-        <v>1900.2</v>
+        <v>2124.806</v>
       </c>
       <c r="AN2">
-        <v>48.13799223144923</v>
+        <v>47.42063740923023</v>
       </c>
       <c r="AO2">
-        <v>1.559467424481634</v>
+        <v>1.705515539596093</v>
       </c>
       <c r="AP2">
-        <v>43.0031141173319</v>
+        <v>42.82420799490027</v>
       </c>
       <c r="AQ2">
-        <v>1.559467424481634</v>
+        <v>1.710674292147142</v>
       </c>
     </row>
     <row r="3">
@@ -716,7 +716,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Cuscal Limited (ASX:CCL)</t>
+          <t>ASX Limited (ASX:ASX)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -725,46 +725,49 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.119</v>
+        <v>0.07730000000000001</v>
       </c>
       <c r="E3">
-        <v>0.0732</v>
+        <v>-0.00734</v>
+      </c>
+      <c r="F3">
+        <v>0.0445</v>
       </c>
       <c r="G3">
-        <v>0.4343720491029273</v>
+        <v>0.7311083720489239</v>
       </c>
       <c r="H3">
-        <v>0.3226314132829713</v>
+        <v>0.7311083720489239</v>
       </c>
       <c r="I3">
-        <v>0.3216871262197041</v>
+        <v>0.7239973452166493</v>
       </c>
       <c r="J3">
-        <v>0.2272198504213826</v>
+        <v>0.5037887838718889</v>
       </c>
       <c r="K3">
-        <v>21.1</v>
+        <v>316.4</v>
       </c>
       <c r="L3">
-        <v>0.06641485678312875</v>
+        <v>0.2999905186308903</v>
       </c>
       <c r="M3">
-        <v>8.74</v>
+        <v>260.6</v>
       </c>
       <c r="N3">
-        <v>0.03262411347517731</v>
+        <v>0.03337687953072568</v>
       </c>
       <c r="O3">
-        <v>0.414218009478673</v>
+        <v>0.8236409608091025</v>
       </c>
       <c r="P3">
-        <v>8.74</v>
+        <v>260.6</v>
       </c>
       <c r="Q3">
-        <v>0.03262411347517731</v>
+        <v>0.03337687953072568</v>
       </c>
       <c r="R3">
-        <v>0.414218009478673</v>
+        <v>0.8236409608091025</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -773,52 +776,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>829.4</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>0.1062271062271062</v>
+      </c>
+      <c r="W3">
+        <v>0.1305819232356583</v>
       </c>
       <c r="X3">
-        <v>0.05617716244534345</v>
+        <v>0.05637782628915503</v>
+      </c>
+      <c r="Y3">
+        <v>0.07420409694650323</v>
+      </c>
+      <c r="Z3">
+        <v>4.03326959847036</v>
+      </c>
+      <c r="AA3">
+        <v>2.031915986040844</v>
       </c>
       <c r="AB3">
-        <v>0.05617716244534345</v>
+        <v>0.05583863028595714</v>
+      </c>
+      <c r="AC3">
+        <v>1.976077355754887</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>223</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>223</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>-606.4</v>
       </c>
       <c r="AH3">
-        <v>0</v>
+        <v>0.02776809284255616</v>
+      </c>
+      <c r="AI3">
+        <v>0.08234555592481814</v>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>-0.08420584886272113</v>
+      </c>
+      <c r="AK3">
+        <v>-0.3227763879278224</v>
       </c>
       <c r="AL3">
-        <v>73.7</v>
+        <v>308.9</v>
       </c>
       <c r="AM3">
-        <v>73.7</v>
+        <v>308.9</v>
       </c>
       <c r="AN3">
-        <v>0</v>
+        <v>0.2891972506808456</v>
       </c>
       <c r="AO3">
-        <v>1.386702849389416</v>
+        <v>2.471997410165102</v>
       </c>
       <c r="AP3">
-        <v>0</v>
+        <v>-0.786409026066658</v>
       </c>
       <c r="AQ3">
-        <v>1.386702849389416</v>
+        <v>2.471997410165102</v>
       </c>
     </row>
     <row r="4">
@@ -829,7 +853,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ASX Limited (ASX:ASX)</t>
+          <t>Litigation Capital Management Limited (AIM:LIT)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -838,124 +862,121 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.07730000000000001</v>
+        <v>0.234</v>
       </c>
       <c r="E4">
-        <v>-0.00734</v>
-      </c>
-      <c r="F4">
-        <v>0.0445</v>
+        <v>0.123</v>
       </c>
       <c r="G4">
-        <v>0.7311083720489239</v>
+        <v>0.7662141779788838</v>
       </c>
       <c r="H4">
-        <v>0.7311083720489239</v>
+        <v>0.7662141779788838</v>
       </c>
       <c r="I4">
-        <v>0.7239973452166493</v>
+        <v>0.7647058823529412</v>
       </c>
       <c r="J4">
-        <v>0.5037887838718889</v>
+        <v>0.6053326003298516</v>
       </c>
       <c r="K4">
-        <v>316.4</v>
+        <v>8.48</v>
       </c>
       <c r="L4">
-        <v>0.2999905186308903</v>
+        <v>0.1279034690799397</v>
       </c>
       <c r="M4">
-        <v>260.6</v>
+        <v>6.92</v>
       </c>
       <c r="N4">
-        <v>0.03337687953072568</v>
+        <v>0.04739726027397261</v>
       </c>
       <c r="O4">
-        <v>0.8236409608091025</v>
+        <v>0.8160377358490566</v>
       </c>
       <c r="P4">
-        <v>260.6</v>
+        <v>3.32</v>
       </c>
       <c r="Q4">
-        <v>0.03337687953072568</v>
+        <v>0.02273972602739726</v>
       </c>
       <c r="R4">
-        <v>0.8236409608091025</v>
+        <v>0.3915094339622641</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>0.5202312138728324</v>
       </c>
       <c r="U4">
-        <v>829.4</v>
+        <v>45.4</v>
       </c>
       <c r="V4">
-        <v>0.1062271062271062</v>
+        <v>0.310958904109589</v>
       </c>
       <c r="W4">
-        <v>0.1305819232356583</v>
+        <v>0.06945126945126946</v>
       </c>
       <c r="X4">
-        <v>0.05638463126597386</v>
+        <v>0.05822399010284961</v>
       </c>
       <c r="Y4">
-        <v>0.0741972919696844</v>
+        <v>0.01122727934841985</v>
       </c>
       <c r="Z4">
-        <v>4.03326959847036</v>
+        <v>0.6730964467005076</v>
       </c>
       <c r="AA4">
-        <v>2.031915986040844</v>
+        <v>0.4074472223540016</v>
       </c>
       <c r="AB4">
-        <v>0.05584524630154788</v>
+        <v>0.05430699709031524</v>
       </c>
       <c r="AC4">
-        <v>1.976070739739296</v>
+        <v>0.3531402252636864</v>
       </c>
       <c r="AD4">
-        <v>223</v>
+        <v>41.3</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>223</v>
+        <v>41.3</v>
       </c>
       <c r="AG4">
-        <v>-606.4</v>
+        <v>-4.100000000000001</v>
       </c>
       <c r="AH4">
-        <v>0.02776809284255616</v>
+        <v>0.2205018686599039</v>
       </c>
       <c r="AI4">
-        <v>0.08234555592481814</v>
+        <v>0.2467144563918758</v>
       </c>
       <c r="AJ4">
-        <v>-0.08420584886272113</v>
+        <v>-0.02889358703312193</v>
       </c>
       <c r="AK4">
-        <v>-0.3227763879278224</v>
+        <v>-0.03360655737704919</v>
       </c>
       <c r="AL4">
-        <v>308.9</v>
+        <v>6.02</v>
       </c>
       <c r="AM4">
-        <v>308.9</v>
+        <v>5.917</v>
       </c>
       <c r="AN4">
-        <v>0.2891972506808456</v>
+        <v>0.812992125984252</v>
       </c>
       <c r="AO4">
-        <v>2.471997410165102</v>
+        <v>8.421926910299005</v>
       </c>
       <c r="AP4">
-        <v>-0.786409026066658</v>
+        <v>-0.08070866141732287</v>
       </c>
       <c r="AQ4">
-        <v>2.471997410165102</v>
+        <v>8.56853135034646</v>
       </c>
     </row>
     <row r="5">
@@ -966,7 +987,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Challenger Limited (ASX:CGF)</t>
+          <t>Tyro Payments Limited (ASX:TYR)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -975,124 +996,118 @@
         </is>
       </c>
       <c r="D5">
-        <v>-0.00028</v>
-      </c>
-      <c r="E5">
-        <v>-0.158</v>
+        <v>0.213</v>
       </c>
       <c r="F5">
-        <v>0.08800000000000001</v>
+        <v>0.374</v>
       </c>
       <c r="G5">
-        <v>0.4993593850096092</v>
+        <v>0.1550737729599518</v>
       </c>
       <c r="H5">
-        <v>0.4993593850096092</v>
+        <v>0.1550737729599518</v>
       </c>
       <c r="I5">
-        <v>0.4972545071840395</v>
+        <v>0.09725986148750375</v>
       </c>
       <c r="J5">
-        <v>0.3524842076241293</v>
+        <v>0.09725986148750375</v>
       </c>
       <c r="K5">
-        <v>86.7</v>
+        <v>17.2</v>
       </c>
       <c r="L5">
-        <v>0.03967237119062872</v>
+        <v>0.05179162902740138</v>
       </c>
       <c r="M5">
-        <v>109.44</v>
+        <v>-0</v>
       </c>
       <c r="N5">
-        <v>0.04304424778761062</v>
+        <v>-0</v>
       </c>
       <c r="O5">
-        <v>1.262283737024221</v>
+        <v>-0</v>
       </c>
       <c r="P5">
-        <v>99.7</v>
+        <v>-0</v>
       </c>
       <c r="Q5">
-        <v>0.0392133726647001</v>
+        <v>-0</v>
       </c>
       <c r="R5">
-        <v>1.149942329873126</v>
+        <v>-0</v>
       </c>
       <c r="S5">
-        <v>9.739999999999995</v>
-      </c>
-      <c r="T5">
-        <v>0.08899853801169585</v>
+        <v>0</v>
       </c>
       <c r="U5">
-        <v>382.4</v>
+        <v>33.9</v>
       </c>
       <c r="V5">
-        <v>0.1504031465093412</v>
+        <v>0.1275395033860045</v>
       </c>
       <c r="W5">
-        <v>0.0333423066569242</v>
+        <v>0.1453930684699915</v>
       </c>
       <c r="X5">
-        <v>0.07046262752305171</v>
+        <v>0.05674402815701542</v>
       </c>
       <c r="Y5">
-        <v>-0.03712032086612752</v>
+        <v>0.08864904031297612</v>
       </c>
       <c r="Z5">
-        <v>0.3646344312076618</v>
+        <v>3.221456979338443</v>
       </c>
       <c r="AA5">
-        <v>0.1285278785567077</v>
+        <v>0.3133184595984091</v>
       </c>
       <c r="AB5">
-        <v>0.04992379000309694</v>
+        <v>0.05542354492376116</v>
       </c>
       <c r="AC5">
-        <v>0.07860408855361078</v>
+        <v>0.257894914674648</v>
       </c>
       <c r="AD5">
-        <v>5000.1</v>
+        <v>21</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>5000.1</v>
+        <v>21</v>
       </c>
       <c r="AG5">
-        <v>4617.700000000001</v>
+        <v>-12.9</v>
       </c>
       <c r="AH5">
-        <v>0.662914644817437</v>
+        <v>0.07322175732217573</v>
       </c>
       <c r="AI5">
-        <v>0.6585751353344836</v>
+        <v>0.131578947368421</v>
       </c>
       <c r="AJ5">
-        <v>0.6449121532918075</v>
+        <v>-0.05100830367734282</v>
       </c>
       <c r="AK5">
-        <v>0.6404665806737958</v>
+        <v>-0.1026252983293556</v>
       </c>
       <c r="AL5">
-        <v>645.6</v>
+        <v>3.31</v>
       </c>
       <c r="AM5">
-        <v>645.6</v>
+        <v>3.31</v>
       </c>
       <c r="AN5">
-        <v>4.581783194355356</v>
+        <v>0.4077669902912621</v>
       </c>
       <c r="AO5">
-        <v>1.683240396530359</v>
+        <v>9.758308157099696</v>
       </c>
       <c r="AP5">
-        <v>4.23137542380647</v>
+        <v>-0.2504854368932038</v>
       </c>
       <c r="AQ5">
-        <v>1.683240396530359</v>
+        <v>9.758308157099696</v>
       </c>
     </row>
     <row r="6">
@@ -1103,7 +1118,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>AMP Limited (ASX:AMP)</t>
+          <t>Helia Group Limited (ASX:HLI)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1112,121 +1127,121 @@
         </is>
       </c>
       <c r="D6">
-        <v>-0.00882</v>
-      </c>
-      <c r="F6">
-        <v>0.134</v>
+        <v>0.0222</v>
+      </c>
+      <c r="E6">
+        <v>0.13</v>
       </c>
       <c r="G6">
-        <v>0.4295685894328648</v>
+        <v>1.011455108359133</v>
       </c>
       <c r="H6">
-        <v>0.4295685894328648</v>
+        <v>1.011455108359133</v>
       </c>
       <c r="I6">
-        <v>0.4899660688317983</v>
+        <v>0.8315789473684211</v>
       </c>
       <c r="J6">
-        <v>0.4899660688317983</v>
+        <v>0.5792457444727059</v>
       </c>
       <c r="K6">
-        <v>71.40000000000001</v>
+        <v>149.9</v>
       </c>
       <c r="L6">
-        <v>0.03460979156568105</v>
+        <v>0.4640866873065015</v>
       </c>
       <c r="M6">
-        <v>238.9</v>
+        <v>122.5</v>
       </c>
       <c r="N6">
-        <v>0.0961755233494364</v>
+        <v>0.1608878381928027</v>
       </c>
       <c r="O6">
-        <v>3.34593837535014</v>
+        <v>0.8172114743162108</v>
       </c>
       <c r="P6">
-        <v>83.40000000000001</v>
+        <v>57</v>
       </c>
       <c r="Q6">
-        <v>0.03357487922705314</v>
+        <v>0.07486209613869188</v>
       </c>
       <c r="R6">
-        <v>1.168067226890756</v>
+        <v>0.3802535023348899</v>
       </c>
       <c r="S6">
-        <v>155.5</v>
+        <v>65.5</v>
       </c>
       <c r="T6">
-        <v>0.6508999581414818</v>
+        <v>0.5346938775510204</v>
       </c>
       <c r="U6">
-        <v>874</v>
+        <v>23.4</v>
       </c>
       <c r="V6">
-        <v>0.3518518518518519</v>
+        <v>0.03073286052009456</v>
       </c>
       <c r="W6">
-        <v>0.0266995737042854</v>
+        <v>0.2024581307401405</v>
       </c>
       <c r="X6">
-        <v>0.1103829639604653</v>
+        <v>0.05742233195347055</v>
       </c>
       <c r="Y6">
-        <v>-0.08368339025617992</v>
+        <v>0.1450357987866699</v>
       </c>
       <c r="Z6">
-        <v>0.09668333512984061</v>
+        <v>0.3841442384310741</v>
       </c>
       <c r="AA6">
-        <v>0.04737155363511531</v>
+        <v>0.2225139153749082</v>
       </c>
       <c r="AB6">
-        <v>0.0487229395761123</v>
+        <v>0.0546700868705864</v>
       </c>
       <c r="AC6">
-        <v>-0.001351385940996992</v>
+        <v>0.1678438285043218</v>
       </c>
       <c r="AD6">
-        <v>18536.2</v>
+        <v>131.3</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>18536.2</v>
+        <v>131.3</v>
       </c>
       <c r="AG6">
-        <v>17662.2</v>
+        <v>107.9</v>
       </c>
       <c r="AH6">
-        <v>0.8818279559661659</v>
+        <v>0.1470818864120085</v>
       </c>
       <c r="AI6">
-        <v>0.8819664175021055</v>
+        <v>0.1564026206075045</v>
       </c>
       <c r="AJ6">
-        <v>0.8767013133990529</v>
+        <v>0.1241228574715288</v>
       </c>
       <c r="AK6">
-        <v>0.8768449428831002</v>
+        <v>0.1322141894375689</v>
       </c>
       <c r="AL6">
-        <v>872</v>
+        <v>55.6</v>
       </c>
       <c r="AM6">
-        <v>872</v>
+        <v>55.6</v>
       </c>
       <c r="AN6">
-        <v>18.14605971610377</v>
+        <v>0.4881040892193309</v>
       </c>
       <c r="AO6">
-        <v>1.159174311926605</v>
+        <v>4.830935251798562</v>
       </c>
       <c r="AP6">
-        <v>17.29045521292218</v>
+        <v>0.4011152416356877</v>
       </c>
       <c r="AQ6">
-        <v>1.159174311926605</v>
+        <v>4.830935251798562</v>
       </c>
     </row>
     <row r="7">
@@ -1237,121 +1252,3993 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>OFX Group Limited (ASX:OFX)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D7">
+        <v>0.129</v>
+      </c>
+      <c r="E7">
+        <v>0.0987</v>
+      </c>
+      <c r="G7">
+        <v>0.1808318264014467</v>
+      </c>
+      <c r="H7">
+        <v>0.1808318264014467</v>
+      </c>
+      <c r="I7">
+        <v>0.1597347799879446</v>
+      </c>
+      <c r="J7">
+        <v>0.1319264069264069</v>
+      </c>
+      <c r="K7">
+        <v>18.2</v>
+      </c>
+      <c r="L7">
+        <v>0.109704641350211</v>
+      </c>
+      <c r="M7">
+        <v>7.34</v>
+      </c>
+      <c r="N7">
+        <v>0.03554479418886199</v>
+      </c>
+      <c r="O7">
+        <v>0.4032967032967033</v>
+      </c>
+      <c r="P7">
+        <v>-0</v>
+      </c>
+      <c r="Q7">
+        <v>-0</v>
+      </c>
+      <c r="R7">
+        <v>-0</v>
+      </c>
+      <c r="S7">
+        <v>7.34</v>
+      </c>
+      <c r="T7">
+        <v>1</v>
+      </c>
+      <c r="U7">
+        <v>24.1</v>
+      </c>
+      <c r="V7">
+        <v>0.1167070217917676</v>
+      </c>
+      <c r="W7">
+        <v>0.1751684311838306</v>
+      </c>
+      <c r="X7">
+        <v>0.0572426941440629</v>
+      </c>
+      <c r="Y7">
+        <v>0.1179257370397677</v>
+      </c>
+      <c r="Z7">
+        <v>1.593659942363113</v>
+      </c>
+      <c r="AA7">
+        <v>0.2102458300585102</v>
+      </c>
+      <c r="AB7">
+        <v>0.05485768498206325</v>
+      </c>
+      <c r="AC7">
+        <v>0.1553881450764469</v>
+      </c>
+      <c r="AD7">
+        <v>30.5</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>30.5</v>
+      </c>
+      <c r="AG7">
+        <v>6.399999999999999</v>
+      </c>
+      <c r="AH7">
+        <v>0.1286919831223629</v>
+      </c>
+      <c r="AI7">
+        <v>0.2021206096752816</v>
+      </c>
+      <c r="AJ7">
+        <v>0.03006106153123531</v>
+      </c>
+      <c r="AK7">
+        <v>0.0504731861198738</v>
+      </c>
+      <c r="AL7">
+        <v>3.88</v>
+      </c>
+      <c r="AM7">
+        <v>3.88</v>
+      </c>
+      <c r="AN7">
+        <v>1.016666666666667</v>
+      </c>
+      <c r="AO7">
+        <v>6.829896907216495</v>
+      </c>
+      <c r="AP7">
+        <v>0.2133333333333333</v>
+      </c>
+      <c r="AQ7">
+        <v>6.829896907216495</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>N1 Holdings Limited (ASX:N1H)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D8">
+        <v>0.353</v>
+      </c>
+      <c r="G8">
+        <v>0.6991935483870968</v>
+      </c>
+      <c r="H8">
+        <v>0.6991935483870968</v>
+      </c>
+      <c r="I8">
+        <v>0.6967741935483871</v>
+      </c>
+      <c r="J8">
+        <v>0.6967741935483871</v>
+      </c>
+      <c r="K8">
+        <v>0.724</v>
+      </c>
+      <c r="L8">
+        <v>0.05838709677419354</v>
+      </c>
+      <c r="M8">
+        <v>0.1762</v>
+      </c>
+      <c r="N8">
+        <v>0.02694189602446483</v>
+      </c>
+      <c r="O8">
+        <v>0.2433701657458563</v>
+      </c>
+      <c r="P8">
+        <v>0.1762</v>
+      </c>
+      <c r="Q8">
+        <v>0.02694189602446483</v>
+      </c>
+      <c r="R8">
+        <v>0.2433701657458563</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>9.029999999999999</v>
+      </c>
+      <c r="V8">
+        <v>1.380733944954128</v>
+      </c>
+      <c r="W8">
+        <v>1.83756345177665</v>
+      </c>
+      <c r="X8">
+        <v>0.1362008690371165</v>
+      </c>
+      <c r="Y8">
+        <v>1.701362582739533</v>
+      </c>
+      <c r="Z8">
+        <v>0.2369849399892975</v>
+      </c>
+      <c r="AA8">
+        <v>0.1651249904441557</v>
+      </c>
+      <c r="AB8">
+        <v>0.04681770960710507</v>
+      </c>
+      <c r="AC8">
+        <v>0.1183072808370506</v>
+      </c>
+      <c r="AD8">
+        <v>72.09999999999999</v>
+      </c>
+      <c r="AE8">
+        <v>0</v>
+      </c>
+      <c r="AF8">
+        <v>72.09999999999999</v>
+      </c>
+      <c r="AG8">
+        <v>63.06999999999999</v>
+      </c>
+      <c r="AH8">
+        <v>0.9168362156663274</v>
+      </c>
+      <c r="AI8">
+        <v>0.9845691656424963</v>
+      </c>
+      <c r="AJ8">
+        <v>0.9060479816118373</v>
+      </c>
+      <c r="AK8">
+        <v>0.982398753894081</v>
+      </c>
+      <c r="AL8">
+        <v>8.050000000000001</v>
+      </c>
+      <c r="AM8">
+        <v>8.050000000000001</v>
+      </c>
+      <c r="AN8">
+        <v>8.316032295271048</v>
+      </c>
+      <c r="AO8">
+        <v>1.073291925465838</v>
+      </c>
+      <c r="AP8">
+        <v>7.274509803921568</v>
+      </c>
+      <c r="AQ8">
+        <v>1.073291925465838</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Challenger Limited (ASX:CGF)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D9">
+        <v>-0.00028</v>
+      </c>
+      <c r="E9">
+        <v>-0.158</v>
+      </c>
+      <c r="F9">
+        <v>0.08800000000000001</v>
+      </c>
+      <c r="G9">
+        <v>0.4993593850096092</v>
+      </c>
+      <c r="H9">
+        <v>0.4993593850096092</v>
+      </c>
+      <c r="I9">
+        <v>0.4972545071840395</v>
+      </c>
+      <c r="J9">
+        <v>0.3524842076241293</v>
+      </c>
+      <c r="K9">
+        <v>86.7</v>
+      </c>
+      <c r="L9">
+        <v>0.03967237119062872</v>
+      </c>
+      <c r="M9">
+        <v>109.44</v>
+      </c>
+      <c r="N9">
+        <v>0.04304424778761062</v>
+      </c>
+      <c r="O9">
+        <v>1.262283737024221</v>
+      </c>
+      <c r="P9">
+        <v>99.7</v>
+      </c>
+      <c r="Q9">
+        <v>0.0392133726647001</v>
+      </c>
+      <c r="R9">
+        <v>1.149942329873126</v>
+      </c>
+      <c r="S9">
+        <v>9.739999999999995</v>
+      </c>
+      <c r="T9">
+        <v>0.08899853801169585</v>
+      </c>
+      <c r="U9">
+        <v>382.4</v>
+      </c>
+      <c r="V9">
+        <v>0.1504031465093412</v>
+      </c>
+      <c r="W9">
+        <v>0.0333423066569242</v>
+      </c>
+      <c r="X9">
+        <v>0.07044677164632171</v>
+      </c>
+      <c r="Y9">
+        <v>-0.03710446498939751</v>
+      </c>
+      <c r="Z9">
+        <v>0.3646344312076618</v>
+      </c>
+      <c r="AA9">
+        <v>0.1285278785567077</v>
+      </c>
+      <c r="AB9">
+        <v>0.04991844521925767</v>
+      </c>
+      <c r="AC9">
+        <v>0.07860943333745005</v>
+      </c>
+      <c r="AD9">
+        <v>5000.1</v>
+      </c>
+      <c r="AE9">
+        <v>0</v>
+      </c>
+      <c r="AF9">
+        <v>5000.1</v>
+      </c>
+      <c r="AG9">
+        <v>4617.700000000001</v>
+      </c>
+      <c r="AH9">
+        <v>0.662914644817437</v>
+      </c>
+      <c r="AI9">
+        <v>0.6585751353344836</v>
+      </c>
+      <c r="AJ9">
+        <v>0.6449121532918075</v>
+      </c>
+      <c r="AK9">
+        <v>0.6404665806737958</v>
+      </c>
+      <c r="AL9">
+        <v>645.6</v>
+      </c>
+      <c r="AM9">
+        <v>645.6</v>
+      </c>
+      <c r="AN9">
+        <v>4.581783194355356</v>
+      </c>
+      <c r="AO9">
+        <v>1.683240396530359</v>
+      </c>
+      <c r="AP9">
+        <v>4.23137542380647</v>
+      </c>
+      <c r="AQ9">
+        <v>1.683240396530359</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Findi Limited (ASX:FND)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D10">
+        <v>0.499</v>
+      </c>
+      <c r="G10">
+        <v>0.3145336225596529</v>
+      </c>
+      <c r="H10">
+        <v>0.3145336225596529</v>
+      </c>
+      <c r="I10">
+        <v>0.1464208242950109</v>
+      </c>
+      <c r="J10">
+        <v>0.1464208242950109</v>
+      </c>
+      <c r="K10">
+        <v>-0.202</v>
+      </c>
+      <c r="L10">
+        <v>-0.00438177874186551</v>
+      </c>
+      <c r="M10">
+        <v>0.661</v>
+      </c>
+      <c r="N10">
+        <v>0.004606271777003484</v>
+      </c>
+      <c r="O10">
+        <v>-3.272277227722772</v>
+      </c>
+      <c r="P10">
+        <v>-0</v>
+      </c>
+      <c r="Q10">
+        <v>-0</v>
+      </c>
+      <c r="R10">
+        <v>0</v>
+      </c>
+      <c r="S10">
+        <v>0.661</v>
+      </c>
+      <c r="T10">
+        <v>1</v>
+      </c>
+      <c r="U10">
+        <v>22.4</v>
+      </c>
+      <c r="V10">
+        <v>0.1560975609756098</v>
+      </c>
+      <c r="W10">
+        <v>-0.01328947368421053</v>
+      </c>
+      <c r="X10">
+        <v>0.0606778602913615</v>
+      </c>
+      <c r="Y10">
+        <v>-0.07396733397557204</v>
+      </c>
+      <c r="Z10">
+        <v>0.7995143947277142</v>
+      </c>
+      <c r="AA10">
+        <v>0.1170655567117586</v>
+      </c>
+      <c r="AB10">
+        <v>0.05462248474553041</v>
+      </c>
+      <c r="AC10">
+        <v>0.06244307196622818</v>
+      </c>
+      <c r="AD10">
+        <v>89.09999999999999</v>
+      </c>
+      <c r="AE10">
+        <v>0</v>
+      </c>
+      <c r="AF10">
+        <v>89.09999999999999</v>
+      </c>
+      <c r="AG10">
+        <v>66.69999999999999</v>
+      </c>
+      <c r="AH10">
+        <v>0.383061049011178</v>
+      </c>
+      <c r="AI10">
+        <v>0.7991031390134529</v>
+      </c>
+      <c r="AJ10">
+        <v>0.3173168411037107</v>
+      </c>
+      <c r="AK10">
+        <v>0.7485970819304152</v>
+      </c>
+      <c r="AL10">
+        <v>10.3</v>
+      </c>
+      <c r="AM10">
+        <v>9.260000000000002</v>
+      </c>
+      <c r="AN10">
+        <v>6.274647887323944</v>
+      </c>
+      <c r="AO10">
+        <v>0.6553398058252426</v>
+      </c>
+      <c r="AP10">
+        <v>4.697183098591549</v>
+      </c>
+      <c r="AQ10">
+        <v>0.7289416846652267</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Solvar Limited (ASX:SVR)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D11">
+        <v>0.187</v>
+      </c>
+      <c r="E11">
+        <v>-0.0969</v>
+      </c>
+      <c r="F11">
+        <v>0.329</v>
+      </c>
+      <c r="G11">
+        <v>0.5859819569743234</v>
+      </c>
+      <c r="H11">
+        <v>0.5523941707147814</v>
+      </c>
+      <c r="I11">
+        <v>0.5475364330326163</v>
+      </c>
+      <c r="J11">
+        <v>0.3356250351670199</v>
+      </c>
+      <c r="K11">
+        <v>11.4</v>
+      </c>
+      <c r="L11">
+        <v>0.0791117279666898</v>
+      </c>
+      <c r="M11">
+        <v>19.19</v>
+      </c>
+      <c r="N11">
+        <v>0.102565473009086</v>
+      </c>
+      <c r="O11">
+        <v>1.683333333333333</v>
+      </c>
+      <c r="P11">
+        <v>17.4</v>
+      </c>
+      <c r="Q11">
+        <v>0.09299839657936931</v>
+      </c>
+      <c r="R11">
+        <v>1.526315789473684</v>
+      </c>
+      <c r="S11">
+        <v>1.789999999999999</v>
+      </c>
+      <c r="T11">
+        <v>0.0932777488275143</v>
+      </c>
+      <c r="U11">
+        <v>102</v>
+      </c>
+      <c r="V11">
+        <v>0.5451630144307857</v>
+      </c>
+      <c r="W11">
+        <v>0.0454183266932271</v>
+      </c>
+      <c r="X11">
+        <v>0.07255542297928816</v>
+      </c>
+      <c r="Y11">
+        <v>-0.02713709628606106</v>
+      </c>
+      <c r="Z11">
+        <v>0.2631002373562169</v>
+      </c>
+      <c r="AA11">
+        <v>0.08830302641513159</v>
+      </c>
+      <c r="AB11">
+        <v>0.04910133350742503</v>
+      </c>
+      <c r="AC11">
+        <v>0.03920169290770656</v>
+      </c>
+      <c r="AD11">
+        <v>422.3</v>
+      </c>
+      <c r="AE11">
+        <v>0</v>
+      </c>
+      <c r="AF11">
+        <v>422.3</v>
+      </c>
+      <c r="AG11">
+        <v>320.3</v>
+      </c>
+      <c r="AH11">
+        <v>0.6929766983918609</v>
+      </c>
+      <c r="AI11">
+        <v>0.6337985892240733</v>
+      </c>
+      <c r="AJ11">
+        <v>0.6312573906188412</v>
+      </c>
+      <c r="AK11">
+        <v>0.5676058833953571</v>
+      </c>
+      <c r="AL11">
+        <v>49.9</v>
+      </c>
+      <c r="AM11">
+        <v>49.9</v>
+      </c>
+      <c r="AN11">
+        <v>5.305276381909549</v>
+      </c>
+      <c r="AO11">
+        <v>1.581162324649299</v>
+      </c>
+      <c r="AP11">
+        <v>4.023869346733669</v>
+      </c>
+      <c r="AQ11">
+        <v>1.581162324649299</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>FleetPartners Group Limited (ASX:FPR)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D12">
+        <v>0.0143</v>
+      </c>
+      <c r="G12">
+        <v>0.4258284415830335</v>
+      </c>
+      <c r="H12">
+        <v>0.4154516190115508</v>
+      </c>
+      <c r="I12">
+        <v>0.1539481158871426</v>
+      </c>
+      <c r="J12">
+        <v>0.1085273924008577</v>
+      </c>
+      <c r="K12">
+        <v>54</v>
+      </c>
+      <c r="L12">
+        <v>0.1022533611058512</v>
+      </c>
+      <c r="M12">
+        <v>45</v>
+      </c>
+      <c r="N12">
+        <v>0.1175241577435362</v>
+      </c>
+      <c r="O12">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="P12">
+        <v>-0</v>
+      </c>
+      <c r="Q12">
+        <v>-0</v>
+      </c>
+      <c r="R12">
+        <v>-0</v>
+      </c>
+      <c r="S12">
+        <v>45</v>
+      </c>
+      <c r="T12">
+        <v>1</v>
+      </c>
+      <c r="U12">
+        <v>63.3</v>
+      </c>
+      <c r="V12">
+        <v>0.1653173152259076</v>
+      </c>
+      <c r="W12">
+        <v>0.1316431009263774</v>
+      </c>
+      <c r="X12">
+        <v>0.07809450478647131</v>
+      </c>
+      <c r="Y12">
+        <v>0.05354859613990606</v>
+      </c>
+      <c r="Z12">
+        <v>0.5488463936811474</v>
+      </c>
+      <c r="AA12">
+        <v>0.0595648679348295</v>
+      </c>
+      <c r="AB12">
+        <v>0.04666630928522046</v>
+      </c>
+      <c r="AC12">
+        <v>0.01289855864960904</v>
+      </c>
+      <c r="AD12">
+        <v>1156.4</v>
+      </c>
+      <c r="AE12">
+        <v>0</v>
+      </c>
+      <c r="AF12">
+        <v>1156.4</v>
+      </c>
+      <c r="AG12">
+        <v>1093.1</v>
+      </c>
+      <c r="AH12">
+        <v>0.7512505684402001</v>
+      </c>
+      <c r="AI12">
+        <v>0.7280740414279419</v>
+      </c>
+      <c r="AJ12">
+        <v>0.7405826558265584</v>
+      </c>
+      <c r="AK12">
+        <v>0.7167868852459017</v>
+      </c>
+      <c r="AL12">
+        <v>4.65</v>
+      </c>
+      <c r="AM12">
+        <v>4.65</v>
+      </c>
+      <c r="AN12">
+        <v>5.27073837739289</v>
+      </c>
+      <c r="AO12">
+        <v>17.48387096774193</v>
+      </c>
+      <c r="AP12">
+        <v>4.982224247948952</v>
+      </c>
+      <c r="AQ12">
+        <v>17.48387096774193</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Earlypay Limited (ASX:EPY)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D13">
+        <v>0.0273</v>
+      </c>
+      <c r="E13">
+        <v>-0.218</v>
+      </c>
+      <c r="F13">
+        <v>0.359</v>
+      </c>
+      <c r="G13">
+        <v>0.4595604395604395</v>
+      </c>
+      <c r="H13">
+        <v>0.445054945054945</v>
+      </c>
+      <c r="I13">
+        <v>0.4230769230769231</v>
+      </c>
+      <c r="J13">
+        <v>0.2936333878887071</v>
+      </c>
+      <c r="K13">
+        <v>1.63</v>
+      </c>
+      <c r="L13">
+        <v>0.04478021978021978</v>
+      </c>
+      <c r="M13">
+        <v>3.1822</v>
+      </c>
+      <c r="N13">
+        <v>0.09442729970326408</v>
+      </c>
+      <c r="O13">
+        <v>1.952269938650307</v>
+      </c>
+      <c r="P13">
+        <v>0.2722</v>
+      </c>
+      <c r="Q13">
+        <v>0.008077151335311571</v>
+      </c>
+      <c r="R13">
+        <v>0.1669938650306748</v>
+      </c>
+      <c r="S13">
+        <v>2.91</v>
+      </c>
+      <c r="T13">
+        <v>0.9144616931682484</v>
+      </c>
+      <c r="U13">
+        <v>26.8</v>
+      </c>
+      <c r="V13">
+        <v>0.7952522255192878</v>
+      </c>
+      <c r="W13">
+        <v>0.03360824742268041</v>
+      </c>
+      <c r="X13">
+        <v>0.09018385447063559</v>
+      </c>
+      <c r="Y13">
+        <v>-0.05657560704795518</v>
+      </c>
+      <c r="Z13">
+        <v>0.2007722007722008</v>
+      </c>
+      <c r="AA13">
+        <v>0.05895342150661299</v>
+      </c>
+      <c r="AB13">
+        <v>0.04776359548883309</v>
+      </c>
+      <c r="AC13">
+        <v>0.0111898260177799</v>
+      </c>
+      <c r="AD13">
+        <v>157.9</v>
+      </c>
+      <c r="AE13">
+        <v>0</v>
+      </c>
+      <c r="AF13">
+        <v>157.9</v>
+      </c>
+      <c r="AG13">
+        <v>131.1</v>
+      </c>
+      <c r="AH13">
+        <v>0.8241127348643006</v>
+      </c>
+      <c r="AI13">
+        <v>0.7653902084343189</v>
+      </c>
+      <c r="AJ13">
+        <v>0.795509708737864</v>
+      </c>
+      <c r="AK13">
+        <v>0.7303621169916434</v>
+      </c>
+      <c r="AL13">
+        <v>13</v>
+      </c>
+      <c r="AM13">
+        <v>13</v>
+      </c>
+      <c r="AN13">
+        <v>9.746913580246915</v>
+      </c>
+      <c r="AO13">
+        <v>1.184615384615385</v>
+      </c>
+      <c r="AP13">
+        <v>8.092592592592593</v>
+      </c>
+      <c r="AQ13">
+        <v>1.184615384615385</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Zip Co Limited (ASX:ZIP)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D14">
+        <v>0.602</v>
+      </c>
+      <c r="F14">
+        <v>1.854</v>
+      </c>
+      <c r="G14">
+        <v>0.4541529960283198</v>
+      </c>
+      <c r="H14">
+        <v>0.4541529960283198</v>
+      </c>
+      <c r="I14">
+        <v>0.4073562424451735</v>
+      </c>
+      <c r="J14">
+        <v>0.2036781212225868</v>
+      </c>
+      <c r="K14">
+        <v>2.44</v>
+      </c>
+      <c r="L14">
+        <v>0.004213434639958556</v>
+      </c>
+      <c r="M14">
+        <v>-0</v>
+      </c>
+      <c r="N14">
+        <v>-0</v>
+      </c>
+      <c r="O14">
+        <v>-0</v>
+      </c>
+      <c r="P14">
+        <v>-0</v>
+      </c>
+      <c r="Q14">
+        <v>-0</v>
+      </c>
+      <c r="R14">
+        <v>-0</v>
+      </c>
+      <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="U14">
+        <v>81</v>
+      </c>
+      <c r="V14">
+        <v>0.03386853988961365</v>
+      </c>
+      <c r="W14">
+        <v>0.01564102564102564</v>
+      </c>
+      <c r="X14">
+        <v>0.06107197439495609</v>
+      </c>
+      <c r="Y14">
+        <v>-0.04543094875393044</v>
+      </c>
+      <c r="Z14">
+        <v>0.3099775184669736</v>
+      </c>
+      <c r="AA14">
+        <v>0.06313563858259287</v>
+      </c>
+      <c r="AB14">
+        <v>0.05276421275034369</v>
+      </c>
+      <c r="AC14">
+        <v>0.01037142583224918</v>
+      </c>
+      <c r="AD14">
+        <v>1614.8</v>
+      </c>
+      <c r="AE14">
+        <v>0</v>
+      </c>
+      <c r="AF14">
+        <v>1614.8</v>
+      </c>
+      <c r="AG14">
+        <v>1533.8</v>
+      </c>
+      <c r="AH14">
+        <v>0.4030551118210863</v>
+      </c>
+      <c r="AI14">
+        <v>0.8586164725899932</v>
+      </c>
+      <c r="AJ14">
+        <v>0.3907372497070363</v>
+      </c>
+      <c r="AK14">
+        <v>0.8522531533033284</v>
+      </c>
+      <c r="AL14">
+        <v>144.5</v>
+      </c>
+      <c r="AM14">
+        <v>144.5</v>
+      </c>
+      <c r="AN14">
+        <v>6.139923954372623</v>
+      </c>
+      <c r="AO14">
+        <v>1.632525951557094</v>
+      </c>
+      <c r="AP14">
+        <v>5.831939163498099</v>
+      </c>
+      <c r="AQ14">
+        <v>1.632525951557094</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>AMP Limited (ASX:AMP)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D15">
+        <v>-0.00882</v>
+      </c>
+      <c r="F15">
+        <v>0.134</v>
+      </c>
+      <c r="G15">
+        <v>0.4295685894328648</v>
+      </c>
+      <c r="H15">
+        <v>0.4295685894328648</v>
+      </c>
+      <c r="I15">
+        <v>0.4899660688317983</v>
+      </c>
+      <c r="J15">
+        <v>0.4899660688317983</v>
+      </c>
+      <c r="K15">
+        <v>71.40000000000001</v>
+      </c>
+      <c r="L15">
+        <v>0.03460979156568105</v>
+      </c>
+      <c r="M15">
+        <v>238.9</v>
+      </c>
+      <c r="N15">
+        <v>0.0961755233494364</v>
+      </c>
+      <c r="O15">
+        <v>3.34593837535014</v>
+      </c>
+      <c r="P15">
+        <v>83.40000000000001</v>
+      </c>
+      <c r="Q15">
+        <v>0.03357487922705314</v>
+      </c>
+      <c r="R15">
+        <v>1.168067226890756</v>
+      </c>
+      <c r="S15">
+        <v>155.5</v>
+      </c>
+      <c r="T15">
+        <v>0.6508999581414818</v>
+      </c>
+      <c r="U15">
+        <v>874</v>
+      </c>
+      <c r="V15">
+        <v>0.3518518518518519</v>
+      </c>
+      <c r="W15">
+        <v>0.0266995737042854</v>
+      </c>
+      <c r="X15">
+        <v>0.1103414428567444</v>
+      </c>
+      <c r="Y15">
+        <v>-0.08364186915245896</v>
+      </c>
+      <c r="Z15">
+        <v>0.09668333512984061</v>
+      </c>
+      <c r="AA15">
+        <v>0.04737155363511531</v>
+      </c>
+      <c r="AB15">
+        <v>0.04871803294241506</v>
+      </c>
+      <c r="AC15">
+        <v>-0.001346479307299746</v>
+      </c>
+      <c r="AD15">
+        <v>18536.2</v>
+      </c>
+      <c r="AE15">
+        <v>0</v>
+      </c>
+      <c r="AF15">
+        <v>18536.2</v>
+      </c>
+      <c r="AG15">
+        <v>17662.2</v>
+      </c>
+      <c r="AH15">
+        <v>0.8818279559661659</v>
+      </c>
+      <c r="AI15">
+        <v>0.8819664175021055</v>
+      </c>
+      <c r="AJ15">
+        <v>0.8767013133990529</v>
+      </c>
+      <c r="AK15">
+        <v>0.8768449428831002</v>
+      </c>
+      <c r="AL15">
+        <v>872</v>
+      </c>
+      <c r="AM15">
+        <v>872</v>
+      </c>
+      <c r="AN15">
+        <v>18.14605971610377</v>
+      </c>
+      <c r="AO15">
+        <v>1.159174311926605</v>
+      </c>
+      <c r="AP15">
+        <v>17.29045521292218</v>
+      </c>
+      <c r="AQ15">
+        <v>1.159174311926605</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Imperial Pacific Limited (ASX:IPC)</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D16">
+        <v>0.453</v>
+      </c>
+      <c r="G16">
+        <v>0.5878787878787879</v>
+      </c>
+      <c r="H16">
+        <v>0.5878787878787879</v>
+      </c>
+      <c r="I16">
+        <v>0.5272727272727273</v>
+      </c>
+      <c r="J16">
+        <v>0.5272727272727273</v>
+      </c>
+      <c r="K16">
+        <v>0.257</v>
+      </c>
+      <c r="L16">
+        <v>0.5191919191919192</v>
+      </c>
+      <c r="M16">
+        <v>0.216</v>
+      </c>
+      <c r="N16">
+        <v>0.03963302752293578</v>
+      </c>
+      <c r="O16">
+        <v>0.8404669260700389</v>
+      </c>
+      <c r="P16">
+        <v>0.216</v>
+      </c>
+      <c r="Q16">
+        <v>0.03963302752293578</v>
+      </c>
+      <c r="R16">
+        <v>0.8404669260700389</v>
+      </c>
+      <c r="S16">
+        <v>0</v>
+      </c>
+      <c r="T16">
+        <v>0</v>
+      </c>
+      <c r="U16">
+        <v>0.016</v>
+      </c>
+      <c r="V16">
+        <v>0.002935779816513761</v>
+      </c>
+      <c r="W16">
+        <v>0.05309917355371901</v>
+      </c>
+      <c r="X16">
+        <v>0.05621178253170442</v>
+      </c>
+      <c r="Y16">
+        <v>-0.003112608977985411</v>
+      </c>
+      <c r="Z16">
+        <v>0.1012684124386252</v>
+      </c>
+      <c r="AA16">
+        <v>0.05339607201309329</v>
+      </c>
+      <c r="AB16">
+        <v>0.0561226919901093</v>
+      </c>
+      <c r="AC16">
+        <v>-0.002726619977016009</v>
+      </c>
+      <c r="AD16">
+        <v>0.031</v>
+      </c>
+      <c r="AE16">
+        <v>0</v>
+      </c>
+      <c r="AF16">
+        <v>0.031</v>
+      </c>
+      <c r="AG16">
+        <v>0.015</v>
+      </c>
+      <c r="AH16">
+        <v>0.005655902207626346</v>
+      </c>
+      <c r="AI16">
+        <v>0.004827908425478897</v>
+      </c>
+      <c r="AJ16">
+        <v>0.002744739249771272</v>
+      </c>
+      <c r="AK16">
+        <v>0.00234192037470726</v>
+      </c>
+      <c r="AL16">
+        <v>0.003</v>
+      </c>
+      <c r="AM16">
+        <v>0.003</v>
+      </c>
+      <c r="AN16">
+        <v>0.1065292096219931</v>
+      </c>
+      <c r="AO16">
+        <v>87</v>
+      </c>
+      <c r="AP16">
+        <v>0.05154639175257732</v>
+      </c>
+      <c r="AQ16">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Resimac Group Limited (ASX:RMC)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D17">
+        <v>0.00419</v>
+      </c>
+      <c r="E17">
+        <v>-0.0602</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>23.1</v>
+      </c>
+      <c r="L17">
+        <v>0.2349949135300102</v>
+      </c>
+      <c r="M17">
+        <v>21.084</v>
+      </c>
+      <c r="N17">
+        <v>0.08734051367025684</v>
+      </c>
+      <c r="O17">
+        <v>0.9127272727272728</v>
+      </c>
+      <c r="P17">
+        <v>20.1</v>
+      </c>
+      <c r="Q17">
+        <v>0.08326429163214583</v>
+      </c>
+      <c r="R17">
+        <v>0.8701298701298701</v>
+      </c>
+      <c r="S17">
+        <v>0.9840000000000018</v>
+      </c>
+      <c r="T17">
+        <v>0.04667046101309057</v>
+      </c>
+      <c r="U17">
+        <v>581.1</v>
+      </c>
+      <c r="V17">
+        <v>2.407207953603977</v>
+      </c>
+      <c r="W17">
+        <v>0.08357452966714907</v>
+      </c>
+      <c r="X17">
+        <v>0.3482733658617924</v>
+      </c>
+      <c r="Y17">
+        <v>-0.2646988361946433</v>
+      </c>
+      <c r="Z17">
+        <v>0.01071634924614898</v>
+      </c>
+      <c r="AA17">
+        <v>0</v>
+      </c>
+      <c r="AB17">
+        <v>0.04621671493626622</v>
+      </c>
+      <c r="AC17">
+        <v>-0.04621671493626622</v>
+      </c>
+      <c r="AD17">
+        <v>9713.5</v>
+      </c>
+      <c r="AE17">
+        <v>0</v>
+      </c>
+      <c r="AF17">
+        <v>9713.5</v>
+      </c>
+      <c r="AG17">
+        <v>9132.4</v>
+      </c>
+      <c r="AH17">
+        <v>0.9757506353654984</v>
+      </c>
+      <c r="AI17">
+        <v>0.9721958103550089</v>
+      </c>
+      <c r="AJ17">
+        <v>0.9742473703300689</v>
+      </c>
+      <c r="AK17">
+        <v>0.9704788421075005</v>
+      </c>
+      <c r="AL17">
+        <v>0</v>
+      </c>
+      <c r="AM17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Pepper Money Limited (ASX:PPM)</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="G18">
+        <v>0.05884586180713744</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>69.7</v>
+      </c>
+      <c r="L18">
+        <v>0.2646165527714503</v>
+      </c>
+      <c r="M18">
+        <v>25</v>
+      </c>
+      <c r="N18">
+        <v>0.06535947712418301</v>
+      </c>
+      <c r="O18">
+        <v>0.3586800573888091</v>
+      </c>
+      <c r="P18">
+        <v>25</v>
+      </c>
+      <c r="Q18">
+        <v>0.06535947712418301</v>
+      </c>
+      <c r="R18">
+        <v>0.3586800573888091</v>
+      </c>
+      <c r="S18">
+        <v>0</v>
+      </c>
+      <c r="T18">
+        <v>0</v>
+      </c>
+      <c r="U18">
+        <v>738.1</v>
+      </c>
+      <c r="V18">
+        <v>1.929673202614379</v>
+      </c>
+      <c r="W18">
+        <v>0.1249551810684833</v>
+      </c>
+      <c r="X18">
+        <v>0.2779268313923255</v>
+      </c>
+      <c r="Y18">
+        <v>-0.1529716503238421</v>
+      </c>
+      <c r="Z18">
+        <v>0.02165263711692753</v>
+      </c>
+      <c r="AA18">
+        <v>0</v>
+      </c>
+      <c r="AB18">
+        <v>0.04629269976030204</v>
+      </c>
+      <c r="AC18">
+        <v>-0.04629269976030204</v>
+      </c>
+      <c r="AD18">
+        <v>11684.5</v>
+      </c>
+      <c r="AE18">
+        <v>0</v>
+      </c>
+      <c r="AF18">
+        <v>11684.5</v>
+      </c>
+      <c r="AG18">
+        <v>10946.4</v>
+      </c>
+      <c r="AH18">
+        <v>0.9683019806082704</v>
+      </c>
+      <c r="AI18">
+        <v>0.953222003768998</v>
+      </c>
+      <c r="AJ18">
+        <v>0.9662367926277043</v>
+      </c>
+      <c r="AK18">
+        <v>0.9502248302921926</v>
+      </c>
+      <c r="AL18">
+        <v>0</v>
+      </c>
+      <c r="AM18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Humm Group Limited (ASX:HUM)</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D19">
+        <v>-0.0288</v>
+      </c>
+      <c r="E19">
+        <v>-0.351</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>4.74</v>
+      </c>
+      <c r="L19">
+        <v>0.02915129151291513</v>
+      </c>
+      <c r="M19">
+        <v>19.37</v>
+      </c>
+      <c r="N19">
+        <v>0.09375605033881897</v>
+      </c>
+      <c r="O19">
+        <v>4.086497890295358</v>
+      </c>
+      <c r="P19">
+        <v>8.67</v>
+      </c>
+      <c r="Q19">
+        <v>0.04196515004840271</v>
+      </c>
+      <c r="R19">
+        <v>1.829113924050633</v>
+      </c>
+      <c r="S19">
+        <v>10.7</v>
+      </c>
+      <c r="T19">
+        <v>0.5524006195147134</v>
+      </c>
+      <c r="U19">
+        <v>83.5</v>
+      </c>
+      <c r="V19">
+        <v>0.404162633107454</v>
+      </c>
+      <c r="W19">
+        <v>0.01137508999280058</v>
+      </c>
+      <c r="X19">
+        <v>0.166785880867027</v>
+      </c>
+      <c r="Y19">
+        <v>-0.1554107908742264</v>
+      </c>
+      <c r="Z19">
+        <v>0.05481022045439223</v>
+      </c>
+      <c r="AA19">
+        <v>0</v>
+      </c>
+      <c r="AB19">
+        <v>0.04659758368471928</v>
+      </c>
+      <c r="AC19">
+        <v>-0.04659758368471928</v>
+      </c>
+      <c r="AD19">
+        <v>3148.1</v>
+      </c>
+      <c r="AE19">
+        <v>0</v>
+      </c>
+      <c r="AF19">
+        <v>3148.1</v>
+      </c>
+      <c r="AG19">
+        <v>3064.6</v>
+      </c>
+      <c r="AH19">
+        <v>0.938414761379557</v>
+      </c>
+      <c r="AI19">
+        <v>0.8907280083750673</v>
+      </c>
+      <c r="AJ19">
+        <v>0.9368427488383468</v>
+      </c>
+      <c r="AK19">
+        <v>0.8880839225686797</v>
+      </c>
+      <c r="AL19">
+        <v>0</v>
+      </c>
+      <c r="AM19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Australian Finance Group Limited (ASX:AFG)</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D20">
+        <v>0.108</v>
+      </c>
+      <c r="E20">
+        <v>-0.0259</v>
+      </c>
+      <c r="G20">
+        <v>0.001524688767659813</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <v>19.3</v>
+      </c>
+      <c r="L20">
+        <v>0.02699678276682053</v>
+      </c>
+      <c r="M20">
+        <v>14.6</v>
+      </c>
+      <c r="N20">
+        <v>0.05770750988142292</v>
+      </c>
+      <c r="O20">
+        <v>0.7564766839378237</v>
+      </c>
+      <c r="P20">
+        <v>14.6</v>
+      </c>
+      <c r="Q20">
+        <v>0.05770750988142292</v>
+      </c>
+      <c r="R20">
+        <v>0.7564766839378237</v>
+      </c>
+      <c r="S20">
+        <v>0</v>
+      </c>
+      <c r="T20">
+        <v>0</v>
+      </c>
+      <c r="U20">
+        <v>45</v>
+      </c>
+      <c r="V20">
+        <v>0.1778656126482213</v>
+      </c>
+      <c r="W20">
+        <v>0.1619127516778524</v>
+      </c>
+      <c r="X20">
+        <v>0.1438937761426813</v>
+      </c>
+      <c r="Y20">
+        <v>0.01801897553517109</v>
+      </c>
+      <c r="Z20">
+        <v>0.2296277262069187</v>
+      </c>
+      <c r="AA20">
+        <v>0</v>
+      </c>
+      <c r="AB20">
+        <v>0.04674899808600379</v>
+      </c>
+      <c r="AC20">
+        <v>-0.04674899808600379</v>
+      </c>
+      <c r="AD20">
+        <v>3057.3</v>
+      </c>
+      <c r="AE20">
+        <v>0</v>
+      </c>
+      <c r="AF20">
+        <v>3057.3</v>
+      </c>
+      <c r="AG20">
+        <v>3012.3</v>
+      </c>
+      <c r="AH20">
+        <v>0.9235718817025648</v>
+      </c>
+      <c r="AI20">
+        <v>0.9567816235839018</v>
+      </c>
+      <c r="AJ20">
+        <v>0.9225186047223839</v>
+      </c>
+      <c r="AK20">
+        <v>0.9561642965972575</v>
+      </c>
+      <c r="AL20">
+        <v>0</v>
+      </c>
+      <c r="AM20">
+        <v>-5.1</v>
+      </c>
+      <c r="AQ20">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Pioneer Credit Limited (ASX:PNC)</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D21">
+        <v>-0.136</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <v>-6.7</v>
+      </c>
+      <c r="L21">
+        <v>-0.3045454545454546</v>
+      </c>
+      <c r="M21">
+        <v>-0</v>
+      </c>
+      <c r="N21">
+        <v>-0</v>
+      </c>
+      <c r="O21">
+        <v>0</v>
+      </c>
+      <c r="P21">
+        <v>-0</v>
+      </c>
+      <c r="Q21">
+        <v>-0</v>
+      </c>
+      <c r="R21">
+        <v>0</v>
+      </c>
+      <c r="S21">
+        <v>0</v>
+      </c>
+      <c r="U21">
+        <v>2.77</v>
+      </c>
+      <c r="V21">
+        <v>0.05641547861507128</v>
+      </c>
+      <c r="W21">
+        <v>-0.2401433691756273</v>
+      </c>
+      <c r="X21">
+        <v>0.08525221968114258</v>
+      </c>
+      <c r="Y21">
+        <v>-0.3253955888567698</v>
+      </c>
+      <c r="Z21">
+        <v>0.1068999028182702</v>
+      </c>
+      <c r="AA21">
+        <v>0</v>
+      </c>
+      <c r="AB21">
+        <v>0.04800708293874736</v>
+      </c>
+      <c r="AC21">
+        <v>-0.04800708293874736</v>
+      </c>
+      <c r="AD21">
+        <v>196.7</v>
+      </c>
+      <c r="AE21">
+        <v>0</v>
+      </c>
+      <c r="AF21">
+        <v>196.7</v>
+      </c>
+      <c r="AG21">
+        <v>193.93</v>
+      </c>
+      <c r="AH21">
+        <v>0.8002441008950366</v>
+      </c>
+      <c r="AI21">
+        <v>0.8695844385499558</v>
+      </c>
+      <c r="AJ21">
+        <v>0.7979673291363206</v>
+      </c>
+      <c r="AK21">
+        <v>0.8679675961151143</v>
+      </c>
+      <c r="AL21">
+        <v>0</v>
+      </c>
+      <c r="AM21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Wisr Limited (ASX:WZR)</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D22">
+        <v>0.509</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>-5.47</v>
+      </c>
+      <c r="L22">
+        <v>-0.3772413793103448</v>
+      </c>
+      <c r="M22">
+        <v>-0</v>
+      </c>
+      <c r="N22">
+        <v>-0</v>
+      </c>
+      <c r="O22">
+        <v>0</v>
+      </c>
+      <c r="P22">
+        <v>-0</v>
+      </c>
+      <c r="Q22">
+        <v>-0</v>
+      </c>
+      <c r="R22">
+        <v>0</v>
+      </c>
+      <c r="S22">
+        <v>0</v>
+      </c>
+      <c r="U22">
+        <v>41.6</v>
+      </c>
+      <c r="V22">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="W22">
+        <v>-0.1207505518763797</v>
+      </c>
+      <c r="X22">
+        <v>0.2265058031053374</v>
+      </c>
+      <c r="Y22">
+        <v>-0.3472563549817171</v>
+      </c>
+      <c r="Z22">
+        <v>0.0230304955527319</v>
+      </c>
+      <c r="AA22">
+        <v>0</v>
+      </c>
+      <c r="AB22">
+        <v>0.04806479195175101</v>
+      </c>
+      <c r="AC22">
+        <v>-0.04806479195175101</v>
+      </c>
+      <c r="AD22">
+        <v>525.6</v>
+      </c>
+      <c r="AE22">
+        <v>0</v>
+      </c>
+      <c r="AF22">
+        <v>525.6</v>
+      </c>
+      <c r="AG22">
+        <v>484</v>
+      </c>
+      <c r="AH22">
+        <v>0.9591240875912409</v>
+      </c>
+      <c r="AI22">
+        <v>0.9426111908177905</v>
+      </c>
+      <c r="AJ22">
+        <v>0.9557661927330174</v>
+      </c>
+      <c r="AK22">
+        <v>0.937984496124031</v>
+      </c>
+      <c r="AL22">
+        <v>0</v>
+      </c>
+      <c r="AM22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>FSA Group Limited (ASX:FSA)</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D23">
+        <v>-0.0549</v>
+      </c>
+      <c r="E23">
+        <v>-0.126</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>4.9</v>
+      </c>
+      <c r="L23">
+        <v>0.1408045977011494</v>
+      </c>
+      <c r="M23">
+        <v>5.67</v>
+      </c>
+      <c r="N23">
+        <v>0.09371900826446281</v>
+      </c>
+      <c r="O23">
+        <v>1.157142857142857</v>
+      </c>
+      <c r="P23">
+        <v>5.67</v>
+      </c>
+      <c r="Q23">
+        <v>0.09371900826446281</v>
+      </c>
+      <c r="R23">
+        <v>1.157142857142857</v>
+      </c>
+      <c r="S23">
+        <v>0</v>
+      </c>
+      <c r="T23">
+        <v>0</v>
+      </c>
+      <c r="U23">
+        <v>3.57</v>
+      </c>
+      <c r="V23">
+        <v>0.05900826446280991</v>
+      </c>
+      <c r="W23">
+        <v>0.08361774744027305</v>
+      </c>
+      <c r="X23">
+        <v>0.1167050172090758</v>
+      </c>
+      <c r="Y23">
+        <v>-0.03308726976880273</v>
+      </c>
+      <c r="Z23">
+        <v>0.07910349373764007</v>
+      </c>
+      <c r="AA23">
+        <v>0</v>
+      </c>
+      <c r="AB23">
+        <v>0.04862428945336122</v>
+      </c>
+      <c r="AC23">
+        <v>-0.04862428945336122</v>
+      </c>
+      <c r="AD23">
+        <v>504.5</v>
+      </c>
+      <c r="AE23">
+        <v>0</v>
+      </c>
+      <c r="AF23">
+        <v>504.5</v>
+      </c>
+      <c r="AG23">
+        <v>500.93</v>
+      </c>
+      <c r="AH23">
+        <v>0.8929203539823009</v>
+      </c>
+      <c r="AI23">
+        <v>0.8829191459572979</v>
+      </c>
+      <c r="AJ23">
+        <v>0.8922394599504835</v>
+      </c>
+      <c r="AK23">
+        <v>0.8821830477431625</v>
+      </c>
+      <c r="AL23">
+        <v>0</v>
+      </c>
+      <c r="AM23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Latitude Group Holdings Limited (ASX:LFS)</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="F24">
+        <v>0.763</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>0</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24">
+        <v>-26.8</v>
+      </c>
+      <c r="L24">
+        <v>-0.09493446687920652</v>
+      </c>
+      <c r="M24">
+        <v>-0</v>
+      </c>
+      <c r="N24">
+        <v>-0</v>
+      </c>
+      <c r="O24">
+        <v>0</v>
+      </c>
+      <c r="P24">
+        <v>-0</v>
+      </c>
+      <c r="Q24">
+        <v>-0</v>
+      </c>
+      <c r="R24">
+        <v>0</v>
+      </c>
+      <c r="S24">
+        <v>0</v>
+      </c>
+      <c r="U24">
+        <v>146.5</v>
+      </c>
+      <c r="V24">
+        <v>0.1979997296932018</v>
+      </c>
+      <c r="W24">
+        <v>-0.03086846348767565</v>
+      </c>
+      <c r="X24">
+        <v>0.09478855049741546</v>
+      </c>
+      <c r="Y24">
+        <v>-0.1256570139850911</v>
+      </c>
+      <c r="Z24">
+        <v>0.06213955535989434</v>
+      </c>
+      <c r="AA24">
+        <v>0</v>
+      </c>
+      <c r="AB24">
+        <v>0.04905659848439643</v>
+      </c>
+      <c r="AC24">
+        <v>-0.04905659848439643</v>
+      </c>
+      <c r="AD24">
+        <v>3936.1</v>
+      </c>
+      <c r="AE24">
+        <v>0</v>
+      </c>
+      <c r="AF24">
+        <v>3936.1</v>
+      </c>
+      <c r="AG24">
+        <v>3789.6</v>
+      </c>
+      <c r="AH24">
+        <v>0.8417664670658682</v>
+      </c>
+      <c r="AI24">
+        <v>0.8275376335043311</v>
+      </c>
+      <c r="AJ24">
+        <v>0.8366486367148692</v>
+      </c>
+      <c r="AK24">
+        <v>0.8220568775895356</v>
+      </c>
+      <c r="AL24">
+        <v>0</v>
+      </c>
+      <c r="AM24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Butn Limited (ASX:BTN)</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>-8.23</v>
+      </c>
+      <c r="L25">
+        <v>-1.754797441364605</v>
+      </c>
+      <c r="M25">
+        <v>-0</v>
+      </c>
+      <c r="N25">
+        <v>-0</v>
+      </c>
+      <c r="O25">
+        <v>0</v>
+      </c>
+      <c r="P25">
+        <v>-0</v>
+      </c>
+      <c r="Q25">
+        <v>-0</v>
+      </c>
+      <c r="R25">
+        <v>0</v>
+      </c>
+      <c r="S25">
+        <v>0</v>
+      </c>
+      <c r="U25">
+        <v>8.91</v>
+      </c>
+      <c r="V25">
+        <v>0.724390243902439</v>
+      </c>
+      <c r="W25">
+        <v>-0.7913461538461538</v>
+      </c>
+      <c r="X25">
+        <v>0.08756862738490587</v>
+      </c>
+      <c r="Y25">
+        <v>-0.8789147812310597</v>
+      </c>
+      <c r="Z25">
+        <v>0.08759805752708257</v>
+      </c>
+      <c r="AA25">
+        <v>0</v>
+      </c>
+      <c r="AB25">
+        <v>0.04930635292876858</v>
+      </c>
+      <c r="AC25">
+        <v>-0.04930635292876858</v>
+      </c>
+      <c r="AD25">
+        <v>53.2</v>
+      </c>
+      <c r="AE25">
+        <v>0</v>
+      </c>
+      <c r="AF25">
+        <v>53.2</v>
+      </c>
+      <c r="AG25">
+        <v>44.29000000000001</v>
+      </c>
+      <c r="AH25">
+        <v>0.8122137404580153</v>
+      </c>
+      <c r="AI25">
+        <v>0.9076949326053575</v>
+      </c>
+      <c r="AJ25">
+        <v>0.7826471107969607</v>
+      </c>
+      <c r="AK25">
+        <v>0.8911468812877265</v>
+      </c>
+      <c r="AL25">
+        <v>0</v>
+      </c>
+      <c r="AM25">
+        <v>-0.184</v>
+      </c>
+      <c r="AQ25">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
           <t>Macquarie Group Limited (ASX:MQG)</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D7">
+      <c r="D26">
         <v>0.05599999999999999</v>
       </c>
-      <c r="E7">
+      <c r="E26">
         <v>0.0352</v>
       </c>
-      <c r="F7">
+      <c r="F26">
         <v>0.112</v>
       </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7">
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26">
         <v>2578.5</v>
       </c>
-      <c r="L7">
+      <c r="L26">
         <v>0.2157794756353716</v>
       </c>
-      <c r="M7">
+      <c r="M26">
         <v>2863.5</v>
       </c>
-      <c r="N7">
+      <c r="N26">
         <v>0.05736327268137992</v>
       </c>
-      <c r="O7">
+      <c r="O26">
         <v>1.110529377545084</v>
       </c>
-      <c r="P7">
+      <c r="P26">
         <v>1698.7</v>
       </c>
-      <c r="Q7">
+      <c r="Q26">
         <v>0.03402933169333337</v>
       </c>
-      <c r="R7">
+      <c r="R26">
         <v>0.6587938724064378</v>
       </c>
-      <c r="S7">
+      <c r="S26">
         <v>1164.8</v>
       </c>
-      <c r="T7">
+      <c r="T26">
         <v>0.406774925790117</v>
       </c>
-      <c r="U7">
+      <c r="U26">
         <v>13249</v>
       </c>
-      <c r="V7">
+      <c r="V26">
         <v>0.2654115591952515</v>
       </c>
-      <c r="W7">
+      <c r="W26">
         <v>0.1223824350236364</v>
       </c>
-      <c r="X7">
-        <v>0.07363918860806103</v>
-      </c>
-      <c r="Y7">
-        <v>0.04874324641557537</v>
-      </c>
-      <c r="Z7">
+      <c r="X26">
+        <v>0.07362129048498309</v>
+      </c>
+      <c r="Y26">
+        <v>0.04876114453865331</v>
+      </c>
+      <c r="Z26">
         <v>0.1030302873539434</v>
       </c>
-      <c r="AA7">
-        <v>0</v>
-      </c>
-      <c r="AB7">
-        <v>0.04951528327587967</v>
-      </c>
-      <c r="AC7">
-        <v>-0.04951528327587967</v>
-      </c>
-      <c r="AD7">
+      <c r="AA26">
+        <v>0</v>
+      </c>
+      <c r="AB26">
+        <v>0.0495100251669341</v>
+      </c>
+      <c r="AC26">
+        <v>-0.0495100251669341</v>
+      </c>
+      <c r="AD26">
         <v>120000</v>
       </c>
-      <c r="AE7">
-        <v>0</v>
-      </c>
-      <c r="AF7">
+      <c r="AE26">
+        <v>0</v>
+      </c>
+      <c r="AF26">
         <v>120000</v>
       </c>
-      <c r="AG7">
+      <c r="AG26">
         <v>106751</v>
       </c>
-      <c r="AH7">
+      <c r="AH26">
         <v>0.7062200923147364</v>
       </c>
-      <c r="AI7">
+      <c r="AI26">
         <v>0.8405421496865478</v>
       </c>
-      <c r="AJ7">
+      <c r="AJ26">
         <v>0.6813761690997047</v>
       </c>
-      <c r="AK7">
+      <c r="AK26">
         <v>0.824230210939189</v>
       </c>
-      <c r="AL7">
-        <v>0</v>
-      </c>
-      <c r="AM7">
-        <v>0</v>
+      <c r="AL26">
+        <v>0</v>
+      </c>
+      <c r="AM26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Cash Converters International Limited (ASX:CCV)</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D27">
+        <v>0.0585</v>
+      </c>
+      <c r="F27">
+        <v>0.2</v>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27">
+        <v>0</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27">
+        <v>11.6</v>
+      </c>
+      <c r="L27">
+        <v>0.04827299209321681</v>
+      </c>
+      <c r="M27">
+        <v>8.818</v>
+      </c>
+      <c r="N27">
+        <v>0.09311510031678985</v>
+      </c>
+      <c r="O27">
+        <v>0.7601724137931034</v>
+      </c>
+      <c r="P27">
+        <v>8.369999999999999</v>
+      </c>
+      <c r="Q27">
+        <v>0.08838437170010559</v>
+      </c>
+      <c r="R27">
+        <v>0.721551724137931</v>
+      </c>
+      <c r="S27">
+        <v>0.4480000000000004</v>
+      </c>
+      <c r="T27">
+        <v>0.05080517124064418</v>
+      </c>
+      <c r="U27">
+        <v>37.6</v>
+      </c>
+      <c r="V27">
+        <v>0.3970432946145723</v>
+      </c>
+      <c r="W27">
+        <v>0.08442503639010189</v>
+      </c>
+      <c r="X27">
+        <v>0.06717065775999212</v>
+      </c>
+      <c r="Y27">
+        <v>0.01725437863010977</v>
+      </c>
+      <c r="Z27">
+        <v>1.086248982912937</v>
+      </c>
+      <c r="AA27">
+        <v>0</v>
+      </c>
+      <c r="AB27">
+        <v>0.05002496343354851</v>
+      </c>
+      <c r="AC27">
+        <v>-0.05002496343354851</v>
+      </c>
+      <c r="AD27">
+        <v>143.5</v>
+      </c>
+      <c r="AE27">
+        <v>0</v>
+      </c>
+      <c r="AF27">
+        <v>143.5</v>
+      </c>
+      <c r="AG27">
+        <v>105.9</v>
+      </c>
+      <c r="AH27">
+        <v>0.6024349286314022</v>
+      </c>
+      <c r="AI27">
+        <v>0.5043936731107206</v>
+      </c>
+      <c r="AJ27">
+        <v>0.5279162512462612</v>
+      </c>
+      <c r="AK27">
+        <v>0.4289185905224788</v>
+      </c>
+      <c r="AL27">
+        <v>0</v>
+      </c>
+      <c r="AM27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>QuickFee Limited (ASX:QFE)</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D28">
+        <v>0.3</v>
+      </c>
+      <c r="G28">
+        <v>0.2692307692307692</v>
+      </c>
+      <c r="H28">
+        <v>0</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28">
+        <v>-3.11</v>
+      </c>
+      <c r="L28">
+        <v>-0.2990384615384615</v>
+      </c>
+      <c r="M28">
+        <v>-0</v>
+      </c>
+      <c r="N28">
+        <v>-0</v>
+      </c>
+      <c r="O28">
+        <v>0</v>
+      </c>
+      <c r="P28">
+        <v>-0</v>
+      </c>
+      <c r="Q28">
+        <v>-0</v>
+      </c>
+      <c r="R28">
+        <v>0</v>
+      </c>
+      <c r="S28">
+        <v>0</v>
+      </c>
+      <c r="U28">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="V28">
+        <v>0.3766666666666666</v>
+      </c>
+      <c r="W28">
+        <v>-0.522689075630252</v>
+      </c>
+      <c r="X28">
+        <v>0.06823914958216204</v>
+      </c>
+      <c r="Y28">
+        <v>-0.5909282252124141</v>
+      </c>
+      <c r="Z28">
+        <v>0.3754512635379061</v>
+      </c>
+      <c r="AA28">
+        <v>0</v>
+      </c>
+      <c r="AB28">
+        <v>0.05089348341114067</v>
+      </c>
+      <c r="AC28">
+        <v>-0.05089348341114067</v>
+      </c>
+      <c r="AD28">
+        <v>39.9</v>
+      </c>
+      <c r="AE28">
+        <v>0</v>
+      </c>
+      <c r="AF28">
+        <v>39.9</v>
+      </c>
+      <c r="AG28">
+        <v>30.86</v>
+      </c>
+      <c r="AH28">
+        <v>0.6244131455399061</v>
+      </c>
+      <c r="AI28">
+        <v>0.8753839403247038</v>
+      </c>
+      <c r="AJ28">
+        <v>0.5625227852716004</v>
+      </c>
+      <c r="AK28">
+        <v>0.8445539135194308</v>
+      </c>
+      <c r="AL28">
+        <v>0</v>
+      </c>
+      <c r="AM28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Plenti Group Limited (ASX:PLT)</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="G29">
+        <v>0.1621342512908778</v>
+      </c>
+      <c r="H29">
+        <v>0</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>0</v>
+      </c>
+      <c r="K29">
+        <v>-9.98</v>
+      </c>
+      <c r="L29">
+        <v>-0.1717728055077453</v>
+      </c>
+      <c r="M29">
+        <v>-0</v>
+      </c>
+      <c r="N29">
+        <v>-0</v>
+      </c>
+      <c r="O29">
+        <v>0</v>
+      </c>
+      <c r="P29">
+        <v>-0</v>
+      </c>
+      <c r="Q29">
+        <v>-0</v>
+      </c>
+      <c r="R29">
+        <v>0</v>
+      </c>
+      <c r="S29">
+        <v>0</v>
+      </c>
+      <c r="U29">
+        <v>103.8</v>
+      </c>
+      <c r="V29">
+        <v>1.40650406504065</v>
+      </c>
+      <c r="W29">
+        <v>-0.2819209039548023</v>
+      </c>
+      <c r="X29">
+        <v>0.2147940339982354</v>
+      </c>
+      <c r="Y29">
+        <v>-0.4967149379530377</v>
+      </c>
+      <c r="Z29">
+        <v>0.04595064852894654</v>
+      </c>
+      <c r="AA29">
+        <v>0</v>
+      </c>
+      <c r="AB29">
+        <v>0.05230619171552998</v>
+      </c>
+      <c r="AC29">
+        <v>-0.05230619171552998</v>
+      </c>
+      <c r="AD29">
+        <v>1612.6</v>
+      </c>
+      <c r="AE29">
+        <v>0</v>
+      </c>
+      <c r="AF29">
+        <v>1612.6</v>
+      </c>
+      <c r="AG29">
+        <v>1508.8</v>
+      </c>
+      <c r="AH29">
+        <v>0.9562381404174574</v>
+      </c>
+      <c r="AI29">
+        <v>0.9916979275567308</v>
+      </c>
+      <c r="AJ29">
+        <v>0.9533678756476685</v>
+      </c>
+      <c r="AK29">
+        <v>0.9911318399789791</v>
+      </c>
+      <c r="AL29">
+        <v>0</v>
+      </c>
+      <c r="AM29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Credit Corp Group Limited (ASX:CCP)</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D30">
+        <v>0.0665</v>
+      </c>
+      <c r="E30">
+        <v>-0.06320000000000001</v>
+      </c>
+      <c r="F30">
+        <v>0.12</v>
+      </c>
+      <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30">
+        <v>0</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>0</v>
+      </c>
+      <c r="K30">
+        <v>33.8</v>
+      </c>
+      <c r="L30">
+        <v>0.1340737802459341</v>
+      </c>
+      <c r="M30">
+        <v>28.1</v>
+      </c>
+      <c r="N30">
+        <v>0.04172234595397179</v>
+      </c>
+      <c r="O30">
+        <v>0.8313609467455623</v>
+      </c>
+      <c r="P30">
+        <v>28.1</v>
+      </c>
+      <c r="Q30">
+        <v>0.04172234595397179</v>
+      </c>
+      <c r="R30">
+        <v>0.8313609467455623</v>
+      </c>
+      <c r="S30">
+        <v>0</v>
+      </c>
+      <c r="T30">
+        <v>0</v>
+      </c>
+      <c r="U30">
+        <v>23.3</v>
+      </c>
+      <c r="V30">
+        <v>0.03459539717891611</v>
+      </c>
+      <c r="W30">
+        <v>0.06213235294117646</v>
+      </c>
+      <c r="X30">
+        <v>0.05913243238243761</v>
+      </c>
+      <c r="Y30">
+        <v>0.002999920558738857</v>
+      </c>
+      <c r="Z30">
+        <v>0.3512365029606409</v>
+      </c>
+      <c r="AA30">
+        <v>0</v>
+      </c>
+      <c r="AB30">
+        <v>0.05321438490938704</v>
+      </c>
+      <c r="AC30">
+        <v>-0.05321438490938704</v>
+      </c>
+      <c r="AD30">
+        <v>274.8</v>
+      </c>
+      <c r="AE30">
+        <v>0</v>
+      </c>
+      <c r="AF30">
+        <v>274.8</v>
+      </c>
+      <c r="AG30">
+        <v>251.5</v>
+      </c>
+      <c r="AH30">
+        <v>0.2897817146472635</v>
+      </c>
+      <c r="AI30">
+        <v>0.3328085260990675</v>
+      </c>
+      <c r="AJ30">
+        <v>0.2718918918918919</v>
+      </c>
+      <c r="AK30">
+        <v>0.3134346959122632</v>
+      </c>
+      <c r="AL30">
+        <v>0</v>
+      </c>
+      <c r="AM30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Beforepay Group Limited (ASX:B4P)</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="G31">
+        <v>0.003043478260869565</v>
+      </c>
+      <c r="H31">
+        <v>0</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>0</v>
+      </c>
+      <c r="K31">
+        <v>2.58</v>
+      </c>
+      <c r="L31">
+        <v>0.1869565217391304</v>
+      </c>
+      <c r="M31">
+        <v>-0</v>
+      </c>
+      <c r="N31">
+        <v>-0</v>
+      </c>
+      <c r="O31">
+        <v>-0</v>
+      </c>
+      <c r="P31">
+        <v>-0</v>
+      </c>
+      <c r="Q31">
+        <v>-0</v>
+      </c>
+      <c r="R31">
+        <v>-0</v>
+      </c>
+      <c r="S31">
+        <v>0</v>
+      </c>
+      <c r="U31">
+        <v>12.8</v>
+      </c>
+      <c r="V31">
+        <v>0.2689075630252101</v>
+      </c>
+      <c r="W31">
+        <v>0.1441340782122905</v>
+      </c>
+      <c r="X31">
+        <v>0.06004417420038696</v>
+      </c>
+      <c r="Y31">
+        <v>0.08408990401190355</v>
+      </c>
+      <c r="Z31">
+        <v>0.5348837209302326</v>
+      </c>
+      <c r="AA31">
+        <v>0</v>
+      </c>
+      <c r="AB31">
+        <v>0.05476439304025232</v>
+      </c>
+      <c r="AC31">
+        <v>-0.05476439304025232</v>
+      </c>
+      <c r="AD31">
+        <v>25.4</v>
+      </c>
+      <c r="AE31">
+        <v>0</v>
+      </c>
+      <c r="AF31">
+        <v>25.4</v>
+      </c>
+      <c r="AG31">
+        <v>12.6</v>
+      </c>
+      <c r="AH31">
+        <v>0.347945205479452</v>
+      </c>
+      <c r="AI31">
+        <v>0.5545851528384279</v>
+      </c>
+      <c r="AJ31">
+        <v>0.2093023255813953</v>
+      </c>
+      <c r="AK31">
+        <v>0.3818181818181818</v>
+      </c>
+      <c r="AL31">
+        <v>0</v>
+      </c>
+      <c r="AM31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Australian Bond Exchange Holdings Limited (ASX:ABE)</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D32">
+        <v>0.255</v>
+      </c>
+      <c r="G32">
+        <v>0.0143859649122807</v>
+      </c>
+      <c r="H32">
+        <v>0</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>0</v>
+      </c>
+      <c r="K32">
+        <v>-3.75</v>
+      </c>
+      <c r="L32">
+        <v>-1.31578947368421</v>
+      </c>
+      <c r="M32">
+        <v>-0</v>
+      </c>
+      <c r="N32">
+        <v>-0</v>
+      </c>
+      <c r="O32">
+        <v>0</v>
+      </c>
+      <c r="P32">
+        <v>-0</v>
+      </c>
+      <c r="Q32">
+        <v>-0</v>
+      </c>
+      <c r="R32">
+        <v>0</v>
+      </c>
+      <c r="S32">
+        <v>0</v>
+      </c>
+      <c r="U32">
+        <v>1.66</v>
+      </c>
+      <c r="V32">
+        <v>0.8829787234042553</v>
+      </c>
+      <c r="W32">
+        <v>-0.6768953068592057</v>
+      </c>
+      <c r="X32">
+        <v>0.06439517269355269</v>
+      </c>
+      <c r="Y32">
+        <v>-0.7412904795527584</v>
+      </c>
+      <c r="Z32">
+        <v>0.9437086092715232</v>
+      </c>
+      <c r="AA32">
+        <v>0</v>
+      </c>
+      <c r="AB32">
+        <v>0.05837424555208955</v>
+      </c>
+      <c r="AC32">
+        <v>-0.05837424555208955</v>
+      </c>
+      <c r="AD32">
+        <v>2.13</v>
+      </c>
+      <c r="AE32">
+        <v>0</v>
+      </c>
+      <c r="AF32">
+        <v>2.13</v>
+      </c>
+      <c r="AG32">
+        <v>0.47</v>
+      </c>
+      <c r="AH32">
+        <v>0.5311720698254364</v>
+      </c>
+      <c r="AI32">
+        <v>0.5406091370558376</v>
+      </c>
+      <c r="AJ32">
+        <v>0.2</v>
+      </c>
+      <c r="AK32">
+        <v>0.206140350877193</v>
+      </c>
+      <c r="AL32">
+        <v>0</v>
+      </c>
+      <c r="AM32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>MoneyMe Limited (ASX:MME)</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D33">
+        <v>0.478</v>
+      </c>
+      <c r="E33">
+        <v>1.34</v>
+      </c>
+      <c r="F33">
+        <v>0.266</v>
+      </c>
+      <c r="G33">
+        <v>0.06624737945492662</v>
+      </c>
+      <c r="H33">
+        <v>0</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>0</v>
+      </c>
+      <c r="K33">
+        <v>15.2</v>
+      </c>
+      <c r="L33">
+        <v>0.3186582809224318</v>
+      </c>
+      <c r="M33">
+        <v>-0</v>
+      </c>
+      <c r="N33">
+        <v>-0</v>
+      </c>
+      <c r="O33">
+        <v>-0</v>
+      </c>
+      <c r="P33">
+        <v>-0</v>
+      </c>
+      <c r="Q33">
+        <v>-0</v>
+      </c>
+      <c r="R33">
+        <v>-0</v>
+      </c>
+      <c r="S33">
+        <v>0</v>
+      </c>
+      <c r="U33">
+        <v>49.1</v>
+      </c>
+      <c r="V33">
+        <v>0.4866204162537165</v>
+      </c>
+      <c r="W33">
+        <v>0.1375565610859728</v>
+      </c>
+      <c r="X33">
+        <v>0.1122811159379788</v>
+      </c>
+      <c r="Y33">
+        <v>0.02527544514799407</v>
+      </c>
+      <c r="Z33">
+        <v>0.06345616602367966</v>
+      </c>
+      <c r="AA33">
+        <v>0</v>
+      </c>
+      <c r="AB33">
+        <v>0.05984407197790879</v>
+      </c>
+      <c r="AC33">
+        <v>-0.05984407197790879</v>
+      </c>
+      <c r="AD33">
+        <v>779.9</v>
+      </c>
+      <c r="AE33">
+        <v>0</v>
+      </c>
+      <c r="AF33">
+        <v>779.9</v>
+      </c>
+      <c r="AG33">
+        <v>730.8</v>
+      </c>
+      <c r="AH33">
+        <v>0.8854450499545867</v>
+      </c>
+      <c r="AI33">
+        <v>0.8602470769909552</v>
+      </c>
+      <c r="AJ33">
+        <v>0.8786822171456053</v>
+      </c>
+      <c r="AK33">
+        <v>0.8522448979591836</v>
+      </c>
+      <c r="AL33">
+        <v>0</v>
+      </c>
+      <c r="AM33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>EML Payments Limited (ASX:EML)</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D34">
+        <v>0.175</v>
+      </c>
+      <c r="G34">
+        <v>0.02572413793103448</v>
+      </c>
+      <c r="H34">
+        <v>0.02572413793103448</v>
+      </c>
+      <c r="I34">
+        <v>-0.0116551724137931</v>
+      </c>
+      <c r="J34">
+        <v>-0.005827586206896551</v>
+      </c>
+      <c r="K34">
+        <v>-17.7</v>
+      </c>
+      <c r="L34">
+        <v>-0.1220689655172414</v>
+      </c>
+      <c r="M34">
+        <v>-0</v>
+      </c>
+      <c r="N34">
+        <v>-0</v>
+      </c>
+      <c r="O34">
+        <v>0</v>
+      </c>
+      <c r="P34">
+        <v>-0</v>
+      </c>
+      <c r="Q34">
+        <v>-0</v>
+      </c>
+      <c r="R34">
+        <v>0</v>
+      </c>
+      <c r="S34">
+        <v>0</v>
+      </c>
+      <c r="U34">
+        <v>28.7</v>
+      </c>
+      <c r="V34">
+        <v>0.1468030690537084</v>
+      </c>
+      <c r="W34">
+        <v>-0.1523235800344234</v>
+      </c>
+      <c r="X34">
+        <v>0.05841698848733652</v>
+      </c>
+      <c r="Y34">
+        <v>-0.2107405685217599</v>
+      </c>
+      <c r="Z34">
+        <v>2.148148148148148</v>
+      </c>
+      <c r="AA34">
+        <v>-0.01251851851851852</v>
+      </c>
+      <c r="AB34">
+        <v>0.05521545409872769</v>
+      </c>
+      <c r="AC34">
+        <v>-0.0677339726172462</v>
+      </c>
+      <c r="AD34">
+        <v>60.5</v>
+      </c>
+      <c r="AE34">
+        <v>0</v>
+      </c>
+      <c r="AF34">
+        <v>60.5</v>
+      </c>
+      <c r="AG34">
+        <v>31.8</v>
+      </c>
+      <c r="AH34">
+        <v>0.236328125</v>
+      </c>
+      <c r="AI34">
+        <v>0.3631452581032413</v>
+      </c>
+      <c r="AJ34">
+        <v>0.1399032116146063</v>
+      </c>
+      <c r="AK34">
+        <v>0.2306018854242204</v>
+      </c>
+      <c r="AL34">
+        <v>3.07</v>
+      </c>
+      <c r="AM34">
+        <v>3.07</v>
+      </c>
+      <c r="AN34">
+        <v>16.21983914209115</v>
+      </c>
+      <c r="AO34">
+        <v>-0.5504885993485342</v>
+      </c>
+      <c r="AP34">
+        <v>8.525469168900804</v>
+      </c>
+      <c r="AQ34">
+        <v>-0.5504885993485342</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Omni Bridgeway Limited (ASX:OBL)</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D35">
+        <v>0.8070000000000001</v>
+      </c>
+      <c r="G35">
+        <v>-0.1670886075949367</v>
+      </c>
+      <c r="H35">
+        <v>-0.1670886075949367</v>
+      </c>
+      <c r="I35">
+        <v>-0.3074141048824593</v>
+      </c>
+      <c r="J35">
+        <v>-0.3074141048824593</v>
+      </c>
+      <c r="K35">
+        <v>-58.4</v>
+      </c>
+      <c r="L35">
+        <v>-1.056057866184448</v>
+      </c>
+      <c r="M35">
+        <v>-0</v>
+      </c>
+      <c r="N35">
+        <v>-0</v>
+      </c>
+      <c r="O35">
+        <v>0</v>
+      </c>
+      <c r="P35">
+        <v>-0</v>
+      </c>
+      <c r="Q35">
+        <v>-0</v>
+      </c>
+      <c r="R35">
+        <v>0</v>
+      </c>
+      <c r="S35">
+        <v>0</v>
+      </c>
+      <c r="U35">
+        <v>90.7</v>
+      </c>
+      <c r="V35">
+        <v>0.3576498422712934</v>
+      </c>
+      <c r="W35">
+        <v>-0.2515073212747632</v>
+      </c>
+      <c r="X35">
+        <v>0.06136023452009557</v>
+      </c>
+      <c r="Y35">
+        <v>-0.3128675557948588</v>
+      </c>
+      <c r="Z35">
+        <v>0.2533211177278973</v>
+      </c>
+      <c r="AA35">
+        <v>-0.07787448465414566</v>
+      </c>
+      <c r="AB35">
+        <v>0.05264739819336913</v>
+      </c>
+      <c r="AC35">
+        <v>-0.1305218828475148</v>
+      </c>
+      <c r="AD35">
+        <v>181.3</v>
+      </c>
+      <c r="AE35">
+        <v>0</v>
+      </c>
+      <c r="AF35">
+        <v>181.3</v>
+      </c>
+      <c r="AG35">
+        <v>90.60000000000001</v>
+      </c>
+      <c r="AH35">
+        <v>0.4168774430903657</v>
+      </c>
+      <c r="AI35">
+        <v>0.2547421666432486</v>
+      </c>
+      <c r="AJ35">
+        <v>0.26321905868681</v>
+      </c>
+      <c r="AK35">
+        <v>0.1458937198067633</v>
+      </c>
+      <c r="AL35">
+        <v>0.698</v>
+      </c>
+      <c r="AM35">
+        <v>0.698</v>
+      </c>
+      <c r="AN35">
+        <v>-19.62121212121212</v>
+      </c>
+      <c r="AO35">
+        <v>-24.35530085959886</v>
+      </c>
+      <c r="AP35">
+        <v>-9.805194805194805</v>
+      </c>
+      <c r="AQ35">
+        <v>-24.35530085959886</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Change Financial Limited (ASX:CCA)</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D36">
+        <v>0.421</v>
+      </c>
+      <c r="G36">
+        <v>-0.130188679245283</v>
+      </c>
+      <c r="H36">
+        <v>-0.2066037735849057</v>
+      </c>
+      <c r="I36">
+        <v>-0.2113207547169812</v>
+      </c>
+      <c r="J36">
+        <v>-0.2113207547169812</v>
+      </c>
+      <c r="K36">
+        <v>-2.57</v>
+      </c>
+      <c r="L36">
+        <v>-0.2424528301886792</v>
+      </c>
+      <c r="M36">
+        <v>-0</v>
+      </c>
+      <c r="N36">
+        <v>-0</v>
+      </c>
+      <c r="O36">
+        <v>0</v>
+      </c>
+      <c r="P36">
+        <v>-0</v>
+      </c>
+      <c r="Q36">
+        <v>-0</v>
+      </c>
+      <c r="R36">
+        <v>0</v>
+      </c>
+      <c r="S36">
+        <v>0</v>
+      </c>
+      <c r="U36">
+        <v>2.59</v>
+      </c>
+      <c r="V36">
+        <v>0.09522058823529411</v>
+      </c>
+      <c r="W36">
+        <v>-0.3045023696682465</v>
+      </c>
+      <c r="X36">
+        <v>0.0562123922107909</v>
+      </c>
+      <c r="Y36">
+        <v>-0.3607147618790373</v>
+      </c>
+      <c r="Z36">
+        <v>3.285802851828891</v>
+      </c>
+      <c r="AA36">
+        <v>-0.6943583384996903</v>
+      </c>
+      <c r="AB36">
+        <v>0.056121990281592</v>
+      </c>
+      <c r="AC36">
+        <v>-0.7504803287812823</v>
+      </c>
+      <c r="AD36">
+        <v>0.157</v>
+      </c>
+      <c r="AE36">
+        <v>0</v>
+      </c>
+      <c r="AF36">
+        <v>0.157</v>
+      </c>
+      <c r="AG36">
+        <v>-2.433</v>
+      </c>
+      <c r="AH36">
+        <v>0.005738933362576306</v>
+      </c>
+      <c r="AI36">
+        <v>0.02600629451714428</v>
+      </c>
+      <c r="AJ36">
+        <v>-0.0982355553761053</v>
+      </c>
+      <c r="AK36">
+        <v>-0.7058311575282854</v>
+      </c>
+      <c r="AL36">
+        <v>0.025</v>
+      </c>
+      <c r="AM36">
+        <v>0.025</v>
+      </c>
+      <c r="AN36">
+        <v>-0.07168949771689498</v>
+      </c>
+      <c r="AO36">
+        <v>-89.60000000000001</v>
+      </c>
+      <c r="AP36">
+        <v>1.110958904109589</v>
+      </c>
+      <c r="AQ36">
+        <v>-89.60000000000001</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Income Asset Management Group Limited (ASX:IAM)</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D37">
+        <v>0.648</v>
+      </c>
+      <c r="G37">
+        <v>-0.8331550802139038</v>
+      </c>
+      <c r="H37">
+        <v>-0.8331550802139038</v>
+      </c>
+      <c r="I37">
+        <v>-0.8481283422459893</v>
+      </c>
+      <c r="J37">
+        <v>-0.8481283422459893</v>
+      </c>
+      <c r="K37">
+        <v>-9.66</v>
+      </c>
+      <c r="L37">
+        <v>-1.033155080213904</v>
+      </c>
+      <c r="M37">
+        <v>-0</v>
+      </c>
+      <c r="N37">
+        <v>-0</v>
+      </c>
+      <c r="O37">
+        <v>0</v>
+      </c>
+      <c r="P37">
+        <v>-0</v>
+      </c>
+      <c r="Q37">
+        <v>-0</v>
+      </c>
+      <c r="R37">
+        <v>0</v>
+      </c>
+      <c r="S37">
+        <v>0</v>
+      </c>
+      <c r="U37">
+        <v>3.15</v>
+      </c>
+      <c r="V37">
+        <v>0.1711956521739131</v>
+      </c>
+      <c r="W37">
+        <v>-1.662650602409639</v>
+      </c>
+      <c r="X37">
+        <v>0.05897559590541286</v>
+      </c>
+      <c r="Y37">
+        <v>-1.721626198315052</v>
+      </c>
+      <c r="Z37">
+        <v>1.826171875</v>
+      </c>
+      <c r="AA37">
+        <v>-1</v>
+      </c>
+      <c r="AB37">
+        <v>0.05381503585494303</v>
+      </c>
+      <c r="AC37">
+        <v>-1.053815035854943</v>
+      </c>
+      <c r="AD37">
+        <v>7.11</v>
+      </c>
+      <c r="AE37">
+        <v>0</v>
+      </c>
+      <c r="AF37">
+        <v>7.11</v>
+      </c>
+      <c r="AG37">
+        <v>3.96</v>
+      </c>
+      <c r="AH37">
+        <v>0.2787142297138377</v>
+      </c>
+      <c r="AI37">
+        <v>1.98050139275766</v>
+      </c>
+      <c r="AJ37">
+        <v>0.1771019677996422</v>
+      </c>
+      <c r="AK37">
+        <v>8.999999999999993</v>
+      </c>
+      <c r="AL37">
+        <v>1.65</v>
+      </c>
+      <c r="AM37">
+        <v>1.65</v>
+      </c>
+      <c r="AN37">
+        <v>-0.9127086007702183</v>
+      </c>
+      <c r="AO37">
+        <v>-4.806060606060607</v>
+      </c>
+      <c r="AP37">
+        <v>-0.5083440308087291</v>
+      </c>
+      <c r="AQ37">
+        <v>-4.806060606060607</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>NSX Limited (ASX:NSX)</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D38">
+        <v>-0.0843</v>
+      </c>
+      <c r="G38">
+        <v>-2.63</v>
+      </c>
+      <c r="H38">
+        <v>-2.63</v>
+      </c>
+      <c r="I38">
+        <v>-2.64</v>
+      </c>
+      <c r="J38">
+        <v>-2.64</v>
+      </c>
+      <c r="K38">
+        <v>-2.74</v>
+      </c>
+      <c r="L38">
+        <v>-2.74</v>
+      </c>
+      <c r="M38">
+        <v>-0</v>
+      </c>
+      <c r="N38">
+        <v>-0</v>
+      </c>
+      <c r="O38">
+        <v>0</v>
+      </c>
+      <c r="P38">
+        <v>-0</v>
+      </c>
+      <c r="Q38">
+        <v>-0</v>
+      </c>
+      <c r="R38">
+        <v>0</v>
+      </c>
+      <c r="S38">
+        <v>0</v>
+      </c>
+      <c r="U38">
+        <v>1.38</v>
+      </c>
+      <c r="V38">
+        <v>0.2110091743119266</v>
+      </c>
+      <c r="W38">
+        <v>-2.124031007751938</v>
+      </c>
+      <c r="X38">
+        <v>0.05740258127950503</v>
+      </c>
+      <c r="Y38">
+        <v>-2.181433589031443</v>
+      </c>
+      <c r="Z38">
+        <v>1.184834123222749</v>
+      </c>
+      <c r="AA38">
+        <v>-1</v>
+      </c>
+      <c r="AB38">
+        <v>0.05494424595659646</v>
+      </c>
+      <c r="AC38">
+        <v>-1.054944245956597</v>
+      </c>
+      <c r="AD38">
+        <v>1.11</v>
+      </c>
+      <c r="AE38">
+        <v>0</v>
+      </c>
+      <c r="AF38">
+        <v>1.11</v>
+      </c>
+      <c r="AG38">
+        <v>-0.2699999999999998</v>
+      </c>
+      <c r="AH38">
+        <v>0.1450980392156863</v>
+      </c>
+      <c r="AI38">
+        <v>2.193675889328063</v>
+      </c>
+      <c r="AJ38">
+        <v>-0.04306220095693776</v>
+      </c>
+      <c r="AK38">
+        <v>0.308924485125858</v>
+      </c>
+      <c r="AL38">
+        <v>0.077</v>
+      </c>
+      <c r="AM38">
+        <v>0.077</v>
+      </c>
+      <c r="AN38">
+        <v>-0.4220532319391636</v>
+      </c>
+      <c r="AO38">
+        <v>-34.28571428571428</v>
+      </c>
+      <c r="AP38">
+        <v>0.1026615969581748</v>
+      </c>
+      <c r="AQ38">
+        <v>-34.28571428571428</v>
       </c>
     </row>
   </sheetData>
